--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7465268817</v>
+        <v>3376.746528748</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.211279558</v>
+        <v>1982150.212375076</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1112,10 +1112,10 @@
         <v>334</v>
       </c>
       <c r="N18" t="n">
-        <v>6272.8539724138</v>
+        <v>6272.8539614856</v>
       </c>
       <c r="O18" t="n">
-        <v>2095133.226786209</v>
+        <v>2095133.22313619</v>
       </c>
       <c r="P18" t="n">
         <v>7900</v>
@@ -1190,10 +1190,10 @@
         <v>450</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371399387</v>
       </c>
       <c r="O20" t="n">
-        <v>1767076.710997455</v>
+        <v>1767076.712972415</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1388,10 +1388,10 @@
         <v>55</v>
       </c>
       <c r="N25" t="n">
-        <v>12793.680086207</v>
+        <v>12793.680085837</v>
       </c>
       <c r="O25" t="n">
-        <v>703652.404741385</v>
+        <v>703652.404721035</v>
       </c>
       <c r="P25" t="n">
         <v>24000</v>
@@ -1583,10 +1583,10 @@
         <v>62</v>
       </c>
       <c r="N30" t="n">
-        <v>14857.62306383</v>
+        <v>14857.623050847</v>
       </c>
       <c r="O30" t="n">
-        <v>921172.62995746</v>
+        <v>921172.629152514</v>
       </c>
       <c r="P30" t="n">
         <v>34900</v>
@@ -1705,10 +1705,10 @@
         <v>135</v>
       </c>
       <c r="N33" t="n">
-        <v>3910.628317757</v>
+        <v>3910.6283208955</v>
       </c>
       <c r="O33" t="n">
-        <v>527934.822897195</v>
+        <v>527934.8233208925</v>
       </c>
       <c r="P33" t="n">
         <v>9100</v>
@@ -1747,10 +1747,10 @@
         <v>42</v>
       </c>
       <c r="N34" t="n">
-        <v>15711.966441948</v>
+        <v>15711.966494465</v>
       </c>
       <c r="O34" t="n">
-        <v>659902.590561816</v>
+        <v>659902.59276753</v>
       </c>
       <c r="P34" t="n">
         <v>28500</v>
@@ -2500,10 +2500,10 @@
         <v>24</v>
       </c>
       <c r="N52" t="n">
-        <v>4878.2852688172</v>
+        <v>4878.2851851852</v>
       </c>
       <c r="O52" t="n">
-        <v>117078.8464516128</v>
+        <v>117078.8444444448</v>
       </c>
       <c r="P52" t="n">
         <v>13500</v>
@@ -2695,10 +2695,10 @@
         <v>178</v>
       </c>
       <c r="N57" t="n">
-        <v>3340.6800775194</v>
+        <v>3340.6800773694</v>
       </c>
       <c r="O57" t="n">
-        <v>594641.0537984532</v>
+        <v>594641.0537717532</v>
       </c>
       <c r="P57" t="n">
         <v>7100</v>
@@ -2999,10 +2999,10 @@
         <v>228</v>
       </c>
       <c r="N64" t="n">
-        <v>1950.2152617329</v>
+        <v>1950.2152745275</v>
       </c>
       <c r="O64" t="n">
-        <v>444649.0796751012</v>
+        <v>444649.08259227</v>
       </c>
       <c r="P64" t="n">
         <v>2900</v>
@@ -3086,10 +3086,10 @@
         <v>434</v>
       </c>
       <c r="N66" t="n">
-        <v>4937.3101589595</v>
+        <v>4937.3101582734</v>
       </c>
       <c r="O66" t="n">
-        <v>2142792.608988423</v>
+        <v>2142792.608690655</v>
       </c>
       <c r="P66" t="n">
         <v>7500</v>
@@ -3440,10 +3440,10 @@
         <v>120</v>
       </c>
       <c r="N74" t="n">
-        <v>1098.0517240829</v>
+        <v>1098.0510925004</v>
       </c>
       <c r="O74" t="n">
-        <v>131766.206889948</v>
+        <v>131766.131100048</v>
       </c>
       <c r="P74" t="n">
         <v>1500</v>
@@ -4911,10 +4911,10 @@
         <v>577</v>
       </c>
       <c r="N107" t="n">
-        <v>3795.7100070286</v>
+        <v>3795.7100070249</v>
       </c>
       <c r="O107" t="n">
-        <v>2190124.674055502</v>
+        <v>2190124.674053367</v>
       </c>
       <c r="P107" t="n">
         <v>6200</v>
@@ -5843,13 +5843,13 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>198</v>
+        <v>278</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M128" t="n">
         <v>198</v>
@@ -6074,10 +6074,10 @@
         <v>535</v>
       </c>
       <c r="N133" t="n">
-        <v>3041.6600119048</v>
+        <v>3041.6600117855</v>
       </c>
       <c r="O133" t="n">
-        <v>1627288.106369068</v>
+        <v>1627288.106305243</v>
       </c>
       <c r="P133" t="n">
         <v>5500</v>
@@ -7659,10 +7659,10 @@
         <v>300</v>
       </c>
       <c r="N168" t="n">
-        <v>1630.9228220183</v>
+        <v>1630.9227791832</v>
       </c>
       <c r="O168" t="n">
-        <v>489276.84660549</v>
+        <v>489276.83375496</v>
       </c>
       <c r="P168" t="n">
         <v>2500</v>
@@ -7705,10 +7705,10 @@
         <v>96</v>
       </c>
       <c r="N169" t="n">
-        <v>1550.1927548066</v>
+        <v>1550.1927149023</v>
       </c>
       <c r="O169" t="n">
-        <v>148818.5044614336</v>
+        <v>148818.5006306208</v>
       </c>
       <c r="P169" t="n">
         <v>2500</v>
@@ -9092,10 +9092,10 @@
         <v>348</v>
       </c>
       <c r="N201" t="n">
-        <v>2029.8734883721</v>
+        <v>2029.8734867503</v>
       </c>
       <c r="O201" t="n">
-        <v>706395.9739534907</v>
+        <v>706395.9733891044</v>
       </c>
       <c r="P201" t="n">
         <v>3600</v>
@@ -9297,10 +9297,10 @@
         <v>170</v>
       </c>
       <c r="N206" t="n">
-        <v>2680.7397012195</v>
+        <v>2680.7397015834</v>
       </c>
       <c r="O206" t="n">
-        <v>455725.749207315</v>
+        <v>455725.749269178</v>
       </c>
       <c r="P206" t="n">
         <v>4900</v>
@@ -9425,10 +9425,10 @@
         <v>237</v>
       </c>
       <c r="N209" t="n">
-        <v>1732.9153957286</v>
+        <v>1732.9154130163</v>
       </c>
       <c r="O209" t="n">
-        <v>410700.9487876782</v>
+        <v>410700.9528848631</v>
       </c>
       <c r="P209" t="n">
         <v>1900</v>
@@ -10806,10 +10806,10 @@
         <v>154</v>
       </c>
       <c r="N241" t="n">
-        <v>548.14729553903</v>
+        <v>548.14741563055</v>
       </c>
       <c r="O241" t="n">
-        <v>84414.68351301062</v>
+        <v>84414.7020071047</v>
       </c>
       <c r="P241" t="n">
         <v>2000</v>
@@ -11939,10 +11939,10 @@
         <v>1215</v>
       </c>
       <c r="N266" t="n">
-        <v>1778.4724932172</v>
+        <v>1778.4724843483</v>
       </c>
       <c r="O266" t="n">
-        <v>2160844.079258898</v>
+        <v>2160844.068483185</v>
       </c>
       <c r="P266" t="n">
         <v>4900</v>
@@ -14253,10 +14253,10 @@
         <v>263</v>
       </c>
       <c r="N316" t="n">
-        <v>2252.2960775371</v>
+        <v>2252.2960568182</v>
       </c>
       <c r="O316" t="n">
-        <v>592353.8683922573</v>
+        <v>592353.8629431867</v>
       </c>
       <c r="P316" t="n">
         <v>3900</v>
@@ -14440,10 +14440,10 @@
         <v>504</v>
       </c>
       <c r="N320" t="n">
-        <v>2328.1187653599</v>
+        <v>2328.1187675234</v>
       </c>
       <c r="O320" t="n">
-        <v>1173371.85774139</v>
+        <v>1173371.858831794</v>
       </c>
       <c r="P320" t="n">
         <v>4500</v>
@@ -14854,10 +14854,10 @@
         <v>184</v>
       </c>
       <c r="N329" t="n">
-        <v>4907.8218731563</v>
+        <v>4907.8218486172</v>
       </c>
       <c r="O329" t="n">
-        <v>903039.2246607592</v>
+        <v>903039.2201455648</v>
       </c>
       <c r="P329" t="n">
         <v>8200</v>
@@ -16321,10 +16321,10 @@
         <v>60</v>
       </c>
       <c r="N361" t="n">
-        <v>4268.7018707483</v>
+        <v>4268.7018305085</v>
       </c>
       <c r="O361" t="n">
-        <v>256122.112244898</v>
+        <v>256122.10983051</v>
       </c>
       <c r="P361" t="n">
         <v>6900</v>
@@ -16827,10 +16827,10 @@
         <v>839</v>
       </c>
       <c r="N372" t="n">
-        <v>1516.0388206553</v>
+        <v>1516.0388215585</v>
       </c>
       <c r="O372" t="n">
-        <v>1271956.570529797</v>
+        <v>1271956.571287582</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
@@ -17234,10 +17234,10 @@
         <v>2243</v>
       </c>
       <c r="N381" t="n">
-        <v>692.1519887834301</v>
+        <v>692.15197854077</v>
       </c>
       <c r="O381" t="n">
-        <v>1552496.910841234</v>
+        <v>1552496.887866947</v>
       </c>
       <c r="P381" t="n">
         <v>1200</v>
@@ -18187,10 +18187,10 @@
         <v>238</v>
       </c>
       <c r="N401" t="n">
-        <v>1690.8700087222</v>
+        <v>1690.8700086994</v>
       </c>
       <c r="O401" t="n">
-        <v>402427.0620758836</v>
+        <v>402427.0620704572</v>
       </c>
       <c r="P401" t="n">
         <v>3000</v>
@@ -18471,10 +18471,10 @@
         <v>78</v>
       </c>
       <c r="N407" t="n">
-        <v>3907.5003162055</v>
+        <v>3907.5003137255</v>
       </c>
       <c r="O407" t="n">
-        <v>304785.024664029</v>
+        <v>304785.024470589</v>
       </c>
       <c r="P407" t="n">
         <v>3900</v>
@@ -18564,10 +18564,10 @@
         <v>7734</v>
       </c>
       <c r="N409" t="n">
-        <v>711.33665018328</v>
+        <v>711.33665411716</v>
       </c>
       <c r="O409" t="n">
-        <v>5501477.652517487</v>
+        <v>5501477.682942116</v>
       </c>
       <c r="P409" t="n">
         <v>900</v>
@@ -19216,10 +19216,10 @@
         <v>2</v>
       </c>
       <c r="N423" t="n">
-        <v>3110.8438819661</v>
+        <v>3110.8439531303</v>
       </c>
       <c r="O423" t="n">
-        <v>6221.6877639322</v>
+        <v>6221.6879062606</v>
       </c>
       <c r="P423" t="n">
         <v>4500</v>
@@ -20150,10 +20150,10 @@
         <v>381</v>
       </c>
       <c r="N443" t="n">
-        <v>1595.5196456996</v>
+        <v>1595.5196827833</v>
       </c>
       <c r="O443" t="n">
-        <v>607892.9850115476</v>
+        <v>607892.9991404372</v>
       </c>
       <c r="P443" t="n">
         <v>2500</v>
@@ -22234,10 +22234,10 @@
         <v>152</v>
       </c>
       <c r="N486" t="n">
-        <v>7046.9398310097</v>
+        <v>7046.9398312236</v>
       </c>
       <c r="O486" t="n">
-        <v>1071134.854313474</v>
+        <v>1071134.854345987</v>
       </c>
       <c r="P486" t="n">
         <v>9900</v>
@@ -22332,10 +22332,10 @@
         <v>9</v>
       </c>
       <c r="N488" t="n">
-        <v>15577.048235294</v>
+        <v>15577.047777778</v>
       </c>
       <c r="O488" t="n">
-        <v>140193.434117646</v>
+        <v>140193.430000002</v>
       </c>
       <c r="P488" t="n">
         <v>19900</v>
@@ -22865,10 +22865,10 @@
         <v>70</v>
       </c>
       <c r="N499" t="n">
-        <v>44113.603675676</v>
+        <v>44113.603597884</v>
       </c>
       <c r="O499" t="n">
-        <v>3087952.25729732</v>
+        <v>3087952.25185188</v>
       </c>
       <c r="P499" t="n">
         <v>71900</v>
@@ -23517,10 +23517,10 @@
         <v>216</v>
       </c>
       <c r="N513" t="n">
-        <v>1008.8197488922</v>
+        <v>1008.8200998573</v>
       </c>
       <c r="O513" t="n">
-        <v>217905.0657607152</v>
+        <v>217905.1415691768</v>
       </c>
       <c r="P513" t="n">
         <v>1500</v>
@@ -23820,10 +23820,10 @@
         <v>11</v>
       </c>
       <c r="N520" t="n">
-        <v>22951.705024752</v>
+        <v>22951.705030902</v>
       </c>
       <c r="O520" t="n">
-        <v>252468.755272272</v>
+        <v>252468.755339922</v>
       </c>
       <c r="P520" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-07-31</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.746528748</v>
+        <v>3376.7465268817</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.212375076</v>
+        <v>1982150.211279558</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1112,10 +1112,10 @@
         <v>334</v>
       </c>
       <c r="N18" t="n">
-        <v>6272.8539614856</v>
+        <v>6272.8539724138</v>
       </c>
       <c r="O18" t="n">
-        <v>2095133.22313619</v>
+        <v>2095133.226786209</v>
       </c>
       <c r="P18" t="n">
         <v>7900</v>
@@ -1190,10 +1190,10 @@
         <v>450</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8371399387</v>
+        <v>3926.8371355499</v>
       </c>
       <c r="O20" t="n">
-        <v>1767076.712972415</v>
+        <v>1767076.710997455</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1388,10 +1388,10 @@
         <v>55</v>
       </c>
       <c r="N25" t="n">
-        <v>12793.680085837</v>
+        <v>12793.680086207</v>
       </c>
       <c r="O25" t="n">
-        <v>703652.404721035</v>
+        <v>703652.404741385</v>
       </c>
       <c r="P25" t="n">
         <v>24000</v>
@@ -1583,10 +1583,10 @@
         <v>62</v>
       </c>
       <c r="N30" t="n">
-        <v>14857.623050847</v>
+        <v>14857.62306383</v>
       </c>
       <c r="O30" t="n">
-        <v>921172.629152514</v>
+        <v>921172.62995746</v>
       </c>
       <c r="P30" t="n">
         <v>34900</v>
@@ -1705,10 +1705,10 @@
         <v>135</v>
       </c>
       <c r="N33" t="n">
-        <v>3910.6283208955</v>
+        <v>3910.628317757</v>
       </c>
       <c r="O33" t="n">
-        <v>527934.8233208925</v>
+        <v>527934.822897195</v>
       </c>
       <c r="P33" t="n">
         <v>9100</v>
@@ -1747,10 +1747,10 @@
         <v>42</v>
       </c>
       <c r="N34" t="n">
-        <v>15711.966494465</v>
+        <v>15711.966441948</v>
       </c>
       <c r="O34" t="n">
-        <v>659902.59276753</v>
+        <v>659902.590561816</v>
       </c>
       <c r="P34" t="n">
         <v>28500</v>
@@ -2500,10 +2500,10 @@
         <v>24</v>
       </c>
       <c r="N52" t="n">
-        <v>4878.2851851852</v>
+        <v>4878.2852688172</v>
       </c>
       <c r="O52" t="n">
-        <v>117078.8444444448</v>
+        <v>117078.8464516128</v>
       </c>
       <c r="P52" t="n">
         <v>13500</v>
@@ -2695,10 +2695,10 @@
         <v>178</v>
       </c>
       <c r="N57" t="n">
-        <v>3340.6800773694</v>
+        <v>3340.6800775194</v>
       </c>
       <c r="O57" t="n">
-        <v>594641.0537717532</v>
+        <v>594641.0537984532</v>
       </c>
       <c r="P57" t="n">
         <v>7100</v>
@@ -2999,10 +2999,10 @@
         <v>228</v>
       </c>
       <c r="N64" t="n">
-        <v>1950.2152745275</v>
+        <v>1950.2152617329</v>
       </c>
       <c r="O64" t="n">
-        <v>444649.08259227</v>
+        <v>444649.0796751012</v>
       </c>
       <c r="P64" t="n">
         <v>2900</v>
@@ -3086,10 +3086,10 @@
         <v>434</v>
       </c>
       <c r="N66" t="n">
-        <v>4937.3101582734</v>
+        <v>4937.3101589595</v>
       </c>
       <c r="O66" t="n">
-        <v>2142792.608690655</v>
+        <v>2142792.608988423</v>
       </c>
       <c r="P66" t="n">
         <v>7500</v>
@@ -3440,10 +3440,10 @@
         <v>120</v>
       </c>
       <c r="N74" t="n">
-        <v>1098.0510925004</v>
+        <v>1098.0517240829</v>
       </c>
       <c r="O74" t="n">
-        <v>131766.131100048</v>
+        <v>131766.206889948</v>
       </c>
       <c r="P74" t="n">
         <v>1500</v>
@@ -4911,10 +4911,10 @@
         <v>577</v>
       </c>
       <c r="N107" t="n">
-        <v>3795.7100070249</v>
+        <v>3795.7100070286</v>
       </c>
       <c r="O107" t="n">
-        <v>2190124.674053367</v>
+        <v>2190124.674055502</v>
       </c>
       <c r="P107" t="n">
         <v>6200</v>
@@ -5843,13 +5843,13 @@
         </is>
       </c>
       <c r="J128" t="n">
-        <v>278</v>
+        <v>198</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
         <v>198</v>
@@ -6074,10 +6074,10 @@
         <v>535</v>
       </c>
       <c r="N133" t="n">
-        <v>3041.6600117855</v>
+        <v>3041.6600119048</v>
       </c>
       <c r="O133" t="n">
-        <v>1627288.106305243</v>
+        <v>1627288.106369068</v>
       </c>
       <c r="P133" t="n">
         <v>5500</v>
@@ -7659,10 +7659,10 @@
         <v>300</v>
       </c>
       <c r="N168" t="n">
-        <v>1630.9227791832</v>
+        <v>1630.9228220183</v>
       </c>
       <c r="O168" t="n">
-        <v>489276.83375496</v>
+        <v>489276.84660549</v>
       </c>
       <c r="P168" t="n">
         <v>2500</v>
@@ -7705,10 +7705,10 @@
         <v>96</v>
       </c>
       <c r="N169" t="n">
-        <v>1550.1927149023</v>
+        <v>1550.1927548066</v>
       </c>
       <c r="O169" t="n">
-        <v>148818.5006306208</v>
+        <v>148818.5044614336</v>
       </c>
       <c r="P169" t="n">
         <v>2500</v>
@@ -9092,10 +9092,10 @@
         <v>348</v>
       </c>
       <c r="N201" t="n">
-        <v>2029.8734867503</v>
+        <v>2029.8734883721</v>
       </c>
       <c r="O201" t="n">
-        <v>706395.9733891044</v>
+        <v>706395.9739534907</v>
       </c>
       <c r="P201" t="n">
         <v>3600</v>
@@ -9297,10 +9297,10 @@
         <v>170</v>
       </c>
       <c r="N206" t="n">
-        <v>2680.7397015834</v>
+        <v>2680.7397012195</v>
       </c>
       <c r="O206" t="n">
-        <v>455725.749269178</v>
+        <v>455725.749207315</v>
       </c>
       <c r="P206" t="n">
         <v>4900</v>
@@ -9425,10 +9425,10 @@
         <v>237</v>
       </c>
       <c r="N209" t="n">
-        <v>1732.9154130163</v>
+        <v>1732.9153957286</v>
       </c>
       <c r="O209" t="n">
-        <v>410700.9528848631</v>
+        <v>410700.9487876782</v>
       </c>
       <c r="P209" t="n">
         <v>1900</v>
@@ -10806,10 +10806,10 @@
         <v>154</v>
       </c>
       <c r="N241" t="n">
-        <v>548.14741563055</v>
+        <v>548.14729553903</v>
       </c>
       <c r="O241" t="n">
-        <v>84414.7020071047</v>
+        <v>84414.68351301062</v>
       </c>
       <c r="P241" t="n">
         <v>2000</v>
@@ -11939,10 +11939,10 @@
         <v>1215</v>
       </c>
       <c r="N266" t="n">
-        <v>1778.4724843483</v>
+        <v>1778.4724932172</v>
       </c>
       <c r="O266" t="n">
-        <v>2160844.068483185</v>
+        <v>2160844.079258898</v>
       </c>
       <c r="P266" t="n">
         <v>4900</v>
@@ -14253,10 +14253,10 @@
         <v>263</v>
       </c>
       <c r="N316" t="n">
-        <v>2252.2960568182</v>
+        <v>2252.2960775371</v>
       </c>
       <c r="O316" t="n">
-        <v>592353.8629431867</v>
+        <v>592353.8683922573</v>
       </c>
       <c r="P316" t="n">
         <v>3900</v>
@@ -14440,10 +14440,10 @@
         <v>504</v>
       </c>
       <c r="N320" t="n">
-        <v>2328.1187675234</v>
+        <v>2328.1187653599</v>
       </c>
       <c r="O320" t="n">
-        <v>1173371.858831794</v>
+        <v>1173371.85774139</v>
       </c>
       <c r="P320" t="n">
         <v>4500</v>
@@ -14854,10 +14854,10 @@
         <v>184</v>
       </c>
       <c r="N329" t="n">
-        <v>4907.8218486172</v>
+        <v>4907.8218731563</v>
       </c>
       <c r="O329" t="n">
-        <v>903039.2201455648</v>
+        <v>903039.2246607592</v>
       </c>
       <c r="P329" t="n">
         <v>8200</v>
@@ -16321,10 +16321,10 @@
         <v>60</v>
       </c>
       <c r="N361" t="n">
-        <v>4268.7018305085</v>
+        <v>4268.7018707483</v>
       </c>
       <c r="O361" t="n">
-        <v>256122.10983051</v>
+        <v>256122.112244898</v>
       </c>
       <c r="P361" t="n">
         <v>6900</v>
@@ -16827,10 +16827,10 @@
         <v>839</v>
       </c>
       <c r="N372" t="n">
-        <v>1516.0388215585</v>
+        <v>1516.0388206553</v>
       </c>
       <c r="O372" t="n">
-        <v>1271956.571287582</v>
+        <v>1271956.570529797</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
@@ -17234,10 +17234,10 @@
         <v>2243</v>
       </c>
       <c r="N381" t="n">
-        <v>692.15197854077</v>
+        <v>692.1519887834301</v>
       </c>
       <c r="O381" t="n">
-        <v>1552496.887866947</v>
+        <v>1552496.910841234</v>
       </c>
       <c r="P381" t="n">
         <v>1200</v>
@@ -18187,10 +18187,10 @@
         <v>238</v>
       </c>
       <c r="N401" t="n">
-        <v>1690.8700086994</v>
+        <v>1690.8700087222</v>
       </c>
       <c r="O401" t="n">
-        <v>402427.0620704572</v>
+        <v>402427.0620758836</v>
       </c>
       <c r="P401" t="n">
         <v>3000</v>
@@ -18471,10 +18471,10 @@
         <v>78</v>
       </c>
       <c r="N407" t="n">
-        <v>3907.5003137255</v>
+        <v>3907.5003162055</v>
       </c>
       <c r="O407" t="n">
-        <v>304785.024470589</v>
+        <v>304785.024664029</v>
       </c>
       <c r="P407" t="n">
         <v>3900</v>
@@ -18564,10 +18564,10 @@
         <v>7734</v>
       </c>
       <c r="N409" t="n">
-        <v>711.33665411716</v>
+        <v>711.33665018328</v>
       </c>
       <c r="O409" t="n">
-        <v>5501477.682942116</v>
+        <v>5501477.652517487</v>
       </c>
       <c r="P409" t="n">
         <v>900</v>
@@ -19216,10 +19216,10 @@
         <v>2</v>
       </c>
       <c r="N423" t="n">
-        <v>3110.8439531303</v>
+        <v>3110.8438819661</v>
       </c>
       <c r="O423" t="n">
-        <v>6221.6879062606</v>
+        <v>6221.6877639322</v>
       </c>
       <c r="P423" t="n">
         <v>4500</v>
@@ -20150,10 +20150,10 @@
         <v>381</v>
       </c>
       <c r="N443" t="n">
-        <v>1595.5196827833</v>
+        <v>1595.5196456996</v>
       </c>
       <c r="O443" t="n">
-        <v>607892.9991404372</v>
+        <v>607892.9850115476</v>
       </c>
       <c r="P443" t="n">
         <v>2500</v>
@@ -22234,10 +22234,10 @@
         <v>152</v>
       </c>
       <c r="N486" t="n">
-        <v>7046.9398312236</v>
+        <v>7046.9398310097</v>
       </c>
       <c r="O486" t="n">
-        <v>1071134.854345987</v>
+        <v>1071134.854313474</v>
       </c>
       <c r="P486" t="n">
         <v>9900</v>
@@ -22332,10 +22332,10 @@
         <v>9</v>
       </c>
       <c r="N488" t="n">
-        <v>15577.047777778</v>
+        <v>15577.048235294</v>
       </c>
       <c r="O488" t="n">
-        <v>140193.430000002</v>
+        <v>140193.434117646</v>
       </c>
       <c r="P488" t="n">
         <v>19900</v>
@@ -22865,10 +22865,10 @@
         <v>70</v>
       </c>
       <c r="N499" t="n">
-        <v>44113.603597884</v>
+        <v>44113.603675676</v>
       </c>
       <c r="O499" t="n">
-        <v>3087952.25185188</v>
+        <v>3087952.25729732</v>
       </c>
       <c r="P499" t="n">
         <v>71900</v>
@@ -23517,10 +23517,10 @@
         <v>216</v>
       </c>
       <c r="N513" t="n">
-        <v>1008.8200998573</v>
+        <v>1008.8197488922</v>
       </c>
       <c r="O513" t="n">
-        <v>217905.1415691768</v>
+        <v>217905.0657607152</v>
       </c>
       <c r="P513" t="n">
         <v>1500</v>
@@ -23820,10 +23820,10 @@
         <v>11</v>
       </c>
       <c r="N520" t="n">
-        <v>22951.705030902</v>
+        <v>22951.705024752</v>
       </c>
       <c r="O520" t="n">
-        <v>252468.755339922</v>
+        <v>252468.755272272</v>
       </c>
       <c r="P520" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7465268817</v>
+        <v>3376.7465222073</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.211279558</v>
+        <v>1982150.208535685</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1190,10 +1190,10 @@
         <v>450</v>
       </c>
       <c r="N20" t="n">
-        <v>3926.8371355499</v>
+        <v>3926.8371340839</v>
       </c>
       <c r="O20" t="n">
-        <v>1767076.710997455</v>
+        <v>1767076.710337755</v>
       </c>
       <c r="P20" t="n">
         <v>4800</v>
@@ -1747,10 +1747,10 @@
         <v>42</v>
       </c>
       <c r="N34" t="n">
-        <v>15711.966441948</v>
+        <v>15711.966415094</v>
       </c>
       <c r="O34" t="n">
-        <v>659902.590561816</v>
+        <v>659902.589433948</v>
       </c>
       <c r="P34" t="n">
         <v>28500</v>
@@ -3440,10 +3440,10 @@
         <v>120</v>
       </c>
       <c r="N74" t="n">
-        <v>1098.0517240829</v>
+        <v>1098.0519160318</v>
       </c>
       <c r="O74" t="n">
-        <v>131766.206889948</v>
+        <v>131766.229923816</v>
       </c>
       <c r="P74" t="n">
         <v>1500</v>
@@ -5090,10 +5090,10 @@
         <v>487</v>
       </c>
       <c r="N111" t="n">
-        <v>4890.9300453258</v>
+        <v>4890.9300453515</v>
       </c>
       <c r="O111" t="n">
-        <v>2381882.932073665</v>
+        <v>2381882.93208618</v>
       </c>
       <c r="P111" t="n">
         <v>8200</v>
@@ -5538,10 +5538,10 @@
         <v>120</v>
       </c>
       <c r="N121" t="n">
-        <v>3240.850028169</v>
+        <v>3240.85002886</v>
       </c>
       <c r="O121" t="n">
-        <v>388902.00338028</v>
+        <v>388902.0034632</v>
       </c>
       <c r="P121" t="n">
         <v>5200</v>
@@ -5623,10 +5623,10 @@
         <v>135</v>
       </c>
       <c r="N123" t="n">
-        <v>5191.4800264901</v>
+        <v>5191.4800265252</v>
       </c>
       <c r="O123" t="n">
-        <v>700849.8035761635</v>
+        <v>700849.8035809019</v>
       </c>
       <c r="P123" t="n">
         <v>9100</v>
@@ -6025,10 +6025,10 @@
         <v>63</v>
       </c>
       <c r="N132" t="n">
-        <v>4193.85</v>
+        <v>4242.3899305556</v>
       </c>
       <c r="O132" t="n">
-        <v>264212.55</v>
+        <v>267270.5656250028</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -6074,10 +6074,10 @@
         <v>535</v>
       </c>
       <c r="N133" t="n">
-        <v>3041.6600119048</v>
+        <v>3041.6600119617</v>
       </c>
       <c r="O133" t="n">
-        <v>1627288.106369068</v>
+        <v>1627288.10639951</v>
       </c>
       <c r="P133" t="n">
         <v>5500</v>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="J142" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -6465,19 +6465,19 @@
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="N142" t="n">
         <v>6242.93</v>
       </c>
       <c r="O142" t="n">
-        <v>1891607.79</v>
+        <v>1885364.86</v>
       </c>
       <c r="P142" t="n">
         <v>10400</v>
       </c>
       <c r="Q142" t="n">
-        <v>3151200</v>
+        <v>3140800</v>
       </c>
     </row>
     <row r="143">
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -7337,19 +7337,19 @@
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="N161" t="n">
-        <v>9635.7603030303</v>
+        <v>9635.760312500001</v>
       </c>
       <c r="O161" t="n">
-        <v>549238.337272727</v>
+        <v>443244.974375</v>
       </c>
       <c r="P161" t="n">
         <v>12500</v>
       </c>
       <c r="Q161" t="n">
-        <v>712500</v>
+        <v>575000</v>
       </c>
     </row>
     <row r="162">
@@ -7426,7 +7426,7 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -7435,19 +7435,19 @@
         <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="N163" t="n">
         <v>5853</v>
       </c>
       <c r="O163" t="n">
-        <v>778449</v>
+        <v>690654</v>
       </c>
       <c r="P163" t="n">
         <v>9900</v>
       </c>
       <c r="Q163" t="n">
-        <v>1316700</v>
+        <v>1168200</v>
       </c>
     </row>
     <row r="164">
@@ -7659,10 +7659,10 @@
         <v>300</v>
       </c>
       <c r="N168" t="n">
-        <v>1630.9228220183</v>
+        <v>1630.9228476208</v>
       </c>
       <c r="O168" t="n">
-        <v>489276.84660549</v>
+        <v>489276.85428624</v>
       </c>
       <c r="P168" t="n">
         <v>2500</v>
@@ -7705,10 +7705,10 @@
         <v>96</v>
       </c>
       <c r="N169" t="n">
-        <v>1550.1927548066</v>
+        <v>1550.1927793589</v>
       </c>
       <c r="O169" t="n">
-        <v>148818.5044614336</v>
+        <v>148818.5068184544</v>
       </c>
       <c r="P169" t="n">
         <v>2500</v>
@@ -7751,10 +7751,10 @@
         <v>48</v>
       </c>
       <c r="N170" t="n">
-        <v>1579.391452381</v>
+        <v>1579.3914319809</v>
       </c>
       <c r="O170" t="n">
-        <v>75810.789714288</v>
+        <v>75810.7887350832</v>
       </c>
       <c r="P170" t="n">
         <v>2900</v>
@@ -9092,10 +9092,10 @@
         <v>348</v>
       </c>
       <c r="N201" t="n">
-        <v>2029.8734883721</v>
+        <v>2029.8735277516</v>
       </c>
       <c r="O201" t="n">
-        <v>706395.9739534907</v>
+        <v>706395.9876575568</v>
       </c>
       <c r="P201" t="n">
         <v>3600</v>
@@ -9297,10 +9297,10 @@
         <v>170</v>
       </c>
       <c r="N206" t="n">
-        <v>2680.7397012195</v>
+        <v>2680.739700672</v>
       </c>
       <c r="O206" t="n">
-        <v>455725.749207315</v>
+        <v>455725.7491142399</v>
       </c>
       <c r="P206" t="n">
         <v>4900</v>
@@ -9558,10 +9558,10 @@
         <v>609</v>
       </c>
       <c r="N212" t="n">
-        <v>998.76124730022</v>
+        <v>998.76125748503</v>
       </c>
       <c r="O212" t="n">
-        <v>608245.599605834</v>
+        <v>608245.6058083833</v>
       </c>
       <c r="P212" t="n">
         <v>1600</v>
@@ -10406,10 +10406,10 @@
         <v>97</v>
       </c>
       <c r="N232" t="n">
-        <v>2568.835631068</v>
+        <v>2568.8356026059</v>
       </c>
       <c r="O232" t="n">
-        <v>249177.056213596</v>
+        <v>249177.0534527723</v>
       </c>
       <c r="P232" t="n">
         <v>4500</v>
@@ -10534,10 +10534,10 @@
         <v>180</v>
       </c>
       <c r="N235" t="n">
-        <v>7969.9501638124</v>
+        <v>7969.9501643017</v>
       </c>
       <c r="O235" t="n">
-        <v>1434591.029486232</v>
+        <v>1434591.029574306</v>
       </c>
       <c r="P235" t="n">
         <v>12900</v>
@@ -11939,10 +11939,10 @@
         <v>1215</v>
       </c>
       <c r="N266" t="n">
-        <v>1778.4724932172</v>
+        <v>1778.4724989266</v>
       </c>
       <c r="O266" t="n">
-        <v>2160844.079258898</v>
+        <v>2160844.086195819</v>
       </c>
       <c r="P266" t="n">
         <v>4900</v>
@@ -14253,10 +14253,10 @@
         <v>263</v>
       </c>
       <c r="N316" t="n">
-        <v>2252.2960775371</v>
+        <v>2252.2960914286</v>
       </c>
       <c r="O316" t="n">
-        <v>592353.8683922573</v>
+        <v>592353.8720457217</v>
       </c>
       <c r="P316" t="n">
         <v>3900</v>
@@ -14440,10 +14440,10 @@
         <v>504</v>
       </c>
       <c r="N320" t="n">
-        <v>2328.1187653599</v>
+        <v>2328.11876101</v>
       </c>
       <c r="O320" t="n">
-        <v>1173371.85774139</v>
+        <v>1173371.85554904</v>
       </c>
       <c r="P320" t="n">
         <v>4500</v>
@@ -14854,10 +14854,10 @@
         <v>184</v>
       </c>
       <c r="N329" t="n">
-        <v>4907.8218731563</v>
+        <v>4907.821884273</v>
       </c>
       <c r="O329" t="n">
-        <v>903039.2246607592</v>
+        <v>903039.2267062321</v>
       </c>
       <c r="P329" t="n">
         <v>8200</v>
@@ -15084,10 +15084,10 @@
         <v>84</v>
       </c>
       <c r="N334" t="n">
-        <v>3903.7357803468</v>
+        <v>3903.7358031838</v>
       </c>
       <c r="O334" t="n">
-        <v>327913.8055491312</v>
+        <v>327913.8074674392</v>
       </c>
       <c r="P334" t="n">
         <v>7500</v>
@@ -16321,10 +16321,10 @@
         <v>60</v>
       </c>
       <c r="N361" t="n">
-        <v>4268.7018707483</v>
+        <v>4268.702245614</v>
       </c>
       <c r="O361" t="n">
-        <v>256122.112244898</v>
+        <v>256122.13473684</v>
       </c>
       <c r="P361" t="n">
         <v>6900</v>
@@ -16827,10 +16827,10 @@
         <v>839</v>
       </c>
       <c r="N372" t="n">
-        <v>1516.0388206553</v>
+        <v>1516.0388192979</v>
       </c>
       <c r="O372" t="n">
-        <v>1271956.570529797</v>
+        <v>1271956.569390938</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
@@ -17234,10 +17234,10 @@
         <v>2243</v>
       </c>
       <c r="N381" t="n">
-        <v>692.1519887834301</v>
+        <v>692.151995671</v>
       </c>
       <c r="O381" t="n">
-        <v>1552496.910841234</v>
+        <v>1552496.926290053</v>
       </c>
       <c r="P381" t="n">
         <v>1200</v>
@@ -17574,10 +17574,10 @@
         <v>31</v>
       </c>
       <c r="N388" t="n">
-        <v>2857.22</v>
+        <v>2861.1357880311</v>
       </c>
       <c r="O388" t="n">
-        <v>88573.81999999999</v>
+        <v>88695.20942896411</v>
       </c>
       <c r="P388" t="n">
         <v>4900</v>
@@ -17767,10 +17767,10 @@
         <v>780</v>
       </c>
       <c r="N392" t="n">
-        <v>1530.4499206664</v>
+        <v>1530.4499206349</v>
       </c>
       <c r="O392" t="n">
-        <v>1193750.938119792</v>
+        <v>1193750.938095222</v>
       </c>
       <c r="P392" t="n">
         <v>2600</v>
@@ -18187,10 +18187,10 @@
         <v>238</v>
       </c>
       <c r="N401" t="n">
-        <v>1690.8700087222</v>
+        <v>1690.8700087336</v>
       </c>
       <c r="O401" t="n">
-        <v>402427.0620758836</v>
+        <v>402427.0620785968</v>
       </c>
       <c r="P401" t="n">
         <v>3000</v>
@@ -18422,10 +18422,10 @@
         <v>5845</v>
       </c>
       <c r="N406" t="n">
-        <v>345.55838654429</v>
+        <v>345.55838640256</v>
       </c>
       <c r="O406" t="n">
-        <v>2019788.769351375</v>
+        <v>2019788.768522963</v>
       </c>
       <c r="P406" t="n">
         <v>600</v>
@@ -19216,10 +19216,10 @@
         <v>2</v>
       </c>
       <c r="N423" t="n">
-        <v>3110.8438819661</v>
+        <v>3110.8436976288</v>
       </c>
       <c r="O423" t="n">
-        <v>6221.6877639322</v>
+        <v>6221.6873952576</v>
       </c>
       <c r="P423" t="n">
         <v>4500</v>
@@ -19406,10 +19406,10 @@
         <v>127</v>
       </c>
       <c r="N427" t="n">
-        <v>3182.2510791367</v>
+        <v>3182.2510752688</v>
       </c>
       <c r="O427" t="n">
-        <v>404145.8870503609</v>
+        <v>404145.8865591376</v>
       </c>
       <c r="P427" t="n">
         <v>6900</v>
@@ -19590,10 +19590,10 @@
         <v>4</v>
       </c>
       <c r="N431" t="n">
-        <v>2501.3856451613</v>
+        <v>2501.3856275304</v>
       </c>
       <c r="O431" t="n">
-        <v>10005.5425806452</v>
+        <v>10005.5425101216</v>
       </c>
       <c r="P431" t="n">
         <v>4100</v>
@@ -20016,10 +20016,10 @@
         <v>21</v>
       </c>
       <c r="N440" t="n">
-        <v>712.62888446215</v>
+        <v>712.62863414634</v>
       </c>
       <c r="O440" t="n">
-        <v>14965.20657370515</v>
+        <v>14965.20131707314</v>
       </c>
       <c r="P440" t="n">
         <v>700</v>
@@ -20150,10 +20150,10 @@
         <v>381</v>
       </c>
       <c r="N443" t="n">
-        <v>1595.5196456996</v>
+        <v>1595.5195815035</v>
       </c>
       <c r="O443" t="n">
-        <v>607892.9850115476</v>
+        <v>607892.9605528335</v>
       </c>
       <c r="P443" t="n">
         <v>2500</v>
@@ -22234,10 +22234,10 @@
         <v>152</v>
       </c>
       <c r="N486" t="n">
-        <v>7046.9398310097</v>
+        <v>7046.9398308668</v>
       </c>
       <c r="O486" t="n">
-        <v>1071134.854313474</v>
+        <v>1071134.854291754</v>
       </c>
       <c r="P486" t="n">
         <v>9900</v>
@@ -23202,10 +23202,10 @@
         <v>288</v>
       </c>
       <c r="N506" t="n">
-        <v>430.6099770247</v>
+        <v>430.60997670355</v>
       </c>
       <c r="O506" t="n">
-        <v>124015.6733831136</v>
+        <v>124015.6732906224</v>
       </c>
       <c r="P506" t="n">
         <v>2200</v>
@@ -23517,10 +23517,10 @@
         <v>216</v>
       </c>
       <c r="N513" t="n">
-        <v>1008.8197488922</v>
+        <v>1008.8186415712</v>
       </c>
       <c r="O513" t="n">
-        <v>217905.0657607152</v>
+        <v>217904.8265793792</v>
       </c>
       <c r="P513" t="n">
         <v>1500</v>
@@ -25353,10 +25353,10 @@
         <v>3</v>
       </c>
       <c r="N553" t="n">
-        <v>2432.1338016529</v>
+        <v>2432.1338655462</v>
       </c>
       <c r="O553" t="n">
-        <v>7296.401404958699</v>
+        <v>7296.4015966386</v>
       </c>
       <c r="P553" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -6025,10 +6025,10 @@
         <v>63</v>
       </c>
       <c r="N132" t="n">
-        <v>4242.3899305556</v>
+        <v>4193.85</v>
       </c>
       <c r="O132" t="n">
-        <v>267270.5656250028</v>
+        <v>264212.55</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -17574,10 +17574,10 @@
         <v>31</v>
       </c>
       <c r="N388" t="n">
-        <v>2861.1357880311</v>
+        <v>2857.22</v>
       </c>
       <c r="O388" t="n">
-        <v>88695.20942896411</v>
+        <v>88573.81999999999</v>
       </c>
       <c r="P388" t="n">
         <v>4900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-04</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7465222073</v>
+        <v>3376.746520334</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.208535685</v>
+        <v>1982150.207436058</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -953,10 +953,10 @@
         <v>178</v>
       </c>
       <c r="N14" t="n">
-        <v>1854.2366666667</v>
+        <v>1854.2367246377</v>
       </c>
       <c r="O14" t="n">
-        <v>330054.1266666726</v>
+        <v>330054.1369855106</v>
       </c>
       <c r="P14" t="n">
         <v>3200</v>
@@ -1310,10 +1310,10 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>2413.0011709602</v>
+        <v>2413.0011723329</v>
       </c>
       <c r="O23" t="n">
-        <v>2413.0011709602</v>
+        <v>2413.0011723329</v>
       </c>
       <c r="P23" t="n">
         <v>4700</v>
@@ -1747,10 +1747,10 @@
         <v>42</v>
       </c>
       <c r="N34" t="n">
-        <v>15711.966415094</v>
+        <v>15711.966317829</v>
       </c>
       <c r="O34" t="n">
-        <v>659902.589433948</v>
+        <v>659902.585348818</v>
       </c>
       <c r="P34" t="n">
         <v>28500</v>
@@ -2233,10 +2233,10 @@
         <v>37</v>
       </c>
       <c r="N46" t="n">
-        <v>61666.873832487</v>
+        <v>61666.873842239</v>
       </c>
       <c r="O46" t="n">
-        <v>2281674.331802019</v>
+        <v>2281674.332162843</v>
       </c>
       <c r="P46" t="n">
         <v>98900</v>
@@ -2695,10 +2695,10 @@
         <v>178</v>
       </c>
       <c r="N57" t="n">
-        <v>3340.6800775194</v>
+        <v>3340.6800784314</v>
       </c>
       <c r="O57" t="n">
-        <v>594641.0537984532</v>
+        <v>594641.0539607892</v>
       </c>
       <c r="P57" t="n">
         <v>7100</v>
@@ -2999,10 +2999,10 @@
         <v>228</v>
       </c>
       <c r="N64" t="n">
-        <v>1950.2152617329</v>
+        <v>1950.2152574526</v>
       </c>
       <c r="O64" t="n">
-        <v>444649.0796751012</v>
+        <v>444649.0786991928</v>
       </c>
       <c r="P64" t="n">
         <v>2900</v>
@@ -3440,10 +3440,10 @@
         <v>120</v>
       </c>
       <c r="N74" t="n">
-        <v>1098.0519160318</v>
+        <v>1098.0523152957</v>
       </c>
       <c r="O74" t="n">
-        <v>131766.229923816</v>
+        <v>131766.277835484</v>
       </c>
       <c r="P74" t="n">
         <v>1500</v>
@@ -4911,10 +4911,10 @@
         <v>577</v>
       </c>
       <c r="N107" t="n">
-        <v>3795.7100070286</v>
+        <v>3795.7100070299</v>
       </c>
       <c r="O107" t="n">
-        <v>2190124.674055502</v>
+        <v>2190124.674056252</v>
       </c>
       <c r="P107" t="n">
         <v>6200</v>
@@ -5538,10 +5538,10 @@
         <v>120</v>
       </c>
       <c r="N121" t="n">
-        <v>3240.85002886</v>
+        <v>3240.8500289017</v>
       </c>
       <c r="O121" t="n">
-        <v>388902.0034632</v>
+        <v>388902.003468204</v>
       </c>
       <c r="P121" t="n">
         <v>5200</v>
@@ -5760,10 +5760,10 @@
         <v>506</v>
       </c>
       <c r="N126" t="n">
-        <v>19098.750004659</v>
+        <v>19098.75000466</v>
       </c>
       <c r="O126" t="n">
-        <v>9663967.502357453</v>
+        <v>9663967.50235796</v>
       </c>
       <c r="P126" t="n">
         <v>15000</v>
@@ -6074,10 +6074,10 @@
         <v>535</v>
       </c>
       <c r="N133" t="n">
-        <v>3041.6600119617</v>
+        <v>3041.6600120048</v>
       </c>
       <c r="O133" t="n">
-        <v>1627288.10639951</v>
+        <v>1627288.106422568</v>
       </c>
       <c r="P133" t="n">
         <v>5500</v>
@@ -7340,10 +7340,10 @@
         <v>46</v>
       </c>
       <c r="N161" t="n">
-        <v>9635.760312500001</v>
+        <v>9635.760317460299</v>
       </c>
       <c r="O161" t="n">
-        <v>443244.974375</v>
+        <v>443244.9746031738</v>
       </c>
       <c r="P161" t="n">
         <v>12500</v>
@@ -7659,10 +7659,10 @@
         <v>300</v>
       </c>
       <c r="N168" t="n">
-        <v>1630.9228476208</v>
+        <v>1630.9229073724</v>
       </c>
       <c r="O168" t="n">
-        <v>489276.85428624</v>
+        <v>489276.87221172</v>
       </c>
       <c r="P168" t="n">
         <v>2500</v>
@@ -7705,10 +7705,10 @@
         <v>96</v>
       </c>
       <c r="N169" t="n">
-        <v>1550.1927793589</v>
+        <v>1550.1928456407</v>
       </c>
       <c r="O169" t="n">
-        <v>148818.5068184544</v>
+        <v>148818.5131815072</v>
       </c>
       <c r="P169" t="n">
         <v>2500</v>
@@ -7751,10 +7751,10 @@
         <v>48</v>
       </c>
       <c r="N170" t="n">
-        <v>1579.3914319809</v>
+        <v>1579.3914114833</v>
       </c>
       <c r="O170" t="n">
-        <v>75810.7887350832</v>
+        <v>75810.7877511984</v>
       </c>
       <c r="P170" t="n">
         <v>2900</v>
@@ -9133,10 +9133,10 @@
         <v>160</v>
       </c>
       <c r="N202" t="n">
-        <v>22485.695964126</v>
+        <v>22485.695955056</v>
       </c>
       <c r="O202" t="n">
-        <v>3597711.35426016</v>
+        <v>3597711.35280896</v>
       </c>
       <c r="P202" t="n">
         <v>36500</v>
@@ -9297,10 +9297,10 @@
         <v>170</v>
       </c>
       <c r="N206" t="n">
-        <v>2680.739700672</v>
+        <v>2680.739700489</v>
       </c>
       <c r="O206" t="n">
-        <v>455725.7491142399</v>
+        <v>455725.74908313</v>
       </c>
       <c r="P206" t="n">
         <v>4900</v>
@@ -9558,10 +9558,10 @@
         <v>609</v>
       </c>
       <c r="N212" t="n">
-        <v>998.76125748503</v>
+        <v>998.76125816993</v>
       </c>
       <c r="O212" t="n">
-        <v>608245.6058083833</v>
+        <v>608245.6062254873</v>
       </c>
       <c r="P212" t="n">
         <v>1600</v>
@@ -10109,10 +10109,10 @@
         <v>40</v>
       </c>
       <c r="N225" t="n">
-        <v>27123.765285451</v>
+        <v>27123.765268022</v>
       </c>
       <c r="O225" t="n">
-        <v>1084950.61141804</v>
+        <v>1084950.61072088</v>
       </c>
       <c r="P225" t="n">
         <v>44500</v>
@@ -11939,10 +11939,10 @@
         <v>1215</v>
       </c>
       <c r="N266" t="n">
-        <v>1778.4724989266</v>
+        <v>1778.4725014327</v>
       </c>
       <c r="O266" t="n">
-        <v>2160844.086195819</v>
+        <v>2160844.089240731</v>
       </c>
       <c r="P266" t="n">
         <v>4900</v>
@@ -14854,10 +14854,10 @@
         <v>184</v>
       </c>
       <c r="N329" t="n">
-        <v>4907.821884273</v>
+        <v>4907.8218926975</v>
       </c>
       <c r="O329" t="n">
-        <v>903039.2267062321</v>
+        <v>903039.2282563399</v>
       </c>
       <c r="P329" t="n">
         <v>8200</v>
@@ -16321,10 +16321,10 @@
         <v>60</v>
       </c>
       <c r="N361" t="n">
-        <v>4268.702245614</v>
+        <v>4268.7022887324</v>
       </c>
       <c r="O361" t="n">
-        <v>256122.13473684</v>
+        <v>256122.137323944</v>
       </c>
       <c r="P361" t="n">
         <v>6900</v>
@@ -16827,10 +16827,10 @@
         <v>839</v>
       </c>
       <c r="N372" t="n">
-        <v>1516.0388192979</v>
+        <v>1516.038818618</v>
       </c>
       <c r="O372" t="n">
-        <v>1271956.569390938</v>
+        <v>1271956.568820502</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
@@ -17234,10 +17234,10 @@
         <v>2243</v>
       </c>
       <c r="N381" t="n">
-        <v>692.151995671</v>
+        <v>692.15200959024</v>
       </c>
       <c r="O381" t="n">
-        <v>1552496.926290053</v>
+        <v>1552496.957510908</v>
       </c>
       <c r="P381" t="n">
         <v>1200</v>
@@ -18187,10 +18187,10 @@
         <v>238</v>
       </c>
       <c r="N401" t="n">
-        <v>1690.8700087336</v>
+        <v>1690.8700087796</v>
       </c>
       <c r="O401" t="n">
-        <v>402427.0620785968</v>
+        <v>402427.0620895448</v>
       </c>
       <c r="P401" t="n">
         <v>3000</v>
@@ -18471,10 +18471,10 @@
         <v>78</v>
       </c>
       <c r="N407" t="n">
-        <v>3907.5003162055</v>
+        <v>3907.5003174603</v>
       </c>
       <c r="O407" t="n">
-        <v>304785.024664029</v>
+        <v>304785.0247619034</v>
       </c>
       <c r="P407" t="n">
         <v>3900</v>
@@ -18564,10 +18564,10 @@
         <v>7734</v>
       </c>
       <c r="N409" t="n">
-        <v>711.33665018328</v>
+        <v>711.33665006743</v>
       </c>
       <c r="O409" t="n">
-        <v>5501477.652517487</v>
+        <v>5501477.651621504</v>
       </c>
       <c r="P409" t="n">
         <v>900</v>
@@ -19216,10 +19216,10 @@
         <v>2</v>
       </c>
       <c r="N423" t="n">
-        <v>3110.8436976288</v>
+        <v>3110.8435374771</v>
       </c>
       <c r="O423" t="n">
-        <v>6221.6873952576</v>
+        <v>6221.6870749542</v>
       </c>
       <c r="P423" t="n">
         <v>4500</v>
@@ -19590,10 +19590,10 @@
         <v>4</v>
       </c>
       <c r="N431" t="n">
-        <v>2501.3856275304</v>
+        <v>2501.3856097561</v>
       </c>
       <c r="O431" t="n">
-        <v>10005.5425101216</v>
+        <v>10005.5424390244</v>
       </c>
       <c r="P431" t="n">
         <v>4100</v>
@@ -20150,10 +20150,10 @@
         <v>381</v>
       </c>
       <c r="N443" t="n">
-        <v>1595.5195815035</v>
+        <v>1595.5194396439</v>
       </c>
       <c r="O443" t="n">
-        <v>607892.9605528335</v>
+        <v>607892.9065043258</v>
       </c>
       <c r="P443" t="n">
         <v>2500</v>
@@ -22234,10 +22234,10 @@
         <v>152</v>
       </c>
       <c r="N486" t="n">
-        <v>7046.9398308668</v>
+        <v>7046.939830831</v>
       </c>
       <c r="O486" t="n">
-        <v>1071134.854291754</v>
+        <v>1071134.854286312</v>
       </c>
       <c r="P486" t="n">
         <v>9900</v>
@@ -22960,10 +22960,10 @@
         <v>1372</v>
       </c>
       <c r="N501" t="n">
-        <v>665.32321943187</v>
+        <v>665.32324616023</v>
       </c>
       <c r="O501" t="n">
-        <v>912823.4570605257</v>
+        <v>912823.4937318356</v>
       </c>
       <c r="P501" t="n">
         <v>2900</v>
@@ -23517,10 +23517,10 @@
         <v>216</v>
       </c>
       <c r="N513" t="n">
-        <v>1008.8186415712</v>
+        <v>1008.8185289256</v>
       </c>
       <c r="O513" t="n">
-        <v>217904.8265793792</v>
+        <v>217904.8022479296</v>
       </c>
       <c r="P513" t="n">
         <v>1500</v>
@@ -25353,10 +25353,10 @@
         <v>3</v>
       </c>
       <c r="N553" t="n">
-        <v>2432.1338655462</v>
+        <v>2432.1340350877</v>
       </c>
       <c r="O553" t="n">
-        <v>7296.4015966386</v>
+        <v>7296.4021052631</v>
       </c>
       <c r="P553" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -634,10 +634,10 @@
         <v>27</v>
       </c>
       <c r="N6" t="n">
-        <v>27225.941422594</v>
+        <v>27000</v>
       </c>
       <c r="O6" t="n">
-        <v>735100.418410038</v>
+        <v>729000</v>
       </c>
       <c r="P6" t="n">
         <v>30000</v>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>2421.5176470588</v>
+        <v>2413.0011764706</v>
       </c>
       <c r="O22" t="n">
-        <v>2421.5176470588</v>
+        <v>2413.0011764706</v>
       </c>
       <c r="P22" t="n">
         <v>4700</v>
@@ -1310,10 +1310,10 @@
         <v>103</v>
       </c>
       <c r="N23" t="n">
-        <v>2487.0572046589</v>
+        <v>2474.7042429285</v>
       </c>
       <c r="O23" t="n">
-        <v>256166.8920798667</v>
+        <v>254894.5370216355</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -1708,10 +1708,10 @@
         <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>15834.716054688</v>
+        <v>15711.966289063</v>
       </c>
       <c r="O33" t="n">
-        <v>665058.074296896</v>
+        <v>659902.584140646</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -2783,10 +2783,10 @@
         <v>15</v>
       </c>
       <c r="N59" t="n">
-        <v>11705.0765</v>
+        <v>11513.19</v>
       </c>
       <c r="O59" t="n">
-        <v>175576.1475</v>
+        <v>172697.85</v>
       </c>
       <c r="P59" t="n">
         <v>17900</v>
@@ -3627,10 +3627,10 @@
         <v>218</v>
       </c>
       <c r="N78" t="n">
-        <v>13624.59908046</v>
+        <v>13593.35</v>
       </c>
       <c r="O78" t="n">
-        <v>2970162.59954028</v>
+        <v>2963350.3</v>
       </c>
       <c r="P78" t="n">
         <v>25500</v>
@@ -7751,10 +7751,10 @@
         <v>48</v>
       </c>
       <c r="N170" t="n">
-        <v>11658.147712418</v>
+        <v>11507.72</v>
       </c>
       <c r="O170" t="n">
-        <v>559591.090196064</v>
+        <v>552370.5599999999</v>
       </c>
       <c r="P170" t="n">
         <v>25800</v>
@@ -8720,10 +8720,10 @@
         <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>2667.5690712743</v>
+        <v>2661.82</v>
       </c>
       <c r="O192" t="n">
-        <v>2667.5690712743</v>
+        <v>2661.82</v>
       </c>
       <c r="P192" t="n">
         <v>3200</v>
@@ -8802,10 +8802,10 @@
         <v>29</v>
       </c>
       <c r="N194" t="n">
-        <v>4508.1255605381</v>
+        <v>4488</v>
       </c>
       <c r="O194" t="n">
-        <v>130735.6412556049</v>
+        <v>130152</v>
       </c>
       <c r="P194" t="n">
         <v>6200</v>
@@ -10070,10 +10070,10 @@
         <v>57</v>
       </c>
       <c r="N224" t="n">
-        <v>5453.6557676349</v>
+        <v>5431.12</v>
       </c>
       <c r="O224" t="n">
-        <v>310858.3787551893</v>
+        <v>309573.84</v>
       </c>
       <c r="P224" t="n">
         <v>8900</v>
@@ -11951,10 +11951,10 @@
         <v>62</v>
       </c>
       <c r="N266" t="n">
-        <v>16092.045229682</v>
+        <v>16058</v>
       </c>
       <c r="O266" t="n">
-        <v>997706.804240284</v>
+        <v>995596</v>
       </c>
       <c r="P266" t="n">
         <v>25900</v>
@@ -13805,10 +13805,10 @@
         <v>49</v>
       </c>
       <c r="N306" t="n">
-        <v>9704.4375</v>
+        <v>8508</v>
       </c>
       <c r="O306" t="n">
-        <v>475517.4375</v>
+        <v>416892</v>
       </c>
       <c r="P306" t="n">
         <v>14500</v>
@@ -14360,10 +14360,10 @@
         <v>81</v>
       </c>
       <c r="N318" t="n">
-        <v>21748.414253898</v>
+        <v>21676</v>
       </c>
       <c r="O318" t="n">
-        <v>1761621.554565738</v>
+        <v>1755756</v>
       </c>
       <c r="P318" t="n">
         <v>34900</v>
@@ -15510,10 +15510,10 @@
         <v>12</v>
       </c>
       <c r="N343" t="n">
-        <v>27422.4</v>
+        <v>27186</v>
       </c>
       <c r="O343" t="n">
-        <v>329068.8</v>
+        <v>326232</v>
       </c>
       <c r="P343" t="n">
         <v>43900</v>
@@ -15556,10 +15556,10 @@
         <v>159</v>
       </c>
       <c r="N344" t="n">
-        <v>3903.9739463602</v>
+        <v>3898</v>
       </c>
       <c r="O344" t="n">
-        <v>620731.8574712718</v>
+        <v>619782</v>
       </c>
       <c r="P344" t="n">
         <v>6900</v>
@@ -16379,10 +16379,10 @@
         <v>256</v>
       </c>
       <c r="N362" t="n">
-        <v>3647.235915493</v>
+        <v>3639.35</v>
       </c>
       <c r="O362" t="n">
-        <v>933692.394366208</v>
+        <v>931673.6</v>
       </c>
       <c r="P362" t="n">
         <v>7500</v>
@@ -16517,10 +16517,10 @@
         <v>6</v>
       </c>
       <c r="N365" t="n">
-        <v>12664.079439252</v>
+        <v>12489</v>
       </c>
       <c r="O365" t="n">
-        <v>75984.47663551199</v>
+        <v>74934</v>
       </c>
       <c r="P365" t="n">
         <v>20900</v>
@@ -20459,10 +20459,10 @@
         <v>23</v>
       </c>
       <c r="N449" t="n">
-        <v>2870.9917808219</v>
+        <v>2832.1946575342</v>
       </c>
       <c r="O449" t="n">
-        <v>66032.8109589037</v>
+        <v>65140.4771232866</v>
       </c>
       <c r="P449" t="n">
         <v>12900</v>
@@ -20652,10 +20652,10 @@
         <v>18</v>
       </c>
       <c r="N453" t="n">
-        <v>10649.1</v>
+        <v>9874.620000000001</v>
       </c>
       <c r="O453" t="n">
-        <v>191683.8</v>
+        <v>177743.16</v>
       </c>
       <c r="P453" t="n">
         <v>14700</v>
@@ -22353,10 +22353,10 @@
         <v>7</v>
       </c>
       <c r="N488" t="n">
-        <v>15827.732631579</v>
+        <v>14320.330526316</v>
       </c>
       <c r="O488" t="n">
-        <v>110794.128421053</v>
+        <v>100242.313684212</v>
       </c>
       <c r="P488" t="n">
         <v>19900</v>
@@ -22402,10 +22402,10 @@
         <v>15</v>
       </c>
       <c r="N489" t="n">
-        <v>17438.2184</v>
+        <v>16146.4984</v>
       </c>
       <c r="O489" t="n">
-        <v>261573.276</v>
+        <v>242197.476</v>
       </c>
       <c r="P489" t="n">
         <v>26900</v>
@@ -23694,10 +23694,10 @@
         <v>11</v>
       </c>
       <c r="N517" t="n">
-        <v>23008.657146402</v>
+        <v>22951.705012407</v>
       </c>
       <c r="O517" t="n">
-        <v>253095.228610422</v>
+        <v>252468.755136477</v>
       </c>
       <c r="P517" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -1073,10 +1073,10 @@
         <v>310</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8541142857</v>
+        <v>6300.2067296512</v>
       </c>
       <c r="O17" t="n">
-        <v>1944584.775428567</v>
+        <v>1953064.086191872</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1151,10 +1151,10 @@
         <v>450</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8371340839</v>
+        <v>3926.8371326165</v>
       </c>
       <c r="O19" t="n">
-        <v>1767076.710337755</v>
+        <v>1767076.709677425</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1708,10 +1708,10 @@
         <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.966289063</v>
+        <v>15711.966215139</v>
       </c>
       <c r="O33" t="n">
-        <v>659902.584140646</v>
+        <v>659902.581035838</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -2277,10 +2277,10 @@
         <v>386</v>
       </c>
       <c r="N47" t="n">
-        <v>3865.67</v>
+        <v>3872.3234767642</v>
       </c>
       <c r="O47" t="n">
-        <v>1492148.62</v>
+        <v>1494716.862030981</v>
       </c>
       <c r="P47" t="n">
         <v>5500</v>
@@ -2415,10 +2415,10 @@
         <v>114</v>
       </c>
       <c r="N50" t="n">
-        <v>2572.67</v>
+        <v>2589.9594489247</v>
       </c>
       <c r="O50" t="n">
-        <v>293284.38</v>
+        <v>295255.3771774158</v>
       </c>
       <c r="P50" t="n">
         <v>4700</v>
@@ -2500,10 +2500,10 @@
         <v>211</v>
       </c>
       <c r="N52" t="n">
-        <v>3114.49</v>
+        <v>3126.0967950311</v>
       </c>
       <c r="O52" t="n">
-        <v>657157.3899999999</v>
+        <v>659606.4237515621</v>
       </c>
       <c r="P52" t="n">
         <v>5500</v>
@@ -2617,10 +2617,10 @@
         <v>126</v>
       </c>
       <c r="N55" t="n">
-        <v>4378</v>
+        <v>4411.4198473282</v>
       </c>
       <c r="O55" t="n">
-        <v>551628</v>
+        <v>555838.9007633532</v>
       </c>
       <c r="P55" t="n">
         <v>3900</v>
@@ -3047,10 +3047,10 @@
         <v>434</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101589595</v>
+        <v>4937.3101595359</v>
       </c>
       <c r="O65" t="n">
-        <v>2142792.608988423</v>
+        <v>2142792.609238581</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0525080824</v>
+        <v>1098.0527732407</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.300969888</v>
+        <v>131766.332788884</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4872,10 +4872,10 @@
         <v>577</v>
       </c>
       <c r="N106" t="n">
-        <v>3795.7100070299</v>
+        <v>3801.7317574476</v>
       </c>
       <c r="O106" t="n">
-        <v>2190124.674056252</v>
+        <v>2193599.224047265</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
@@ -4918,10 +4918,10 @@
         <v>162</v>
       </c>
       <c r="N107" t="n">
-        <v>3684</v>
+        <v>3695.2967632027</v>
       </c>
       <c r="O107" t="n">
-        <v>596808</v>
+        <v>598638.0756388374</v>
       </c>
       <c r="P107" t="n">
         <v>6200</v>
@@ -5051,10 +5051,10 @@
         <v>487</v>
       </c>
       <c r="N110" t="n">
-        <v>4890.9300454545</v>
+        <v>4890.930045977</v>
       </c>
       <c r="O110" t="n">
-        <v>2381882.932136341</v>
+        <v>2381882.932390799</v>
       </c>
       <c r="P110" t="n">
         <v>8200</v>
@@ -5281,10 +5281,10 @@
         <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>8662</v>
+        <v>8687.96003996</v>
       </c>
       <c r="O115" t="n">
-        <v>17324</v>
+        <v>17375.92007992</v>
       </c>
       <c r="P115" t="n">
         <v>14200</v>
@@ -5499,10 +5499,10 @@
         <v>120</v>
       </c>
       <c r="N120" t="n">
-        <v>3240.8500291121</v>
+        <v>3240.8500291545</v>
       </c>
       <c r="O120" t="n">
-        <v>388902.003493452</v>
+        <v>388902.00349854</v>
       </c>
       <c r="P120" t="n">
         <v>5200</v>
@@ -5584,10 +5584,10 @@
         <v>135</v>
       </c>
       <c r="N122" t="n">
-        <v>5191.4800265252</v>
+        <v>5191.4800265604</v>
       </c>
       <c r="O122" t="n">
-        <v>700849.8035809019</v>
+        <v>700849.803585654</v>
       </c>
       <c r="P122" t="n">
         <v>9100</v>
@@ -5767,10 +5767,10 @@
         <v>22</v>
       </c>
       <c r="N126" t="n">
-        <v>12267.6513</v>
+        <v>12267.651212121</v>
       </c>
       <c r="O126" t="n">
-        <v>269888.3286</v>
+        <v>269888.326666662</v>
       </c>
       <c r="P126" t="n">
         <v>19900</v>
@@ -6035,10 +6035,10 @@
         <v>501</v>
       </c>
       <c r="N132" t="n">
-        <v>3041.6600123153</v>
+        <v>3041.6600123457</v>
       </c>
       <c r="O132" t="n">
-        <v>1523871.666169965</v>
+        <v>1523871.666185196</v>
       </c>
       <c r="P132" t="n">
         <v>5500</v>
@@ -6122,16 +6122,16 @@
         <v>1122</v>
       </c>
       <c r="N134" t="n">
-        <v>4086.2</v>
+        <v>4372.2107862617</v>
       </c>
       <c r="O134" t="n">
-        <v>4584716.399999999</v>
+        <v>4905620.502185628</v>
       </c>
       <c r="P134" t="n">
-        <v>6900</v>
+        <v>7500</v>
       </c>
       <c r="Q134" t="n">
-        <v>7741800</v>
+        <v>8415000</v>
       </c>
     </row>
     <row r="135">
@@ -6214,10 +6214,10 @@
         <v>763</v>
       </c>
       <c r="N136" t="n">
-        <v>3655.96</v>
+        <v>3660.708</v>
       </c>
       <c r="O136" t="n">
-        <v>2789497.48</v>
+        <v>2793120.204</v>
       </c>
       <c r="P136" t="n">
         <v>5500</v>
@@ -7446,10 +7446,10 @@
         <v>65</v>
       </c>
       <c r="N163" t="n">
-        <v>9678.9</v>
+        <v>9795.0468</v>
       </c>
       <c r="O163" t="n">
-        <v>629128.5</v>
+        <v>636678.042</v>
       </c>
       <c r="P163" t="n">
         <v>15500</v>
@@ -7574,10 +7574,10 @@
         <v>300</v>
       </c>
       <c r="N166" t="n">
-        <v>1630.9229356747</v>
+        <v>1630.9229788882</v>
       </c>
       <c r="O166" t="n">
-        <v>489276.88070241</v>
+        <v>489276.89366646</v>
       </c>
       <c r="P166" t="n">
         <v>2500</v>
@@ -7620,10 +7620,10 @@
         <v>96</v>
       </c>
       <c r="N167" t="n">
-        <v>1550.192872291</v>
+        <v>1550.1929105882</v>
       </c>
       <c r="O167" t="n">
-        <v>148818.515739936</v>
+        <v>148818.5194164672</v>
       </c>
       <c r="P167" t="n">
         <v>2500</v>
@@ -7666,10 +7666,10 @@
         <v>48</v>
       </c>
       <c r="N168" t="n">
-        <v>1579.3914114833</v>
+        <v>1579.3913493976</v>
       </c>
       <c r="O168" t="n">
-        <v>75810.7877511984</v>
+        <v>75810.7847710848</v>
       </c>
       <c r="P168" t="n">
         <v>2900</v>
@@ -7877,10 +7877,10 @@
         <v>1057</v>
       </c>
       <c r="N173" t="n">
-        <v>1301.3994046938</v>
+        <v>1303.6380504587</v>
       </c>
       <c r="O173" t="n">
-        <v>1375579.170761347</v>
+        <v>1377945.419334846</v>
       </c>
       <c r="P173" t="n">
         <v>2000</v>
@@ -8020,10 +8020,10 @@
         <v>192</v>
       </c>
       <c r="N176" t="n">
-        <v>1965</v>
+        <v>2030.7740585774</v>
       </c>
       <c r="O176" t="n">
-        <v>377280</v>
+        <v>389908.6192468608</v>
       </c>
       <c r="P176" t="n">
         <v>3700</v>
@@ -8720,10 +8720,10 @@
         <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>2661.82</v>
+        <v>2696.7673085339</v>
       </c>
       <c r="O192" t="n">
-        <v>2661.82</v>
+        <v>2696.7673085339</v>
       </c>
       <c r="P192" t="n">
         <v>3200</v>
@@ -8802,10 +8802,10 @@
         <v>29</v>
       </c>
       <c r="N194" t="n">
-        <v>4488</v>
+        <v>4550.9158878505</v>
       </c>
       <c r="O194" t="n">
-        <v>130152</v>
+        <v>131976.5607476645</v>
       </c>
       <c r="P194" t="n">
         <v>6200</v>
@@ -8843,10 +8843,10 @@
         <v>195</v>
       </c>
       <c r="N195" t="n">
-        <v>8794.48</v>
+        <v>8818.9498942682</v>
       </c>
       <c r="O195" t="n">
-        <v>1714923.6</v>
+        <v>1719695.229382299</v>
       </c>
       <c r="P195" t="n">
         <v>14500</v>
@@ -8966,10 +8966,10 @@
         <v>551</v>
       </c>
       <c r="N198" t="n">
-        <v>2517.22</v>
+        <v>2558.6841592313</v>
       </c>
       <c r="O198" t="n">
-        <v>1386988.22</v>
+        <v>1409834.971736446</v>
       </c>
       <c r="P198" t="n">
         <v>4200</v>
@@ -9007,10 +9007,10 @@
         <v>348</v>
       </c>
       <c r="N199" t="n">
-        <v>2029.8735344015</v>
+        <v>2035.7801454898</v>
       </c>
       <c r="O199" t="n">
-        <v>706395.989971722</v>
+        <v>708451.4906304504</v>
       </c>
       <c r="P199" t="n">
         <v>3600</v>
@@ -9048,10 +9048,10 @@
         <v>160</v>
       </c>
       <c r="N200" t="n">
-        <v>22485.695945946</v>
+        <v>22561.918644068</v>
       </c>
       <c r="O200" t="n">
-        <v>3597711.35135136</v>
+        <v>3609906.98305088</v>
       </c>
       <c r="P200" t="n">
         <v>36500</v>
@@ -9130,10 +9130,10 @@
         <v>214</v>
       </c>
       <c r="N202" t="n">
-        <v>7103</v>
+        <v>7136.7702060222</v>
       </c>
       <c r="O202" t="n">
-        <v>1520042</v>
+        <v>1527268.824088751</v>
       </c>
       <c r="P202" t="n">
         <v>10700</v>
@@ -10680,10 +10680,10 @@
         <v>154</v>
       </c>
       <c r="N238" t="n">
-        <v>548.14729553903</v>
+        <v>548.14728797763</v>
       </c>
       <c r="O238" t="n">
-        <v>84414.68351301062</v>
+        <v>84414.68234855501</v>
       </c>
       <c r="P238" t="n">
         <v>2000</v>
@@ -11075,10 +11075,10 @@
         <v>119</v>
       </c>
       <c r="N247" t="n">
-        <v>3590.77</v>
+        <v>3779.7578947368</v>
       </c>
       <c r="O247" t="n">
-        <v>427301.63</v>
+        <v>449791.1894736792</v>
       </c>
       <c r="P247" t="n">
         <v>3900</v>
@@ -11685,10 +11685,10 @@
         <v>3</v>
       </c>
       <c r="N260" t="n">
-        <v>23521.624927536</v>
+        <v>23521.624852941</v>
       </c>
       <c r="O260" t="n">
-        <v>70564.87478260799</v>
+        <v>70564.87455882301</v>
       </c>
       <c r="P260" t="n">
         <v>39000</v>
@@ -11813,10 +11813,10 @@
         <v>1215</v>
       </c>
       <c r="N263" t="n">
-        <v>1778.4725043029</v>
+        <v>1778.4725093418</v>
       </c>
       <c r="O263" t="n">
-        <v>2160844.092728023</v>
+        <v>2160844.098850287</v>
       </c>
       <c r="P263" t="n">
         <v>4900</v>
@@ -12135,10 +12135,10 @@
         <v>68</v>
       </c>
       <c r="N270" t="n">
-        <v>11450</v>
+        <v>11682.094594595</v>
       </c>
       <c r="O270" t="n">
-        <v>778600</v>
+        <v>794382.43243246</v>
       </c>
       <c r="P270" t="n">
         <v>18300</v>
@@ -12181,10 +12181,10 @@
         <v>131</v>
       </c>
       <c r="N271" t="n">
-        <v>6300</v>
+        <v>6365.625</v>
       </c>
       <c r="O271" t="n">
-        <v>825300</v>
+        <v>833896.875</v>
       </c>
       <c r="P271" t="n">
         <v>10200</v>
@@ -12365,10 +12365,10 @@
         <v>61</v>
       </c>
       <c r="N275" t="n">
-        <v>7230</v>
+        <v>7371.3029315961</v>
       </c>
       <c r="O275" t="n">
-        <v>441030</v>
+        <v>449649.4788273621</v>
       </c>
       <c r="P275" t="n">
         <v>11600</v>
@@ -12411,10 +12411,10 @@
         <v>79</v>
       </c>
       <c r="N276" t="n">
-        <v>5200</v>
+        <v>5291.8727915194</v>
       </c>
       <c r="O276" t="n">
-        <v>410800</v>
+        <v>418057.9505300326</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -12457,10 +12457,10 @@
         <v>87</v>
       </c>
       <c r="N277" t="n">
-        <v>1400</v>
+        <v>1420.3389830508</v>
       </c>
       <c r="O277" t="n">
-        <v>121800</v>
+        <v>123569.4915254196</v>
       </c>
       <c r="P277" t="n">
         <v>2300</v>
@@ -12503,10 +12503,10 @@
         <v>66</v>
       </c>
       <c r="N278" t="n">
-        <v>6000</v>
+        <v>6085.1063829787</v>
       </c>
       <c r="O278" t="n">
-        <v>396000</v>
+        <v>401617.0212765942</v>
       </c>
       <c r="P278" t="n">
         <v>10000</v>
@@ -12595,10 +12595,10 @@
         <v>6</v>
       </c>
       <c r="N280" t="n">
-        <v>1230</v>
+        <v>1243.273381295</v>
       </c>
       <c r="O280" t="n">
-        <v>7380</v>
+        <v>7459.64028777</v>
       </c>
       <c r="P280" t="n">
         <v>2000</v>
@@ -12787,10 +12787,10 @@
         <v>82</v>
       </c>
       <c r="N284" t="n">
-        <v>1870</v>
+        <v>1944.3046357616</v>
       </c>
       <c r="O284" t="n">
-        <v>153340</v>
+        <v>159432.9801324512</v>
       </c>
       <c r="P284" t="n">
         <v>3000</v>
@@ -12833,10 +12833,10 @@
         <v>2</v>
       </c>
       <c r="N285" t="n">
-        <v>2019.86</v>
+        <v>2110.9815037594</v>
       </c>
       <c r="O285" t="n">
-        <v>4039.72</v>
+        <v>4221.9630075188</v>
       </c>
       <c r="P285" t="n">
         <v>3300</v>
@@ -12879,10 +12879,10 @@
         <v>45</v>
       </c>
       <c r="N286" t="n">
-        <v>520</v>
+        <v>539.28902627512</v>
       </c>
       <c r="O286" t="n">
-        <v>23400</v>
+        <v>24268.0061823804</v>
       </c>
       <c r="P286" t="n">
         <v>850</v>
@@ -12971,10 +12971,10 @@
         <v>17</v>
       </c>
       <c r="N288" t="n">
-        <v>2260</v>
+        <v>2318.1974248927</v>
       </c>
       <c r="O288" t="n">
-        <v>38420</v>
+        <v>39409.3562231759</v>
       </c>
       <c r="P288" t="n">
         <v>3800</v>
@@ -13063,10 +13063,10 @@
         <v>55</v>
       </c>
       <c r="N290" t="n">
-        <v>1840</v>
+        <v>1872.4705882353</v>
       </c>
       <c r="O290" t="n">
-        <v>101200</v>
+        <v>102985.8823529415</v>
       </c>
       <c r="P290" t="n">
         <v>3000</v>
@@ -13155,10 +13155,10 @@
         <v>80</v>
       </c>
       <c r="N292" t="n">
-        <v>2840</v>
+        <v>2878.4650112867</v>
       </c>
       <c r="O292" t="n">
-        <v>227200</v>
+        <v>230277.200902936</v>
       </c>
       <c r="P292" t="n">
         <v>4600</v>
@@ -13345,10 +13345,10 @@
         <v>76</v>
       </c>
       <c r="N296" t="n">
-        <v>13687</v>
+        <v>13863.987068966</v>
       </c>
       <c r="O296" t="n">
-        <v>1040212</v>
+        <v>1053663.017241416</v>
       </c>
       <c r="P296" t="n">
         <v>21900</v>
@@ -14081,10 +14081,10 @@
         <v>93</v>
       </c>
       <c r="N312" t="n">
-        <v>5858</v>
+        <v>6112.6956521739</v>
       </c>
       <c r="O312" t="n">
-        <v>544794</v>
+        <v>568480.6956521727</v>
       </c>
       <c r="P312" t="n">
         <v>9500</v>
@@ -14127,10 +14127,10 @@
         <v>263</v>
       </c>
       <c r="N313" t="n">
-        <v>2252.2962193699</v>
+        <v>2252.2963076923</v>
       </c>
       <c r="O313" t="n">
-        <v>592353.9056942837</v>
+        <v>592353.928923075</v>
       </c>
       <c r="P313" t="n">
         <v>3900</v>
@@ -14314,10 +14314,10 @@
         <v>504</v>
       </c>
       <c r="N317" t="n">
-        <v>2328.1187566293</v>
+        <v>2328.1187536917</v>
       </c>
       <c r="O317" t="n">
-        <v>1173371.853341167</v>
+        <v>1173371.851860617</v>
       </c>
       <c r="P317" t="n">
         <v>4500</v>
@@ -14452,10 +14452,10 @@
         <v>57</v>
       </c>
       <c r="N320" t="n">
-        <v>9003</v>
+        <v>9045.4669811321</v>
       </c>
       <c r="O320" t="n">
-        <v>513171</v>
+        <v>515591.6179245297</v>
       </c>
       <c r="P320" t="n">
         <v>14900</v>
@@ -15050,10 +15050,10 @@
         <v>73</v>
       </c>
       <c r="N333" t="n">
-        <v>4202</v>
+        <v>4223.6597938144</v>
       </c>
       <c r="O333" t="n">
-        <v>306746</v>
+        <v>308327.1649484512</v>
       </c>
       <c r="P333" t="n">
         <v>7900</v>
@@ -16195,10 +16195,10 @@
         <v>60</v>
       </c>
       <c r="N358" t="n">
-        <v>4268.7030223881</v>
+        <v>4268.7033206107</v>
       </c>
       <c r="O358" t="n">
-        <v>256122.181343286</v>
+        <v>256122.199236642</v>
       </c>
       <c r="P358" t="n">
         <v>6900</v>
@@ -16701,10 +16701,10 @@
         <v>839</v>
       </c>
       <c r="N369" t="n">
-        <v>1516.0388180509</v>
+        <v>1516.0388166875</v>
       </c>
       <c r="O369" t="n">
-        <v>1271956.568344705</v>
+        <v>1271956.567200813</v>
       </c>
       <c r="P369" t="n">
         <v>2300</v>
@@ -16977,10 +16977,10 @@
         <v>48</v>
       </c>
       <c r="N375" t="n">
-        <v>2980</v>
+        <v>3051.52</v>
       </c>
       <c r="O375" t="n">
-        <v>143040</v>
+        <v>146472.96</v>
       </c>
       <c r="P375" t="n">
         <v>4800</v>
@@ -17064,10 +17064,10 @@
         <v>145</v>
       </c>
       <c r="N377" t="n">
-        <v>2842.2738509317</v>
+        <v>2842.2738221529</v>
       </c>
       <c r="O377" t="n">
-        <v>412129.7083850965</v>
+        <v>412129.7042121704</v>
       </c>
       <c r="P377" t="n">
         <v>4900</v>
@@ -17108,10 +17108,10 @@
         <v>2243</v>
       </c>
       <c r="N378" t="n">
-        <v>692.15203442189</v>
+        <v>692.1520380194499</v>
       </c>
       <c r="O378" t="n">
-        <v>1552497.013208299</v>
+        <v>1552497.021277626</v>
       </c>
       <c r="P378" t="n">
         <v>1200</v>
@@ -17592,10 +17592,10 @@
         <v>32</v>
       </c>
       <c r="N388" t="n">
-        <v>2682.71</v>
+        <v>2769.7168108108</v>
       </c>
       <c r="O388" t="n">
-        <v>85846.72</v>
+        <v>88630.9379459456</v>
       </c>
       <c r="P388" t="n">
         <v>10900</v>
@@ -18061,10 +18061,10 @@
         <v>238</v>
       </c>
       <c r="N398" t="n">
-        <v>1690.8700087835</v>
+        <v>1690.8700088067</v>
       </c>
       <c r="O398" t="n">
-        <v>402427.062090473</v>
+        <v>402427.0620959946</v>
       </c>
       <c r="P398" t="n">
         <v>3000</v>
@@ -18208,10 +18208,10 @@
         <v>47</v>
       </c>
       <c r="N401" t="n">
-        <v>2270.320952381</v>
+        <v>2483.1635416667</v>
       </c>
       <c r="O401" t="n">
-        <v>106705.084761907</v>
+        <v>116708.6864583349</v>
       </c>
       <c r="P401" t="n">
         <v>3900</v>
@@ -19090,10 +19090,10 @@
         <v>2</v>
       </c>
       <c r="N420" t="n">
-        <v>3110.8434146796</v>
+        <v>3110.8433414956</v>
       </c>
       <c r="O420" t="n">
-        <v>6221.6868293592</v>
+        <v>6221.6866829912</v>
       </c>
       <c r="P420" t="n">
         <v>4500</v>
@@ -19280,10 +19280,10 @@
         <v>127</v>
       </c>
       <c r="N424" t="n">
-        <v>3182.2510791367</v>
+        <v>3216.9665454545</v>
       </c>
       <c r="O424" t="n">
-        <v>404145.8870503609</v>
+        <v>408554.7512727215</v>
       </c>
       <c r="P424" t="n">
         <v>6900</v>
@@ -19464,10 +19464,10 @@
         <v>4</v>
       </c>
       <c r="N428" t="n">
-        <v>2501.3856097561</v>
+        <v>2501.3854811715</v>
       </c>
       <c r="O428" t="n">
-        <v>10005.5424390244</v>
+        <v>10005.541924686</v>
       </c>
       <c r="P428" t="n">
         <v>4100</v>
@@ -20024,10 +20024,10 @@
         <v>381</v>
       </c>
       <c r="N440" t="n">
-        <v>1595.5193419662</v>
+        <v>1595.51921946</v>
       </c>
       <c r="O440" t="n">
-        <v>607892.8692891222</v>
+        <v>607892.82261426</v>
       </c>
       <c r="P440" t="n">
         <v>2500</v>
@@ -20168,10 +20168,10 @@
         <v>73</v>
       </c>
       <c r="N443" t="n">
-        <v>2098.4047658402</v>
+        <v>2098.4047922438</v>
       </c>
       <c r="O443" t="n">
-        <v>153183.5479063346</v>
+        <v>153183.5498337974</v>
       </c>
       <c r="P443" t="n">
         <v>9500</v>
@@ -22059,10 +22059,10 @@
         <v>356</v>
       </c>
       <c r="N482" t="n">
-        <v>711.48</v>
+        <v>713.93197013211</v>
       </c>
       <c r="O482" t="n">
-        <v>253286.88</v>
+        <v>254159.7813670312</v>
       </c>
       <c r="P482" t="n">
         <v>2500</v>
@@ -22108,10 +22108,10 @@
         <v>152</v>
       </c>
       <c r="N483" t="n">
-        <v>7046.9398307595</v>
+        <v>7046.9398305803</v>
       </c>
       <c r="O483" t="n">
-        <v>1071134.854275444</v>
+        <v>1071134.854248206</v>
       </c>
       <c r="P483" t="n">
         <v>9900</v>
@@ -22255,10 +22255,10 @@
         <v>9</v>
       </c>
       <c r="N486" t="n">
-        <v>15571.057333333</v>
+        <v>15571.057142857</v>
       </c>
       <c r="O486" t="n">
-        <v>140139.515999997</v>
+        <v>140139.514285713</v>
       </c>
       <c r="P486" t="n">
         <v>19900</v>
@@ -23391,10 +23391,10 @@
         <v>216</v>
       </c>
       <c r="N510" t="n">
-        <v>1008.8181771721</v>
+        <v>1008.8176731794</v>
       </c>
       <c r="O510" t="n">
-        <v>217904.7262691736</v>
+        <v>217904.6174067504</v>
       </c>
       <c r="P510" t="n">
         <v>1500</v>
@@ -23476,10 +23476,10 @@
         <v>772</v>
       </c>
       <c r="N512" t="n">
-        <v>3181.9</v>
+        <v>3192.6751439214</v>
       </c>
       <c r="O512" t="n">
-        <v>2456426.8</v>
+        <v>2464745.211107321</v>
       </c>
       <c r="P512" t="n">
         <v>5100</v>
@@ -23561,10 +23561,10 @@
         <v>-72</v>
       </c>
       <c r="N514" t="n">
-        <v>1794.2879877441</v>
+        <v>1803.5408695029</v>
       </c>
       <c r="O514" t="n">
-        <v>-129188.7351175752</v>
+        <v>-129854.9426042088</v>
       </c>
       <c r="P514" t="n">
         <v>1600</v>
@@ -25324,10 +25324,10 @@
         <v>271</v>
       </c>
       <c r="N552" t="n">
-        <v>227.41590317919</v>
+        <v>229.9076771366</v>
       </c>
       <c r="O552" t="n">
-        <v>61629.70976156049</v>
+        <v>62304.9805040186</v>
       </c>
       <c r="P552" t="n">
         <v>1200</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1073,10 +1073,10 @@
         <v>310</v>
       </c>
       <c r="N17" t="n">
-        <v>6300.2067296512</v>
+        <v>6272.8541860465</v>
       </c>
       <c r="O17" t="n">
-        <v>1953064.086191872</v>
+        <v>1944584.797674415</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -2277,10 +2277,10 @@
         <v>386</v>
       </c>
       <c r="N47" t="n">
-        <v>3872.3234767642</v>
+        <v>3865.67</v>
       </c>
       <c r="O47" t="n">
-        <v>1494716.862030981</v>
+        <v>1492148.62</v>
       </c>
       <c r="P47" t="n">
         <v>5500</v>
@@ -2415,10 +2415,10 @@
         <v>114</v>
       </c>
       <c r="N50" t="n">
-        <v>2589.9594489247</v>
+        <v>2572.67</v>
       </c>
       <c r="O50" t="n">
-        <v>295255.3771774158</v>
+        <v>293284.38</v>
       </c>
       <c r="P50" t="n">
         <v>4700</v>
@@ -2500,10 +2500,10 @@
         <v>211</v>
       </c>
       <c r="N52" t="n">
-        <v>3126.0967950311</v>
+        <v>3114.49</v>
       </c>
       <c r="O52" t="n">
-        <v>659606.4237515621</v>
+        <v>657157.3899999999</v>
       </c>
       <c r="P52" t="n">
         <v>5500</v>
@@ -2617,10 +2617,10 @@
         <v>126</v>
       </c>
       <c r="N55" t="n">
-        <v>4411.4198473282</v>
+        <v>4378</v>
       </c>
       <c r="O55" t="n">
-        <v>555838.9007633532</v>
+        <v>551628</v>
       </c>
       <c r="P55" t="n">
         <v>3900</v>
@@ -4872,10 +4872,10 @@
         <v>577</v>
       </c>
       <c r="N106" t="n">
-        <v>3801.7317574476</v>
+        <v>3795.7100070509</v>
       </c>
       <c r="O106" t="n">
-        <v>2193599.224047265</v>
+        <v>2190124.674068369</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
@@ -4918,10 +4918,10 @@
         <v>162</v>
       </c>
       <c r="N107" t="n">
-        <v>3695.2967632027</v>
+        <v>3684</v>
       </c>
       <c r="O107" t="n">
-        <v>598638.0756388374</v>
+        <v>596808</v>
       </c>
       <c r="P107" t="n">
         <v>6200</v>
@@ -5281,10 +5281,10 @@
         <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>8687.96003996</v>
+        <v>8662</v>
       </c>
       <c r="O115" t="n">
-        <v>17375.92007992</v>
+        <v>17324</v>
       </c>
       <c r="P115" t="n">
         <v>14200</v>
@@ -6214,10 +6214,10 @@
         <v>763</v>
       </c>
       <c r="N136" t="n">
-        <v>3660.708</v>
+        <v>3655.96</v>
       </c>
       <c r="O136" t="n">
-        <v>2793120.204</v>
+        <v>2789497.48</v>
       </c>
       <c r="P136" t="n">
         <v>5500</v>
@@ -7446,10 +7446,10 @@
         <v>65</v>
       </c>
       <c r="N163" t="n">
-        <v>9795.0468</v>
+        <v>9678.9</v>
       </c>
       <c r="O163" t="n">
-        <v>636678.042</v>
+        <v>629128.5</v>
       </c>
       <c r="P163" t="n">
         <v>15500</v>
@@ -7877,10 +7877,10 @@
         <v>1057</v>
       </c>
       <c r="N173" t="n">
-        <v>1303.6380504587</v>
+        <v>1301.3994036697</v>
       </c>
       <c r="O173" t="n">
-        <v>1377945.419334846</v>
+        <v>1375579.169678873</v>
       </c>
       <c r="P173" t="n">
         <v>2000</v>
@@ -8020,10 +8020,10 @@
         <v>192</v>
       </c>
       <c r="N176" t="n">
-        <v>2030.7740585774</v>
+        <v>1965</v>
       </c>
       <c r="O176" t="n">
-        <v>389908.6192468608</v>
+        <v>377280</v>
       </c>
       <c r="P176" t="n">
         <v>3700</v>
@@ -8720,10 +8720,10 @@
         <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>2696.7673085339</v>
+        <v>2661.82</v>
       </c>
       <c r="O192" t="n">
-        <v>2696.7673085339</v>
+        <v>2661.82</v>
       </c>
       <c r="P192" t="n">
         <v>3200</v>
@@ -8802,10 +8802,10 @@
         <v>29</v>
       </c>
       <c r="N194" t="n">
-        <v>4550.9158878505</v>
+        <v>4488</v>
       </c>
       <c r="O194" t="n">
-        <v>131976.5607476645</v>
+        <v>130152</v>
       </c>
       <c r="P194" t="n">
         <v>6200</v>
@@ -8843,10 +8843,10 @@
         <v>195</v>
       </c>
       <c r="N195" t="n">
-        <v>8818.9498942682</v>
+        <v>8794.48</v>
       </c>
       <c r="O195" t="n">
-        <v>1719695.229382299</v>
+        <v>1714923.6</v>
       </c>
       <c r="P195" t="n">
         <v>14500</v>
@@ -8966,10 +8966,10 @@
         <v>551</v>
       </c>
       <c r="N198" t="n">
-        <v>2558.6841592313</v>
+        <v>2517.22</v>
       </c>
       <c r="O198" t="n">
-        <v>1409834.971736446</v>
+        <v>1386988.22</v>
       </c>
       <c r="P198" t="n">
         <v>4200</v>
@@ -9007,10 +9007,10 @@
         <v>348</v>
       </c>
       <c r="N199" t="n">
-        <v>2035.7801454898</v>
+        <v>2029.8736372454</v>
       </c>
       <c r="O199" t="n">
-        <v>708451.4906304504</v>
+        <v>706396.0257613992</v>
       </c>
       <c r="P199" t="n">
         <v>3600</v>
@@ -9048,10 +9048,10 @@
         <v>160</v>
       </c>
       <c r="N200" t="n">
-        <v>22561.918644068</v>
+        <v>22485.695932203</v>
       </c>
       <c r="O200" t="n">
-        <v>3609906.98305088</v>
+        <v>3597711.34915248</v>
       </c>
       <c r="P200" t="n">
         <v>36500</v>
@@ -9130,10 +9130,10 @@
         <v>214</v>
       </c>
       <c r="N202" t="n">
-        <v>7136.7702060222</v>
+        <v>7103</v>
       </c>
       <c r="O202" t="n">
-        <v>1527268.824088751</v>
+        <v>1520042</v>
       </c>
       <c r="P202" t="n">
         <v>10700</v>
@@ -11075,10 +11075,10 @@
         <v>119</v>
       </c>
       <c r="N247" t="n">
-        <v>3779.7578947368</v>
+        <v>3590.77</v>
       </c>
       <c r="O247" t="n">
-        <v>449791.1894736792</v>
+        <v>427301.63</v>
       </c>
       <c r="P247" t="n">
         <v>3900</v>
@@ -12135,10 +12135,10 @@
         <v>68</v>
       </c>
       <c r="N270" t="n">
-        <v>11682.094594595</v>
+        <v>11450</v>
       </c>
       <c r="O270" t="n">
-        <v>794382.43243246</v>
+        <v>778600</v>
       </c>
       <c r="P270" t="n">
         <v>18300</v>
@@ -12181,10 +12181,10 @@
         <v>131</v>
       </c>
       <c r="N271" t="n">
-        <v>6365.625</v>
+        <v>6300</v>
       </c>
       <c r="O271" t="n">
-        <v>833896.875</v>
+        <v>825300</v>
       </c>
       <c r="P271" t="n">
         <v>10200</v>
@@ -12365,10 +12365,10 @@
         <v>61</v>
       </c>
       <c r="N275" t="n">
-        <v>7371.3029315961</v>
+        <v>7230</v>
       </c>
       <c r="O275" t="n">
-        <v>449649.4788273621</v>
+        <v>441030</v>
       </c>
       <c r="P275" t="n">
         <v>11600</v>
@@ -12411,10 +12411,10 @@
         <v>79</v>
       </c>
       <c r="N276" t="n">
-        <v>5291.8727915194</v>
+        <v>5200</v>
       </c>
       <c r="O276" t="n">
-        <v>418057.9505300326</v>
+        <v>410800</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -12457,10 +12457,10 @@
         <v>87</v>
       </c>
       <c r="N277" t="n">
-        <v>1420.3389830508</v>
+        <v>1400</v>
       </c>
       <c r="O277" t="n">
-        <v>123569.4915254196</v>
+        <v>121800</v>
       </c>
       <c r="P277" t="n">
         <v>2300</v>
@@ -12503,10 +12503,10 @@
         <v>66</v>
       </c>
       <c r="N278" t="n">
-        <v>6085.1063829787</v>
+        <v>6000</v>
       </c>
       <c r="O278" t="n">
-        <v>401617.0212765942</v>
+        <v>396000</v>
       </c>
       <c r="P278" t="n">
         <v>10000</v>
@@ -12595,10 +12595,10 @@
         <v>6</v>
       </c>
       <c r="N280" t="n">
-        <v>1243.273381295</v>
+        <v>1230</v>
       </c>
       <c r="O280" t="n">
-        <v>7459.64028777</v>
+        <v>7380</v>
       </c>
       <c r="P280" t="n">
         <v>2000</v>
@@ -12787,10 +12787,10 @@
         <v>82</v>
       </c>
       <c r="N284" t="n">
-        <v>1944.3046357616</v>
+        <v>1870</v>
       </c>
       <c r="O284" t="n">
-        <v>159432.9801324512</v>
+        <v>153340</v>
       </c>
       <c r="P284" t="n">
         <v>3000</v>
@@ -12833,10 +12833,10 @@
         <v>2</v>
       </c>
       <c r="N285" t="n">
-        <v>2110.9815037594</v>
+        <v>2019.86</v>
       </c>
       <c r="O285" t="n">
-        <v>4221.9630075188</v>
+        <v>4039.72</v>
       </c>
       <c r="P285" t="n">
         <v>3300</v>
@@ -12879,10 +12879,10 @@
         <v>45</v>
       </c>
       <c r="N286" t="n">
-        <v>539.28902627512</v>
+        <v>520</v>
       </c>
       <c r="O286" t="n">
-        <v>24268.0061823804</v>
+        <v>23400</v>
       </c>
       <c r="P286" t="n">
         <v>850</v>
@@ -12971,10 +12971,10 @@
         <v>17</v>
       </c>
       <c r="N288" t="n">
-        <v>2318.1974248927</v>
+        <v>2260</v>
       </c>
       <c r="O288" t="n">
-        <v>39409.3562231759</v>
+        <v>38420</v>
       </c>
       <c r="P288" t="n">
         <v>3800</v>
@@ -13063,10 +13063,10 @@
         <v>55</v>
       </c>
       <c r="N290" t="n">
-        <v>1872.4705882353</v>
+        <v>1840</v>
       </c>
       <c r="O290" t="n">
-        <v>102985.8823529415</v>
+        <v>101200</v>
       </c>
       <c r="P290" t="n">
         <v>3000</v>
@@ -13155,10 +13155,10 @@
         <v>80</v>
       </c>
       <c r="N292" t="n">
-        <v>2878.4650112867</v>
+        <v>2840</v>
       </c>
       <c r="O292" t="n">
-        <v>230277.200902936</v>
+        <v>227200</v>
       </c>
       <c r="P292" t="n">
         <v>4600</v>
@@ -13345,10 +13345,10 @@
         <v>76</v>
       </c>
       <c r="N296" t="n">
-        <v>13863.987068966</v>
+        <v>13687</v>
       </c>
       <c r="O296" t="n">
-        <v>1053663.017241416</v>
+        <v>1040212</v>
       </c>
       <c r="P296" t="n">
         <v>21900</v>
@@ -14081,10 +14081,10 @@
         <v>93</v>
       </c>
       <c r="N312" t="n">
-        <v>6112.6956521739</v>
+        <v>5858</v>
       </c>
       <c r="O312" t="n">
-        <v>568480.6956521727</v>
+        <v>544794</v>
       </c>
       <c r="P312" t="n">
         <v>9500</v>
@@ -14452,10 +14452,10 @@
         <v>57</v>
       </c>
       <c r="N320" t="n">
-        <v>9045.4669811321</v>
+        <v>9003</v>
       </c>
       <c r="O320" t="n">
-        <v>515591.6179245297</v>
+        <v>513171</v>
       </c>
       <c r="P320" t="n">
         <v>14900</v>
@@ -15050,10 +15050,10 @@
         <v>73</v>
       </c>
       <c r="N333" t="n">
-        <v>4223.6597938144</v>
+        <v>4202</v>
       </c>
       <c r="O333" t="n">
-        <v>308327.1649484512</v>
+        <v>306746</v>
       </c>
       <c r="P333" t="n">
         <v>7900</v>
@@ -16977,10 +16977,10 @@
         <v>48</v>
       </c>
       <c r="N375" t="n">
-        <v>3051.52</v>
+        <v>2980</v>
       </c>
       <c r="O375" t="n">
-        <v>146472.96</v>
+        <v>143040</v>
       </c>
       <c r="P375" t="n">
         <v>4800</v>
@@ -17592,10 +17592,10 @@
         <v>32</v>
       </c>
       <c r="N388" t="n">
-        <v>2769.7168108108</v>
+        <v>2682.71</v>
       </c>
       <c r="O388" t="n">
-        <v>88630.9379459456</v>
+        <v>85846.72</v>
       </c>
       <c r="P388" t="n">
         <v>10900</v>
@@ -18208,10 +18208,10 @@
         <v>47</v>
       </c>
       <c r="N401" t="n">
-        <v>2483.1635416667</v>
+        <v>2270.3210416667</v>
       </c>
       <c r="O401" t="n">
-        <v>116708.6864583349</v>
+        <v>106705.0889583349</v>
       </c>
       <c r="P401" t="n">
         <v>3900</v>
@@ -19280,10 +19280,10 @@
         <v>127</v>
       </c>
       <c r="N424" t="n">
-        <v>3216.9665454545</v>
+        <v>3182.2510909091</v>
       </c>
       <c r="O424" t="n">
-        <v>408554.7512727215</v>
+        <v>404145.8885454557</v>
       </c>
       <c r="P424" t="n">
         <v>6900</v>
@@ -22059,10 +22059,10 @@
         <v>356</v>
       </c>
       <c r="N482" t="n">
-        <v>713.93197013211</v>
+        <v>711.48</v>
       </c>
       <c r="O482" t="n">
-        <v>254159.7813670312</v>
+        <v>253286.88</v>
       </c>
       <c r="P482" t="n">
         <v>2500</v>
@@ -23476,10 +23476,10 @@
         <v>772</v>
       </c>
       <c r="N512" t="n">
-        <v>3192.6751439214</v>
+        <v>3181.9</v>
       </c>
       <c r="O512" t="n">
-        <v>2464745.211107321</v>
+        <v>2456426.8</v>
       </c>
       <c r="P512" t="n">
         <v>5100</v>
@@ -23561,10 +23561,10 @@
         <v>-72</v>
       </c>
       <c r="N514" t="n">
-        <v>1803.5408695029</v>
+        <v>1794.2879773671</v>
       </c>
       <c r="O514" t="n">
-        <v>-129854.9426042088</v>
+        <v>-129188.7343704312</v>
       </c>
       <c r="P514" t="n">
         <v>1600</v>
@@ -25324,10 +25324,10 @@
         <v>271</v>
       </c>
       <c r="N552" t="n">
-        <v>229.9076771366</v>
+        <v>227.41596785975</v>
       </c>
       <c r="O552" t="n">
-        <v>62304.9805040186</v>
+        <v>61629.72728999225</v>
       </c>
       <c r="P552" t="n">
         <v>1200</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-08</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1073,10 +1073,10 @@
         <v>310</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8541860465</v>
+        <v>6272.8542228739</v>
       </c>
       <c r="O17" t="n">
-        <v>1944584.797674415</v>
+        <v>1944584.809090909</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1151,10 +1151,10 @@
         <v>450</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8371326165</v>
+        <v>3926.8371296771</v>
       </c>
       <c r="O19" t="n">
-        <v>1767076.709677425</v>
+        <v>1767076.708354695</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>2413.0011764706</v>
+        <v>2413.0010330579</v>
       </c>
       <c r="O22" t="n">
-        <v>2413.0011764706</v>
+        <v>2413.0010330579</v>
       </c>
       <c r="P22" t="n">
         <v>4700</v>
@@ -1349,10 +1349,10 @@
         <v>55</v>
       </c>
       <c r="N24" t="n">
-        <v>12793.680086207</v>
+        <v>12793.68008658</v>
       </c>
       <c r="O24" t="n">
-        <v>703652.404741385</v>
+        <v>703652.4047619</v>
       </c>
       <c r="P24" t="n">
         <v>24000</v>
@@ -1388,10 +1388,10 @@
         <v>48</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.330188383</v>
+        <v>3716.3301889764</v>
       </c>
       <c r="O25" t="n">
-        <v>178383.849042384</v>
+        <v>178383.8490708672</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -1708,10 +1708,10 @@
         <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.966215139</v>
+        <v>15711.9662</v>
       </c>
       <c r="O33" t="n">
-        <v>659902.581035838</v>
+        <v>659902.5804</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.873842239</v>
+        <v>61666.873852041</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.332162843</v>
+        <v>2281674.332525517</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -3047,10 +3047,10 @@
         <v>434</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101595359</v>
+        <v>4937.3101601164</v>
       </c>
       <c r="O65" t="n">
-        <v>2142792.609238581</v>
+        <v>2142792.609490518</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0527732407</v>
+        <v>1098.0529624405</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.332788884</v>
+        <v>131766.35549286</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4228,22 +4228,22 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M92" t="n">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="N92" t="n">
         <v>5182.57</v>
       </c>
       <c r="O92" t="n">
-        <v>171024.81</v>
+        <v>93286.25999999999</v>
       </c>
       <c r="P92" t="n">
         <v>6500</v>
       </c>
       <c r="Q92" t="n">
-        <v>214500</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="93">
@@ -5051,10 +5051,10 @@
         <v>487</v>
       </c>
       <c r="N110" t="n">
-        <v>4890.930045977</v>
+        <v>4890.9300460299</v>
       </c>
       <c r="O110" t="n">
-        <v>2381882.932390799</v>
+        <v>2381882.932416562</v>
       </c>
       <c r="P110" t="n">
         <v>8200</v>
@@ -5499,10 +5499,10 @@
         <v>120</v>
       </c>
       <c r="N120" t="n">
-        <v>3240.8500291545</v>
+        <v>3240.8500293255</v>
       </c>
       <c r="O120" t="n">
-        <v>388902.00349854</v>
+        <v>388902.00351906</v>
       </c>
       <c r="P120" t="n">
         <v>5200</v>
@@ -5584,10 +5584,10 @@
         <v>135</v>
       </c>
       <c r="N122" t="n">
-        <v>5191.4800265604</v>
+        <v>5191.4800268456</v>
       </c>
       <c r="O122" t="n">
-        <v>700849.803585654</v>
+        <v>700849.803624156</v>
       </c>
       <c r="P122" t="n">
         <v>9100</v>
@@ -5810,22 +5810,22 @@
         <v>0</v>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="M127" t="n">
-        <v>198</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
         <v>1381.75</v>
       </c>
       <c r="O127" t="n">
-        <v>273586.5</v>
+        <v>0</v>
       </c>
       <c r="P127" t="n">
         <v>2500</v>
       </c>
       <c r="Q127" t="n">
-        <v>495000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -6035,10 +6035,10 @@
         <v>501</v>
       </c>
       <c r="N132" t="n">
-        <v>3041.6600123457</v>
+        <v>3041.6600124378</v>
       </c>
       <c r="O132" t="n">
-        <v>1523871.666185196</v>
+        <v>1523871.666231338</v>
       </c>
       <c r="P132" t="n">
         <v>5500</v>
@@ -6122,10 +6122,10 @@
         <v>1122</v>
       </c>
       <c r="N134" t="n">
-        <v>4372.2107862617</v>
+        <v>4372.2107863175</v>
       </c>
       <c r="O134" t="n">
-        <v>4905620.502185628</v>
+        <v>4905620.502248235</v>
       </c>
       <c r="P134" t="n">
         <v>7500</v>
@@ -7574,10 +7574,10 @@
         <v>300</v>
       </c>
       <c r="N166" t="n">
-        <v>1630.9229788882</v>
+        <v>1630.9230192383</v>
       </c>
       <c r="O166" t="n">
-        <v>489276.89366646</v>
+        <v>489276.90577149</v>
       </c>
       <c r="P166" t="n">
         <v>2500</v>
@@ -7620,10 +7620,10 @@
         <v>96</v>
       </c>
       <c r="N167" t="n">
-        <v>1550.1929105882</v>
+        <v>1550.19293615</v>
       </c>
       <c r="O167" t="n">
-        <v>148818.5194164672</v>
+        <v>148818.5218704</v>
       </c>
       <c r="P167" t="n">
         <v>2500</v>
@@ -7666,10 +7666,10 @@
         <v>48</v>
       </c>
       <c r="N168" t="n">
-        <v>1579.3913493976</v>
+        <v>1579.3910696517</v>
       </c>
       <c r="O168" t="n">
-        <v>75810.7847710848</v>
+        <v>75810.77134328161</v>
       </c>
       <c r="P168" t="n">
         <v>2900</v>
@@ -9048,10 +9048,10 @@
         <v>160</v>
       </c>
       <c r="N200" t="n">
-        <v>22485.695932203</v>
+        <v>22485.695927602</v>
       </c>
       <c r="O200" t="n">
-        <v>3597711.34915248</v>
+        <v>3597711.34841632</v>
       </c>
       <c r="P200" t="n">
         <v>36500</v>
@@ -9212,10 +9212,10 @@
         <v>170</v>
       </c>
       <c r="N204" t="n">
-        <v>2680.739700489</v>
+        <v>2680.7396999388</v>
       </c>
       <c r="O204" t="n">
-        <v>455725.74908313</v>
+        <v>455725.748989596</v>
       </c>
       <c r="P204" t="n">
         <v>4900</v>
@@ -9340,10 +9340,10 @@
         <v>237</v>
       </c>
       <c r="N207" t="n">
-        <v>1732.9153957286</v>
+        <v>1732.9153666245</v>
       </c>
       <c r="O207" t="n">
-        <v>410700.9487876782</v>
+        <v>410700.9418900065</v>
       </c>
       <c r="P207" t="n">
         <v>1900</v>
@@ -9427,10 +9427,10 @@
         <v>24</v>
       </c>
       <c r="N209" t="n">
-        <v>3731.0243234323</v>
+        <v>3731.0243377483</v>
       </c>
       <c r="O209" t="n">
-        <v>89544.5837623752</v>
+        <v>89544.58410595919</v>
       </c>
       <c r="P209" t="n">
         <v>5200</v>
@@ -9983,10 +9983,10 @@
         <v>40</v>
       </c>
       <c r="N222" t="n">
-        <v>27123.765259259</v>
+        <v>27123.765250464</v>
       </c>
       <c r="O222" t="n">
-        <v>1084950.61037036</v>
+        <v>1084950.61001856</v>
       </c>
       <c r="P222" t="n">
         <v>44500</v>
@@ -10408,10 +10408,10 @@
         <v>180</v>
       </c>
       <c r="N232" t="n">
-        <v>7969.9501643017</v>
+        <v>7969.950164794</v>
       </c>
       <c r="O232" t="n">
-        <v>1434591.029574306</v>
+        <v>1434591.02966292</v>
       </c>
       <c r="P232" t="n">
         <v>12900</v>
@@ -10680,10 +10680,10 @@
         <v>154</v>
       </c>
       <c r="N238" t="n">
-        <v>548.14728797763</v>
+        <v>548.14728291317</v>
       </c>
       <c r="O238" t="n">
-        <v>84414.68234855501</v>
+        <v>84414.68156862818</v>
       </c>
       <c r="P238" t="n">
         <v>2000</v>
@@ -11813,10 +11813,10 @@
         <v>1215</v>
       </c>
       <c r="N263" t="n">
-        <v>1778.4725093418</v>
+        <v>1778.4725198441</v>
       </c>
       <c r="O263" t="n">
-        <v>2160844.098850287</v>
+        <v>2160844.111610581</v>
       </c>
       <c r="P263" t="n">
         <v>4900</v>
@@ -14314,10 +14314,10 @@
         <v>504</v>
       </c>
       <c r="N317" t="n">
-        <v>2328.1187536917</v>
+        <v>2328.1187525865</v>
       </c>
       <c r="O317" t="n">
-        <v>1173371.851860617</v>
+        <v>1173371.851303596</v>
       </c>
       <c r="P317" t="n">
         <v>4500</v>
@@ -14728,10 +14728,10 @@
         <v>184</v>
       </c>
       <c r="N326" t="n">
-        <v>4907.821904048</v>
+        <v>4907.8219155354</v>
       </c>
       <c r="O326" t="n">
-        <v>903039.2303448319</v>
+        <v>903039.2324585136</v>
       </c>
       <c r="P326" t="n">
         <v>8200</v>
@@ -14958,10 +14958,10 @@
         <v>84</v>
       </c>
       <c r="N331" t="n">
-        <v>3903.7358605664</v>
+        <v>3903.7358951965</v>
       </c>
       <c r="O331" t="n">
-        <v>327913.8122875776</v>
+        <v>327913.815196506</v>
       </c>
       <c r="P331" t="n">
         <v>7500</v>
@@ -16195,10 +16195,10 @@
         <v>60</v>
       </c>
       <c r="N358" t="n">
-        <v>4268.7033206107</v>
+        <v>4268.7035271318</v>
       </c>
       <c r="O358" t="n">
-        <v>256122.199236642</v>
+        <v>256122.211627908</v>
       </c>
       <c r="P358" t="n">
         <v>6900</v>
@@ -16701,10 +16701,10 @@
         <v>839</v>
       </c>
       <c r="N369" t="n">
-        <v>1516.0388166875</v>
+        <v>1516.0388137227</v>
       </c>
       <c r="O369" t="n">
-        <v>1271956.567200813</v>
+        <v>1271956.564713345</v>
       </c>
       <c r="P369" t="n">
         <v>2300</v>
@@ -17064,10 +17064,10 @@
         <v>145</v>
       </c>
       <c r="N377" t="n">
-        <v>2842.2738221529</v>
+        <v>2842.2737931034</v>
       </c>
       <c r="O377" t="n">
-        <v>412129.7042121704</v>
+        <v>412129.699999993</v>
       </c>
       <c r="P377" t="n">
         <v>4900</v>
@@ -17108,10 +17108,10 @@
         <v>2243</v>
       </c>
       <c r="N378" t="n">
-        <v>692.1520380194499</v>
+        <v>692.15204525288</v>
       </c>
       <c r="O378" t="n">
-        <v>1552497.021277626</v>
+        <v>1552497.03750221</v>
       </c>
       <c r="P378" t="n">
         <v>1200</v>
@@ -18208,10 +18208,10 @@
         <v>47</v>
       </c>
       <c r="N401" t="n">
-        <v>2270.3210416667</v>
+        <v>2270.3210752688</v>
       </c>
       <c r="O401" t="n">
-        <v>106705.0889583349</v>
+        <v>106705.0905376336</v>
       </c>
       <c r="P401" t="n">
         <v>3900</v>
@@ -18252,10 +18252,10 @@
         <v>1602</v>
       </c>
       <c r="N402" t="n">
-        <v>481.48791484103</v>
+        <v>481.48791460674</v>
       </c>
       <c r="O402" t="n">
-        <v>771343.6395753301</v>
+        <v>771343.6391999974</v>
       </c>
       <c r="P402" t="n">
         <v>650</v>
@@ -18345,10 +18345,10 @@
         <v>78</v>
       </c>
       <c r="N404" t="n">
-        <v>3907.5003187251</v>
+        <v>3907.5003212851</v>
       </c>
       <c r="O404" t="n">
-        <v>304785.0248605578</v>
+        <v>304785.0250602378</v>
       </c>
       <c r="P404" t="n">
         <v>3900</v>
@@ -19090,10 +19090,10 @@
         <v>2</v>
       </c>
       <c r="N420" t="n">
-        <v>3110.8433414956</v>
+        <v>3110.843282022</v>
       </c>
       <c r="O420" t="n">
-        <v>6221.6866829912</v>
+        <v>6221.686564044</v>
       </c>
       <c r="P420" t="n">
         <v>4500</v>
@@ -19464,10 +19464,10 @@
         <v>4</v>
       </c>
       <c r="N428" t="n">
-        <v>2501.3854811715</v>
+        <v>2501.3854621849</v>
       </c>
       <c r="O428" t="n">
-        <v>10005.541924686</v>
+        <v>10005.5418487396</v>
       </c>
       <c r="P428" t="n">
         <v>4100</v>
@@ -20024,10 +20024,10 @@
         <v>381</v>
       </c>
       <c r="N440" t="n">
-        <v>1595.51921946</v>
+        <v>1595.5191410878</v>
       </c>
       <c r="O440" t="n">
-        <v>607892.82261426</v>
+        <v>607892.7927544519</v>
       </c>
       <c r="P440" t="n">
         <v>2500</v>
@@ -20845,10 +20845,10 @@
         <v>22</v>
       </c>
       <c r="N457" t="n">
-        <v>12448.353125</v>
+        <v>12448.353225806</v>
       </c>
       <c r="O457" t="n">
-        <v>273863.76875</v>
+        <v>273863.770967732</v>
       </c>
       <c r="P457" t="n">
         <v>22900</v>
@@ -22108,10 +22108,10 @@
         <v>152</v>
       </c>
       <c r="N483" t="n">
-        <v>7046.9398305803</v>
+        <v>7046.9398302567</v>
       </c>
       <c r="O483" t="n">
-        <v>1071134.854248206</v>
+        <v>1071134.854199018</v>
       </c>
       <c r="P483" t="n">
         <v>9900</v>
@@ -22834,10 +22834,10 @@
         <v>1372</v>
       </c>
       <c r="N498" t="n">
-        <v>665.32324616023</v>
+        <v>665.32330236486</v>
       </c>
       <c r="O498" t="n">
-        <v>912823.4937318356</v>
+        <v>912823.5708445879</v>
       </c>
       <c r="P498" t="n">
         <v>2900</v>
@@ -23517,10 +23517,10 @@
         <v>116</v>
       </c>
       <c r="N513" t="n">
-        <v>1213.6821153846</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O513" t="n">
-        <v>140787.1253846136</v>
+        <v>140787.125857418</v>
       </c>
       <c r="P513" t="n">
         <v>1500</v>
@@ -23694,10 +23694,10 @@
         <v>11</v>
       </c>
       <c r="N517" t="n">
-        <v>22951.705012407</v>
+        <v>22951.704981273</v>
       </c>
       <c r="O517" t="n">
-        <v>252468.755136477</v>
+        <v>252468.754794003</v>
       </c>
       <c r="P517" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7465175202</v>
+        <v>3376.746511879</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.205784357</v>
+        <v>1982150.202472973</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -793,10 +793,10 @@
         <v>42</v>
       </c>
       <c r="N10" t="n">
-        <v>27815.961111111</v>
+        <v>27815.961126761</v>
       </c>
       <c r="O10" t="n">
-        <v>1168270.366666662</v>
+        <v>1168270.367323962</v>
       </c>
       <c r="P10" t="n">
         <v>58600</v>
@@ -1073,10 +1073,10 @@
         <v>310</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8542228739</v>
+        <v>6272.8542666667</v>
       </c>
       <c r="O17" t="n">
-        <v>1944584.809090909</v>
+        <v>1944584.822666677</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1310,10 +1310,10 @@
         <v>103</v>
       </c>
       <c r="N23" t="n">
-        <v>2474.7042429285</v>
+        <v>2474.7042140468</v>
       </c>
       <c r="O23" t="n">
-        <v>254894.5370216355</v>
+        <v>254894.5340468204</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -1708,10 +1708,10 @@
         <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.9662</v>
+        <v>15711.966184739</v>
       </c>
       <c r="O33" t="n">
-        <v>659902.5804</v>
+        <v>659902.5797590379</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0529624405</v>
+        <v>1098.053336357</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.35549286</v>
+        <v>131766.40036284</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -5499,10 +5499,10 @@
         <v>120</v>
       </c>
       <c r="N120" t="n">
-        <v>3240.8500293255</v>
+        <v>3240.8500293686</v>
       </c>
       <c r="O120" t="n">
-        <v>388902.00351906</v>
+        <v>388902.003524232</v>
       </c>
       <c r="P120" t="n">
         <v>5200</v>
@@ -5986,10 +5986,10 @@
         <v>501</v>
       </c>
       <c r="N131" t="n">
-        <v>3041.6600124378</v>
+        <v>3041.6600124456</v>
       </c>
       <c r="O131" t="n">
-        <v>1523871.666231338</v>
+        <v>1523871.666235246</v>
       </c>
       <c r="P131" t="n">
         <v>5500</v>
@@ -7525,10 +7525,10 @@
         <v>300</v>
       </c>
       <c r="N165" t="n">
-        <v>1630.9230192383</v>
+        <v>1630.9230407276</v>
       </c>
       <c r="O165" t="n">
-        <v>489276.90577149</v>
+        <v>489276.91221828</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -7571,10 +7571,10 @@
         <v>96</v>
       </c>
       <c r="N166" t="n">
-        <v>1550.19293615</v>
+        <v>1550.1929579149</v>
       </c>
       <c r="O166" t="n">
-        <v>148818.5218704</v>
+        <v>148818.5239598304</v>
       </c>
       <c r="P166" t="n">
         <v>2500</v>
@@ -8958,10 +8958,10 @@
         <v>348</v>
       </c>
       <c r="N198" t="n">
-        <v>2029.8736372454</v>
+        <v>2029.8736443149</v>
       </c>
       <c r="O198" t="n">
-        <v>706396.0257613992</v>
+        <v>706396.0282215852</v>
       </c>
       <c r="P198" t="n">
         <v>3600</v>
@@ -11636,10 +11636,10 @@
         <v>3</v>
       </c>
       <c r="N259" t="n">
-        <v>23521.624852941</v>
+        <v>23521.624776119</v>
       </c>
       <c r="O259" t="n">
-        <v>70564.87455882301</v>
+        <v>70564.87432835699</v>
       </c>
       <c r="P259" t="n">
         <v>39000</v>
@@ -11764,10 +11764,10 @@
         <v>1215</v>
       </c>
       <c r="N262" t="n">
-        <v>1778.4725198441</v>
+        <v>1778.4725231214</v>
       </c>
       <c r="O262" t="n">
-        <v>2160844.111610581</v>
+        <v>2160844.115592501</v>
       </c>
       <c r="P262" t="n">
         <v>4900</v>
@@ -14078,10 +14078,10 @@
         <v>263</v>
       </c>
       <c r="N312" t="n">
-        <v>2252.2963076923</v>
+        <v>2252.2963603819</v>
       </c>
       <c r="O312" t="n">
-        <v>592353.928923075</v>
+        <v>592353.9427804396</v>
       </c>
       <c r="P312" t="n">
         <v>3900</v>
@@ -14679,10 +14679,10 @@
         <v>184</v>
       </c>
       <c r="N325" t="n">
-        <v>4907.8219155354</v>
+        <v>4907.8219300912</v>
       </c>
       <c r="O325" t="n">
-        <v>903039.2324585136</v>
+        <v>903039.2351367808</v>
       </c>
       <c r="P325" t="n">
         <v>8200</v>
@@ -14909,10 +14909,10 @@
         <v>84</v>
       </c>
       <c r="N330" t="n">
-        <v>3903.7358951965</v>
+        <v>3903.7359183673</v>
       </c>
       <c r="O330" t="n">
-        <v>327913.815196506</v>
+        <v>327913.8171428532</v>
       </c>
       <c r="P330" t="n">
         <v>7500</v>
@@ -16652,10 +16652,10 @@
         <v>839</v>
       </c>
       <c r="N368" t="n">
-        <v>1516.0388137227</v>
+        <v>1516.0388131508</v>
       </c>
       <c r="O368" t="n">
-        <v>1271956.564713345</v>
+        <v>1271956.564233521</v>
       </c>
       <c r="P368" t="n">
         <v>2300</v>
@@ -17059,10 +17059,10 @@
         <v>2243</v>
       </c>
       <c r="N377" t="n">
-        <v>692.15204525288</v>
+        <v>692.15205253785</v>
       </c>
       <c r="O377" t="n">
-        <v>1552497.03750221</v>
+        <v>1552497.053842397</v>
       </c>
       <c r="P377" t="n">
         <v>1200</v>
@@ -18012,10 +18012,10 @@
         <v>238</v>
       </c>
       <c r="N397" t="n">
-        <v>1690.8700088067</v>
+        <v>1690.8700088574</v>
       </c>
       <c r="O397" t="n">
-        <v>402427.0620959946</v>
+        <v>402427.0621080612</v>
       </c>
       <c r="P397" t="n">
         <v>3000</v>
@@ -19041,10 +19041,10 @@
         <v>2</v>
       </c>
       <c r="N419" t="n">
-        <v>3110.843282022</v>
+        <v>3110.8431677619</v>
       </c>
       <c r="O419" t="n">
-        <v>6221.686564044</v>
+        <v>6221.6863355238</v>
       </c>
       <c r="P419" t="n">
         <v>4500</v>
@@ -19231,10 +19231,10 @@
         <v>127</v>
       </c>
       <c r="N423" t="n">
-        <v>3182.2510909091</v>
+        <v>3182.2510928962</v>
       </c>
       <c r="O423" t="n">
-        <v>404145.8885454557</v>
+        <v>404145.8887978174</v>
       </c>
       <c r="P423" t="n">
         <v>6900</v>
@@ -19415,10 +19415,10 @@
         <v>4</v>
       </c>
       <c r="N427" t="n">
-        <v>2501.3854621849</v>
+        <v>2501.385443038</v>
       </c>
       <c r="O427" t="n">
-        <v>10005.5418487396</v>
+        <v>10005.541772152</v>
       </c>
       <c r="P427" t="n">
         <v>4100</v>
@@ -19975,10 +19975,10 @@
         <v>381</v>
       </c>
       <c r="N439" t="n">
-        <v>1595.5191410878</v>
+        <v>1595.5191323094</v>
       </c>
       <c r="O439" t="n">
-        <v>607892.7927544519</v>
+        <v>607892.7894098813</v>
       </c>
       <c r="P439" t="n">
         <v>2500</v>
@@ -20119,10 +20119,10 @@
         <v>73</v>
       </c>
       <c r="N442" t="n">
-        <v>2098.4047922438</v>
+        <v>2098.4048459384</v>
       </c>
       <c r="O442" t="n">
-        <v>153183.5498337974</v>
+        <v>153183.5537535032</v>
       </c>
       <c r="P442" t="n">
         <v>9500</v>
@@ -22785,10 +22785,10 @@
         <v>1372</v>
       </c>
       <c r="N497" t="n">
-        <v>665.32330236486</v>
+        <v>665.3233262441501</v>
       </c>
       <c r="O497" t="n">
-        <v>912823.5708445879</v>
+        <v>912823.6036069739</v>
       </c>
       <c r="P497" t="n">
         <v>2900</v>
@@ -23645,10 +23645,10 @@
         <v>11</v>
       </c>
       <c r="N516" t="n">
-        <v>22951.704981273</v>
+        <v>22951.704968711</v>
       </c>
       <c r="O516" t="n">
-        <v>252468.754794003</v>
+        <v>252468.754655821</v>
       </c>
       <c r="P516" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-10</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -556,10 +556,10 @@
         <v>41</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27043.062200957</v>
       </c>
       <c r="O4" t="n">
-        <v>1107000</v>
+        <v>1108765.550239237</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.746511879</v>
+        <v>3376.7465109371</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.202472973</v>
+        <v>1982150.201920078</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1151,10 +1151,10 @@
         <v>450</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8371296771</v>
+        <v>3926.8371267317</v>
       </c>
       <c r="O19" t="n">
-        <v>1767076.708354695</v>
+        <v>1767076.707029265</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1388,10 +1388,10 @@
         <v>48</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301889764</v>
+        <v>3716.3301892744</v>
       </c>
       <c r="O25" t="n">
-        <v>178383.8490708672</v>
+        <v>178383.8490851712</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -1708,10 +1708,10 @@
         <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.966184739</v>
+        <v>15711.966106557</v>
       </c>
       <c r="O33" t="n">
-        <v>659902.5797590379</v>
+        <v>659902.576475394</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.873852041</v>
+        <v>61666.873861893</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.332525517</v>
+        <v>2281674.332890041</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -2960,10 +2960,10 @@
         <v>228</v>
       </c>
       <c r="N63" t="n">
-        <v>1950.2152574526</v>
+        <v>1950.2152424105</v>
       </c>
       <c r="O63" t="n">
-        <v>444649.0786991928</v>
+        <v>444649.075269594</v>
       </c>
       <c r="P63" t="n">
         <v>2900</v>
@@ -3047,10 +3047,10 @@
         <v>434</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101601164</v>
+        <v>4937.3101603499</v>
       </c>
       <c r="O65" t="n">
-        <v>2142792.609490518</v>
+        <v>2142792.609591857</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.053336357</v>
+        <v>1098.0535004591</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.40036284</v>
+        <v>131766.420055092</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -3668,10 +3668,10 @@
         <v>98</v>
       </c>
       <c r="N79" t="n">
-        <v>17207.41</v>
+        <v>17261.351724138</v>
       </c>
       <c r="O79" t="n">
-        <v>1686326.18</v>
+        <v>1691612.468965524</v>
       </c>
       <c r="P79" t="n">
         <v>20000</v>
@@ -3924,10 +3924,10 @@
         <v>336</v>
       </c>
       <c r="N85" t="n">
-        <v>2804.33</v>
+        <v>2808.0329005282</v>
       </c>
       <c r="O85" t="n">
-        <v>942254.88</v>
+        <v>943499.0545774752</v>
       </c>
       <c r="P85" t="n">
         <v>4900</v>
@@ -4744,10 +4744,10 @@
         <v>507</v>
       </c>
       <c r="N103" t="n">
-        <v>6507</v>
+        <v>6511.2612966601</v>
       </c>
       <c r="O103" t="n">
-        <v>3299049</v>
+        <v>3301209.477406671</v>
       </c>
       <c r="P103" t="n">
         <v>9900</v>
@@ -4872,10 +4872,10 @@
         <v>577</v>
       </c>
       <c r="N106" t="n">
-        <v>3795.7100070509</v>
+        <v>3795.7100070547</v>
       </c>
       <c r="O106" t="n">
-        <v>2190124.674068369</v>
+        <v>2190124.674070562</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
@@ -5051,10 +5051,10 @@
         <v>487</v>
       </c>
       <c r="N110" t="n">
-        <v>4890.9300460299</v>
+        <v>4890.9300461095</v>
       </c>
       <c r="O110" t="n">
-        <v>2381882.932416562</v>
+        <v>2381882.932455326</v>
       </c>
       <c r="P110" t="n">
         <v>8200</v>
@@ -5235,10 +5235,10 @@
         <v>580</v>
       </c>
       <c r="N114" t="n">
-        <v>5667.94</v>
+        <v>5672.995244381</v>
       </c>
       <c r="O114" t="n">
-        <v>3287405.2</v>
+        <v>3290337.24174098</v>
       </c>
       <c r="P114" t="n">
         <v>9500</v>
@@ -5281,10 +5281,10 @@
         <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>8662</v>
+        <v>8688.0641925777</v>
       </c>
       <c r="O115" t="n">
-        <v>17324</v>
+        <v>17376.1283851554</v>
       </c>
       <c r="P115" t="n">
         <v>14200</v>
@@ -5499,10 +5499,10 @@
         <v>120</v>
       </c>
       <c r="N120" t="n">
-        <v>3240.8500293686</v>
+        <v>3259.9983308715</v>
       </c>
       <c r="O120" t="n">
-        <v>388902.003524232</v>
+        <v>391199.79970458</v>
       </c>
       <c r="P120" t="n">
         <v>5200</v>
@@ -5584,10 +5584,10 @@
         <v>135</v>
       </c>
       <c r="N122" t="n">
-        <v>5191.4800268456</v>
+        <v>5191.4800270636</v>
       </c>
       <c r="O122" t="n">
-        <v>700849.803624156</v>
+        <v>700849.803653586</v>
       </c>
       <c r="P122" t="n">
         <v>9100</v>
@@ -5672,10 +5672,10 @@
         <v>650</v>
       </c>
       <c r="N124" t="n">
-        <v>2665.4</v>
+        <v>2670.3450834879</v>
       </c>
       <c r="O124" t="n">
-        <v>1732510</v>
+        <v>1735724.304267135</v>
       </c>
       <c r="P124" t="n">
         <v>20900</v>
@@ -5761,22 +5761,22 @@
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M126" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="N126" t="n">
-        <v>12267.651212121</v>
+        <v>12267.650842105</v>
       </c>
       <c r="O126" t="n">
-        <v>269888.326666662</v>
+        <v>196282.41347368</v>
       </c>
       <c r="P126" t="n">
         <v>19900</v>
       </c>
       <c r="Q126" t="n">
-        <v>437800</v>
+        <v>318400</v>
       </c>
     </row>
     <row r="127">
@@ -5986,10 +5986,10 @@
         <v>501</v>
       </c>
       <c r="N131" t="n">
-        <v>3041.6600124456</v>
+        <v>3041.6600125549</v>
       </c>
       <c r="O131" t="n">
-        <v>1523871.666235246</v>
+        <v>1523871.666290005</v>
       </c>
       <c r="P131" t="n">
         <v>5500</v>
@@ -6073,10 +6073,10 @@
         <v>1122</v>
       </c>
       <c r="N133" t="n">
-        <v>4372.2107863175</v>
+        <v>4372.2107866525</v>
       </c>
       <c r="O133" t="n">
-        <v>4905620.502248235</v>
+        <v>4905620.502624106</v>
       </c>
       <c r="P133" t="n">
         <v>7500</v>
@@ -7525,10 +7525,10 @@
         <v>300</v>
       </c>
       <c r="N165" t="n">
-        <v>1630.9230407276</v>
+        <v>1630.9230521929</v>
       </c>
       <c r="O165" t="n">
-        <v>489276.91221828</v>
+        <v>489276.91565787</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -7571,10 +7571,10 @@
         <v>96</v>
       </c>
       <c r="N166" t="n">
-        <v>1550.1929579149</v>
+        <v>1550.1930031561</v>
       </c>
       <c r="O166" t="n">
-        <v>148818.5239598304</v>
+        <v>148818.5283029856</v>
       </c>
       <c r="P166" t="n">
         <v>2500</v>
@@ -7617,10 +7617,10 @@
         <v>48</v>
       </c>
       <c r="N167" t="n">
-        <v>1579.3910696517</v>
+        <v>1579.3910473815</v>
       </c>
       <c r="O167" t="n">
-        <v>75810.77134328161</v>
+        <v>75810.770274312</v>
       </c>
       <c r="P167" t="n">
         <v>2900</v>
@@ -8017,10 +8017,10 @@
         <v>31</v>
       </c>
       <c r="N176" t="n">
-        <v>10034.5</v>
+        <v>10089.035326087</v>
       </c>
       <c r="O176" t="n">
-        <v>311069.5</v>
+        <v>312760.095108697</v>
       </c>
       <c r="P176" t="n">
         <v>12900</v>
@@ -8630,10 +8630,10 @@
         <v>93</v>
       </c>
       <c r="N190" t="n">
-        <v>7537.4721014493</v>
+        <v>7537.4721167883</v>
       </c>
       <c r="O190" t="n">
-        <v>700984.9054347848</v>
+        <v>700984.9068613119</v>
       </c>
       <c r="P190" t="n">
         <v>8900</v>
@@ -8671,10 +8671,10 @@
         <v>1</v>
       </c>
       <c r="N191" t="n">
-        <v>2661.82</v>
+        <v>2673.5203076923</v>
       </c>
       <c r="O191" t="n">
-        <v>2661.82</v>
+        <v>2673.5203076923</v>
       </c>
       <c r="P191" t="n">
         <v>3200</v>
@@ -8753,10 +8753,10 @@
         <v>29</v>
       </c>
       <c r="N193" t="n">
-        <v>4488</v>
+        <v>4530.3396226415</v>
       </c>
       <c r="O193" t="n">
-        <v>130152</v>
+        <v>131379.8490566035</v>
       </c>
       <c r="P193" t="n">
         <v>6200</v>
@@ -8958,10 +8958,10 @@
         <v>348</v>
       </c>
       <c r="N198" t="n">
-        <v>2029.8736443149</v>
+        <v>2029.8736460865</v>
       </c>
       <c r="O198" t="n">
-        <v>706396.0282215852</v>
+        <v>706396.028838102</v>
       </c>
       <c r="P198" t="n">
         <v>3600</v>
@@ -8999,10 +8999,10 @@
         <v>160</v>
       </c>
       <c r="N199" t="n">
-        <v>22485.695927602</v>
+        <v>22485.695904437</v>
       </c>
       <c r="O199" t="n">
-        <v>3597711.34841632</v>
+        <v>3597711.34470992</v>
       </c>
       <c r="P199" t="n">
         <v>36500</v>
@@ -9424,10 +9424,10 @@
         <v>609</v>
       </c>
       <c r="N209" t="n">
-        <v>998.76125816993</v>
+        <v>998.76125988546</v>
       </c>
       <c r="O209" t="n">
-        <v>608245.6062254873</v>
+        <v>608245.6072702452</v>
       </c>
       <c r="P209" t="n">
         <v>1600</v>
@@ -9806,10 +9806,10 @@
         <v>1078</v>
       </c>
       <c r="N218" t="n">
-        <v>3591.13</v>
+        <v>3592.9712903777</v>
       </c>
       <c r="O218" t="n">
-        <v>3871238.14</v>
+        <v>3873223.051027161</v>
       </c>
       <c r="P218" t="n">
         <v>6300</v>
@@ -9975,10 +9975,10 @@
         <v>233</v>
       </c>
       <c r="N222" t="n">
-        <v>4100.45</v>
+        <v>4107.7418494369</v>
       </c>
       <c r="O222" t="n">
-        <v>955404.85</v>
+        <v>957103.8509187978</v>
       </c>
       <c r="P222" t="n">
         <v>26900</v>
@@ -11764,10 +11764,10 @@
         <v>1215</v>
       </c>
       <c r="N262" t="n">
-        <v>1778.4725231214</v>
+        <v>1778.4725400058</v>
       </c>
       <c r="O262" t="n">
-        <v>2160844.115592501</v>
+        <v>2160844.136107047</v>
       </c>
       <c r="P262" t="n">
         <v>4900</v>
@@ -11902,10 +11902,10 @@
         <v>62</v>
       </c>
       <c r="N265" t="n">
-        <v>16058</v>
+        <v>16069.364472753</v>
       </c>
       <c r="O265" t="n">
-        <v>995596</v>
+        <v>996300.597310686</v>
       </c>
       <c r="P265" t="n">
         <v>25900</v>
@@ -14449,10 +14449,10 @@
         <v>77</v>
       </c>
       <c r="N320" t="n">
-        <v>9178</v>
+        <v>9197.9305103149</v>
       </c>
       <c r="O320" t="n">
-        <v>706706</v>
+        <v>708240.6492942473</v>
       </c>
       <c r="P320" t="n">
         <v>14900</v>
@@ -14541,10 +14541,10 @@
         <v>106</v>
       </c>
       <c r="N322" t="n">
-        <v>13922</v>
+        <v>13973.183823529</v>
       </c>
       <c r="O322" t="n">
-        <v>1475732</v>
+        <v>1481157.485294074</v>
       </c>
       <c r="P322" t="n">
         <v>22900</v>
@@ -14679,10 +14679,10 @@
         <v>184</v>
       </c>
       <c r="N325" t="n">
-        <v>4907.8219300912</v>
+        <v>4907.8219330289</v>
       </c>
       <c r="O325" t="n">
-        <v>903039.2351367808</v>
+        <v>903039.2356773176</v>
       </c>
       <c r="P325" t="n">
         <v>8200</v>
@@ -14909,10 +14909,10 @@
         <v>84</v>
       </c>
       <c r="N330" t="n">
-        <v>3903.7359183673</v>
+        <v>3903.7359649123</v>
       </c>
       <c r="O330" t="n">
-        <v>327913.8171428532</v>
+        <v>327913.8210526332</v>
       </c>
       <c r="P330" t="n">
         <v>7500</v>
@@ -15645,10 +15645,10 @@
         <v>90</v>
       </c>
       <c r="N346" t="n">
-        <v>17992</v>
+        <v>18015.037131882</v>
       </c>
       <c r="O346" t="n">
-        <v>1619280</v>
+        <v>1621353.34186938</v>
       </c>
       <c r="P346" t="n">
         <v>28900</v>
@@ -16146,10 +16146,10 @@
         <v>60</v>
       </c>
       <c r="N357" t="n">
-        <v>4268.7035271318</v>
+        <v>4268.7037401575</v>
       </c>
       <c r="O357" t="n">
-        <v>256122.211627908</v>
+        <v>256122.22440945</v>
       </c>
       <c r="P357" t="n">
         <v>6900</v>
@@ -16652,10 +16652,10 @@
         <v>839</v>
       </c>
       <c r="N368" t="n">
-        <v>1516.0388131508</v>
+        <v>1516.0388129219</v>
       </c>
       <c r="O368" t="n">
-        <v>1271956.564233521</v>
+        <v>1271956.564041474</v>
       </c>
       <c r="P368" t="n">
         <v>2300</v>
@@ -17015,10 +17015,10 @@
         <v>145</v>
       </c>
       <c r="N376" t="n">
-        <v>2842.2737931034</v>
+        <v>2842.2737735849</v>
       </c>
       <c r="O376" t="n">
-        <v>412129.699999993</v>
+        <v>412129.6971698105</v>
       </c>
       <c r="P376" t="n">
         <v>4900</v>
@@ -17592,10 +17592,10 @@
         <v>780</v>
       </c>
       <c r="N388" t="n">
-        <v>1530.4499204455</v>
+        <v>1530.4499204138</v>
       </c>
       <c r="O388" t="n">
-        <v>1193750.93794749</v>
+        <v>1193750.937922764</v>
       </c>
       <c r="P388" t="n">
         <v>2600</v>
@@ -18012,10 +18012,10 @@
         <v>238</v>
       </c>
       <c r="N397" t="n">
-        <v>1690.8700088574</v>
+        <v>1690.8700089286</v>
       </c>
       <c r="O397" t="n">
-        <v>402427.0621080612</v>
+        <v>402427.0621250068</v>
       </c>
       <c r="P397" t="n">
         <v>3000</v>
@@ -18159,10 +18159,10 @@
         <v>47</v>
       </c>
       <c r="N400" t="n">
-        <v>2270.3210752688</v>
+        <v>2270.3211494253</v>
       </c>
       <c r="O400" t="n">
-        <v>106705.0905376336</v>
+        <v>106705.0940229891</v>
       </c>
       <c r="P400" t="n">
         <v>3900</v>
@@ -19041,10 +19041,10 @@
         <v>2</v>
       </c>
       <c r="N419" t="n">
-        <v>3110.8431677619</v>
+        <v>3110.8430699863</v>
       </c>
       <c r="O419" t="n">
-        <v>6221.6863355238</v>
+        <v>6221.6861399726</v>
       </c>
       <c r="P419" t="n">
         <v>4500</v>
@@ -19231,10 +19231,10 @@
         <v>127</v>
       </c>
       <c r="N423" t="n">
-        <v>3182.2510928962</v>
+        <v>3182.2511009174</v>
       </c>
       <c r="O423" t="n">
-        <v>404145.8887978174</v>
+        <v>404145.8898165098</v>
       </c>
       <c r="P423" t="n">
         <v>6900</v>
@@ -19317,22 +19317,22 @@
         <v>0</v>
       </c>
       <c r="L425" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M425" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="N425" t="n">
         <v>7570.87</v>
       </c>
       <c r="O425" t="n">
-        <v>174130.01</v>
+        <v>83279.56999999999</v>
       </c>
       <c r="P425" t="n">
         <v>9500</v>
       </c>
       <c r="Q425" t="n">
-        <v>218500</v>
+        <v>104500</v>
       </c>
     </row>
     <row r="426">
@@ -20119,10 +20119,10 @@
         <v>73</v>
       </c>
       <c r="N442" t="n">
-        <v>2098.4048459384</v>
+        <v>2098.4048595506</v>
       </c>
       <c r="O442" t="n">
-        <v>153183.5537535032</v>
+        <v>153183.5547471938</v>
       </c>
       <c r="P442" t="n">
         <v>9500</v>
@@ -20796,10 +20796,10 @@
         <v>22</v>
       </c>
       <c r="N456" t="n">
-        <v>12448.353225806</v>
+        <v>12448.353333333</v>
       </c>
       <c r="O456" t="n">
-        <v>273863.770967732</v>
+        <v>273863.773333326</v>
       </c>
       <c r="P456" t="n">
         <v>22900</v>
@@ -22785,10 +22785,10 @@
         <v>1372</v>
       </c>
       <c r="N497" t="n">
-        <v>665.3233262441501</v>
+        <v>665.32333760137</v>
       </c>
       <c r="O497" t="n">
-        <v>912823.6036069739</v>
+        <v>912823.6191890796</v>
       </c>
       <c r="P497" t="n">
         <v>2900</v>
@@ -25178,10 +25178,10 @@
         <v>3</v>
       </c>
       <c r="N549" t="n">
-        <v>2432.1340350877</v>
+        <v>2432.1341071429</v>
       </c>
       <c r="O549" t="n">
-        <v>7296.4021052631</v>
+        <v>7296.402321428701</v>
       </c>
       <c r="P549" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-11</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-12</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>41</v>
       </c>
       <c r="N4" t="n">
-        <v>27043.062200957</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>1108765.550239237</v>
+        <v>1107000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -3668,10 +3668,10 @@
         <v>98</v>
       </c>
       <c r="N79" t="n">
-        <v>17261.351724138</v>
+        <v>17207.41</v>
       </c>
       <c r="O79" t="n">
-        <v>1691612.468965524</v>
+        <v>1686326.18</v>
       </c>
       <c r="P79" t="n">
         <v>20000</v>
@@ -3924,10 +3924,10 @@
         <v>336</v>
       </c>
       <c r="N85" t="n">
-        <v>2808.0329005282</v>
+        <v>2804.33</v>
       </c>
       <c r="O85" t="n">
-        <v>943499.0545774752</v>
+        <v>942254.88</v>
       </c>
       <c r="P85" t="n">
         <v>4900</v>
@@ -4744,10 +4744,10 @@
         <v>507</v>
       </c>
       <c r="N103" t="n">
-        <v>6511.2612966601</v>
+        <v>6507</v>
       </c>
       <c r="O103" t="n">
-        <v>3301209.477406671</v>
+        <v>3299049</v>
       </c>
       <c r="P103" t="n">
         <v>9900</v>
@@ -5235,10 +5235,10 @@
         <v>580</v>
       </c>
       <c r="N114" t="n">
-        <v>5672.995244381</v>
+        <v>5667.94</v>
       </c>
       <c r="O114" t="n">
-        <v>3290337.24174098</v>
+        <v>3287405.2</v>
       </c>
       <c r="P114" t="n">
         <v>9500</v>
@@ -5281,10 +5281,10 @@
         <v>2</v>
       </c>
       <c r="N115" t="n">
-        <v>8688.0641925777</v>
+        <v>8662</v>
       </c>
       <c r="O115" t="n">
-        <v>17376.1283851554</v>
+        <v>17324</v>
       </c>
       <c r="P115" t="n">
         <v>14200</v>
@@ -5499,10 +5499,10 @@
         <v>120</v>
       </c>
       <c r="N120" t="n">
-        <v>3259.9983308715</v>
+        <v>3240.8500295421</v>
       </c>
       <c r="O120" t="n">
-        <v>391199.79970458</v>
+        <v>388902.003545052</v>
       </c>
       <c r="P120" t="n">
         <v>5200</v>
@@ -5672,10 +5672,10 @@
         <v>650</v>
       </c>
       <c r="N124" t="n">
-        <v>2670.3450834879</v>
+        <v>2665.4</v>
       </c>
       <c r="O124" t="n">
-        <v>1735724.304267135</v>
+        <v>1732510</v>
       </c>
       <c r="P124" t="n">
         <v>20900</v>
@@ -5755,13 +5755,13 @@
         </is>
       </c>
       <c r="J126" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
         <v>16</v>
@@ -8017,10 +8017,10 @@
         <v>31</v>
       </c>
       <c r="N176" t="n">
-        <v>10089.035326087</v>
+        <v>10034.5</v>
       </c>
       <c r="O176" t="n">
-        <v>312760.095108697</v>
+        <v>311069.5</v>
       </c>
       <c r="P176" t="n">
         <v>12900</v>
@@ -8671,10 +8671,10 @@
         <v>1</v>
       </c>
       <c r="N191" t="n">
-        <v>2673.5203076923</v>
+        <v>2661.82</v>
       </c>
       <c r="O191" t="n">
-        <v>2673.5203076923</v>
+        <v>2661.82</v>
       </c>
       <c r="P191" t="n">
         <v>3200</v>
@@ -8753,10 +8753,10 @@
         <v>29</v>
       </c>
       <c r="N193" t="n">
-        <v>4530.3396226415</v>
+        <v>4488</v>
       </c>
       <c r="O193" t="n">
-        <v>131379.8490566035</v>
+        <v>130152</v>
       </c>
       <c r="P193" t="n">
         <v>6200</v>
@@ -9806,10 +9806,10 @@
         <v>1078</v>
       </c>
       <c r="N218" t="n">
-        <v>3592.9712903777</v>
+        <v>3591.13</v>
       </c>
       <c r="O218" t="n">
-        <v>3873223.051027161</v>
+        <v>3871238.14</v>
       </c>
       <c r="P218" t="n">
         <v>6300</v>
@@ -9975,10 +9975,10 @@
         <v>233</v>
       </c>
       <c r="N222" t="n">
-        <v>4107.7418494369</v>
+        <v>4100.45</v>
       </c>
       <c r="O222" t="n">
-        <v>957103.8509187978</v>
+        <v>955404.85</v>
       </c>
       <c r="P222" t="n">
         <v>26900</v>
@@ -11902,10 +11902,10 @@
         <v>62</v>
       </c>
       <c r="N265" t="n">
-        <v>16069.364472753</v>
+        <v>16058</v>
       </c>
       <c r="O265" t="n">
-        <v>996300.597310686</v>
+        <v>995596</v>
       </c>
       <c r="P265" t="n">
         <v>25900</v>
@@ -14449,10 +14449,10 @@
         <v>77</v>
       </c>
       <c r="N320" t="n">
-        <v>9197.9305103149</v>
+        <v>9178</v>
       </c>
       <c r="O320" t="n">
-        <v>708240.6492942473</v>
+        <v>706706</v>
       </c>
       <c r="P320" t="n">
         <v>14900</v>
@@ -14541,10 +14541,10 @@
         <v>106</v>
       </c>
       <c r="N322" t="n">
-        <v>13973.183823529</v>
+        <v>13922</v>
       </c>
       <c r="O322" t="n">
-        <v>1481157.485294074</v>
+        <v>1475732</v>
       </c>
       <c r="P322" t="n">
         <v>22900</v>
@@ -15645,10 +15645,10 @@
         <v>90</v>
       </c>
       <c r="N346" t="n">
-        <v>18015.037131882</v>
+        <v>17992</v>
       </c>
       <c r="O346" t="n">
-        <v>1621353.34186938</v>
+        <v>1619280</v>
       </c>
       <c r="P346" t="n">
         <v>28900</v>
@@ -19311,13 +19311,13 @@
         </is>
       </c>
       <c r="J425" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K425" t="n">
         <v>0</v>
       </c>
       <c r="L425" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M425" t="n">
         <v>11</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7465109371</v>
+        <v>3376.7465014893</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.201920078</v>
+        <v>1982150.196374219</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1073,10 +1073,10 @@
         <v>310</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8542666667</v>
+        <v>6272.8544651163</v>
       </c>
       <c r="O17" t="n">
-        <v>1944584.822666677</v>
+        <v>1944584.884186053</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>2413.0010330579</v>
+        <v>2413.001059322</v>
       </c>
       <c r="O22" t="n">
-        <v>2413.0010330579</v>
+        <v>2413.001059322</v>
       </c>
       <c r="P22" t="n">
         <v>4700</v>
@@ -1544,10 +1544,10 @@
         <v>62</v>
       </c>
       <c r="N29" t="n">
-        <v>14857.623171806</v>
+        <v>14857.623185841</v>
       </c>
       <c r="O29" t="n">
-        <v>921172.6366519721</v>
+        <v>921172.6375221419</v>
       </c>
       <c r="P29" t="n">
         <v>34900</v>
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.628245614</v>
+        <v>3910.6282352941</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.274210522</v>
+        <v>481007.2729411743</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -1708,10 +1708,10 @@
         <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.966106557</v>
+        <v>15711.966058091</v>
       </c>
       <c r="O33" t="n">
-        <v>659902.576475394</v>
+        <v>659902.574439822</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.873861893</v>
+        <v>61666.873932292</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.332890041</v>
+        <v>2281674.335494804</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -2954,22 +2954,22 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M63" t="n">
-        <v>228</v>
+        <v>148</v>
       </c>
       <c r="N63" t="n">
-        <v>1950.2152424105</v>
+        <v>1950.2151724138</v>
       </c>
       <c r="O63" t="n">
-        <v>444649.075269594</v>
+        <v>288631.8455172424</v>
       </c>
       <c r="P63" t="n">
         <v>2900</v>
       </c>
       <c r="Q63" t="n">
-        <v>661200</v>
+        <v>429200</v>
       </c>
     </row>
     <row r="64">
@@ -3047,10 +3047,10 @@
         <v>434</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101603499</v>
+        <v>4937.3101608187</v>
       </c>
       <c r="O65" t="n">
-        <v>2142792.609591857</v>
+        <v>2142792.609795316</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0535004591</v>
+        <v>1098.0541801698</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.420055092</v>
+        <v>131766.501620376</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4418,22 +4418,22 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="M96" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
         <v>1903</v>
       </c>
       <c r="O96" t="n">
-        <v>418660</v>
+        <v>0</v>
       </c>
       <c r="P96" t="n">
         <v>3200</v>
       </c>
       <c r="Q96" t="n">
-        <v>704000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4820,22 +4820,22 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M105" t="n">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="N105" t="n">
         <v>3719.06</v>
       </c>
       <c r="O105" t="n">
-        <v>364467.88</v>
+        <v>290086.68</v>
       </c>
       <c r="P105" t="n">
         <v>6000</v>
       </c>
       <c r="Q105" t="n">
-        <v>588000</v>
+        <v>468000</v>
       </c>
     </row>
     <row r="106">
@@ -5051,10 +5051,10 @@
         <v>487</v>
       </c>
       <c r="N110" t="n">
-        <v>4890.9300461095</v>
+        <v>4890.9300462963</v>
       </c>
       <c r="O110" t="n">
-        <v>2381882.932455326</v>
+        <v>2381882.932546298</v>
       </c>
       <c r="P110" t="n">
         <v>8200</v>
@@ -5537,22 +5537,22 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M121" t="n">
-        <v>2802</v>
+        <v>2706</v>
       </c>
       <c r="N121" t="n">
         <v>2090.85</v>
       </c>
       <c r="O121" t="n">
-        <v>5858561.7</v>
+        <v>5657840.1</v>
       </c>
       <c r="P121" t="n">
         <v>2900</v>
       </c>
       <c r="Q121" t="n">
-        <v>8125800</v>
+        <v>7847400</v>
       </c>
     </row>
     <row r="122">
@@ -5767,10 +5767,10 @@
         <v>16</v>
       </c>
       <c r="N126" t="n">
-        <v>12267.650842105</v>
+        <v>12267.650645161</v>
       </c>
       <c r="O126" t="n">
-        <v>196282.41347368</v>
+        <v>196282.410322576</v>
       </c>
       <c r="P126" t="n">
         <v>19900</v>
@@ -5852,10 +5852,10 @@
         <v>91</v>
       </c>
       <c r="N128" t="n">
-        <v>15851.61</v>
+        <v>15957.996644295</v>
       </c>
       <c r="O128" t="n">
-        <v>1442496.51</v>
+        <v>1452177.694630845</v>
       </c>
       <c r="P128" t="n">
         <v>23900</v>
@@ -5986,10 +5986,10 @@
         <v>501</v>
       </c>
       <c r="N131" t="n">
-        <v>3041.6600125549</v>
+        <v>3041.6600125945</v>
       </c>
       <c r="O131" t="n">
-        <v>1523871.666290005</v>
+        <v>1523871.666309844</v>
       </c>
       <c r="P131" t="n">
         <v>5500</v>
@@ -6073,10 +6073,10 @@
         <v>1122</v>
       </c>
       <c r="N133" t="n">
-        <v>4372.2107866525</v>
+        <v>4372.2107869318</v>
       </c>
       <c r="O133" t="n">
-        <v>4905620.502624106</v>
+        <v>4905620.502937479</v>
       </c>
       <c r="P133" t="n">
         <v>7500</v>
@@ -6159,22 +6159,22 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M135" t="n">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="N135" t="n">
         <v>3655.96</v>
       </c>
       <c r="O135" t="n">
-        <v>2789497.48</v>
+        <v>2763905.76</v>
       </c>
       <c r="P135" t="n">
         <v>5500</v>
       </c>
       <c r="Q135" t="n">
-        <v>4196500</v>
+        <v>4158000</v>
       </c>
     </row>
     <row r="136">
@@ -6374,22 +6374,22 @@
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M140" t="n">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="N140" t="n">
         <v>6242.93</v>
       </c>
       <c r="O140" t="n">
-        <v>1885364.86</v>
+        <v>1791720.91</v>
       </c>
       <c r="P140" t="n">
         <v>10400</v>
       </c>
       <c r="Q140" t="n">
-        <v>3140800</v>
+        <v>2984800</v>
       </c>
     </row>
     <row r="141">
@@ -6658,10 +6658,10 @@
         <v>2595</v>
       </c>
       <c r="N146" t="n">
-        <v>17472.91</v>
+        <v>17476.031091396</v>
       </c>
       <c r="O146" t="n">
-        <v>45342201.45</v>
+        <v>45350300.68217262</v>
       </c>
       <c r="P146" t="n">
         <v>2900</v>
@@ -6828,22 +6828,22 @@
         <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M150" t="n">
-        <v>5127</v>
+        <v>5007</v>
       </c>
       <c r="N150" t="n">
         <v>1387.55</v>
       </c>
       <c r="O150" t="n">
-        <v>7113968.85</v>
+        <v>6947462.85</v>
       </c>
       <c r="P150" t="n">
         <v>2300</v>
       </c>
       <c r="Q150" t="n">
-        <v>11792100</v>
+        <v>11516100</v>
       </c>
     </row>
     <row r="151">
@@ -7162,10 +7162,10 @@
         <v>85</v>
       </c>
       <c r="N157" t="n">
-        <v>8341.030000000001</v>
+        <v>8367.5094603175</v>
       </c>
       <c r="O157" t="n">
-        <v>708987.55</v>
+        <v>711238.3041269875</v>
       </c>
       <c r="P157" t="n">
         <v>13900</v>
@@ -7519,22 +7519,22 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M165" t="n">
-        <v>300</v>
+        <v>228</v>
       </c>
       <c r="N165" t="n">
-        <v>1630.9230521929</v>
+        <v>1630.9231064431</v>
       </c>
       <c r="O165" t="n">
-        <v>489276.91565787</v>
+        <v>371850.4682690268</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
       </c>
       <c r="Q165" t="n">
-        <v>750000</v>
+        <v>570000</v>
       </c>
     </row>
     <row r="166">
@@ -7571,10 +7571,10 @@
         <v>96</v>
       </c>
       <c r="N166" t="n">
-        <v>1550.1930031561</v>
+        <v>1550.1930735465</v>
       </c>
       <c r="O166" t="n">
-        <v>148818.5283029856</v>
+        <v>148818.535060464</v>
       </c>
       <c r="P166" t="n">
         <v>2500</v>
@@ -8630,10 +8630,10 @@
         <v>93</v>
       </c>
       <c r="N190" t="n">
-        <v>7537.4721167883</v>
+        <v>7537.4721481481</v>
       </c>
       <c r="O190" t="n">
-        <v>700984.9068613119</v>
+        <v>700984.9097777733</v>
       </c>
       <c r="P190" t="n">
         <v>8900</v>
@@ -8958,10 +8958,10 @@
         <v>348</v>
       </c>
       <c r="N198" t="n">
-        <v>2029.8736460865</v>
+        <v>2029.8736549708</v>
       </c>
       <c r="O198" t="n">
-        <v>706396.028838102</v>
+        <v>706396.0319298385</v>
       </c>
       <c r="P198" t="n">
         <v>3600</v>
@@ -9075,22 +9075,22 @@
         <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M201" t="n">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="N201" t="n">
         <v>7103</v>
       </c>
       <c r="O201" t="n">
-        <v>1520042</v>
+        <v>1477424</v>
       </c>
       <c r="P201" t="n">
         <v>10700</v>
       </c>
       <c r="Q201" t="n">
-        <v>2289800</v>
+        <v>2225600</v>
       </c>
     </row>
     <row r="202">
@@ -9928,22 +9928,22 @@
         <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M221" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="N221" t="n">
-        <v>27123.765250464</v>
+        <v>27123.765241636</v>
       </c>
       <c r="O221" t="n">
-        <v>1084950.61001856</v>
+        <v>1003579.313940532</v>
       </c>
       <c r="P221" t="n">
         <v>44500</v>
       </c>
       <c r="Q221" t="n">
-        <v>1780000</v>
+        <v>1646500</v>
       </c>
     </row>
     <row r="222">
@@ -10102,22 +10102,22 @@
         <v>0</v>
       </c>
       <c r="L225" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M225" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="N225" t="n">
         <v>4958</v>
       </c>
       <c r="O225" t="n">
-        <v>109076</v>
+        <v>59496</v>
       </c>
       <c r="P225" t="n">
         <v>8500</v>
       </c>
       <c r="Q225" t="n">
-        <v>187000</v>
+        <v>102000</v>
       </c>
     </row>
     <row r="226">
@@ -10231,10 +10231,10 @@
         <v>97</v>
       </c>
       <c r="N228" t="n">
-        <v>2568.8356026059</v>
+        <v>2568.8355</v>
       </c>
       <c r="O228" t="n">
-        <v>249177.0534527723</v>
+        <v>249177.0435</v>
       </c>
       <c r="P228" t="n">
         <v>4500</v>
@@ -10359,10 +10359,10 @@
         <v>180</v>
       </c>
       <c r="N231" t="n">
-        <v>7969.950164794</v>
+        <v>7969.9501649175</v>
       </c>
       <c r="O231" t="n">
-        <v>1434591.02966292</v>
+        <v>1434591.02968515</v>
       </c>
       <c r="P231" t="n">
         <v>12900</v>
@@ -10712,22 +10712,22 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M239" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="N239" t="n">
         <v>5956</v>
       </c>
       <c r="O239" t="n">
-        <v>131032</v>
+        <v>41692</v>
       </c>
       <c r="P239" t="n">
         <v>10200</v>
       </c>
       <c r="Q239" t="n">
-        <v>224400</v>
+        <v>71400</v>
       </c>
     </row>
     <row r="240">
@@ -11764,10 +11764,10 @@
         <v>1215</v>
       </c>
       <c r="N262" t="n">
-        <v>1778.4725400058</v>
+        <v>1778.4725489051</v>
       </c>
       <c r="O262" t="n">
-        <v>2160844.136107047</v>
+        <v>2160844.146919697</v>
       </c>
       <c r="P262" t="n">
         <v>4900</v>
@@ -11850,22 +11850,22 @@
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M264" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="N264" t="n">
         <v>18016</v>
       </c>
       <c r="O264" t="n">
-        <v>1423264</v>
+        <v>1315168</v>
       </c>
       <c r="P264" t="n">
         <v>29900</v>
       </c>
       <c r="Q264" t="n">
-        <v>2362100</v>
+        <v>2182700</v>
       </c>
     </row>
     <row r="265">
@@ -12686,22 +12686,22 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M282" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="N282" t="n">
         <v>15851.09</v>
       </c>
       <c r="O282" t="n">
-        <v>285319.62</v>
+        <v>253617.44</v>
       </c>
       <c r="P282" t="n">
         <v>19900</v>
       </c>
       <c r="Q282" t="n">
-        <v>358200</v>
+        <v>318400</v>
       </c>
     </row>
     <row r="283">
@@ -13388,10 +13388,10 @@
         <v>104</v>
       </c>
       <c r="N297" t="n">
-        <v>8293</v>
+        <v>8329.056521739099</v>
       </c>
       <c r="O297" t="n">
-        <v>862472</v>
+        <v>866221.8782608664</v>
       </c>
       <c r="P297" t="n">
         <v>13500</v>
@@ -13704,22 +13704,22 @@
         <v>0</v>
       </c>
       <c r="L304" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M304" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N304" t="n">
         <v>10385</v>
       </c>
       <c r="O304" t="n">
-        <v>249240</v>
+        <v>93465</v>
       </c>
       <c r="P304" t="n">
         <v>16900</v>
       </c>
       <c r="Q304" t="n">
-        <v>405600</v>
+        <v>152100</v>
       </c>
     </row>
     <row r="305">
@@ -14026,22 +14026,22 @@
         <v>0</v>
       </c>
       <c r="L311" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M311" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="N311" t="n">
         <v>5858</v>
       </c>
       <c r="O311" t="n">
-        <v>544794</v>
+        <v>486214</v>
       </c>
       <c r="P311" t="n">
         <v>9500</v>
       </c>
       <c r="Q311" t="n">
-        <v>883500</v>
+        <v>788500</v>
       </c>
     </row>
     <row r="312">
@@ -14078,10 +14078,10 @@
         <v>263</v>
       </c>
       <c r="N312" t="n">
-        <v>2252.2963603819</v>
+        <v>2252.2964527845</v>
       </c>
       <c r="O312" t="n">
-        <v>592353.9427804396</v>
+        <v>592353.9670823235</v>
       </c>
       <c r="P312" t="n">
         <v>3900</v>
@@ -14265,10 +14265,10 @@
         <v>504</v>
       </c>
       <c r="N316" t="n">
-        <v>2328.1187525865</v>
+        <v>2328.1187507401</v>
       </c>
       <c r="O316" t="n">
-        <v>1173371.851303596</v>
+        <v>1173371.85037301</v>
       </c>
       <c r="P316" t="n">
         <v>4500</v>
@@ -14909,10 +14909,10 @@
         <v>84</v>
       </c>
       <c r="N330" t="n">
-        <v>3903.7359649123</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O330" t="n">
-        <v>327913.8210526332</v>
+        <v>327913.8369230808</v>
       </c>
       <c r="P330" t="n">
         <v>7500</v>
@@ -15001,10 +15001,10 @@
         <v>73</v>
       </c>
       <c r="N332" t="n">
-        <v>4202</v>
+        <v>4213.1164021164</v>
       </c>
       <c r="O332" t="n">
-        <v>306746</v>
+        <v>307557.4973544972</v>
       </c>
       <c r="P332" t="n">
         <v>7900</v>
@@ -15271,22 +15271,22 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M338" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="N338" t="n">
         <v>8637</v>
       </c>
       <c r="O338" t="n">
-        <v>155466</v>
+        <v>69096</v>
       </c>
       <c r="P338" t="n">
         <v>14500</v>
       </c>
       <c r="Q338" t="n">
-        <v>261000</v>
+        <v>116000</v>
       </c>
     </row>
     <row r="339">
@@ -16146,10 +16146,10 @@
         <v>60</v>
       </c>
       <c r="N357" t="n">
-        <v>4268.7037401575</v>
+        <v>4268.7041295547</v>
       </c>
       <c r="O357" t="n">
-        <v>256122.22440945</v>
+        <v>256122.247773282</v>
       </c>
       <c r="P357" t="n">
         <v>6900</v>
@@ -16370,22 +16370,22 @@
         <v>0</v>
       </c>
       <c r="L362" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M362" t="n">
-        <v>1798</v>
+        <v>1778</v>
       </c>
       <c r="N362" t="n">
         <v>1326</v>
       </c>
       <c r="O362" t="n">
-        <v>2384148</v>
+        <v>2357628</v>
       </c>
       <c r="P362" t="n">
         <v>2500</v>
       </c>
       <c r="Q362" t="n">
-        <v>4495000</v>
+        <v>4445000</v>
       </c>
     </row>
     <row r="363">
@@ -17059,10 +17059,10 @@
         <v>2243</v>
       </c>
       <c r="N377" t="n">
-        <v>692.15205253785</v>
+        <v>692.15206356312</v>
       </c>
       <c r="O377" t="n">
-        <v>1552497.053842397</v>
+        <v>1552497.078572078</v>
       </c>
       <c r="P377" t="n">
         <v>1200</v>
@@ -18290,22 +18290,22 @@
         <v>0</v>
       </c>
       <c r="L403" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M403" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="N403" t="n">
-        <v>3907.5003212851</v>
+        <v>3907.5003292181</v>
       </c>
       <c r="O403" t="n">
-        <v>304785.0250602378</v>
+        <v>265710.0223868308</v>
       </c>
       <c r="P403" t="n">
         <v>3900</v>
       </c>
       <c r="Q403" t="n">
-        <v>304200</v>
+        <v>265200</v>
       </c>
     </row>
     <row r="404">
@@ -18339,22 +18339,22 @@
         <v>0</v>
       </c>
       <c r="L404" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M404" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N404" t="n">
         <v>3913.26</v>
       </c>
       <c r="O404" t="n">
-        <v>70438.68000000001</v>
+        <v>50872.38</v>
       </c>
       <c r="P404" t="n">
         <v>3900</v>
       </c>
       <c r="Q404" t="n">
-        <v>70200</v>
+        <v>50700</v>
       </c>
     </row>
     <row r="405">
@@ -19041,10 +19041,10 @@
         <v>2</v>
       </c>
       <c r="N419" t="n">
-        <v>3110.8430699863</v>
+        <v>3110.8429819337</v>
       </c>
       <c r="O419" t="n">
-        <v>6221.6861399726</v>
+        <v>6221.6859638674</v>
       </c>
       <c r="P419" t="n">
         <v>4500</v>
@@ -19363,22 +19363,22 @@
         <v>0</v>
       </c>
       <c r="L426" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M426" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="N426" t="n">
         <v>14089.24</v>
       </c>
       <c r="O426" t="n">
-        <v>366320.24</v>
+        <v>295874.04</v>
       </c>
       <c r="P426" t="n">
         <v>17900</v>
       </c>
       <c r="Q426" t="n">
-        <v>465400</v>
+        <v>375900</v>
       </c>
     </row>
     <row r="427">
@@ -19415,10 +19415,10 @@
         <v>4</v>
       </c>
       <c r="N427" t="n">
-        <v>2501.385443038</v>
+        <v>2501.3854237288</v>
       </c>
       <c r="O427" t="n">
-        <v>10005.541772152</v>
+        <v>10005.5416949152</v>
       </c>
       <c r="P427" t="n">
         <v>4100</v>
@@ -19841,10 +19841,10 @@
         <v>21</v>
       </c>
       <c r="N436" t="n">
-        <v>712.62863414634</v>
+        <v>712.6285492228</v>
       </c>
       <c r="O436" t="n">
-        <v>14965.20131707314</v>
+        <v>14965.1995336788</v>
       </c>
       <c r="P436" t="n">
         <v>700</v>
@@ -19975,10 +19975,10 @@
         <v>381</v>
       </c>
       <c r="N439" t="n">
-        <v>1595.5191323094</v>
+        <v>1595.5190941049</v>
       </c>
       <c r="O439" t="n">
-        <v>607892.7894098813</v>
+        <v>607892.7748539669</v>
       </c>
       <c r="P439" t="n">
         <v>2500</v>
@@ -20119,10 +20119,10 @@
         <v>73</v>
       </c>
       <c r="N442" t="n">
-        <v>2098.4048595506</v>
+        <v>2098.4049008499</v>
       </c>
       <c r="O442" t="n">
-        <v>153183.5547471938</v>
+        <v>153183.5577620427</v>
       </c>
       <c r="P442" t="n">
         <v>9500</v>
@@ -20410,10 +20410,10 @@
         <v>23</v>
       </c>
       <c r="N448" t="n">
-        <v>2832.1946575342</v>
+        <v>2832.1948571429</v>
       </c>
       <c r="O448" t="n">
-        <v>65140.4771232866</v>
+        <v>65140.4817142867</v>
       </c>
       <c r="P448" t="n">
         <v>12900</v>
@@ -20790,22 +20790,22 @@
         <v>0</v>
       </c>
       <c r="L456" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M456" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="N456" t="n">
-        <v>12448.353333333</v>
+        <v>12448.353571429</v>
       </c>
       <c r="O456" t="n">
-        <v>273863.773333326</v>
+        <v>224070.364285722</v>
       </c>
       <c r="P456" t="n">
         <v>22900</v>
       </c>
       <c r="Q456" t="n">
-        <v>503800</v>
+        <v>412200</v>
       </c>
     </row>
     <row r="457">
@@ -21473,22 +21473,22 @@
         <v>0</v>
       </c>
       <c r="L470" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M470" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="N470" t="n">
         <v>4578.04</v>
       </c>
       <c r="O470" t="n">
-        <v>1103307.64</v>
+        <v>1057527.24</v>
       </c>
       <c r="P470" t="n">
         <v>7500</v>
       </c>
       <c r="Q470" t="n">
-        <v>1807500</v>
+        <v>1732500</v>
       </c>
     </row>
     <row r="471">
@@ -21955,22 +21955,22 @@
         <v>0</v>
       </c>
       <c r="L480" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M480" t="n">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="N480" t="n">
         <v>1024.29</v>
       </c>
       <c r="O480" t="n">
-        <v>333918.54</v>
+        <v>313432.74</v>
       </c>
       <c r="P480" t="n">
         <v>2900</v>
       </c>
       <c r="Q480" t="n">
-        <v>945400</v>
+        <v>887400</v>
       </c>
     </row>
     <row r="481">
@@ -22004,22 +22004,22 @@
         <v>0</v>
       </c>
       <c r="L481" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M481" t="n">
-        <v>356</v>
+        <v>336</v>
       </c>
       <c r="N481" t="n">
         <v>711.48</v>
       </c>
       <c r="O481" t="n">
-        <v>253286.88</v>
+        <v>239057.28</v>
       </c>
       <c r="P481" t="n">
         <v>2500</v>
       </c>
       <c r="Q481" t="n">
-        <v>890000</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="482">
@@ -22059,10 +22059,10 @@
         <v>152</v>
       </c>
       <c r="N482" t="n">
-        <v>7046.9398302567</v>
+        <v>7046.9398299681</v>
       </c>
       <c r="O482" t="n">
-        <v>1071134.854199018</v>
+        <v>1071134.854155151</v>
       </c>
       <c r="P482" t="n">
         <v>9900</v>
@@ -22779,22 +22779,22 @@
         <v>0</v>
       </c>
       <c r="L497" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M497" t="n">
-        <v>1372</v>
+        <v>1228</v>
       </c>
       <c r="N497" t="n">
-        <v>665.32333760137</v>
+        <v>665.32334188034</v>
       </c>
       <c r="O497" t="n">
-        <v>912823.6191890796</v>
+        <v>817017.0638290575</v>
       </c>
       <c r="P497" t="n">
         <v>2900</v>
       </c>
       <c r="Q497" t="n">
-        <v>3978800</v>
+        <v>3561200</v>
       </c>
     </row>
     <row r="498">
@@ -23342,10 +23342,10 @@
         <v>216</v>
       </c>
       <c r="N509" t="n">
-        <v>1008.8176731794</v>
+        <v>1019.6846499102</v>
       </c>
       <c r="O509" t="n">
-        <v>217904.6174067504</v>
+        <v>220251.8843806032</v>
       </c>
       <c r="P509" t="n">
         <v>1500</v>
@@ -23468,10 +23468,10 @@
         <v>116</v>
       </c>
       <c r="N512" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821442495</v>
       </c>
       <c r="O512" t="n">
-        <v>140787.125857418</v>
+        <v>140787.128732942</v>
       </c>
       <c r="P512" t="n">
         <v>1500</v>
@@ -23512,10 +23512,10 @@
         <v>-72</v>
       </c>
       <c r="N513" t="n">
-        <v>1794.2879773671</v>
+        <v>1794.2879767875</v>
       </c>
       <c r="O513" t="n">
-        <v>-129188.7343704312</v>
+        <v>-129188.7343287</v>
       </c>
       <c r="P513" t="n">
         <v>1600</v>
@@ -24600,22 +24600,22 @@
         <v>0</v>
       </c>
       <c r="L537" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M537" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="N537" t="n">
         <v>3840</v>
       </c>
       <c r="O537" t="n">
-        <v>103680</v>
+        <v>65280</v>
       </c>
       <c r="P537" t="n">
         <v>3900</v>
       </c>
       <c r="Q537" t="n">
-        <v>105300</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="538">
@@ -25275,10 +25275,10 @@
         <v>271</v>
       </c>
       <c r="N551" t="n">
-        <v>227.41596785975</v>
+        <v>227.41597222222</v>
       </c>
       <c r="O551" t="n">
-        <v>61629.72728999225</v>
+        <v>61629.72847222162</v>
       </c>
       <c r="P551" t="n">
         <v>1200</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1028,22 +1028,22 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>658</v>
+        <v>648</v>
       </c>
       <c r="N16" t="n">
         <v>3585</v>
       </c>
       <c r="O16" t="n">
-        <v>2358930</v>
+        <v>2323080</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
       </c>
       <c r="Q16" t="n">
-        <v>2961000</v>
+        <v>2916000</v>
       </c>
     </row>
     <row r="17">
@@ -1067,22 +1067,22 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M17" t="n">
-        <v>310</v>
+        <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8544651163</v>
+        <v>6272.8545</v>
       </c>
       <c r="O17" t="n">
-        <v>1944584.884186053</v>
+        <v>1794036.387</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
       </c>
       <c r="Q17" t="n">
-        <v>2449000</v>
+        <v>2259400</v>
       </c>
     </row>
     <row r="18">
@@ -1145,22 +1145,22 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8371267317</v>
+        <v>3926.8371237802</v>
       </c>
       <c r="O19" t="n">
-        <v>1767076.707029265</v>
+        <v>1727808.334463288</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
       </c>
       <c r="Q19" t="n">
-        <v>2160000</v>
+        <v>2112000</v>
       </c>
     </row>
     <row r="20">
@@ -1193,10 +1193,10 @@
         <v>36</v>
       </c>
       <c r="N20" t="n">
-        <v>11491.09631068</v>
+        <v>11955.383030303</v>
       </c>
       <c r="O20" t="n">
-        <v>413679.46718448</v>
+        <v>430393.789090908</v>
       </c>
       <c r="P20" t="n">
         <v>23000</v>
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.6282352941</v>
+        <v>3933.7680473373</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.2729411743</v>
+        <v>483853.4698224879</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -1869,10 +1869,10 @@
         <v>6</v>
       </c>
       <c r="N37" t="n">
-        <v>33582</v>
+        <v>36634.909090909</v>
       </c>
       <c r="O37" t="n">
-        <v>201492</v>
+        <v>219809.454545454</v>
       </c>
       <c r="P37" t="n">
         <v>53900</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.873932292</v>
+        <v>61666.873994709</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.335494804</v>
+        <v>2281674.337804233</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -2533,22 +2533,22 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="N53" t="n">
         <v>2791.02</v>
       </c>
       <c r="O53" t="n">
-        <v>357250.56</v>
+        <v>329340.36</v>
       </c>
       <c r="P53" t="n">
         <v>3900</v>
       </c>
       <c r="Q53" t="n">
-        <v>499200</v>
+        <v>460200</v>
       </c>
     </row>
     <row r="54">
@@ -2960,10 +2960,10 @@
         <v>148</v>
       </c>
       <c r="N63" t="n">
-        <v>1950.2151724138</v>
+        <v>1950.2147262682</v>
       </c>
       <c r="O63" t="n">
-        <v>288631.8455172424</v>
+        <v>288631.7794876936</v>
       </c>
       <c r="P63" t="n">
         <v>2900</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0541801698</v>
+        <v>1098.0548595108</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.501620376</v>
+        <v>131766.583141296</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -3540,10 +3540,10 @@
         <v>108</v>
       </c>
       <c r="N76" t="n">
-        <v>7569</v>
+        <v>7632.3389121339</v>
       </c>
       <c r="O76" t="n">
-        <v>817452</v>
+        <v>824292.6025104611</v>
       </c>
       <c r="P76" t="n">
         <v>12900</v>
@@ -4826,10 +4826,10 @@
         <v>577</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100070547</v>
+        <v>3795.7100070621</v>
       </c>
       <c r="O105" t="n">
-        <v>2190124.674070562</v>
+        <v>2190124.674074832</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
@@ -5005,10 +5005,10 @@
         <v>487</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300462963</v>
+        <v>4890.9300463499</v>
       </c>
       <c r="O109" t="n">
-        <v>2381882.932546298</v>
+        <v>2381882.932572402</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500295421</v>
+        <v>3240.850029985</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003545052</v>
+        <v>388902.0035982</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -6027,10 +6027,10 @@
         <v>1122</v>
       </c>
       <c r="N132" t="n">
-        <v>4372.2107869318</v>
+        <v>4372.2107876031</v>
       </c>
       <c r="O132" t="n">
-        <v>4905620.502937479</v>
+        <v>4905620.503690678</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -6328,22 +6328,22 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M139" t="n">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="N139" t="n">
         <v>6242.93</v>
       </c>
       <c r="O139" t="n">
-        <v>1791720.91</v>
+        <v>1666862.31</v>
       </c>
       <c r="P139" t="n">
         <v>10400</v>
       </c>
       <c r="Q139" t="n">
-        <v>2984800</v>
+        <v>2776800</v>
       </c>
     </row>
     <row r="140">
@@ -7072,10 +7072,10 @@
         <v>126</v>
       </c>
       <c r="N155" t="n">
-        <v>16897</v>
+        <v>17010.976391231</v>
       </c>
       <c r="O155" t="n">
-        <v>2129022</v>
+        <v>2143383.025295106</v>
       </c>
       <c r="P155" t="n">
         <v>27900</v>
@@ -7479,10 +7479,10 @@
         <v>228</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9231064431</v>
+        <v>1630.923147125</v>
       </c>
       <c r="O164" t="n">
-        <v>371850.4682690268</v>
+        <v>371850.4775445</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>96</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1930735465</v>
+        <v>1550.1931350849</v>
       </c>
       <c r="O165" t="n">
-        <v>148818.535060464</v>
+        <v>148818.5409681504</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -8584,10 +8584,10 @@
         <v>93</v>
       </c>
       <c r="N189" t="n">
-        <v>7537.4721481481</v>
+        <v>7537.4721641791</v>
       </c>
       <c r="O189" t="n">
-        <v>700984.9097777733</v>
+        <v>700984.9112686564</v>
       </c>
       <c r="P189" t="n">
         <v>8900</v>
@@ -8912,10 +8912,10 @@
         <v>348</v>
       </c>
       <c r="N197" t="n">
-        <v>2029.8736549708</v>
+        <v>2029.8736782737</v>
       </c>
       <c r="O197" t="n">
-        <v>706396.0319298385</v>
+        <v>706396.0400392476</v>
       </c>
       <c r="P197" t="n">
         <v>3600</v>
@@ -8953,10 +8953,10 @@
         <v>160</v>
       </c>
       <c r="N198" t="n">
-        <v>22485.695904437</v>
+        <v>22511.306036446</v>
       </c>
       <c r="O198" t="n">
-        <v>3597711.34470992</v>
+        <v>3601808.96583136</v>
       </c>
       <c r="P198" t="n">
         <v>36500</v>
@@ -9888,10 +9888,10 @@
         <v>37</v>
       </c>
       <c r="N220" t="n">
-        <v>27123.765241636</v>
+        <v>27123.765232775</v>
       </c>
       <c r="O220" t="n">
-        <v>1003579.313940532</v>
+        <v>1003579.313612675</v>
       </c>
       <c r="P220" t="n">
         <v>44500</v>
@@ -9975,10 +9975,10 @@
         <v>57</v>
       </c>
       <c r="N222" t="n">
-        <v>5431.12</v>
+        <v>5465.2779874214</v>
       </c>
       <c r="O222" t="n">
-        <v>309573.84</v>
+        <v>311520.8452830198</v>
       </c>
       <c r="P222" t="n">
         <v>8900</v>
@@ -10313,10 +10313,10 @@
         <v>180</v>
       </c>
       <c r="N230" t="n">
-        <v>7969.9501649175</v>
+        <v>7987.9139894816</v>
       </c>
       <c r="O230" t="n">
-        <v>1434591.02968515</v>
+        <v>1437824.518106688</v>
       </c>
       <c r="P230" t="n">
         <v>12900</v>
@@ -11452,10 +11452,10 @@
         <v>18</v>
       </c>
       <c r="N255" t="n">
-        <v>15824</v>
+        <v>15908.394666667</v>
       </c>
       <c r="O255" t="n">
-        <v>284832</v>
+        <v>286351.104000006</v>
       </c>
       <c r="P255" t="n">
         <v>26900</v>
@@ -11590,10 +11590,10 @@
         <v>3</v>
       </c>
       <c r="N258" t="n">
-        <v>23521.624776119</v>
+        <v>23878.013030303</v>
       </c>
       <c r="O258" t="n">
-        <v>70564.87432835699</v>
+        <v>71634.03909090899</v>
       </c>
       <c r="P258" t="n">
         <v>39000</v>
@@ -11672,10 +11672,10 @@
         <v>620</v>
       </c>
       <c r="N260" t="n">
-        <v>3486</v>
+        <v>3502.5901249256</v>
       </c>
       <c r="O260" t="n">
-        <v>2161320</v>
+        <v>2171605.877453872</v>
       </c>
       <c r="P260" t="n">
         <v>6900</v>
@@ -11718,10 +11718,10 @@
         <v>1215</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4725489051</v>
+        <v>1786.8332290289</v>
       </c>
       <c r="O261" t="n">
-        <v>2160844.146919697</v>
+        <v>2171002.373270113</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
@@ -13342,10 +13342,10 @@
         <v>104</v>
       </c>
       <c r="N296" t="n">
-        <v>8293</v>
+        <v>8329.2139737991</v>
       </c>
       <c r="O296" t="n">
-        <v>862472</v>
+        <v>866238.2532751064</v>
       </c>
       <c r="P296" t="n">
         <v>13500</v>
@@ -13388,10 +13388,10 @@
         <v>88</v>
       </c>
       <c r="N297" t="n">
-        <v>7713</v>
+        <v>7735.3565217391</v>
       </c>
       <c r="O297" t="n">
-        <v>678744</v>
+        <v>680711.3739130407</v>
       </c>
       <c r="P297" t="n">
         <v>12500</v>
@@ -13520,22 +13520,22 @@
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M300" t="n">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="N300" t="n">
         <v>3424</v>
       </c>
       <c r="O300" t="n">
-        <v>653984</v>
+        <v>585504</v>
       </c>
       <c r="P300" t="n">
         <v>5900</v>
       </c>
       <c r="Q300" t="n">
-        <v>1126900</v>
+        <v>1008900</v>
       </c>
     </row>
     <row r="301">
@@ -14219,10 +14219,10 @@
         <v>504</v>
       </c>
       <c r="N315" t="n">
-        <v>2328.1187507401</v>
+        <v>2328.1187488882</v>
       </c>
       <c r="O315" t="n">
-        <v>1173371.85037301</v>
+        <v>1173371.849439653</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -14633,10 +14633,10 @@
         <v>184</v>
       </c>
       <c r="N324" t="n">
-        <v>4907.8219330289</v>
+        <v>4907.821941896</v>
       </c>
       <c r="O324" t="n">
-        <v>903039.2356773176</v>
+        <v>903039.237308864</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -14679,10 +14679,10 @@
         <v>24</v>
       </c>
       <c r="N325" t="n">
-        <v>6414</v>
+        <v>6426.7641791045</v>
       </c>
       <c r="O325" t="n">
-        <v>153936</v>
+        <v>154242.340298508</v>
       </c>
       <c r="P325" t="n">
         <v>10900</v>
@@ -14863,10 +14863,10 @@
         <v>84</v>
       </c>
       <c r="N329" t="n">
-        <v>3903.7361538462</v>
+        <v>3903.7361658031</v>
       </c>
       <c r="O329" t="n">
-        <v>327913.8369230808</v>
+        <v>327913.8379274604</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -14955,10 +14955,10 @@
         <v>73</v>
       </c>
       <c r="N331" t="n">
-        <v>4202</v>
+        <v>4235.616</v>
       </c>
       <c r="O331" t="n">
-        <v>306746</v>
+        <v>309199.968</v>
       </c>
       <c r="P331" t="n">
         <v>7900</v>
@@ -15047,10 +15047,10 @@
         <v>120</v>
       </c>
       <c r="N333" t="n">
-        <v>2629</v>
+        <v>2655.7582697201</v>
       </c>
       <c r="O333" t="n">
-        <v>315480</v>
+        <v>318690.992366412</v>
       </c>
       <c r="P333" t="n">
         <v>4500</v>
@@ -15139,10 +15139,10 @@
         <v>262</v>
       </c>
       <c r="N335" t="n">
-        <v>5772</v>
+        <v>5789.4673839946</v>
       </c>
       <c r="O335" t="n">
-        <v>1512264</v>
+        <v>1516840.454606585</v>
       </c>
       <c r="P335" t="n">
         <v>9900</v>
@@ -15179,22 +15179,22 @@
         <v>0</v>
       </c>
       <c r="L336" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="M336" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="N336" t="n">
         <v>6268</v>
       </c>
       <c r="O336" t="n">
-        <v>319668</v>
+        <v>0</v>
       </c>
       <c r="P336" t="n">
         <v>10900</v>
       </c>
       <c r="Q336" t="n">
-        <v>555900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -15231,10 +15231,10 @@
         <v>8</v>
       </c>
       <c r="N337" t="n">
-        <v>8637</v>
+        <v>9222.5593220339</v>
       </c>
       <c r="O337" t="n">
-        <v>69096</v>
+        <v>73780.4745762712</v>
       </c>
       <c r="P337" t="n">
         <v>14500</v>
@@ -15323,10 +15323,10 @@
         <v>260</v>
       </c>
       <c r="N339" t="n">
-        <v>6645</v>
+        <v>6663.0865541644</v>
       </c>
       <c r="O339" t="n">
-        <v>1727700</v>
+        <v>1732402.504082744</v>
       </c>
       <c r="P339" t="n">
         <v>10900</v>
@@ -15369,10 +15369,10 @@
         <v>109</v>
       </c>
       <c r="N340" t="n">
-        <v>13098</v>
+        <v>13167.485411141</v>
       </c>
       <c r="O340" t="n">
-        <v>1427682</v>
+        <v>1435255.909814369</v>
       </c>
       <c r="P340" t="n">
         <v>21200</v>
@@ -15461,10 +15461,10 @@
         <v>159</v>
       </c>
       <c r="N342" t="n">
-        <v>3898</v>
+        <v>3913.1437451437</v>
       </c>
       <c r="O342" t="n">
-        <v>619782</v>
+        <v>622189.8554778483</v>
       </c>
       <c r="P342" t="n">
         <v>6900</v>
@@ -15962,10 +15962,10 @@
         <v>84</v>
       </c>
       <c r="N353" t="n">
-        <v>10219</v>
+        <v>10293.773170732</v>
       </c>
       <c r="O353" t="n">
-        <v>858396</v>
+        <v>864676.946341488</v>
       </c>
       <c r="P353" t="n">
         <v>16900</v>
@@ -16054,10 +16054,10 @@
         <v>81</v>
       </c>
       <c r="N355" t="n">
-        <v>27254</v>
+        <v>27323.703324808</v>
       </c>
       <c r="O355" t="n">
-        <v>2207574</v>
+        <v>2213219.969309448</v>
       </c>
       <c r="P355" t="n">
         <v>43900</v>
@@ -16100,10 +16100,10 @@
         <v>60</v>
       </c>
       <c r="N356" t="n">
-        <v>4268.7041295547</v>
+        <v>4268.7044813278</v>
       </c>
       <c r="O356" t="n">
-        <v>256122.247773282</v>
+        <v>256122.268879668</v>
       </c>
       <c r="P356" t="n">
         <v>6900</v>
@@ -16284,10 +16284,10 @@
         <v>256</v>
       </c>
       <c r="N360" t="n">
-        <v>3639.35</v>
+        <v>3659.324478595</v>
       </c>
       <c r="O360" t="n">
-        <v>931673.6</v>
+        <v>936787.06652032</v>
       </c>
       <c r="P360" t="n">
         <v>7500</v>
@@ -16376,10 +16376,10 @@
         <v>27</v>
       </c>
       <c r="N362" t="n">
-        <v>5640</v>
+        <v>5732.1568627451</v>
       </c>
       <c r="O362" t="n">
-        <v>152280</v>
+        <v>154768.2352941177</v>
       </c>
       <c r="P362" t="n">
         <v>9900</v>
@@ -16468,10 +16468,10 @@
         <v>1189</v>
       </c>
       <c r="N364" t="n">
-        <v>3821</v>
+        <v>3828.7583756345</v>
       </c>
       <c r="O364" t="n">
-        <v>4543169</v>
+        <v>4552393.708629421</v>
       </c>
       <c r="P364" t="n">
         <v>5900</v>
@@ -16560,10 +16560,10 @@
         <v>56</v>
       </c>
       <c r="N366" t="n">
-        <v>5476</v>
+        <v>5504.4467532468</v>
       </c>
       <c r="O366" t="n">
-        <v>306656</v>
+        <v>308249.0181818208</v>
       </c>
       <c r="P366" t="n">
         <v>8900</v>
@@ -16606,10 +16606,10 @@
         <v>839</v>
       </c>
       <c r="N367" t="n">
-        <v>1516.0388129219</v>
+        <v>1517.7951815022</v>
       </c>
       <c r="O367" t="n">
-        <v>1271956.564041474</v>
+        <v>1273430.157280346</v>
       </c>
       <c r="P367" t="n">
         <v>2300</v>
@@ -16928,10 +16928,10 @@
         <v>175</v>
       </c>
       <c r="N374" t="n">
-        <v>2944</v>
+        <v>2991.7405405405</v>
       </c>
       <c r="O374" t="n">
-        <v>515200</v>
+        <v>523554.5945945875</v>
       </c>
       <c r="P374" t="n">
         <v>4900</v>
@@ -16969,10 +16969,10 @@
         <v>145</v>
       </c>
       <c r="N375" t="n">
-        <v>2842.2737735849</v>
+        <v>2851.2399369085</v>
       </c>
       <c r="O375" t="n">
-        <v>412129.6971698105</v>
+        <v>413429.7908517325</v>
       </c>
       <c r="P375" t="n">
         <v>4900</v>
@@ -17013,10 +17013,10 @@
         <v>2243</v>
       </c>
       <c r="N376" t="n">
-        <v>692.15206356312</v>
+        <v>692.15208975521</v>
       </c>
       <c r="O376" t="n">
-        <v>1552497.078572078</v>
+        <v>1552497.137320936</v>
       </c>
       <c r="P376" t="n">
         <v>1200</v>
@@ -17353,10 +17353,10 @@
         <v>31</v>
       </c>
       <c r="N383" t="n">
-        <v>2857.22</v>
+        <v>2865.3179310345</v>
       </c>
       <c r="O383" t="n">
-        <v>88573.81999999999</v>
+        <v>88824.8558620695</v>
       </c>
       <c r="P383" t="n">
         <v>4900</v>
@@ -17402,10 +17402,10 @@
         <v>1051</v>
       </c>
       <c r="N384" t="n">
-        <v>8945.379999999999</v>
+        <v>8947.9898847557</v>
       </c>
       <c r="O384" t="n">
-        <v>9401594.379999999</v>
+        <v>9404337.36887824</v>
       </c>
       <c r="P384" t="n">
         <v>14900</v>
@@ -17546,10 +17546,10 @@
         <v>780</v>
       </c>
       <c r="N387" t="n">
-        <v>1530.4499204138</v>
+        <v>1530.4499206034</v>
       </c>
       <c r="O387" t="n">
-        <v>1193750.937922764</v>
+        <v>1193750.938070652</v>
       </c>
       <c r="P387" t="n">
         <v>2600</v>
@@ -17825,10 +17825,10 @@
         <v>114</v>
       </c>
       <c r="N393" t="n">
-        <v>6898.4</v>
+        <v>6979.7970501475</v>
       </c>
       <c r="O393" t="n">
-        <v>786417.6</v>
+        <v>795696.863716815</v>
       </c>
       <c r="P393" t="n">
         <v>12900</v>
@@ -17966,10 +17966,10 @@
         <v>238</v>
       </c>
       <c r="N396" t="n">
-        <v>1690.8700089286</v>
+        <v>1690.8700089526</v>
       </c>
       <c r="O396" t="n">
-        <v>402427.0621250068</v>
+        <v>402427.0621307188</v>
       </c>
       <c r="P396" t="n">
         <v>3000</v>
@@ -18995,10 +18995,10 @@
         <v>2</v>
       </c>
       <c r="N418" t="n">
-        <v>3110.8429819337</v>
+        <v>3110.8429525518</v>
       </c>
       <c r="O418" t="n">
-        <v>6221.6859638674</v>
+        <v>6221.6859051036</v>
       </c>
       <c r="P418" t="n">
         <v>4500</v>
@@ -19929,10 +19929,10 @@
         <v>381</v>
       </c>
       <c r="N438" t="n">
-        <v>1595.5190941049</v>
+        <v>1595.5190882035</v>
       </c>
       <c r="O438" t="n">
-        <v>607892.7748539669</v>
+        <v>607892.7726055335</v>
       </c>
       <c r="P438" t="n">
         <v>2500</v>
@@ -21384,10 +21384,10 @@
         <v>246</v>
       </c>
       <c r="N468" t="n">
-        <v>5347.88</v>
+        <v>5377.3043741403</v>
       </c>
       <c r="O468" t="n">
-        <v>1315578.48</v>
+        <v>1322816.876038514</v>
       </c>
       <c r="P468" t="n">
         <v>7900</v>
@@ -21433,10 +21433,10 @@
         <v>231</v>
       </c>
       <c r="N469" t="n">
-        <v>4578.04</v>
+        <v>4597.9229098806</v>
       </c>
       <c r="O469" t="n">
-        <v>1057527.24</v>
+        <v>1062120.192182419</v>
       </c>
       <c r="P469" t="n">
         <v>7500</v>
@@ -22733,22 +22733,22 @@
         <v>0</v>
       </c>
       <c r="L496" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M496" t="n">
-        <v>1228</v>
+        <v>1216</v>
       </c>
       <c r="N496" t="n">
-        <v>665.32334188034</v>
+        <v>665.32342381786</v>
       </c>
       <c r="O496" t="n">
-        <v>817017.0638290575</v>
+        <v>809033.2833625177</v>
       </c>
       <c r="P496" t="n">
         <v>2900</v>
       </c>
       <c r="Q496" t="n">
-        <v>3561200</v>
+        <v>3526400</v>
       </c>
     </row>
     <row r="497">
@@ -23381,10 +23381,10 @@
         <v>772</v>
       </c>
       <c r="N510" t="n">
-        <v>3181.9</v>
+        <v>3209.0377398721</v>
       </c>
       <c r="O510" t="n">
-        <v>2456426.8</v>
+        <v>2477377.135181261</v>
       </c>
       <c r="P510" t="n">
         <v>5100</v>
@@ -23422,10 +23422,10 @@
         <v>116</v>
       </c>
       <c r="N511" t="n">
-        <v>1213.6821442495</v>
+        <v>1213.6821194605</v>
       </c>
       <c r="O511" t="n">
-        <v>140787.128732942</v>
+        <v>140787.125857418</v>
       </c>
       <c r="P511" t="n">
         <v>1500</v>
@@ -23466,10 +23466,10 @@
         <v>-72</v>
       </c>
       <c r="N512" t="n">
-        <v>1794.2879767875</v>
+        <v>1794.2879750466</v>
       </c>
       <c r="O512" t="n">
-        <v>-129188.7343287</v>
+        <v>-129188.7342033552</v>
       </c>
       <c r="P512" t="n">
         <v>1600</v>
@@ -24846,10 +24846,10 @@
         <v>81</v>
       </c>
       <c r="N542" t="n">
-        <v>1129.14</v>
+        <v>1151.172</v>
       </c>
       <c r="O542" t="n">
-        <v>91460.34000000001</v>
+        <v>93244.932</v>
       </c>
       <c r="P542" t="n">
         <v>6900</v>
@@ -25132,10 +25132,10 @@
         <v>3</v>
       </c>
       <c r="N548" t="n">
-        <v>2432.1341071429</v>
+        <v>2432.1345098039</v>
       </c>
       <c r="O548" t="n">
-        <v>7296.402321428701</v>
+        <v>7296.4035294117</v>
       </c>
       <c r="P548" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.746498645</v>
+        <v>3376.7464976959</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.194704615</v>
+        <v>1982150.194147493</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>2413.0010615711</v>
+        <v>2413.0010626993</v>
       </c>
       <c r="O22" t="n">
-        <v>2413.0010615711</v>
+        <v>2413.0010626993</v>
       </c>
       <c r="P22" t="n">
         <v>4700</v>
@@ -1310,10 +1310,10 @@
         <v>103</v>
       </c>
       <c r="N23" t="n">
-        <v>2474.7042043551</v>
+        <v>2474.7041652614</v>
       </c>
       <c r="O23" t="n">
-        <v>254894.5330485753</v>
+        <v>254894.5290219242</v>
       </c>
       <c r="P23" t="n">
         <v>4500</v>
@@ -1544,10 +1544,10 @@
         <v>62</v>
       </c>
       <c r="N29" t="n">
-        <v>14857.623185841</v>
+        <v>14857.6232</v>
       </c>
       <c r="O29" t="n">
-        <v>921172.6375221419</v>
+        <v>921172.6384000001</v>
       </c>
       <c r="P29" t="n">
         <v>34900</v>
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.6281963928</v>
+        <v>3910.6281927711</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.2681563144</v>
+        <v>481007.2677108453</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.873994709</v>
+        <v>61666.874005305</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.337804233</v>
+        <v>2281674.338196285</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -3047,10 +3047,10 @@
         <v>434</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101611722</v>
+        <v>4937.3101612903</v>
       </c>
       <c r="O65" t="n">
-        <v>2142792.609948735</v>
+        <v>2142792.60999999</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0555939754</v>
+        <v>1098.055952691</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.671277048</v>
+        <v>131766.71432292</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4826,10 +4826,10 @@
         <v>577</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100070621</v>
+        <v>3795.7100070671</v>
       </c>
       <c r="O105" t="n">
-        <v>2190124.674074832</v>
+        <v>2190124.674077717</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
@@ -5005,10 +5005,10 @@
         <v>487</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300464306</v>
+        <v>4890.9300465929</v>
       </c>
       <c r="O109" t="n">
-        <v>2381882.932611702</v>
+        <v>2381882.932690742</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500301659</v>
+        <v>3240.8500302572</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003619908</v>
+        <v>388902.003630864</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5940,10 +5940,10 @@
         <v>501</v>
       </c>
       <c r="N130" t="n">
-        <v>3041.6600126502</v>
+        <v>3041.6600127551</v>
       </c>
       <c r="O130" t="n">
-        <v>1523871.66633775</v>
+        <v>1523871.666390305</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -7479,10 +7479,10 @@
         <v>228</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9231587595</v>
+        <v>1630.9231730968</v>
       </c>
       <c r="O164" t="n">
-        <v>371850.480197166</v>
+        <v>371850.4834660704</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>96</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1931558806</v>
+        <v>1550.193183768</v>
       </c>
       <c r="O165" t="n">
-        <v>148818.5429645376</v>
+        <v>148818.545641728</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -7571,10 +7571,10 @@
         <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>1579.391025</v>
+        <v>1579.3909343434</v>
       </c>
       <c r="O166" t="n">
-        <v>75810.7692</v>
+        <v>75810.7648484832</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -8912,10 +8912,10 @@
         <v>348</v>
       </c>
       <c r="N197" t="n">
-        <v>2029.8737073653</v>
+        <v>2029.8737091988</v>
       </c>
       <c r="O197" t="n">
-        <v>706396.0501631245</v>
+        <v>706396.0508011824</v>
       </c>
       <c r="P197" t="n">
         <v>3600</v>
@@ -9378,10 +9378,10 @@
         <v>609</v>
       </c>
       <c r="N208" t="n">
-        <v>998.76125988546</v>
+        <v>998.76126091703</v>
       </c>
       <c r="O208" t="n">
-        <v>608245.6072702452</v>
+        <v>608245.6078984713</v>
       </c>
       <c r="P208" t="n">
         <v>1600</v>
@@ -9748,7 +9748,7 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>1078</v>
+        <v>1028</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
@@ -9757,19 +9757,19 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>1078</v>
+        <v>1028</v>
       </c>
       <c r="N217" t="n">
         <v>3591.13</v>
       </c>
       <c r="O217" t="n">
-        <v>3871238.14</v>
+        <v>3691681.64</v>
       </c>
       <c r="P217" t="n">
         <v>6300</v>
       </c>
       <c r="Q217" t="n">
-        <v>6791400</v>
+        <v>6476400</v>
       </c>
     </row>
     <row r="218">
@@ -10185,10 +10185,10 @@
         <v>97</v>
       </c>
       <c r="N227" t="n">
-        <v>2568.8355</v>
+        <v>2568.8354697987</v>
       </c>
       <c r="O227" t="n">
-        <v>249177.0435</v>
+        <v>249177.0405704739</v>
       </c>
       <c r="P227" t="n">
         <v>4500</v>
@@ -10585,10 +10585,10 @@
         <v>154</v>
       </c>
       <c r="N236" t="n">
-        <v>548.14725212465</v>
+        <v>548.14724692526</v>
       </c>
       <c r="O236" t="n">
-        <v>84414.67682719609</v>
+        <v>84414.67602649004</v>
       </c>
       <c r="P236" t="n">
         <v>2000</v>
@@ -14032,10 +14032,10 @@
         <v>263</v>
       </c>
       <c r="N311" t="n">
-        <v>2252.2965479115</v>
+        <v>2252.2965559656</v>
       </c>
       <c r="O311" t="n">
-        <v>592353.9921007245</v>
+        <v>592353.9942189528</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
@@ -14633,10 +14633,10 @@
         <v>184</v>
       </c>
       <c r="N324" t="n">
-        <v>4907.8219448698</v>
+        <v>4907.8219751166</v>
       </c>
       <c r="O324" t="n">
-        <v>903039.2378560433</v>
+        <v>903039.2434214543</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -16514,10 +16514,10 @@
         <v>839</v>
       </c>
       <c r="N365" t="n">
-        <v>1516.0388110875</v>
+        <v>1516.0388102832</v>
       </c>
       <c r="O365" t="n">
-        <v>1271956.562502413</v>
+        <v>1271956.561827605</v>
       </c>
       <c r="P365" t="n">
         <v>2300</v>
@@ -16921,10 +16921,10 @@
         <v>2243</v>
       </c>
       <c r="N374" t="n">
-        <v>692.15208975521</v>
+        <v>692.15209736124</v>
       </c>
       <c r="O374" t="n">
-        <v>1552497.137320936</v>
+        <v>1552497.154381261</v>
       </c>
       <c r="P374" t="n">
         <v>1200</v>
@@ -17874,10 +17874,10 @@
         <v>238</v>
       </c>
       <c r="N394" t="n">
-        <v>1690.8700089526</v>
+        <v>1690.8700089606</v>
       </c>
       <c r="O394" t="n">
-        <v>402427.0621307188</v>
+        <v>402427.0621326228</v>
       </c>
       <c r="P394" t="n">
         <v>3000</v>
@@ -18482,10 +18482,10 @@
         <v>45</v>
       </c>
       <c r="N407" t="n">
-        <v>4032.3968542199</v>
+        <v>4032.3968461538</v>
       </c>
       <c r="O407" t="n">
-        <v>181457.8584398955</v>
+        <v>181457.858076921</v>
       </c>
       <c r="P407" t="n">
         <v>4200</v>
@@ -18767,10 +18767,10 @@
         <v>132</v>
       </c>
       <c r="N413" t="n">
-        <v>3259.1342205323</v>
+        <v>3259.1342528736</v>
       </c>
       <c r="O413" t="n">
-        <v>430205.7171102636</v>
+        <v>430205.7213793152</v>
       </c>
       <c r="P413" t="n">
         <v>3600</v>
@@ -18903,10 +18903,10 @@
         <v>2</v>
       </c>
       <c r="N416" t="n">
-        <v>3110.8427709611</v>
+        <v>3110.8426932617</v>
       </c>
       <c r="O416" t="n">
-        <v>6221.6855419222</v>
+        <v>6221.6853865234</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -19277,10 +19277,10 @@
         <v>4</v>
       </c>
       <c r="N424" t="n">
-        <v>2501.3852212389</v>
+        <v>2501.3851351351</v>
       </c>
       <c r="O424" t="n">
-        <v>10005.5408849556</v>
+        <v>10005.5405405404</v>
       </c>
       <c r="P424" t="n">
         <v>4100</v>
@@ -19837,10 +19837,10 @@
         <v>381</v>
       </c>
       <c r="N436" t="n">
-        <v>1595.5155551576</v>
+        <v>1595.5155292429</v>
       </c>
       <c r="O436" t="n">
-        <v>607891.4265150456</v>
+        <v>607891.4166415449</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -21921,10 +21921,10 @@
         <v>152</v>
       </c>
       <c r="N479" t="n">
-        <v>7046.939829932</v>
+        <v>7046.9398298958</v>
       </c>
       <c r="O479" t="n">
-        <v>1071134.854149664</v>
+        <v>1071134.854144162</v>
       </c>
       <c r="P479" t="n">
         <v>9900</v>
@@ -22647,10 +22647,10 @@
         <v>1216</v>
       </c>
       <c r="N494" t="n">
-        <v>665.32343283582</v>
+        <v>665.3234571176</v>
       </c>
       <c r="O494" t="n">
-        <v>809033.2943283571</v>
+        <v>809033.3238550016</v>
       </c>
       <c r="P494" t="n">
         <v>2900</v>
@@ -22889,10 +22889,10 @@
         <v>288</v>
       </c>
       <c r="N499" t="n">
-        <v>430.60997670355</v>
+        <v>430.60997668998</v>
       </c>
       <c r="O499" t="n">
-        <v>124015.6732906224</v>
+        <v>124015.6732867142</v>
       </c>
       <c r="P499" t="n">
         <v>2200</v>
@@ -24079,22 +24079,22 @@
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M526" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="N526" t="n">
         <v>15920</v>
       </c>
       <c r="O526" t="n">
-        <v>684560</v>
+        <v>525360</v>
       </c>
       <c r="P526" t="n">
         <v>19900</v>
       </c>
       <c r="Q526" t="n">
-        <v>855700</v>
+        <v>656700</v>
       </c>
     </row>
     <row r="527">
@@ -25040,10 +25040,10 @@
         <v>3</v>
       </c>
       <c r="N546" t="n">
-        <v>2432.1345544554</v>
+        <v>2432.1346</v>
       </c>
       <c r="O546" t="n">
-        <v>7296.4036633662</v>
+        <v>7296.4038</v>
       </c>
       <c r="P546" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-15</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
         </is>
       </c>
     </row>
@@ -24073,13 +24073,13 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
       </c>
       <c r="L526" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M526" t="n">
         <v>33</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-17</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464976959</v>
+        <v>3376.7464891304</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.194147493</v>
+        <v>1982150.189119545</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -947,22 +947,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14" t="n">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="N14" t="n">
-        <v>1854.2372274143</v>
+        <v>1854.2404977376</v>
       </c>
       <c r="O14" t="n">
-        <v>292969.4819314594</v>
+        <v>107545.9488687808</v>
       </c>
       <c r="P14" t="n">
         <v>3200</v>
       </c>
       <c r="Q14" t="n">
-        <v>505600</v>
+        <v>185600</v>
       </c>
     </row>
     <row r="15">
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8545786963</v>
+        <v>6272.8545933014</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.409507142</v>
+        <v>1794036.4136842</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1151,10 +1151,10 @@
         <v>440</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8371237802</v>
+        <v>3926.8371059432</v>
       </c>
       <c r="O19" t="n">
-        <v>1727808.334463288</v>
+        <v>1727808.326615008</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>2413.0010626993</v>
+        <v>2413.0010683761</v>
       </c>
       <c r="O22" t="n">
-        <v>2413.0010626993</v>
+        <v>2413.0010683761</v>
       </c>
       <c r="P22" t="n">
         <v>4700</v>
@@ -1388,10 +1388,10 @@
         <v>48</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301892744</v>
+        <v>3716.3301923077</v>
       </c>
       <c r="O25" t="n">
-        <v>178383.8490851712</v>
+        <v>178383.8492307696</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.6281927711</v>
+        <v>3910.6281818182</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.2677108453</v>
+        <v>481007.2663636386</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.874005305</v>
+        <v>61666.874015957</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.338196285</v>
+        <v>2281674.338590409</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -2960,10 +2960,10 @@
         <v>148</v>
       </c>
       <c r="N63" t="n">
-        <v>1950.2147262682</v>
+        <v>1950.2147103275</v>
       </c>
       <c r="O63" t="n">
-        <v>288631.7794876936</v>
+        <v>288631.77712847</v>
       </c>
       <c r="P63" t="n">
         <v>2900</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.055952691</v>
+        <v>1098.0561100153</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.71432292</v>
+        <v>131766.733201836</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4323,22 +4323,22 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M94" t="n">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="N94" t="n">
         <v>3154</v>
       </c>
       <c r="O94" t="n">
-        <v>1002972</v>
+        <v>939892</v>
       </c>
       <c r="P94" t="n">
         <v>5500</v>
       </c>
       <c r="Q94" t="n">
-        <v>1749000</v>
+        <v>1639000</v>
       </c>
     </row>
     <row r="95">
@@ -4826,10 +4826,10 @@
         <v>577</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100070671</v>
+        <v>3795.7100070822</v>
       </c>
       <c r="O105" t="n">
-        <v>2190124.674077717</v>
+        <v>2190124.674086429</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
@@ -5005,10 +5005,10 @@
         <v>487</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300465929</v>
+        <v>4890.9300467563</v>
       </c>
       <c r="O109" t="n">
-        <v>2381882.932690742</v>
+        <v>2381882.932770318</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500302572</v>
+        <v>3240.8500303951</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003630864</v>
+        <v>388902.003647412</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5715,22 +5715,22 @@
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M125" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N125" t="n">
         <v>12267.65043956</v>
       </c>
       <c r="O125" t="n">
-        <v>196282.40703296</v>
+        <v>171747.10615384</v>
       </c>
       <c r="P125" t="n">
         <v>19900</v>
       </c>
       <c r="Q125" t="n">
-        <v>318400</v>
+        <v>278600</v>
       </c>
     </row>
     <row r="126">
@@ -5940,10 +5940,10 @@
         <v>501</v>
       </c>
       <c r="N130" t="n">
-        <v>3041.6600127551</v>
+        <v>3041.6600128617</v>
       </c>
       <c r="O130" t="n">
-        <v>1523871.666390305</v>
+        <v>1523871.666443712</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -6027,10 +6027,10 @@
         <v>1122</v>
       </c>
       <c r="N132" t="n">
-        <v>4372.2107877711</v>
+        <v>4372.2107879391</v>
       </c>
       <c r="O132" t="n">
-        <v>4905620.503879174</v>
+        <v>4905620.50406767</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -7479,10 +7479,10 @@
         <v>228</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9231730968</v>
+        <v>1630.9233118002</v>
       </c>
       <c r="O164" t="n">
-        <v>371850.4834660704</v>
+        <v>371850.5150904456</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>96</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.193183768</v>
+        <v>1550.1933219945</v>
       </c>
       <c r="O165" t="n">
-        <v>148818.545641728</v>
+        <v>148818.558911472</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -7571,10 +7571,10 @@
         <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>1579.3909343434</v>
+        <v>1579.3908883249</v>
       </c>
       <c r="O166" t="n">
-        <v>75810.7648484832</v>
+        <v>75810.7626395952</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -7732,22 +7732,22 @@
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M170" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="N170" t="n">
         <v>2069.4652683897</v>
       </c>
       <c r="O170" t="n">
-        <v>910564.7180914681</v>
+        <v>869175.4127236741</v>
       </c>
       <c r="P170" t="n">
         <v>6500</v>
       </c>
       <c r="Q170" t="n">
-        <v>2860000</v>
+        <v>2730000</v>
       </c>
     </row>
     <row r="171">
@@ -9332,10 +9332,10 @@
         <v>24</v>
       </c>
       <c r="N207" t="n">
-        <v>3731.0243377483</v>
+        <v>3731.0243521595</v>
       </c>
       <c r="O207" t="n">
-        <v>89544.58410595919</v>
+        <v>89544.58445182799</v>
       </c>
       <c r="P207" t="n">
         <v>5200</v>
@@ -10585,10 +10585,10 @@
         <v>154</v>
       </c>
       <c r="N236" t="n">
-        <v>548.14724692526</v>
+        <v>548.14724170616</v>
       </c>
       <c r="O236" t="n">
-        <v>84414.67602649004</v>
+        <v>84414.67522274864</v>
       </c>
       <c r="P236" t="n">
         <v>2000</v>
@@ -11718,10 +11718,10 @@
         <v>1215</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4725680247</v>
+        <v>1778.4725740823</v>
       </c>
       <c r="O261" t="n">
-        <v>2160844.17015001</v>
+        <v>2160844.177509995</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
@@ -14633,10 +14633,10 @@
         <v>184</v>
       </c>
       <c r="N324" t="n">
-        <v>4907.8219751166</v>
+        <v>4907.8219812793</v>
       </c>
       <c r="O324" t="n">
-        <v>903039.2434214543</v>
+        <v>903039.2445553913</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -16514,10 +16514,10 @@
         <v>839</v>
       </c>
       <c r="N365" t="n">
-        <v>1516.0388102832</v>
+        <v>1516.0388052024</v>
       </c>
       <c r="O365" t="n">
-        <v>1271956.561827605</v>
+        <v>1271956.557564814</v>
       </c>
       <c r="P365" t="n">
         <v>2300</v>
@@ -16921,10 +16921,10 @@
         <v>2243</v>
       </c>
       <c r="N374" t="n">
-        <v>692.15209736124</v>
+        <v>692.15211662075</v>
       </c>
       <c r="O374" t="n">
-        <v>1552497.154381261</v>
+        <v>1552497.197580342</v>
       </c>
       <c r="P374" t="n">
         <v>1200</v>
@@ -17454,10 +17454,10 @@
         <v>780</v>
       </c>
       <c r="N385" t="n">
-        <v>1530.4499206034</v>
+        <v>1530.4499195171</v>
       </c>
       <c r="O385" t="n">
-        <v>1193750.938070652</v>
+        <v>1193750.937223338</v>
       </c>
       <c r="P385" t="n">
         <v>2600</v>
@@ -17874,10 +17874,10 @@
         <v>238</v>
       </c>
       <c r="N394" t="n">
-        <v>1690.8700089606</v>
+        <v>1690.8700089847</v>
       </c>
       <c r="O394" t="n">
-        <v>402427.0621326228</v>
+        <v>402427.0621383586</v>
       </c>
       <c r="P394" t="n">
         <v>3000</v>
@@ -18021,10 +18021,10 @@
         <v>47</v>
       </c>
       <c r="N397" t="n">
-        <v>2270.3211494253</v>
+        <v>2270.3211627907</v>
       </c>
       <c r="O397" t="n">
-        <v>106705.0940229891</v>
+        <v>106705.0946511629</v>
       </c>
       <c r="P397" t="n">
         <v>3900</v>
@@ -18903,10 +18903,10 @@
         <v>2</v>
       </c>
       <c r="N416" t="n">
-        <v>3110.8426932617</v>
+        <v>3110.8426185007</v>
       </c>
       <c r="O416" t="n">
-        <v>6221.6853865234</v>
+        <v>6221.6852370014</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -19837,10 +19837,10 @@
         <v>381</v>
       </c>
       <c r="N436" t="n">
-        <v>1595.5155292429</v>
+        <v>1595.5153131828</v>
       </c>
       <c r="O436" t="n">
-        <v>607891.4166415449</v>
+        <v>607891.3343226467</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -19981,10 +19981,10 @@
         <v>73</v>
       </c>
       <c r="N439" t="n">
-        <v>2098.4049147727</v>
+        <v>2098.4049570201</v>
       </c>
       <c r="O439" t="n">
-        <v>153183.5587784071</v>
+        <v>153183.5618624673</v>
       </c>
       <c r="P439" t="n">
         <v>9500</v>
@@ -21090,22 +21090,22 @@
         <v>0</v>
       </c>
       <c r="L462" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M462" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N462" t="n">
         <v>27577.72</v>
       </c>
       <c r="O462" t="n">
-        <v>248199.48</v>
+        <v>193044.04</v>
       </c>
       <c r="P462" t="n">
         <v>120900</v>
       </c>
       <c r="Q462" t="n">
-        <v>1088100</v>
+        <v>846300</v>
       </c>
     </row>
     <row r="463">
@@ -21673,22 +21673,22 @@
         <v>0</v>
       </c>
       <c r="L474" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M474" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N474" t="n">
         <v>11939.92</v>
       </c>
       <c r="O474" t="n">
-        <v>131339.12</v>
+        <v>59699.6</v>
       </c>
       <c r="P474" t="n">
         <v>25900</v>
       </c>
       <c r="Q474" t="n">
-        <v>284900</v>
+        <v>129500</v>
       </c>
     </row>
     <row r="475">
@@ -21921,10 +21921,10 @@
         <v>152</v>
       </c>
       <c r="N479" t="n">
-        <v>7046.9398298958</v>
+        <v>7046.9398286204</v>
       </c>
       <c r="O479" t="n">
-        <v>1071134.854144162</v>
+        <v>1071134.853950301</v>
       </c>
       <c r="P479" t="n">
         <v>9900</v>
@@ -22647,10 +22647,10 @@
         <v>1216</v>
       </c>
       <c r="N494" t="n">
-        <v>665.3234571176</v>
+        <v>665.32347555556</v>
       </c>
       <c r="O494" t="n">
-        <v>809033.3238550016</v>
+        <v>809033.3462755609</v>
       </c>
       <c r="P494" t="n">
         <v>2900</v>
@@ -23507,10 +23507,10 @@
         <v>11</v>
       </c>
       <c r="N513" t="n">
-        <v>22951.704968711</v>
+        <v>22951.704962406</v>
       </c>
       <c r="O513" t="n">
-        <v>252468.754655821</v>
+        <v>252468.754586466</v>
       </c>
       <c r="P513" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
         </is>
       </c>
     </row>
@@ -941,13 +941,13 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>58</v>
@@ -4317,13 +4317,13 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>298</v>
@@ -5709,13 +5709,13 @@
         </is>
       </c>
       <c r="J125" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
       </c>
       <c r="L125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
         <v>14</v>
@@ -7726,13 +7726,13 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="K170" t="n">
         <v>0</v>
       </c>
       <c r="L170" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M170" t="n">
         <v>420</v>
@@ -21084,13 +21084,13 @@
         </is>
       </c>
       <c r="J462" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K462" t="n">
         <v>0</v>
       </c>
       <c r="L462" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M462" t="n">
         <v>7</v>
@@ -21667,13 +21667,13 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
       </c>
       <c r="L474" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M474" t="n">
         <v>5</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1388,10 +1388,10 @@
         <v>48</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301923077</v>
+        <v>3716.3301935484</v>
       </c>
       <c r="O25" t="n">
-        <v>178383.8492307696</v>
+        <v>178383.8492903232</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -2960,10 +2960,10 @@
         <v>148</v>
       </c>
       <c r="N63" t="n">
-        <v>1950.2147103275</v>
+        <v>1950.21469429</v>
       </c>
       <c r="O63" t="n">
-        <v>288631.77712847</v>
+        <v>288631.77475492</v>
       </c>
       <c r="P63" t="n">
         <v>2900</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0561100153</v>
+        <v>1098.0566124294</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.733201836</v>
+        <v>131766.793491528</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4820,22 +4820,22 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M105" t="n">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100070822</v>
+        <v>3795.7100070872</v>
       </c>
       <c r="O105" t="n">
-        <v>2190124.674086429</v>
+        <v>2182533.25407514</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
       </c>
       <c r="Q105" t="n">
-        <v>3577400</v>
+        <v>3565000</v>
       </c>
     </row>
     <row r="106">
@@ -4953,22 +4953,22 @@
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="M108" t="n">
-        <v>616</v>
+        <v>540</v>
       </c>
       <c r="N108" t="n">
         <v>4357.55</v>
       </c>
       <c r="O108" t="n">
-        <v>2684250.8</v>
+        <v>2353077</v>
       </c>
       <c r="P108" t="n">
         <v>7500</v>
       </c>
       <c r="Q108" t="n">
-        <v>4620000</v>
+        <v>4050000</v>
       </c>
     </row>
     <row r="109">
@@ -5005,10 +5005,10 @@
         <v>487</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300467563</v>
+        <v>4890.9300468384</v>
       </c>
       <c r="O109" t="n">
-        <v>2381882.932770318</v>
+        <v>2381882.932810301</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500303951</v>
+        <v>3240.8500305344</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003647412</v>
+        <v>388902.003664128</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5940,10 +5940,10 @@
         <v>501</v>
       </c>
       <c r="N130" t="n">
-        <v>3041.6600128617</v>
+        <v>3041.660012945</v>
       </c>
       <c r="O130" t="n">
-        <v>1523871.666443712</v>
+        <v>1523871.666485445</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -7110,22 +7110,22 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M156" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="N156" t="n">
         <v>8341.030000000001</v>
       </c>
       <c r="O156" t="n">
-        <v>708987.55</v>
+        <v>583872.1000000001</v>
       </c>
       <c r="P156" t="n">
         <v>13900</v>
       </c>
       <c r="Q156" t="n">
-        <v>1181500</v>
+        <v>973000</v>
       </c>
     </row>
     <row r="157">
@@ -7479,10 +7479,10 @@
         <v>228</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9233118002</v>
+        <v>1630.9233376736</v>
       </c>
       <c r="O164" t="n">
-        <v>371850.5150904456</v>
+        <v>371850.5209895808</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>96</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1933219945</v>
+        <v>1550.1933547279</v>
       </c>
       <c r="O165" t="n">
-        <v>148818.558911472</v>
+        <v>148818.5620538784</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -7571,10 +7571,10 @@
         <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>1579.3908883249</v>
+        <v>1579.3908418367</v>
       </c>
       <c r="O166" t="n">
-        <v>75810.7626395952</v>
+        <v>75810.7604081616</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -8912,10 +8912,10 @@
         <v>348</v>
       </c>
       <c r="N197" t="n">
-        <v>2029.8737091988</v>
+        <v>2029.8737110341</v>
       </c>
       <c r="O197" t="n">
-        <v>706396.0508011824</v>
+        <v>706396.0514398669</v>
       </c>
       <c r="P197" t="n">
         <v>3600</v>
@@ -11020,22 +11020,22 @@
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M246" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="N246" t="n">
         <v>7700</v>
       </c>
       <c r="O246" t="n">
-        <v>839300</v>
+        <v>746900</v>
       </c>
       <c r="P246" t="n">
         <v>13900</v>
       </c>
       <c r="Q246" t="n">
-        <v>1515100</v>
+        <v>1348300</v>
       </c>
     </row>
     <row r="247">
@@ -11590,10 +11590,10 @@
         <v>3</v>
       </c>
       <c r="N258" t="n">
-        <v>23521.62453125</v>
+        <v>23521.624354839</v>
       </c>
       <c r="O258" t="n">
-        <v>70564.87359375</v>
+        <v>70564.873064517</v>
       </c>
       <c r="P258" t="n">
         <v>39000</v>
@@ -11718,10 +11718,10 @@
         <v>1215</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4725740823</v>
+        <v>1778.4725809313</v>
       </c>
       <c r="O261" t="n">
-        <v>2160844.177509995</v>
+        <v>2160844.18583153</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
@@ -14219,10 +14219,10 @@
         <v>504</v>
       </c>
       <c r="N315" t="n">
-        <v>2328.1187488882</v>
+        <v>2328.118739546</v>
       </c>
       <c r="O315" t="n">
-        <v>1173371.849439653</v>
+        <v>1173371.844731184</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -14863,10 +14863,10 @@
         <v>84</v>
       </c>
       <c r="N329" t="n">
-        <v>3903.7362017804</v>
+        <v>3903.736812933</v>
       </c>
       <c r="O329" t="n">
-        <v>327913.8409495536</v>
+        <v>327913.892286372</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -16008,10 +16008,10 @@
         <v>60</v>
       </c>
       <c r="N354" t="n">
-        <v>4268.7047257384</v>
+        <v>4268.7051082251</v>
       </c>
       <c r="O354" t="n">
-        <v>256122.283544304</v>
+        <v>256122.306493506</v>
       </c>
       <c r="P354" t="n">
         <v>6900</v>
@@ -16921,10 +16921,10 @@
         <v>2243</v>
       </c>
       <c r="N374" t="n">
-        <v>692.15211662075</v>
+        <v>692.1521205151799</v>
       </c>
       <c r="O374" t="n">
-        <v>1552497.197580342</v>
+        <v>1552497.206315549</v>
       </c>
       <c r="P374" t="n">
         <v>1200</v>
@@ -17868,22 +17868,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M394" t="n">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="N394" t="n">
-        <v>1690.8700089847</v>
+        <v>1690.870009009</v>
       </c>
       <c r="O394" t="n">
-        <v>402427.0621383586</v>
+        <v>351700.961873872</v>
       </c>
       <c r="P394" t="n">
         <v>3000</v>
       </c>
       <c r="Q394" t="n">
-        <v>714000</v>
+        <v>624000</v>
       </c>
     </row>
     <row r="395">
@@ -18903,10 +18903,10 @@
         <v>2</v>
       </c>
       <c r="N416" t="n">
-        <v>3110.8426185007</v>
+        <v>3110.8425641565</v>
       </c>
       <c r="O416" t="n">
-        <v>6221.6852370014</v>
+        <v>6221.685128313</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -19277,10 +19277,10 @@
         <v>4</v>
       </c>
       <c r="N424" t="n">
-        <v>2501.3851351351</v>
+        <v>2501.3850684932</v>
       </c>
       <c r="O424" t="n">
-        <v>10005.5405405404</v>
+        <v>10005.5402739728</v>
       </c>
       <c r="P424" t="n">
         <v>4100</v>
@@ -19837,10 +19837,10 @@
         <v>381</v>
       </c>
       <c r="N436" t="n">
-        <v>1595.5153131828</v>
+        <v>1595.5151400147</v>
       </c>
       <c r="O436" t="n">
-        <v>607891.3343226467</v>
+        <v>607891.2683456007</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -22647,10 +22647,10 @@
         <v>1216</v>
       </c>
       <c r="N494" t="n">
-        <v>665.32347555556</v>
+        <v>665.32351302785</v>
       </c>
       <c r="O494" t="n">
-        <v>809033.3462755609</v>
+        <v>809033.3918418656</v>
       </c>
       <c r="P494" t="n">
         <v>2900</v>
@@ -22889,10 +22889,10 @@
         <v>288</v>
       </c>
       <c r="N499" t="n">
-        <v>430.60997668998</v>
+        <v>430.6099765808</v>
       </c>
       <c r="O499" t="n">
-        <v>124015.6732867142</v>
+        <v>124015.6732552704</v>
       </c>
       <c r="P499" t="n">
         <v>2200</v>
@@ -23507,10 +23507,10 @@
         <v>11</v>
       </c>
       <c r="N513" t="n">
-        <v>22951.704962406</v>
+        <v>22951.704956085</v>
       </c>
       <c r="O513" t="n">
-        <v>252468.754586466</v>
+        <v>252468.754516935</v>
       </c>
       <c r="P513" t="n">
         <v>37900</v>
@@ -25040,10 +25040,10 @@
         <v>3</v>
       </c>
       <c r="N546" t="n">
-        <v>2432.1346</v>
+        <v>2432.1346938776</v>
       </c>
       <c r="O546" t="n">
-        <v>7296.4038</v>
+        <v>7296.4040816328</v>
       </c>
       <c r="P546" t="n">
         <v>4500</v>
@@ -25443,22 +25443,22 @@
         <v>0</v>
       </c>
       <c r="L555" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M555" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="N555" t="n">
         <v>1950.7</v>
       </c>
       <c r="O555" t="n">
-        <v>83880.10000000001</v>
+        <v>64373.1</v>
       </c>
       <c r="P555" t="n">
         <v>7500</v>
       </c>
       <c r="Q555" t="n">
-        <v>322500</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="556">

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-19</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
         </is>
       </c>
     </row>
@@ -4814,13 +4814,13 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>575</v>
@@ -4947,13 +4947,13 @@
         </is>
       </c>
       <c r="J108" t="n">
-        <v>616</v>
+        <v>540</v>
       </c>
       <c r="K108" t="n">
         <v>0</v>
       </c>
       <c r="L108" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
         <v>540</v>
@@ -7104,13 +7104,13 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
         <v>70</v>
@@ -11014,13 +11014,13 @@
         </is>
       </c>
       <c r="J246" t="n">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
         <v>97</v>
@@ -17862,13 +17862,13 @@
         </is>
       </c>
       <c r="J394" t="n">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="K394" t="n">
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M394" t="n">
         <v>208</v>
@@ -25437,13 +25437,13 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
       </c>
       <c r="L555" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M555" t="n">
         <v>33</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -550,22 +550,22 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="N4" t="n">
         <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>1107000</v>
+        <v>999000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
       </c>
       <c r="Q4" t="n">
-        <v>820000</v>
+        <v>740000</v>
       </c>
     </row>
     <row r="5">
@@ -589,22 +589,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="N5" t="n">
         <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>6723000</v>
+        <v>6615000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
       </c>
       <c r="Q5" t="n">
-        <v>4980000</v>
+        <v>4900000</v>
       </c>
     </row>
     <row r="6">
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8545933014</v>
+        <v>6272.854608</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.4136842</v>
+        <v>1794036.417888</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1544,10 +1544,10 @@
         <v>62</v>
       </c>
       <c r="N29" t="n">
-        <v>14857.6232</v>
+        <v>14857.623214286</v>
       </c>
       <c r="O29" t="n">
-        <v>921172.6384000001</v>
+        <v>921172.6392857321</v>
       </c>
       <c r="P29" t="n">
         <v>34900</v>
@@ -2271,22 +2271,22 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M47" t="n">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="N47" t="n">
         <v>3865.67</v>
       </c>
       <c r="O47" t="n">
-        <v>1492148.62</v>
+        <v>1399372.54</v>
       </c>
       <c r="P47" t="n">
         <v>5500</v>
       </c>
       <c r="Q47" t="n">
-        <v>2123000</v>
+        <v>1991000</v>
       </c>
     </row>
     <row r="48">
@@ -2494,22 +2494,22 @@
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M52" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="N52" t="n">
         <v>3114.49</v>
       </c>
       <c r="O52" t="n">
-        <v>657157.3899999999</v>
+        <v>582409.63</v>
       </c>
       <c r="P52" t="n">
         <v>5500</v>
       </c>
       <c r="Q52" t="n">
-        <v>1160500</v>
+        <v>1028500</v>
       </c>
     </row>
     <row r="53">
@@ -2960,10 +2960,10 @@
         <v>148</v>
       </c>
       <c r="N63" t="n">
-        <v>1950.21469429</v>
+        <v>1950.2146835443</v>
       </c>
       <c r="O63" t="n">
-        <v>288631.77475492</v>
+        <v>288631.7731645564</v>
       </c>
       <c r="P63" t="n">
         <v>2900</v>
@@ -3047,10 +3047,10 @@
         <v>434</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101612903</v>
+        <v>4937.3101616458</v>
       </c>
       <c r="O65" t="n">
-        <v>2142792.60999999</v>
+        <v>2142792.610154277</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0566124294</v>
+        <v>1098.0571872808</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.793491528</v>
+        <v>131766.862473696</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4142,10 +4142,10 @@
         <v>53</v>
       </c>
       <c r="N90" t="n">
-        <v>3247</v>
+        <v>3250.4653148346</v>
       </c>
       <c r="O90" t="n">
-        <v>172091</v>
+        <v>172274.6616862338</v>
       </c>
       <c r="P90" t="n">
         <v>5200</v>
@@ -4826,10 +4826,10 @@
         <v>575</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100070872</v>
+        <v>3795.7100071023</v>
       </c>
       <c r="O105" t="n">
-        <v>2182533.25407514</v>
+        <v>2182533.254083822</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
@@ -4999,22 +4999,22 @@
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M109" t="n">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300468384</v>
+        <v>4890.9300473934</v>
       </c>
       <c r="O109" t="n">
-        <v>2381882.932810301</v>
+        <v>2284064.332132718</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
       </c>
       <c r="Q109" t="n">
-        <v>3993400</v>
+        <v>3829400</v>
       </c>
     </row>
     <row r="110">
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500305344</v>
+        <v>3240.850030581</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003664128</v>
+        <v>388902.00366972</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5538,10 +5538,10 @@
         <v>135</v>
       </c>
       <c r="N121" t="n">
-        <v>5191.4800270636</v>
+        <v>5191.4800271739</v>
       </c>
       <c r="O121" t="n">
-        <v>700849.803653586</v>
+        <v>700849.8036684765</v>
       </c>
       <c r="P121" t="n">
         <v>9100</v>
@@ -5675,10 +5675,10 @@
         <v>506</v>
       </c>
       <c r="N124" t="n">
-        <v>19098.75000466</v>
+        <v>19098.750004662</v>
       </c>
       <c r="O124" t="n">
-        <v>9663967.50235796</v>
+        <v>9663967.502358973</v>
       </c>
       <c r="P124" t="n">
         <v>15000</v>
@@ -6021,22 +6021,22 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M132" t="n">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="N132" t="n">
-        <v>4372.2107879391</v>
+        <v>4372.210788556</v>
       </c>
       <c r="O132" t="n">
-        <v>4905620.50406767</v>
+        <v>4879387.240028496</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
       </c>
       <c r="Q132" t="n">
-        <v>8415000</v>
+        <v>8370000</v>
       </c>
     </row>
     <row r="133">
@@ -6606,22 +6606,22 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M145" t="n">
-        <v>2595</v>
+        <v>2575</v>
       </c>
       <c r="N145" t="n">
         <v>17472.91</v>
       </c>
       <c r="O145" t="n">
-        <v>45342201.45</v>
+        <v>44992743.25</v>
       </c>
       <c r="P145" t="n">
         <v>2900</v>
       </c>
       <c r="Q145" t="n">
-        <v>7525500</v>
+        <v>7467500</v>
       </c>
     </row>
     <row r="146">
@@ -6650,22 +6650,22 @@
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M146" t="n">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="N146" t="n">
         <v>1343.77</v>
       </c>
       <c r="O146" t="n">
-        <v>3198172.6</v>
+        <v>3171297.2</v>
       </c>
       <c r="P146" t="n">
         <v>2500</v>
       </c>
       <c r="Q146" t="n">
-        <v>5950000</v>
+        <v>5900000</v>
       </c>
     </row>
     <row r="147">
@@ -6694,22 +6694,22 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M147" t="n">
-        <v>2680</v>
+        <v>2660</v>
       </c>
       <c r="N147" t="n">
         <v>1530.63</v>
       </c>
       <c r="O147" t="n">
-        <v>4102088.4</v>
+        <v>4071475.8</v>
       </c>
       <c r="P147" t="n">
         <v>2900</v>
       </c>
       <c r="Q147" t="n">
-        <v>7772000</v>
+        <v>7714000</v>
       </c>
     </row>
     <row r="148">
@@ -6738,22 +6738,22 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M148" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="N148" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O148" t="n">
-        <v>593101.5299999999</v>
+        <v>555444.2899999999</v>
       </c>
       <c r="P148" t="n">
         <v>16900</v>
       </c>
       <c r="Q148" t="n">
-        <v>1064700</v>
+        <v>997100</v>
       </c>
     </row>
     <row r="149">
@@ -7066,22 +7066,22 @@
         <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M155" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="N155" t="n">
         <v>16897</v>
       </c>
       <c r="O155" t="n">
-        <v>2129022</v>
+        <v>1960052</v>
       </c>
       <c r="P155" t="n">
         <v>27900</v>
       </c>
       <c r="Q155" t="n">
-        <v>3515400</v>
+        <v>3236400</v>
       </c>
     </row>
     <row r="156">
@@ -7110,22 +7110,22 @@
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M156" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N156" t="n">
         <v>8341.030000000001</v>
       </c>
       <c r="O156" t="n">
-        <v>583872.1000000001</v>
+        <v>550507.9800000001</v>
       </c>
       <c r="P156" t="n">
         <v>13900</v>
       </c>
       <c r="Q156" t="n">
-        <v>973000</v>
+        <v>917400</v>
       </c>
     </row>
     <row r="157">
@@ -7479,10 +7479,10 @@
         <v>228</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9233376736</v>
+        <v>1630.9233676374</v>
       </c>
       <c r="O164" t="n">
-        <v>371850.5209895808</v>
+        <v>371850.5278213272</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>96</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1933547279</v>
+        <v>1550.1933908991</v>
       </c>
       <c r="O165" t="n">
-        <v>148818.5620538784</v>
+        <v>148818.5655263136</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -8584,10 +8584,10 @@
         <v>93</v>
       </c>
       <c r="N189" t="n">
-        <v>7537.4721804511</v>
+        <v>7537.4721969697</v>
       </c>
       <c r="O189" t="n">
-        <v>700984.9127819523</v>
+        <v>700984.9143181822</v>
       </c>
       <c r="P189" t="n">
         <v>8900</v>
@@ -8625,10 +8625,10 @@
         <v>1</v>
       </c>
       <c r="N190" t="n">
-        <v>2661.82</v>
+        <v>2679.7246188341</v>
       </c>
       <c r="O190" t="n">
-        <v>2661.82</v>
+        <v>2679.7246188341</v>
       </c>
       <c r="P190" t="n">
         <v>3200</v>
@@ -8660,22 +8660,22 @@
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M191" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="N191" t="n">
         <v>8456</v>
       </c>
       <c r="O191" t="n">
-        <v>295960</v>
+        <v>245224</v>
       </c>
       <c r="P191" t="n">
         <v>8900</v>
       </c>
       <c r="Q191" t="n">
-        <v>311500</v>
+        <v>258100</v>
       </c>
     </row>
     <row r="192">
@@ -8748,10 +8748,10 @@
         <v>195</v>
       </c>
       <c r="N193" t="n">
-        <v>8794.48</v>
+        <v>8799.395863611</v>
       </c>
       <c r="O193" t="n">
-        <v>1714923.6</v>
+        <v>1715882.193404145</v>
       </c>
       <c r="P193" t="n">
         <v>14500</v>
@@ -8912,10 +8912,10 @@
         <v>348</v>
       </c>
       <c r="N197" t="n">
-        <v>2029.8737110341</v>
+        <v>2029.8737332006</v>
       </c>
       <c r="O197" t="n">
-        <v>706396.0514398669</v>
+        <v>706396.0591538089</v>
       </c>
       <c r="P197" t="n">
         <v>3600</v>
@@ -9245,10 +9245,10 @@
         <v>237</v>
       </c>
       <c r="N205" t="n">
-        <v>1732.9153666245</v>
+        <v>1733.4632374328</v>
       </c>
       <c r="O205" t="n">
-        <v>410700.9418900065</v>
+        <v>410830.7872715736</v>
       </c>
       <c r="P205" t="n">
         <v>1900</v>
@@ -9754,22 +9754,22 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M217" t="n">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="N217" t="n">
         <v>3591.13</v>
       </c>
       <c r="O217" t="n">
-        <v>3691681.64</v>
+        <v>3637814.69</v>
       </c>
       <c r="P217" t="n">
         <v>6300</v>
       </c>
       <c r="Q217" t="n">
-        <v>6476400</v>
+        <v>6381900</v>
       </c>
     </row>
     <row r="218">
@@ -10138,22 +10138,22 @@
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M226" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="N226" t="n">
         <v>6925.19</v>
       </c>
       <c r="O226" t="n">
-        <v>470912.92</v>
+        <v>401661.02</v>
       </c>
       <c r="P226" t="n">
         <v>12800</v>
       </c>
       <c r="Q226" t="n">
-        <v>870400</v>
+        <v>742400</v>
       </c>
     </row>
     <row r="227">
@@ -10313,10 +10313,10 @@
         <v>180</v>
       </c>
       <c r="N230" t="n">
-        <v>7969.9501652893</v>
+        <v>7969.9501660377</v>
       </c>
       <c r="O230" t="n">
-        <v>1434591.029752074</v>
+        <v>1434591.029886786</v>
       </c>
       <c r="P230" t="n">
         <v>12900</v>
@@ -10980,10 +10980,10 @@
         <v>119</v>
       </c>
       <c r="N245" t="n">
-        <v>3590.77</v>
+        <v>3656.0567272727</v>
       </c>
       <c r="O245" t="n">
-        <v>427301.63</v>
+        <v>435070.7505454513</v>
       </c>
       <c r="P245" t="n">
         <v>3900</v>
@@ -11538,22 +11538,22 @@
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M257" t="n">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="N257" t="n">
         <v>3646</v>
       </c>
       <c r="O257" t="n">
-        <v>809412</v>
+        <v>721908</v>
       </c>
       <c r="P257" t="n">
         <v>6900</v>
       </c>
       <c r="Q257" t="n">
-        <v>1531800</v>
+        <v>1366200</v>
       </c>
     </row>
     <row r="258">
@@ -11590,10 +11590,10 @@
         <v>3</v>
       </c>
       <c r="N258" t="n">
-        <v>23521.624354839</v>
+        <v>23521.624262295</v>
       </c>
       <c r="O258" t="n">
-        <v>70564.873064517</v>
+        <v>70564.87278688501</v>
       </c>
       <c r="P258" t="n">
         <v>39000</v>
@@ -11712,22 +11712,22 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="M261" t="n">
-        <v>1215</v>
+        <v>1111</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4725809313</v>
+        <v>1778.4725908889</v>
       </c>
       <c r="O261" t="n">
-        <v>2160844.18583153</v>
+        <v>1975883.048477568</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
       </c>
       <c r="Q261" t="n">
-        <v>5953500</v>
+        <v>5443900</v>
       </c>
     </row>
     <row r="262">
@@ -12640,22 +12640,22 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M281" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="N281" t="n">
         <v>15851.09</v>
       </c>
       <c r="O281" t="n">
-        <v>253617.44</v>
+        <v>174361.99</v>
       </c>
       <c r="P281" t="n">
         <v>19900</v>
       </c>
       <c r="Q281" t="n">
-        <v>318400</v>
+        <v>218900</v>
       </c>
     </row>
     <row r="282">
@@ -13244,22 +13244,22 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M294" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="N294" t="n">
         <v>13687</v>
       </c>
       <c r="O294" t="n">
-        <v>1040212</v>
+        <v>903342</v>
       </c>
       <c r="P294" t="n">
         <v>21900</v>
       </c>
       <c r="Q294" t="n">
-        <v>1664400</v>
+        <v>1445400</v>
       </c>
     </row>
     <row r="295">
@@ -13750,22 +13750,22 @@
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M305" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="N305" t="n">
         <v>8858.16</v>
       </c>
       <c r="O305" t="n">
-        <v>3242086.56</v>
+        <v>3188937.6</v>
       </c>
       <c r="P305" t="n">
         <v>15500</v>
       </c>
       <c r="Q305" t="n">
-        <v>5673000</v>
+        <v>5580000</v>
       </c>
     </row>
     <row r="306">
@@ -14032,10 +14032,10 @@
         <v>263</v>
       </c>
       <c r="N311" t="n">
-        <v>2252.2965559656</v>
+        <v>2252.2966541823</v>
       </c>
       <c r="O311" t="n">
-        <v>592353.9942189528</v>
+        <v>592354.0200499449</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
@@ -14219,10 +14219,10 @@
         <v>504</v>
       </c>
       <c r="N315" t="n">
-        <v>2328.118739546</v>
+        <v>2328.1187258454</v>
       </c>
       <c r="O315" t="n">
-        <v>1173371.844731184</v>
+        <v>1173371.837826082</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -14351,22 +14351,22 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M318" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="N318" t="n">
         <v>9003</v>
       </c>
       <c r="O318" t="n">
-        <v>513171</v>
+        <v>423141</v>
       </c>
       <c r="P318" t="n">
         <v>14900</v>
       </c>
       <c r="Q318" t="n">
-        <v>849300</v>
+        <v>700300</v>
       </c>
     </row>
     <row r="319">
@@ -14489,22 +14489,22 @@
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M321" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="N321" t="n">
         <v>13922</v>
       </c>
       <c r="O321" t="n">
-        <v>1475732</v>
+        <v>1433966</v>
       </c>
       <c r="P321" t="n">
         <v>22900</v>
       </c>
       <c r="Q321" t="n">
-        <v>2427400</v>
+        <v>2358700</v>
       </c>
     </row>
     <row r="322">
@@ -14541,10 +14541,10 @@
         <v>85</v>
       </c>
       <c r="N322" t="n">
-        <v>3396.38</v>
+        <v>3418.6270305677</v>
       </c>
       <c r="O322" t="n">
-        <v>288692.3</v>
+        <v>290583.2975982545</v>
       </c>
       <c r="P322" t="n">
         <v>6500</v>
@@ -14633,10 +14633,10 @@
         <v>184</v>
       </c>
       <c r="N324" t="n">
-        <v>4907.8219812793</v>
+        <v>4907.8220190779</v>
       </c>
       <c r="O324" t="n">
-        <v>903039.2445553913</v>
+        <v>903039.2515103336</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -14719,22 +14719,22 @@
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M326" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N326" t="n">
         <v>4240</v>
       </c>
       <c r="O326" t="n">
-        <v>610560</v>
+        <v>568160</v>
       </c>
       <c r="P326" t="n">
         <v>7300</v>
       </c>
       <c r="Q326" t="n">
-        <v>1051200</v>
+        <v>978200</v>
       </c>
     </row>
     <row r="327">
@@ -14863,10 +14863,10 @@
         <v>84</v>
       </c>
       <c r="N329" t="n">
-        <v>3903.736812933</v>
+        <v>3903.7361538462</v>
       </c>
       <c r="O329" t="n">
-        <v>327913.892286372</v>
+        <v>327913.8369230808</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -15047,10 +15047,10 @@
         <v>120</v>
       </c>
       <c r="N333" t="n">
-        <v>2629</v>
+        <v>2637.9574105622</v>
       </c>
       <c r="O333" t="n">
-        <v>315480</v>
+        <v>316554.889267464</v>
       </c>
       <c r="P333" t="n">
         <v>4500</v>
@@ -15139,10 +15139,10 @@
         <v>262</v>
       </c>
       <c r="N335" t="n">
-        <v>5772</v>
+        <v>5775.9026369168</v>
       </c>
       <c r="O335" t="n">
-        <v>1512264</v>
+        <v>1513286.490872202</v>
       </c>
       <c r="P335" t="n">
         <v>9900</v>
@@ -15415,10 +15415,10 @@
         <v>159</v>
       </c>
       <c r="N341" t="n">
-        <v>3898</v>
+        <v>3904.1097178683</v>
       </c>
       <c r="O341" t="n">
-        <v>619782</v>
+        <v>620753.4451410597</v>
       </c>
       <c r="P341" t="n">
         <v>6900</v>
@@ -15547,22 +15547,22 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M344" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N344" t="n">
         <v>11348</v>
       </c>
       <c r="O344" t="n">
-        <v>1282324</v>
+        <v>1236932</v>
       </c>
       <c r="P344" t="n">
         <v>19900</v>
       </c>
       <c r="Q344" t="n">
-        <v>2248700</v>
+        <v>2169100</v>
       </c>
     </row>
     <row r="345">
@@ -16514,10 +16514,10 @@
         <v>839</v>
       </c>
       <c r="N365" t="n">
-        <v>1516.0388052024</v>
+        <v>1516.0388047383</v>
       </c>
       <c r="O365" t="n">
-        <v>1271956.557564814</v>
+        <v>1271956.557175434</v>
       </c>
       <c r="P365" t="n">
         <v>2300</v>
@@ -17733,10 +17733,10 @@
         <v>114</v>
       </c>
       <c r="N391" t="n">
-        <v>6898.4</v>
+        <v>6939.3400593472</v>
       </c>
       <c r="O391" t="n">
-        <v>786417.6</v>
+        <v>791084.7667655807</v>
       </c>
       <c r="P391" t="n">
         <v>12900</v>
@@ -17776,22 +17776,22 @@
         <v>0</v>
       </c>
       <c r="L392" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M392" t="n">
-        <v>596</v>
+        <v>556</v>
       </c>
       <c r="N392" t="n">
         <v>7103.81</v>
       </c>
       <c r="O392" t="n">
-        <v>4233870.76</v>
+        <v>3949718.36</v>
       </c>
       <c r="P392" t="n">
         <v>8900</v>
       </c>
       <c r="Q392" t="n">
-        <v>5304400</v>
+        <v>4948400</v>
       </c>
     </row>
     <row r="393">
@@ -17874,10 +17874,10 @@
         <v>208</v>
       </c>
       <c r="N394" t="n">
-        <v>1690.870009009</v>
+        <v>1690.8700090131</v>
       </c>
       <c r="O394" t="n">
-        <v>351700.961873872</v>
+        <v>351700.9618747248</v>
       </c>
       <c r="P394" t="n">
         <v>3000</v>
@@ -17966,22 +17966,22 @@
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M396" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="N396" t="n">
         <v>6090.22</v>
       </c>
       <c r="O396" t="n">
-        <v>633382.88</v>
+        <v>572480.6800000001</v>
       </c>
       <c r="P396" t="n">
         <v>8500</v>
       </c>
       <c r="Q396" t="n">
-        <v>884000</v>
+        <v>799000</v>
       </c>
     </row>
     <row r="397">
@@ -18432,22 +18432,22 @@
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M406" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="N406" t="n">
         <v>1326</v>
       </c>
       <c r="O406" t="n">
-        <v>124644</v>
+        <v>71604</v>
       </c>
       <c r="P406" t="n">
         <v>2900</v>
       </c>
       <c r="Q406" t="n">
-        <v>272600</v>
+        <v>156600</v>
       </c>
     </row>
     <row r="407">
@@ -18767,10 +18767,10 @@
         <v>132</v>
       </c>
       <c r="N413" t="n">
-        <v>3259.1342528736</v>
+        <v>3259.1342692308</v>
       </c>
       <c r="O413" t="n">
-        <v>430205.7213793152</v>
+        <v>430205.7235384656</v>
       </c>
       <c r="P413" t="n">
         <v>3600</v>
@@ -18903,10 +18903,10 @@
         <v>2</v>
       </c>
       <c r="N416" t="n">
-        <v>3110.8425641565</v>
+        <v>3110.8424546425</v>
       </c>
       <c r="O416" t="n">
-        <v>6221.685128313</v>
+        <v>6221.684909285</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -19093,10 +19093,10 @@
         <v>127</v>
       </c>
       <c r="N420" t="n">
-        <v>3182.2511009174</v>
+        <v>3182.2511070111</v>
       </c>
       <c r="O420" t="n">
-        <v>404145.8898165098</v>
+        <v>404145.8905904097</v>
       </c>
       <c r="P420" t="n">
         <v>6900</v>
@@ -19277,10 +19277,10 @@
         <v>4</v>
       </c>
       <c r="N424" t="n">
-        <v>2501.3850684932</v>
+        <v>2501.3850230415</v>
       </c>
       <c r="O424" t="n">
-        <v>10005.5402739728</v>
+        <v>10005.540092166</v>
       </c>
       <c r="P424" t="n">
         <v>4100</v>
@@ -19837,10 +19837,10 @@
         <v>381</v>
       </c>
       <c r="N436" t="n">
-        <v>1595.5151400147</v>
+        <v>1595.5132932891</v>
       </c>
       <c r="O436" t="n">
-        <v>607891.2683456007</v>
+        <v>607890.5647431471</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -19975,22 +19975,22 @@
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M439" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="N439" t="n">
         <v>2098.4049570201</v>
       </c>
       <c r="O439" t="n">
-        <v>153183.5618624673</v>
+        <v>113313.8676790854</v>
       </c>
       <c r="P439" t="n">
         <v>9500</v>
       </c>
       <c r="Q439" t="n">
-        <v>693500</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="440">
@@ -20272,10 +20272,10 @@
         <v>23</v>
       </c>
       <c r="N445" t="n">
-        <v>2832.1948571429</v>
+        <v>2832.1949275362</v>
       </c>
       <c r="O445" t="n">
-        <v>65140.4817142867</v>
+        <v>65140.4833333326</v>
       </c>
       <c r="P445" t="n">
         <v>12900</v>
@@ -21921,10 +21921,10 @@
         <v>152</v>
       </c>
       <c r="N479" t="n">
-        <v>7046.9398286204</v>
+        <v>7046.9398281418</v>
       </c>
       <c r="O479" t="n">
-        <v>1071134.853950301</v>
+        <v>1071134.853877553</v>
       </c>
       <c r="P479" t="n">
         <v>9900</v>
@@ -22117,10 +22117,10 @@
         <v>4</v>
       </c>
       <c r="N483" t="n">
-        <v>8931.4408695652</v>
+        <v>8931.440952381001</v>
       </c>
       <c r="O483" t="n">
-        <v>35725.7634782608</v>
+        <v>35725.763809524</v>
       </c>
       <c r="P483" t="n">
         <v>19900</v>
@@ -23198,22 +23198,22 @@
         <v>0</v>
       </c>
       <c r="L506" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M506" t="n">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="N506" t="n">
         <v>1008.817540395</v>
       </c>
       <c r="O506" t="n">
-        <v>217904.58872532</v>
+        <v>193692.96775584</v>
       </c>
       <c r="P506" t="n">
         <v>1500</v>
       </c>
       <c r="Q506" t="n">
-        <v>324000</v>
+        <v>288000</v>
       </c>
     </row>
     <row r="507">
@@ -23374,10 +23374,10 @@
         <v>-72</v>
       </c>
       <c r="N510" t="n">
-        <v>1794.2879750466</v>
+        <v>1794.2879721384</v>
       </c>
       <c r="O510" t="n">
-        <v>-129188.7342033552</v>
+        <v>-129188.7339939648</v>
       </c>
       <c r="P510" t="n">
         <v>1600</v>
@@ -23507,10 +23507,10 @@
         <v>11</v>
       </c>
       <c r="N513" t="n">
-        <v>22951.704956085</v>
+        <v>22951.704917826</v>
       </c>
       <c r="O513" t="n">
-        <v>252468.754516935</v>
+        <v>252468.754096086</v>
       </c>
       <c r="P513" t="n">
         <v>37900</v>
@@ -25137,10 +25137,10 @@
         <v>271</v>
       </c>
       <c r="N548" t="n">
-        <v>227.41597222222</v>
+        <v>229.09061119293</v>
       </c>
       <c r="O548" t="n">
-        <v>61629.72847222162</v>
+        <v>62083.55563328403</v>
       </c>
       <c r="P548" t="n">
         <v>1200</v>
@@ -25715,10 +25715,10 @@
         <v>53</v>
       </c>
       <c r="N561" t="n">
-        <v>341.02142276423</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O561" t="n">
-        <v>18074.13540650419</v>
+        <v>18074.13602459019</v>
       </c>
       <c r="P561" t="n">
         <v>14500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
         </is>
       </c>
     </row>
@@ -544,13 +544,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>37</v>
@@ -583,13 +583,13 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>245</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>386</v>
+        <v>362</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>362</v>
@@ -2488,13 +2488,13 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
         <v>187</v>
@@ -4142,10 +4142,10 @@
         <v>53</v>
       </c>
       <c r="N90" t="n">
-        <v>3250.4653148346</v>
+        <v>3247</v>
       </c>
       <c r="O90" t="n">
-        <v>172274.6616862338</v>
+        <v>172091</v>
       </c>
       <c r="P90" t="n">
         <v>5200</v>
@@ -4993,13 +4993,13 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
       </c>
       <c r="L109" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
         <v>467</v>
@@ -6015,13 +6015,13 @@
         </is>
       </c>
       <c r="J132" t="n">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
         <v>1116</v>
@@ -6600,13 +6600,13 @@
         </is>
       </c>
       <c r="J145" t="n">
-        <v>2595</v>
+        <v>2575</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
         <v>2575</v>
@@ -6644,13 +6644,13 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>2380</v>
+        <v>2360</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M146" t="n">
         <v>2360</v>
@@ -6688,13 +6688,13 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>2680</v>
+        <v>2660</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
         <v>2660</v>
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
         <v>59</v>
@@ -7060,13 +7060,13 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="K155" t="n">
         <v>0</v>
       </c>
       <c r="L155" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M155" t="n">
         <v>116</v>
@@ -7104,13 +7104,13 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
         <v>66</v>
@@ -8625,10 +8625,10 @@
         <v>1</v>
       </c>
       <c r="N190" t="n">
-        <v>2679.7246188341</v>
+        <v>2661.82</v>
       </c>
       <c r="O190" t="n">
-        <v>2679.7246188341</v>
+        <v>2661.82</v>
       </c>
       <c r="P190" t="n">
         <v>3200</v>
@@ -8654,13 +8654,13 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="K191" t="n">
         <v>0</v>
       </c>
       <c r="L191" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M191" t="n">
         <v>29</v>
@@ -8748,10 +8748,10 @@
         <v>195</v>
       </c>
       <c r="N193" t="n">
-        <v>8799.395863611</v>
+        <v>8794.48</v>
       </c>
       <c r="O193" t="n">
-        <v>1715882.193404145</v>
+        <v>1714923.6</v>
       </c>
       <c r="P193" t="n">
         <v>14500</v>
@@ -9245,10 +9245,10 @@
         <v>237</v>
       </c>
       <c r="N205" t="n">
-        <v>1733.4632374328</v>
+        <v>1732.9153651597</v>
       </c>
       <c r="O205" t="n">
-        <v>410830.7872715736</v>
+        <v>410700.9415428489</v>
       </c>
       <c r="P205" t="n">
         <v>1900</v>
@@ -9748,13 +9748,13 @@
         </is>
       </c>
       <c r="J217" t="n">
-        <v>1028</v>
+        <v>1013</v>
       </c>
       <c r="K217" t="n">
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
         <v>1013</v>
@@ -10132,13 +10132,13 @@
         </is>
       </c>
       <c r="J226" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
       </c>
       <c r="L226" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
         <v>58</v>
@@ -10980,10 +10980,10 @@
         <v>119</v>
       </c>
       <c r="N245" t="n">
-        <v>3656.0567272727</v>
+        <v>3590.77</v>
       </c>
       <c r="O245" t="n">
-        <v>435070.7505454513</v>
+        <v>427301.63</v>
       </c>
       <c r="P245" t="n">
         <v>3900</v>
@@ -11532,13 +11532,13 @@
         </is>
       </c>
       <c r="J257" t="n">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="K257" t="n">
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M257" t="n">
         <v>198</v>
@@ -11706,13 +11706,13 @@
         </is>
       </c>
       <c r="J261" t="n">
-        <v>1215</v>
+        <v>1111</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
         <v>1111</v>
@@ -12634,13 +12634,13 @@
         </is>
       </c>
       <c r="J281" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
         <v>11</v>
@@ -13238,13 +13238,13 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
         <v>66</v>
@@ -13744,13 +13744,13 @@
         </is>
       </c>
       <c r="J305" t="n">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="K305" t="n">
         <v>0</v>
       </c>
       <c r="L305" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M305" t="n">
         <v>360</v>
@@ -14345,13 +14345,13 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M318" t="n">
         <v>47</v>
@@ -14483,13 +14483,13 @@
         </is>
       </c>
       <c r="J321" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="K321" t="n">
         <v>0</v>
       </c>
       <c r="L321" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M321" t="n">
         <v>103</v>
@@ -14541,10 +14541,10 @@
         <v>85</v>
       </c>
       <c r="N322" t="n">
-        <v>3418.6270305677</v>
+        <v>3396.38</v>
       </c>
       <c r="O322" t="n">
-        <v>290583.2975982545</v>
+        <v>288692.3</v>
       </c>
       <c r="P322" t="n">
         <v>6500</v>
@@ -14713,13 +14713,13 @@
         </is>
       </c>
       <c r="J326" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
         <v>134</v>
@@ -15047,10 +15047,10 @@
         <v>120</v>
       </c>
       <c r="N333" t="n">
-        <v>2637.9574105622</v>
+        <v>2629</v>
       </c>
       <c r="O333" t="n">
-        <v>316554.889267464</v>
+        <v>315480</v>
       </c>
       <c r="P333" t="n">
         <v>4500</v>
@@ -15139,10 +15139,10 @@
         <v>262</v>
       </c>
       <c r="N335" t="n">
-        <v>5775.9026369168</v>
+        <v>5772</v>
       </c>
       <c r="O335" t="n">
-        <v>1513286.490872202</v>
+        <v>1512264</v>
       </c>
       <c r="P335" t="n">
         <v>9900</v>
@@ -15415,10 +15415,10 @@
         <v>159</v>
       </c>
       <c r="N341" t="n">
-        <v>3904.1097178683</v>
+        <v>3898</v>
       </c>
       <c r="O341" t="n">
-        <v>620753.4451410597</v>
+        <v>619782</v>
       </c>
       <c r="P341" t="n">
         <v>6900</v>
@@ -15541,13 +15541,13 @@
         </is>
       </c>
       <c r="J344" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M344" t="n">
         <v>109</v>
@@ -17733,10 +17733,10 @@
         <v>114</v>
       </c>
       <c r="N391" t="n">
-        <v>6939.3400593472</v>
+        <v>6898.4</v>
       </c>
       <c r="O391" t="n">
-        <v>791084.7667655807</v>
+        <v>786417.6</v>
       </c>
       <c r="P391" t="n">
         <v>12900</v>
@@ -17770,13 +17770,13 @@
         </is>
       </c>
       <c r="J392" t="n">
-        <v>596</v>
+        <v>556</v>
       </c>
       <c r="K392" t="n">
         <v>0</v>
       </c>
       <c r="L392" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M392" t="n">
         <v>556</v>
@@ -17960,13 +17960,13 @@
         </is>
       </c>
       <c r="J396" t="n">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="K396" t="n">
         <v>0</v>
       </c>
       <c r="L396" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M396" t="n">
         <v>94</v>
@@ -18426,13 +18426,13 @@
         </is>
       </c>
       <c r="J406" t="n">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="K406" t="n">
         <v>0</v>
       </c>
       <c r="L406" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="M406" t="n">
         <v>54</v>
@@ -19969,13 +19969,13 @@
         </is>
       </c>
       <c r="J439" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="K439" t="n">
         <v>0</v>
       </c>
       <c r="L439" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M439" t="n">
         <v>54</v>
@@ -23192,13 +23192,13 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>216</v>
+        <v>192</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
       </c>
       <c r="L506" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M506" t="n">
         <v>192</v>
@@ -25137,10 +25137,10 @@
         <v>271</v>
       </c>
       <c r="N548" t="n">
-        <v>229.09061119293</v>
+        <v>227.41601620029</v>
       </c>
       <c r="O548" t="n">
-        <v>62083.55563328403</v>
+        <v>61629.74039027859</v>
       </c>
       <c r="P548" t="n">
         <v>1200</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-22</t>
         </is>
       </c>
     </row>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.854608</v>
+        <v>6272.8546153846</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.417888</v>
+        <v>1794036.419999996</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1708,10 +1708,10 @@
         <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.966058091</v>
+        <v>15711.966041667</v>
       </c>
       <c r="O33" t="n">
-        <v>659902.574439822</v>
+        <v>659902.573750014</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.874015957</v>
+        <v>61666.874026667</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.338590409</v>
+        <v>2281674.338986679</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0571872808</v>
+        <v>1098.0574483741</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.862473696</v>
+        <v>131766.893804892</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4823,19 +4823,19 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100071023</v>
+        <v>3795.7100071073</v>
       </c>
       <c r="O105" t="n">
-        <v>2182533.254083822</v>
+        <v>2167350.414058269</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
       </c>
       <c r="Q105" t="n">
-        <v>3565000</v>
+        <v>3540200</v>
       </c>
     </row>
     <row r="106">
@@ -5005,10 +5005,10 @@
         <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300473934</v>
+        <v>4890.9300476474</v>
       </c>
       <c r="O109" t="n">
-        <v>2284064.332132718</v>
+        <v>2284064.332251336</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.850030581</v>
+        <v>3240.8500313972</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.00366972</v>
+        <v>388902.003767664</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5538,10 +5538,10 @@
         <v>135</v>
       </c>
       <c r="N121" t="n">
-        <v>5191.4800271739</v>
+        <v>5191.4800275862</v>
       </c>
       <c r="O121" t="n">
-        <v>700849.8036684765</v>
+        <v>700849.803724137</v>
       </c>
       <c r="P121" t="n">
         <v>9100</v>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="J124" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5672,19 +5672,19 @@
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="N124" t="n">
-        <v>19098.750004662</v>
+        <v>19098.750004663</v>
       </c>
       <c r="O124" t="n">
-        <v>9663967.502358973</v>
+        <v>9644868.752354816</v>
       </c>
       <c r="P124" t="n">
         <v>15000</v>
       </c>
       <c r="Q124" t="n">
-        <v>7590000</v>
+        <v>7575000</v>
       </c>
     </row>
     <row r="125">
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="N125" t="n">
-        <v>12267.65043956</v>
+        <v>12267.650113636</v>
       </c>
       <c r="O125" t="n">
-        <v>171747.10615384</v>
+        <v>171747.101590904</v>
       </c>
       <c r="P125" t="n">
         <v>19900</v>
@@ -5940,10 +5940,10 @@
         <v>501</v>
       </c>
       <c r="N130" t="n">
-        <v>3041.660012945</v>
+        <v>3041.6600129618</v>
       </c>
       <c r="O130" t="n">
-        <v>1523871.666485445</v>
+        <v>1523871.666493862</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -7479,10 +7479,10 @@
         <v>228</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9233676374</v>
+        <v>1630.9234162594</v>
       </c>
       <c r="O164" t="n">
-        <v>371850.5278213272</v>
+        <v>371850.5389071432</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>96</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1933908991</v>
+        <v>1550.1934418475</v>
       </c>
       <c r="O165" t="n">
-        <v>148818.5655263136</v>
+        <v>148818.57041736</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -8461,10 +8461,10 @@
         <v>674</v>
       </c>
       <c r="N186" t="n">
-        <v>4196.8725263158</v>
+        <v>4196.872528417</v>
       </c>
       <c r="O186" t="n">
-        <v>2828692.082736849</v>
+        <v>2828692.084153058</v>
       </c>
       <c r="P186" t="n">
         <v>5900</v>
@@ -8543,10 +8543,10 @@
         <v>46</v>
       </c>
       <c r="N188" t="n">
-        <v>5162.2540116279</v>
+        <v>5162.2539766082</v>
       </c>
       <c r="O188" t="n">
-        <v>237463.6845348834</v>
+        <v>237463.6829239772</v>
       </c>
       <c r="P188" t="n">
         <v>8200</v>
@@ -8953,10 +8953,10 @@
         <v>160</v>
       </c>
       <c r="N198" t="n">
-        <v>22485.695899772</v>
+        <v>22485.695890411</v>
       </c>
       <c r="O198" t="n">
-        <v>3597711.34396352</v>
+        <v>3597711.34246576</v>
       </c>
       <c r="P198" t="n">
         <v>36500</v>
@@ -11718,10 +11718,10 @@
         <v>1111</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4725908889</v>
+        <v>1778.4725974412</v>
       </c>
       <c r="O261" t="n">
-        <v>1975883.048477568</v>
+        <v>1975883.055757173</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -13247,19 +13247,19 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>66</v>
+        <v>42</v>
       </c>
       <c r="N294" t="n">
         <v>13687</v>
       </c>
       <c r="O294" t="n">
-        <v>903342</v>
+        <v>574854</v>
       </c>
       <c r="P294" t="n">
         <v>21900</v>
       </c>
       <c r="Q294" t="n">
-        <v>1445400</v>
+        <v>919800</v>
       </c>
     </row>
     <row r="295">
@@ -14633,10 +14633,10 @@
         <v>184</v>
       </c>
       <c r="N324" t="n">
-        <v>4907.8220190779</v>
+        <v>4907.8220483871</v>
       </c>
       <c r="O324" t="n">
-        <v>903039.2515103336</v>
+        <v>903039.2569032264</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -14863,10 +14863,10 @@
         <v>84</v>
       </c>
       <c r="N329" t="n">
-        <v>3903.7361538462</v>
+        <v>3903.7363106796</v>
       </c>
       <c r="O329" t="n">
-        <v>327913.8369230808</v>
+        <v>327913.8500970864</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -16008,10 +16008,10 @@
         <v>60</v>
       </c>
       <c r="N354" t="n">
-        <v>4268.7051082251</v>
+        <v>4268.7057207207</v>
       </c>
       <c r="O354" t="n">
-        <v>256122.306493506</v>
+        <v>256122.343243242</v>
       </c>
       <c r="P354" t="n">
         <v>6900</v>
@@ -16514,10 +16514,10 @@
         <v>839</v>
       </c>
       <c r="N365" t="n">
-        <v>1516.0388047383</v>
+        <v>1516.0388031113</v>
       </c>
       <c r="O365" t="n">
-        <v>1271956.557175434</v>
+        <v>1271956.555810381</v>
       </c>
       <c r="P365" t="n">
         <v>2300</v>
@@ -16921,10 +16921,10 @@
         <v>2243</v>
       </c>
       <c r="N374" t="n">
-        <v>692.1521205151799</v>
+        <v>692.15220363289</v>
       </c>
       <c r="O374" t="n">
-        <v>1552497.206315549</v>
+        <v>1552497.392748572</v>
       </c>
       <c r="P374" t="n">
         <v>1200</v>
@@ -17874,10 +17874,10 @@
         <v>208</v>
       </c>
       <c r="N394" t="n">
-        <v>1690.8700090131</v>
+        <v>1690.870009058</v>
       </c>
       <c r="O394" t="n">
-        <v>351700.9618747248</v>
+        <v>351700.961884064</v>
       </c>
       <c r="P394" t="n">
         <v>3000</v>
@@ -18903,10 +18903,10 @@
         <v>2</v>
       </c>
       <c r="N416" t="n">
-        <v>3110.8424546425</v>
+        <v>3110.8423302235</v>
       </c>
       <c r="O416" t="n">
-        <v>6221.684909285</v>
+        <v>6221.684660447</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -19277,10 +19277,10 @@
         <v>4</v>
       </c>
       <c r="N424" t="n">
-        <v>2501.3850230415</v>
+        <v>2501.385</v>
       </c>
       <c r="O424" t="n">
-        <v>10005.540092166</v>
+        <v>10005.54</v>
       </c>
       <c r="P424" t="n">
         <v>4100</v>
@@ -19363,7 +19363,7 @@
         </is>
       </c>
       <c r="J426" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="K426" t="n">
         <v>0</v>
@@ -19372,19 +19372,19 @@
         <v>0</v>
       </c>
       <c r="M426" t="n">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="N426" t="n">
         <v>14260.14</v>
       </c>
       <c r="O426" t="n">
-        <v>1454534.28</v>
+        <v>1311932.88</v>
       </c>
       <c r="P426" t="n">
         <v>15900</v>
       </c>
       <c r="Q426" t="n">
-        <v>1621800</v>
+        <v>1462800</v>
       </c>
     </row>
     <row r="427">
@@ -19837,10 +19837,10 @@
         <v>381</v>
       </c>
       <c r="N436" t="n">
-        <v>1595.5132932891</v>
+        <v>1595.5132863655</v>
       </c>
       <c r="O436" t="n">
-        <v>607890.5647431471</v>
+        <v>607890.5621052556</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -22117,10 +22117,10 @@
         <v>4</v>
       </c>
       <c r="N483" t="n">
-        <v>8931.440952381001</v>
+        <v>8931.441000000001</v>
       </c>
       <c r="O483" t="n">
-        <v>35725.763809524</v>
+        <v>35725.764</v>
       </c>
       <c r="P483" t="n">
         <v>19900</v>
@@ -22540,7 +22540,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -22549,19 +22549,19 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N492" t="n">
-        <v>44113.603675676</v>
+        <v>44113.603820225</v>
       </c>
       <c r="O492" t="n">
-        <v>3087952.25729732</v>
+        <v>2955611.455955075</v>
       </c>
       <c r="P492" t="n">
         <v>71900</v>
       </c>
       <c r="Q492" t="n">
-        <v>5033000</v>
+        <v>4817300</v>
       </c>
     </row>
     <row r="493">
@@ -22889,10 +22889,10 @@
         <v>288</v>
       </c>
       <c r="N499" t="n">
-        <v>430.6099765808</v>
+        <v>430.60997630332</v>
       </c>
       <c r="O499" t="n">
-        <v>124015.6732552704</v>
+        <v>124015.6731753562</v>
       </c>
       <c r="P499" t="n">
         <v>2200</v>
@@ -23160,10 +23160,10 @@
         <v>34</v>
       </c>
       <c r="N505" t="n">
-        <v>4703.6207920792</v>
+        <v>4703.6208602151</v>
       </c>
       <c r="O505" t="n">
-        <v>159923.1069306928</v>
+        <v>159923.1092473134</v>
       </c>
       <c r="P505" t="n">
         <v>5900</v>
@@ -23204,10 +23204,10 @@
         <v>192</v>
       </c>
       <c r="N506" t="n">
-        <v>1008.817540395</v>
+        <v>1008.817266055</v>
       </c>
       <c r="O506" t="n">
-        <v>193692.96775584</v>
+        <v>193692.91508256</v>
       </c>
       <c r="P506" t="n">
         <v>1500</v>
@@ -23507,10 +23507,10 @@
         <v>11</v>
       </c>
       <c r="N513" t="n">
-        <v>22951.704917826</v>
+        <v>22951.704911392</v>
       </c>
       <c r="O513" t="n">
-        <v>252468.754096086</v>
+        <v>252468.754025312</v>
       </c>
       <c r="P513" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464891304</v>
+        <v>3376.7464843537</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.189119545</v>
+        <v>1982150.186315622</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8546153846</v>
+        <v>6272.8546302251</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.419999996</v>
+        <v>1794036.424244378</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1271,10 +1271,10 @@
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>2413.0010683761</v>
+        <v>2413.0010706638</v>
       </c>
       <c r="O22" t="n">
-        <v>2413.0010683761</v>
+        <v>2413.0010706638</v>
       </c>
       <c r="P22" t="n">
         <v>4700</v>
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.6281818182</v>
+        <v>3910.6281707317</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.2663636386</v>
+        <v>481007.2649999991</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -1708,10 +1708,10 @@
         <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.966041667</v>
+        <v>15711.966008403</v>
       </c>
       <c r="O33" t="n">
-        <v>659902.573750014</v>
+        <v>659902.572352926</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -2960,10 +2960,10 @@
         <v>148</v>
       </c>
       <c r="N63" t="n">
-        <v>1950.2146835443</v>
+        <v>1950.2146537678</v>
       </c>
       <c r="O63" t="n">
-        <v>288631.7731645564</v>
+        <v>288631.7687576344</v>
       </c>
       <c r="P63" t="n">
         <v>2900</v>
@@ -3047,10 +3047,10 @@
         <v>434</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101616458</v>
+        <v>4937.3101623616</v>
       </c>
       <c r="O65" t="n">
-        <v>2142792.610154277</v>
+        <v>2142792.610464935</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0574483741</v>
+        <v>1098.0580436917</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.893804892</v>
+        <v>131766.965243004</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -5005,10 +5005,10 @@
         <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300476474</v>
+        <v>4890.9300481348</v>
       </c>
       <c r="O109" t="n">
-        <v>2284064.332251336</v>
+        <v>2284064.332478952</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500313972</v>
+        <v>3240.8500314961</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003767664</v>
+        <v>388902.003779532</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5538,10 +5538,10 @@
         <v>135</v>
       </c>
       <c r="N121" t="n">
-        <v>5191.4800275862</v>
+        <v>5191.4800277778</v>
       </c>
       <c r="O121" t="n">
-        <v>700849.803724137</v>
+        <v>700849.8037500031</v>
       </c>
       <c r="P121" t="n">
         <v>9100</v>
@@ -5940,10 +5940,10 @@
         <v>501</v>
       </c>
       <c r="N130" t="n">
-        <v>3041.6600129618</v>
+        <v>3041.6600129786</v>
       </c>
       <c r="O130" t="n">
-        <v>1523871.666493862</v>
+        <v>1523871.666502279</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -6027,10 +6027,10 @@
         <v>1116</v>
       </c>
       <c r="N132" t="n">
-        <v>4372.210788556</v>
+        <v>4372.2107886682</v>
       </c>
       <c r="O132" t="n">
-        <v>4879387.240028496</v>
+        <v>4879387.240153711</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -7479,10 +7479,10 @@
         <v>228</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9234162594</v>
+        <v>1630.9234624043</v>
       </c>
       <c r="O164" t="n">
-        <v>371850.5389071432</v>
+        <v>371850.5494281804</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>96</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1934418475</v>
+        <v>1550.1935205388</v>
       </c>
       <c r="O165" t="n">
-        <v>148818.57041736</v>
+        <v>148818.5779717248</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -7571,10 +7571,10 @@
         <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>1579.3908418367</v>
+        <v>1579.3907948718</v>
       </c>
       <c r="O166" t="n">
-        <v>75810.7604081616</v>
+        <v>75810.7581538464</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -8912,10 +8912,10 @@
         <v>348</v>
       </c>
       <c r="N197" t="n">
-        <v>2029.8737332006</v>
+        <v>2029.8737350598</v>
       </c>
       <c r="O197" t="n">
-        <v>706396.0591538089</v>
+        <v>706396.0598008104</v>
       </c>
       <c r="P197" t="n">
         <v>3600</v>
@@ -8953,10 +8953,10 @@
         <v>160</v>
       </c>
       <c r="N198" t="n">
-        <v>22485.695890411</v>
+        <v>22485.695885714</v>
       </c>
       <c r="O198" t="n">
-        <v>3597711.34246576</v>
+        <v>3597711.34171424</v>
       </c>
       <c r="P198" t="n">
         <v>36500</v>
@@ -9117,10 +9117,10 @@
         <v>170</v>
       </c>
       <c r="N202" t="n">
-        <v>2680.7396999388</v>
+        <v>2680.7396995708</v>
       </c>
       <c r="O202" t="n">
-        <v>455725.748989596</v>
+        <v>455725.748927036</v>
       </c>
       <c r="P202" t="n">
         <v>4900</v>
@@ -10313,10 +10313,10 @@
         <v>180</v>
       </c>
       <c r="N230" t="n">
-        <v>7969.9501660377</v>
+        <v>7969.9501665405</v>
       </c>
       <c r="O230" t="n">
-        <v>1434591.029886786</v>
+        <v>1434591.02997729</v>
       </c>
       <c r="P230" t="n">
         <v>12900</v>
@@ -11718,10 +11718,10 @@
         <v>1111</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4725974412</v>
+        <v>1778.4725978277</v>
       </c>
       <c r="O261" t="n">
-        <v>1975883.055757173</v>
+        <v>1975883.056186575</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
@@ -14633,10 +14633,10 @@
         <v>184</v>
       </c>
       <c r="N324" t="n">
-        <v>4907.8220483871</v>
+        <v>4907.8220583468</v>
       </c>
       <c r="O324" t="n">
-        <v>903039.2569032264</v>
+        <v>903039.2587358112</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -14863,10 +14863,10 @@
         <v>84</v>
       </c>
       <c r="N329" t="n">
-        <v>3903.7363106796</v>
+        <v>3903.7364457831</v>
       </c>
       <c r="O329" t="n">
-        <v>327913.8500970864</v>
+        <v>327913.8614457804</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -16514,10 +16514,10 @@
         <v>839</v>
       </c>
       <c r="N365" t="n">
-        <v>1516.0388031113</v>
+        <v>1516.0388018299</v>
       </c>
       <c r="O365" t="n">
-        <v>1271956.555810381</v>
+        <v>1271956.554735286</v>
       </c>
       <c r="P365" t="n">
         <v>2300</v>
@@ -16877,10 +16877,10 @@
         <v>145</v>
       </c>
       <c r="N373" t="n">
-        <v>2842.2737539432</v>
+        <v>2842.2737341772</v>
       </c>
       <c r="O373" t="n">
-        <v>412129.694321764</v>
+        <v>412129.691455694</v>
       </c>
       <c r="P373" t="n">
         <v>4900</v>
@@ -16921,10 +16921,10 @@
         <v>2243</v>
       </c>
       <c r="N374" t="n">
-        <v>692.15220363289</v>
+        <v>692.15222061657</v>
       </c>
       <c r="O374" t="n">
-        <v>1552497.392748572</v>
+        <v>1552497.430842967</v>
       </c>
       <c r="P374" t="n">
         <v>1200</v>
@@ -17874,10 +17874,10 @@
         <v>208</v>
       </c>
       <c r="N394" t="n">
-        <v>1690.870009058</v>
+        <v>1690.8700090909</v>
       </c>
       <c r="O394" t="n">
-        <v>351700.961884064</v>
+        <v>351700.9618909072</v>
       </c>
       <c r="P394" t="n">
         <v>3000</v>
@@ -18903,10 +18903,10 @@
         <v>2</v>
       </c>
       <c r="N416" t="n">
-        <v>3110.8423302235</v>
+        <v>3110.842321894</v>
       </c>
       <c r="O416" t="n">
-        <v>6221.684660447</v>
+        <v>6221.684643788</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -19093,10 +19093,10 @@
         <v>127</v>
       </c>
       <c r="N420" t="n">
-        <v>3182.2511070111</v>
+        <v>3182.2511214953</v>
       </c>
       <c r="O420" t="n">
-        <v>404145.8905904097</v>
+        <v>404145.8924299031</v>
       </c>
       <c r="P420" t="n">
         <v>6900</v>
@@ -19837,10 +19837,10 @@
         <v>381</v>
       </c>
       <c r="N436" t="n">
-        <v>1595.5132863655</v>
+        <v>1595.513125523</v>
       </c>
       <c r="O436" t="n">
-        <v>607890.5621052556</v>
+        <v>607890.5008242631</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -22647,10 +22647,10 @@
         <v>1216</v>
       </c>
       <c r="N494" t="n">
-        <v>665.32351302785</v>
+        <v>665.32352410996</v>
       </c>
       <c r="O494" t="n">
-        <v>809033.3918418656</v>
+        <v>809033.4053177113</v>
       </c>
       <c r="P494" t="n">
         <v>2900</v>
@@ -22889,10 +22889,10 @@
         <v>288</v>
       </c>
       <c r="N499" t="n">
-        <v>430.60997630332</v>
+        <v>430.60997624703</v>
       </c>
       <c r="O499" t="n">
-        <v>124015.6731753562</v>
+        <v>124015.6731591446</v>
       </c>
       <c r="P499" t="n">
         <v>2200</v>
@@ -23204,10 +23204,10 @@
         <v>192</v>
       </c>
       <c r="N506" t="n">
-        <v>1008.817266055</v>
+        <v>1008.8171243043</v>
       </c>
       <c r="O506" t="n">
-        <v>193692.91508256</v>
+        <v>193692.8878664256</v>
       </c>
       <c r="P506" t="n">
         <v>1500</v>
@@ -23507,10 +23507,10 @@
         <v>11</v>
       </c>
       <c r="N513" t="n">
-        <v>22951.704911392</v>
+        <v>22951.704904943</v>
       </c>
       <c r="O513" t="n">
-        <v>252468.754025312</v>
+        <v>252468.753954373</v>
       </c>
       <c r="P513" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-22</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464843537</v>
+        <v>3376.7464728365</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.186315622</v>
+        <v>1982150.179555025</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8546302251</v>
+        <v>6272.8546451613</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.424244378</v>
+        <v>1794036.428516132</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1112,10 +1112,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.960416667</v>
+        <v>12357.96041958</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.575000012</v>
+        <v>444886.57510488</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -1193,10 +1193,10 @@
         <v>36</v>
       </c>
       <c r="N20" t="n">
-        <v>11491.096565657</v>
+        <v>11491.096989247</v>
       </c>
       <c r="O20" t="n">
-        <v>413679.476363652</v>
+        <v>413679.491612892</v>
       </c>
       <c r="P20" t="n">
         <v>23000</v>
@@ -1544,10 +1544,10 @@
         <v>62</v>
       </c>
       <c r="N29" t="n">
-        <v>14857.623214286</v>
+        <v>14857.623243243</v>
       </c>
       <c r="O29" t="n">
-        <v>921172.6392857321</v>
+        <v>921172.641081066</v>
       </c>
       <c r="P29" t="n">
         <v>34900</v>
@@ -1702,22 +1702,22 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="M33" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.966008403</v>
+        <v>15711.965957447</v>
       </c>
       <c r="O33" t="n">
-        <v>659902.572352926</v>
+        <v>282815.387234046</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
       </c>
       <c r="Q33" t="n">
-        <v>1197000</v>
+        <v>513000</v>
       </c>
     </row>
     <row r="34">
@@ -2110,22 +2110,22 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M43" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="N43" t="n">
         <v>26280.41</v>
       </c>
       <c r="O43" t="n">
-        <v>946094.76</v>
+        <v>630729.84</v>
       </c>
       <c r="P43" t="n">
         <v>46500</v>
       </c>
       <c r="Q43" t="n">
-        <v>1674000</v>
+        <v>1116000</v>
       </c>
     </row>
     <row r="44">
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0580436917</v>
+        <v>1098.0583408184</v>
       </c>
       <c r="O73" t="n">
-        <v>131766.965243004</v>
+        <v>131767.000898208</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -3540,10 +3540,10 @@
         <v>108</v>
       </c>
       <c r="N76" t="n">
-        <v>7569</v>
+        <v>7769.0616740088</v>
       </c>
       <c r="O76" t="n">
-        <v>817452</v>
+        <v>839058.6607929504</v>
       </c>
       <c r="P76" t="n">
         <v>12900</v>
@@ -4771,25 +4771,25 @@
         <v>78</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="N104" t="n">
         <v>3719.06</v>
       </c>
       <c r="O104" t="n">
-        <v>290086.68</v>
+        <v>937203.12</v>
       </c>
       <c r="P104" t="n">
         <v>6000</v>
       </c>
       <c r="Q104" t="n">
-        <v>468000</v>
+        <v>1512000</v>
       </c>
     </row>
     <row r="105">
@@ -4820,22 +4820,22 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>342</v>
       </c>
       <c r="M105" t="n">
-        <v>571</v>
+        <v>229</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100071073</v>
+        <v>3795.7100075415</v>
       </c>
       <c r="O105" t="n">
-        <v>2167350.414058269</v>
+        <v>869217.5917270036</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
       </c>
       <c r="Q105" t="n">
-        <v>3540200</v>
+        <v>1419800</v>
       </c>
     </row>
     <row r="106">
@@ -4863,25 +4863,25 @@
         <v>162</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>162</v>
+        <v>302</v>
       </c>
       <c r="N106" t="n">
         <v>3684</v>
       </c>
       <c r="O106" t="n">
-        <v>596808</v>
+        <v>1112568</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
       </c>
       <c r="Q106" t="n">
-        <v>1004400</v>
+        <v>1872400</v>
       </c>
     </row>
     <row r="107">
@@ -5005,10 +5005,10 @@
         <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300481348</v>
+        <v>4914.5862998791</v>
       </c>
       <c r="O109" t="n">
-        <v>2284064.332478952</v>
+        <v>2295111.802043539</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5675,10 +5675,10 @@
         <v>505</v>
       </c>
       <c r="N124" t="n">
-        <v>19098.750004663</v>
+        <v>19098.750004664</v>
       </c>
       <c r="O124" t="n">
-        <v>9644868.752354816</v>
+        <v>9644868.75235532</v>
       </c>
       <c r="P124" t="n">
         <v>15000</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="N125" t="n">
-        <v>12267.650113636</v>
+        <v>12267.649642857</v>
       </c>
       <c r="O125" t="n">
-        <v>171747.101590904</v>
+        <v>171747.094999998</v>
       </c>
       <c r="P125" t="n">
         <v>19900</v>
@@ -6027,10 +6027,10 @@
         <v>1116</v>
       </c>
       <c r="N132" t="n">
-        <v>4372.2107886682</v>
+        <v>4374.7024319704</v>
       </c>
       <c r="O132" t="n">
-        <v>4879387.240153711</v>
+        <v>4882167.914078966</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -7307,10 +7307,10 @@
         <v>279</v>
       </c>
       <c r="N160" t="n">
-        <v>3761.6</v>
+        <v>3788.0590855803</v>
       </c>
       <c r="O160" t="n">
-        <v>1049486.4</v>
+        <v>1056868.484876904</v>
       </c>
       <c r="P160" t="n">
         <v>6900</v>
@@ -7386,22 +7386,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M162" t="n">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="N162" t="n">
         <v>3751</v>
       </c>
       <c r="O162" t="n">
-        <v>2550680</v>
+        <v>2438150</v>
       </c>
       <c r="P162" t="n">
         <v>6400</v>
       </c>
       <c r="Q162" t="n">
-        <v>4352000</v>
+        <v>4160000</v>
       </c>
     </row>
     <row r="163">
@@ -7473,22 +7473,22 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="M164" t="n">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9234624043</v>
+        <v>1630.9234875283</v>
       </c>
       <c r="O164" t="n">
-        <v>371850.5494281804</v>
+        <v>311506.3861179053</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
       </c>
       <c r="Q164" t="n">
-        <v>570000</v>
+        <v>477500</v>
       </c>
     </row>
     <row r="165">
@@ -7519,22 +7519,22 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M165" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1935205388</v>
+        <v>1550.1935332762</v>
       </c>
       <c r="O165" t="n">
-        <v>148818.5779717248</v>
+        <v>55806.9671979432</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
       </c>
       <c r="Q165" t="n">
-        <v>240000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="166">
@@ -7571,10 +7571,10 @@
         <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>1579.3907948718</v>
+        <v>1579.3907235142</v>
       </c>
       <c r="O166" t="n">
-        <v>75810.7581538464</v>
+        <v>75810.75472868161</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -7738,10 +7738,10 @@
         <v>420</v>
       </c>
       <c r="N170" t="n">
-        <v>2069.4652683897</v>
+        <v>2069.4656884058</v>
       </c>
       <c r="O170" t="n">
-        <v>869175.4127236741</v>
+        <v>869175.589130436</v>
       </c>
       <c r="P170" t="n">
         <v>6500</v>
@@ -8543,10 +8543,10 @@
         <v>46</v>
       </c>
       <c r="N188" t="n">
-        <v>5162.2539766082</v>
+        <v>5162.2539411765</v>
       </c>
       <c r="O188" t="n">
-        <v>237463.6829239772</v>
+        <v>237463.681294119</v>
       </c>
       <c r="P188" t="n">
         <v>8200</v>
@@ -8871,10 +8871,10 @@
         <v>551</v>
       </c>
       <c r="N196" t="n">
-        <v>2517.22</v>
+        <v>2528.6359637188</v>
       </c>
       <c r="O196" t="n">
-        <v>1386988.22</v>
+        <v>1393278.416009059</v>
       </c>
       <c r="P196" t="n">
         <v>4200</v>
@@ -8912,10 +8912,10 @@
         <v>348</v>
       </c>
       <c r="N197" t="n">
-        <v>2029.8737350598</v>
+        <v>2029.8737443834</v>
       </c>
       <c r="O197" t="n">
-        <v>706396.0598008104</v>
+        <v>706396.0630454232</v>
       </c>
       <c r="P197" t="n">
         <v>3600</v>
@@ -8953,10 +8953,10 @@
         <v>160</v>
       </c>
       <c r="N198" t="n">
-        <v>22485.695885714</v>
+        <v>22485.695881007</v>
       </c>
       <c r="O198" t="n">
-        <v>3597711.34171424</v>
+        <v>3597711.34096112</v>
       </c>
       <c r="P198" t="n">
         <v>36500</v>
@@ -9760,10 +9760,10 @@
         <v>1013</v>
       </c>
       <c r="N217" t="n">
-        <v>3591.13</v>
+        <v>3598.612819934</v>
       </c>
       <c r="O217" t="n">
-        <v>3637814.69</v>
+        <v>3645394.786593142</v>
       </c>
       <c r="P217" t="n">
         <v>6300</v>
@@ -10585,10 +10585,10 @@
         <v>154</v>
       </c>
       <c r="N236" t="n">
-        <v>548.14724170616</v>
+        <v>548.14722592946</v>
       </c>
       <c r="O236" t="n">
-        <v>84414.67522274864</v>
+        <v>84414.67279313684</v>
       </c>
       <c r="P236" t="n">
         <v>2000</v>
@@ -11718,10 +11718,10 @@
         <v>1111</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4725978277</v>
+        <v>1778.4726172988</v>
       </c>
       <c r="O261" t="n">
-        <v>1975883.056186575</v>
+        <v>1975883.077818967</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
@@ -14032,10 +14032,10 @@
         <v>263</v>
       </c>
       <c r="N311" t="n">
-        <v>2252.2966541823</v>
+        <v>2252.2966708385</v>
       </c>
       <c r="O311" t="n">
-        <v>592354.0200499449</v>
+        <v>592354.0244305255</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
@@ -14219,10 +14219,10 @@
         <v>504</v>
       </c>
       <c r="N315" t="n">
-        <v>2328.1187258454</v>
+        <v>2328.1187254606</v>
       </c>
       <c r="O315" t="n">
-        <v>1173371.837826082</v>
+        <v>1173371.837632142</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -14863,10 +14863,10 @@
         <v>84</v>
       </c>
       <c r="N329" t="n">
-        <v>3903.7364457831</v>
+        <v>3903.7364581763</v>
       </c>
       <c r="O329" t="n">
-        <v>327913.8614457804</v>
+        <v>327913.8624868092</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -15185,10 +15185,10 @@
         <v>8</v>
       </c>
       <c r="N336" t="n">
-        <v>8637</v>
+        <v>9422.1818181818</v>
       </c>
       <c r="O336" t="n">
-        <v>69096</v>
+        <v>75377.4545454544</v>
       </c>
       <c r="P336" t="n">
         <v>14500</v>
@@ -15277,10 +15277,10 @@
         <v>260</v>
       </c>
       <c r="N338" t="n">
-        <v>6645</v>
+        <v>6666.7987971569</v>
       </c>
       <c r="O338" t="n">
-        <v>1727700</v>
+        <v>1733367.687260794</v>
       </c>
       <c r="P338" t="n">
         <v>10900</v>
@@ -16008,10 +16008,10 @@
         <v>60</v>
       </c>
       <c r="N354" t="n">
-        <v>4268.7057207207</v>
+        <v>4268.7068599034</v>
       </c>
       <c r="O354" t="n">
-        <v>256122.343243242</v>
+        <v>256122.411594204</v>
       </c>
       <c r="P354" t="n">
         <v>6900</v>
@@ -17874,10 +17874,10 @@
         <v>208</v>
       </c>
       <c r="N394" t="n">
-        <v>1690.8700090909</v>
+        <v>1690.870009095</v>
       </c>
       <c r="O394" t="n">
-        <v>351700.9618909072</v>
+        <v>351700.96189176</v>
       </c>
       <c r="P394" t="n">
         <v>3000</v>
@@ -18158,10 +18158,10 @@
         <v>68</v>
       </c>
       <c r="N400" t="n">
-        <v>3907.5003292181</v>
+        <v>3907.5003305785</v>
       </c>
       <c r="O400" t="n">
-        <v>265710.0223868308</v>
+        <v>265710.022479338</v>
       </c>
       <c r="P400" t="n">
         <v>3900</v>
@@ -18903,10 +18903,10 @@
         <v>2</v>
       </c>
       <c r="N416" t="n">
-        <v>3110.842321894</v>
+        <v>3110.8421999117</v>
       </c>
       <c r="O416" t="n">
-        <v>6221.684643788</v>
+        <v>6221.6843998234</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -19277,10 +19277,10 @@
         <v>4</v>
       </c>
       <c r="N424" t="n">
-        <v>2501.385</v>
+        <v>2501.3849767442</v>
       </c>
       <c r="O424" t="n">
-        <v>10005.54</v>
+        <v>10005.5399069768</v>
       </c>
       <c r="P424" t="n">
         <v>4100</v>
@@ -19837,10 +19837,10 @@
         <v>381</v>
       </c>
       <c r="N436" t="n">
-        <v>1595.513125523</v>
+        <v>1595.5130117944</v>
       </c>
       <c r="O436" t="n">
-        <v>607890.5008242631</v>
+        <v>607890.4574936664</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -19981,10 +19981,10 @@
         <v>54</v>
       </c>
       <c r="N439" t="n">
-        <v>2098.4049570201</v>
+        <v>2098.4049712644</v>
       </c>
       <c r="O439" t="n">
-        <v>113313.8676790854</v>
+        <v>113313.8684482776</v>
       </c>
       <c r="P439" t="n">
         <v>9500</v>
@@ -22117,10 +22117,10 @@
         <v>4</v>
       </c>
       <c r="N483" t="n">
-        <v>8931.441000000001</v>
+        <v>8931.441052631601</v>
       </c>
       <c r="O483" t="n">
-        <v>35725.764</v>
+        <v>35725.7642105264</v>
       </c>
       <c r="P483" t="n">
         <v>19900</v>
@@ -22552,10 +22552,10 @@
         <v>67</v>
       </c>
       <c r="N492" t="n">
-        <v>44113.603820225</v>
+        <v>44113.603841808</v>
       </c>
       <c r="O492" t="n">
-        <v>2955611.455955075</v>
+        <v>2955611.457401136</v>
       </c>
       <c r="P492" t="n">
         <v>71900</v>
@@ -23245,10 +23245,10 @@
         <v>1083</v>
       </c>
       <c r="N507" t="n">
-        <v>1176.57</v>
+        <v>1179.3131202642</v>
       </c>
       <c r="O507" t="n">
-        <v>1274225.31</v>
+        <v>1277196.109246129</v>
       </c>
       <c r="P507" t="n">
         <v>1900</v>
@@ -23507,10 +23507,10 @@
         <v>11</v>
       </c>
       <c r="N513" t="n">
-        <v>22951.704904943</v>
+        <v>22951.7048659</v>
       </c>
       <c r="O513" t="n">
-        <v>252468.753954373</v>
+        <v>252468.7535249</v>
       </c>
       <c r="P513" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-24</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-25</t>
         </is>
       </c>
     </row>
@@ -1696,13 +1696,13 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>18</v>
@@ -2104,13 +2104,13 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>24</v>
@@ -3540,10 +3540,10 @@
         <v>108</v>
       </c>
       <c r="N76" t="n">
-        <v>7769.0616740088</v>
+        <v>7569</v>
       </c>
       <c r="O76" t="n">
-        <v>839058.6607929504</v>
+        <v>817452</v>
       </c>
       <c r="P76" t="n">
         <v>12900</v>
@@ -4768,10 +4768,10 @@
         </is>
       </c>
       <c r="J104" t="n">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="K104" t="n">
-        <v>174</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -4814,13 +4814,13 @@
         </is>
       </c>
       <c r="J105" t="n">
-        <v>571</v>
+        <v>229</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>229</v>
@@ -4860,10 +4860,10 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>162</v>
+        <v>302</v>
       </c>
       <c r="K106" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5005,10 +5005,10 @@
         <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4914.5862998791</v>
+        <v>4890.9300483676</v>
       </c>
       <c r="O109" t="n">
-        <v>2295111.802043539</v>
+        <v>2284064.332587669</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -6027,10 +6027,10 @@
         <v>1116</v>
       </c>
       <c r="N132" t="n">
-        <v>4374.7024319704</v>
+        <v>4372.2107892862</v>
       </c>
       <c r="O132" t="n">
-        <v>4882167.914078966</v>
+        <v>4879387.240843399</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -7307,10 +7307,10 @@
         <v>279</v>
       </c>
       <c r="N160" t="n">
-        <v>3788.0590855803</v>
+        <v>3761.6</v>
       </c>
       <c r="O160" t="n">
-        <v>1056868.484876904</v>
+        <v>1049486.4</v>
       </c>
       <c r="P160" t="n">
         <v>6900</v>
@@ -7380,13 +7380,13 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
         <v>650</v>
@@ -7467,13 +7467,13 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>228</v>
+        <v>191</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
         <v>191</v>
@@ -7513,13 +7513,13 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
         <v>36</v>
@@ -8871,10 +8871,10 @@
         <v>551</v>
       </c>
       <c r="N196" t="n">
-        <v>2528.6359637188</v>
+        <v>2517.22</v>
       </c>
       <c r="O196" t="n">
-        <v>1393278.416009059</v>
+        <v>1386988.22</v>
       </c>
       <c r="P196" t="n">
         <v>4200</v>
@@ -9760,10 +9760,10 @@
         <v>1013</v>
       </c>
       <c r="N217" t="n">
-        <v>3598.612819934</v>
+        <v>3591.13</v>
       </c>
       <c r="O217" t="n">
-        <v>3645394.786593142</v>
+        <v>3637814.69</v>
       </c>
       <c r="P217" t="n">
         <v>6300</v>
@@ -15185,10 +15185,10 @@
         <v>8</v>
       </c>
       <c r="N336" t="n">
-        <v>9422.1818181818</v>
+        <v>8637</v>
       </c>
       <c r="O336" t="n">
-        <v>75377.4545454544</v>
+        <v>69096</v>
       </c>
       <c r="P336" t="n">
         <v>14500</v>
@@ -15277,10 +15277,10 @@
         <v>260</v>
       </c>
       <c r="N338" t="n">
-        <v>6666.7987971569</v>
+        <v>6645</v>
       </c>
       <c r="O338" t="n">
-        <v>1733367.687260794</v>
+        <v>1727700</v>
       </c>
       <c r="P338" t="n">
         <v>10900</v>
@@ -23245,10 +23245,10 @@
         <v>1083</v>
       </c>
       <c r="N507" t="n">
-        <v>1179.3131202642</v>
+        <v>1176.57</v>
       </c>
       <c r="O507" t="n">
-        <v>1277196.109246129</v>
+        <v>1274225.31</v>
       </c>
       <c r="P507" t="n">
         <v>1900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1388,10 +1388,10 @@
         <v>48</v>
       </c>
       <c r="N25" t="n">
-        <v>3716.3301935484</v>
+        <v>3716.3301938611</v>
       </c>
       <c r="O25" t="n">
-        <v>178383.8492903232</v>
+        <v>178383.8493053328</v>
       </c>
       <c r="P25" t="n">
         <v>9500</v>
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.6281707317</v>
+        <v>3910.6281632653</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.2649999991</v>
+        <v>481007.2640816319</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.874026667</v>
+        <v>61666.874048257</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.338986679</v>
+        <v>2281674.339785509</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -2960,10 +2960,10 @@
         <v>148</v>
       </c>
       <c r="N63" t="n">
-        <v>1950.2146537678</v>
+        <v>1950.2145987654</v>
       </c>
       <c r="O63" t="n">
-        <v>288631.7687576344</v>
+        <v>288631.7606172792</v>
       </c>
       <c r="P63" t="n">
         <v>2900</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0583408184</v>
+        <v>1098.0591631908</v>
       </c>
       <c r="O73" t="n">
-        <v>131767.000898208</v>
+        <v>131767.099582896</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -3918,22 +3918,22 @@
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M85" t="n">
-        <v>336</v>
+        <v>300</v>
       </c>
       <c r="N85" t="n">
         <v>2804.33</v>
       </c>
       <c r="O85" t="n">
-        <v>942254.88</v>
+        <v>841299</v>
       </c>
       <c r="P85" t="n">
         <v>4900</v>
       </c>
       <c r="Q85" t="n">
-        <v>1646400</v>
+        <v>1470000</v>
       </c>
     </row>
     <row r="86">
@@ -4136,22 +4136,22 @@
         <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M90" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="N90" t="n">
         <v>3247</v>
       </c>
       <c r="O90" t="n">
-        <v>172091</v>
+        <v>152609</v>
       </c>
       <c r="P90" t="n">
         <v>5200</v>
       </c>
       <c r="Q90" t="n">
-        <v>275600</v>
+        <v>244400</v>
       </c>
     </row>
     <row r="91">
@@ -4774,22 +4774,22 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M104" t="n">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="N104" t="n">
         <v>3719.06</v>
       </c>
       <c r="O104" t="n">
-        <v>937203.12</v>
+        <v>900012.52</v>
       </c>
       <c r="P104" t="n">
         <v>6000</v>
       </c>
       <c r="Q104" t="n">
-        <v>1512000</v>
+        <v>1452000</v>
       </c>
     </row>
     <row r="105">
@@ -4820,22 +4820,22 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M105" t="n">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="N105" t="n">
         <v>3795.7100075415</v>
       </c>
       <c r="O105" t="n">
-        <v>869217.5917270036</v>
+        <v>831260.4916515885</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
       </c>
       <c r="Q105" t="n">
-        <v>1419800</v>
+        <v>1357800</v>
       </c>
     </row>
     <row r="106">
@@ -4866,22 +4866,22 @@
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M106" t="n">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="N106" t="n">
         <v>3684</v>
       </c>
       <c r="O106" t="n">
-        <v>1112568</v>
+        <v>1075728</v>
       </c>
       <c r="P106" t="n">
         <v>6200</v>
       </c>
       <c r="Q106" t="n">
-        <v>1872400</v>
+        <v>1810400</v>
       </c>
     </row>
     <row r="107">
@@ -5005,10 +5005,10 @@
         <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300483676</v>
+        <v>4890.9300485437</v>
       </c>
       <c r="O109" t="n">
-        <v>2284064.332587669</v>
+        <v>2284064.332669908</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500314961</v>
+        <v>3240.850031746</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003779532</v>
+        <v>388902.00380952</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5538,10 +5538,10 @@
         <v>135</v>
       </c>
       <c r="N121" t="n">
-        <v>5191.4800277778</v>
+        <v>5191.4800278552</v>
       </c>
       <c r="O121" t="n">
-        <v>700849.8037500031</v>
+        <v>700849.8037604521</v>
       </c>
       <c r="P121" t="n">
         <v>9100</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="N125" t="n">
-        <v>12267.649642857</v>
+        <v>12267.648987342</v>
       </c>
       <c r="O125" t="n">
-        <v>171747.094999998</v>
+        <v>171747.085822788</v>
       </c>
       <c r="P125" t="n">
         <v>19900</v>
@@ -5940,10 +5940,10 @@
         <v>501</v>
       </c>
       <c r="N130" t="n">
-        <v>3041.6600129786</v>
+        <v>3041.6600130804</v>
       </c>
       <c r="O130" t="n">
-        <v>1523871.666502279</v>
+        <v>1523871.66655328</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -6027,10 +6027,10 @@
         <v>1116</v>
       </c>
       <c r="N132" t="n">
-        <v>4372.2107892862</v>
+        <v>4372.2107896237</v>
       </c>
       <c r="O132" t="n">
-        <v>4879387.240843399</v>
+        <v>4879387.24122005</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -6650,22 +6650,22 @@
         <v>0</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M146" t="n">
-        <v>2360</v>
+        <v>2344</v>
       </c>
       <c r="N146" t="n">
         <v>1343.77</v>
       </c>
       <c r="O146" t="n">
-        <v>3171297.2</v>
+        <v>3149796.88</v>
       </c>
       <c r="P146" t="n">
         <v>2500</v>
       </c>
       <c r="Q146" t="n">
-        <v>5900000</v>
+        <v>5860000</v>
       </c>
     </row>
     <row r="147">
@@ -6738,22 +6738,22 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M148" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N148" t="n">
         <v>9414.309999999999</v>
       </c>
       <c r="O148" t="n">
-        <v>555444.2899999999</v>
+        <v>517787.05</v>
       </c>
       <c r="P148" t="n">
         <v>16900</v>
       </c>
       <c r="Q148" t="n">
-        <v>997100</v>
+        <v>929500</v>
       </c>
     </row>
     <row r="149">
@@ -7151,25 +7151,25 @@
         <v>55</v>
       </c>
       <c r="K157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N157" t="n">
         <v>76846.14999999999</v>
       </c>
       <c r="O157" t="n">
-        <v>4226538.25</v>
+        <v>4380230.55</v>
       </c>
       <c r="P157" t="n">
         <v>99900</v>
       </c>
       <c r="Q157" t="n">
-        <v>5494500</v>
+        <v>5694300</v>
       </c>
     </row>
     <row r="158">
@@ -7252,22 +7252,22 @@
         <v>0</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M159" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="N159" t="n">
         <v>5853</v>
       </c>
       <c r="O159" t="n">
-        <v>690654</v>
+        <v>655536</v>
       </c>
       <c r="P159" t="n">
         <v>9900</v>
       </c>
       <c r="Q159" t="n">
-        <v>1168200</v>
+        <v>1108800</v>
       </c>
     </row>
     <row r="160">
@@ -7386,22 +7386,22 @@
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M162" t="n">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="N162" t="n">
         <v>3751</v>
       </c>
       <c r="O162" t="n">
-        <v>2438150</v>
+        <v>2363130</v>
       </c>
       <c r="P162" t="n">
         <v>6400</v>
       </c>
       <c r="Q162" t="n">
-        <v>4160000</v>
+        <v>4032000</v>
       </c>
     </row>
     <row r="163">
@@ -7479,10 +7479,10 @@
         <v>191</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9234875283</v>
+        <v>1630.9235527836</v>
       </c>
       <c r="O164" t="n">
-        <v>311506.3861179053</v>
+        <v>311506.3985816676</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>36</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1935332762</v>
+        <v>1550.1935823921</v>
       </c>
       <c r="O165" t="n">
-        <v>55806.9671979432</v>
+        <v>55806.9689661156</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -7571,10 +7571,10 @@
         <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>1579.3907235142</v>
+        <v>1579.3906753247</v>
       </c>
       <c r="O166" t="n">
-        <v>75810.75472868161</v>
+        <v>75810.75241558559</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -7738,10 +7738,10 @@
         <v>420</v>
       </c>
       <c r="N170" t="n">
-        <v>2069.4656884058</v>
+        <v>2069.4655925926</v>
       </c>
       <c r="O170" t="n">
-        <v>869175.589130436</v>
+        <v>869175.5488888919</v>
       </c>
       <c r="P170" t="n">
         <v>6500</v>
@@ -8947,22 +8947,22 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M198" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="N198" t="n">
-        <v>22485.695881007</v>
+        <v>22485.695577396</v>
       </c>
       <c r="O198" t="n">
-        <v>3597711.34096112</v>
+        <v>3530254.205651172</v>
       </c>
       <c r="P198" t="n">
         <v>36500</v>
       </c>
       <c r="Q198" t="n">
-        <v>5840000</v>
+        <v>5730500</v>
       </c>
     </row>
     <row r="199">
@@ -9070,22 +9070,22 @@
         <v>0</v>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M201" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N201" t="n">
         <v>15355</v>
       </c>
       <c r="O201" t="n">
-        <v>337810</v>
+        <v>307100</v>
       </c>
       <c r="P201" t="n">
         <v>17900</v>
       </c>
       <c r="Q201" t="n">
-        <v>393800</v>
+        <v>358000</v>
       </c>
     </row>
     <row r="202">
@@ -9285,22 +9285,22 @@
         <v>0</v>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M206" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N206" t="n">
         <v>30611</v>
       </c>
       <c r="O206" t="n">
-        <v>2510102</v>
+        <v>2418269</v>
       </c>
       <c r="P206" t="n">
         <v>38900</v>
       </c>
       <c r="Q206" t="n">
-        <v>3189800</v>
+        <v>3073100</v>
       </c>
     </row>
     <row r="207">
@@ -9549,22 +9549,22 @@
         <v>0</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M212" t="n">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="N212" t="n">
         <v>2178.64</v>
       </c>
       <c r="O212" t="n">
-        <v>400869.76</v>
+        <v>357296.96</v>
       </c>
       <c r="P212" t="n">
         <v>3600</v>
       </c>
       <c r="Q212" t="n">
-        <v>662400</v>
+        <v>590400</v>
       </c>
     </row>
     <row r="213">
@@ -9754,22 +9754,22 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M217" t="n">
-        <v>1013</v>
+        <v>993</v>
       </c>
       <c r="N217" t="n">
         <v>3591.13</v>
       </c>
       <c r="O217" t="n">
-        <v>3637814.69</v>
+        <v>3565992.09</v>
       </c>
       <c r="P217" t="n">
         <v>6300</v>
       </c>
       <c r="Q217" t="n">
-        <v>6381900</v>
+        <v>6255900</v>
       </c>
     </row>
     <row r="218">
@@ -10585,10 +10585,10 @@
         <v>154</v>
       </c>
       <c r="N236" t="n">
-        <v>548.14722592946</v>
+        <v>548.14720461095</v>
       </c>
       <c r="O236" t="n">
-        <v>84414.67279313684</v>
+        <v>84414.6695100863</v>
       </c>
       <c r="P236" t="n">
         <v>2000</v>
@@ -11538,22 +11538,22 @@
         <v>0</v>
       </c>
       <c r="L257" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M257" t="n">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="N257" t="n">
         <v>3646</v>
       </c>
       <c r="O257" t="n">
-        <v>721908</v>
+        <v>685448</v>
       </c>
       <c r="P257" t="n">
         <v>6900</v>
       </c>
       <c r="Q257" t="n">
-        <v>1366200</v>
+        <v>1297200</v>
       </c>
     </row>
     <row r="258">
@@ -14032,10 +14032,10 @@
         <v>263</v>
       </c>
       <c r="N311" t="n">
-        <v>2252.2966708385</v>
+        <v>2252.2968774194</v>
       </c>
       <c r="O311" t="n">
-        <v>592354.0244305255</v>
+        <v>592354.0787613022</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
@@ -14219,10 +14219,10 @@
         <v>504</v>
       </c>
       <c r="N315" t="n">
-        <v>2328.1187254606</v>
+        <v>2328.1187184938</v>
       </c>
       <c r="O315" t="n">
-        <v>1173371.837632142</v>
+        <v>1173371.834120875</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -14627,22 +14627,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M324" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="N324" t="n">
-        <v>4907.8220583468</v>
+        <v>4907.8220751634</v>
       </c>
       <c r="O324" t="n">
-        <v>903039.2587358112</v>
+        <v>834329.752777778</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
       </c>
       <c r="Q324" t="n">
-        <v>1508800</v>
+        <v>1394000</v>
       </c>
     </row>
     <row r="325">
@@ -15501,22 +15501,22 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M343" t="n">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="N343" t="n">
         <v>17992</v>
       </c>
       <c r="O343" t="n">
-        <v>1619280</v>
+        <v>1475344</v>
       </c>
       <c r="P343" t="n">
         <v>28900</v>
       </c>
       <c r="Q343" t="n">
-        <v>2601000</v>
+        <v>2369800</v>
       </c>
     </row>
     <row r="344">
@@ -16186,22 +16186,22 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M358" t="n">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="N358" t="n">
         <v>3639.35</v>
       </c>
       <c r="O358" t="n">
-        <v>931673.6</v>
+        <v>869804.65</v>
       </c>
       <c r="P358" t="n">
         <v>7500</v>
       </c>
       <c r="Q358" t="n">
-        <v>1920000</v>
+        <v>1792500</v>
       </c>
     </row>
     <row r="359">
@@ -16232,22 +16232,22 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M359" t="n">
-        <v>1778</v>
+        <v>1766</v>
       </c>
       <c r="N359" t="n">
         <v>1326</v>
       </c>
       <c r="O359" t="n">
-        <v>2357628</v>
+        <v>2341716</v>
       </c>
       <c r="P359" t="n">
         <v>2500</v>
       </c>
       <c r="Q359" t="n">
-        <v>4445000</v>
+        <v>4415000</v>
       </c>
     </row>
     <row r="360">
@@ -16278,22 +16278,22 @@
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M360" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="N360" t="n">
         <v>5640</v>
       </c>
       <c r="O360" t="n">
-        <v>152280</v>
+        <v>78960</v>
       </c>
       <c r="P360" t="n">
         <v>9900</v>
       </c>
       <c r="Q360" t="n">
-        <v>267300</v>
+        <v>138600</v>
       </c>
     </row>
     <row r="361">
@@ -16324,22 +16324,22 @@
         <v>0</v>
       </c>
       <c r="L361" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M361" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N361" t="n">
         <v>12489</v>
       </c>
       <c r="O361" t="n">
-        <v>74934</v>
+        <v>0</v>
       </c>
       <c r="P361" t="n">
         <v>20900</v>
       </c>
       <c r="Q361" t="n">
-        <v>125400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -16514,10 +16514,10 @@
         <v>839</v>
       </c>
       <c r="N365" t="n">
-        <v>1516.0388018299</v>
+        <v>1516.038799961</v>
       </c>
       <c r="O365" t="n">
-        <v>1271956.554735286</v>
+        <v>1271956.553167279</v>
       </c>
       <c r="P365" t="n">
         <v>2300</v>
@@ -17595,10 +17595,10 @@
         <v>4</v>
       </c>
       <c r="N388" t="n">
-        <v>1591.0394292804</v>
+        <v>1591.0394056848</v>
       </c>
       <c r="O388" t="n">
-        <v>6364.1577171216</v>
+        <v>6364.1576227392</v>
       </c>
       <c r="P388" t="n">
         <v>2400</v>
@@ -17635,22 +17635,22 @@
         <v>0</v>
       </c>
       <c r="L389" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M389" t="n">
-        <v>721</v>
+        <v>701</v>
       </c>
       <c r="N389" t="n">
         <v>1426.39</v>
       </c>
       <c r="O389" t="n">
-        <v>1028427.19</v>
+        <v>999899.39</v>
       </c>
       <c r="P389" t="n">
         <v>2500</v>
       </c>
       <c r="Q389" t="n">
-        <v>1802500</v>
+        <v>1752500</v>
       </c>
     </row>
     <row r="390">
@@ -17868,22 +17868,22 @@
         <v>0</v>
       </c>
       <c r="L394" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M394" t="n">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="N394" t="n">
         <v>1690.870009095</v>
       </c>
       <c r="O394" t="n">
-        <v>351700.96189176</v>
+        <v>300974.86161891</v>
       </c>
       <c r="P394" t="n">
         <v>3000</v>
       </c>
       <c r="Q394" t="n">
-        <v>624000</v>
+        <v>534000</v>
       </c>
     </row>
     <row r="395">
@@ -18251,10 +18251,10 @@
         <v>7734</v>
       </c>
       <c r="N402" t="n">
-        <v>711.3366499515799</v>
+        <v>711.33664971986</v>
       </c>
       <c r="O402" t="n">
-        <v>5501477.650725519</v>
+        <v>5501477.648933398</v>
       </c>
       <c r="P402" t="n">
         <v>900</v>
@@ -18903,10 +18903,10 @@
         <v>2</v>
       </c>
       <c r="N416" t="n">
-        <v>3110.8421999117</v>
+        <v>3110.8418772978</v>
       </c>
       <c r="O416" t="n">
-        <v>6221.6843998234</v>
+        <v>6221.6837545956</v>
       </c>
       <c r="P416" t="n">
         <v>4500</v>
@@ -18943,22 +18943,22 @@
         <v>0</v>
       </c>
       <c r="L417" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M417" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="N417" t="n">
         <v>6300.61</v>
       </c>
       <c r="O417" t="n">
-        <v>604858.5599999999</v>
+        <v>554453.6799999999</v>
       </c>
       <c r="P417" t="n">
         <v>8900</v>
       </c>
       <c r="Q417" t="n">
-        <v>854400</v>
+        <v>783200</v>
       </c>
     </row>
     <row r="418">
@@ -19038,22 +19038,22 @@
         <v>0</v>
       </c>
       <c r="L419" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M419" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="N419" t="n">
         <v>7200</v>
       </c>
       <c r="O419" t="n">
-        <v>280800</v>
+        <v>237600</v>
       </c>
       <c r="P419" t="n">
         <v>9000</v>
       </c>
       <c r="Q419" t="n">
-        <v>351000</v>
+        <v>297000</v>
       </c>
     </row>
     <row r="420">
@@ -19837,10 +19837,10 @@
         <v>381</v>
       </c>
       <c r="N436" t="n">
-        <v>1595.5130117944</v>
+        <v>1595.5128965225</v>
       </c>
       <c r="O436" t="n">
-        <v>607890.4574936664</v>
+        <v>607890.4135750724</v>
       </c>
       <c r="P436" t="n">
         <v>2500</v>
@@ -20364,22 +20364,22 @@
         <v>0</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M447" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N447" t="n">
         <v>8869.360000000001</v>
       </c>
       <c r="O447" t="n">
-        <v>478945.4400000001</v>
+        <v>452337.36</v>
       </c>
       <c r="P447" t="n">
         <v>15500</v>
       </c>
       <c r="Q447" t="n">
-        <v>837000</v>
+        <v>790500</v>
       </c>
     </row>
     <row r="448">
@@ -21090,22 +21090,22 @@
         <v>0</v>
       </c>
       <c r="L462" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M462" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N462" t="n">
         <v>27577.72</v>
       </c>
       <c r="O462" t="n">
-        <v>193044.04</v>
+        <v>137888.6</v>
       </c>
       <c r="P462" t="n">
         <v>120900</v>
       </c>
       <c r="Q462" t="n">
-        <v>846300</v>
+        <v>604500</v>
       </c>
     </row>
     <row r="463">
@@ -22647,10 +22647,10 @@
         <v>1216</v>
       </c>
       <c r="N494" t="n">
-        <v>665.32352410996</v>
+        <v>665.32358222629</v>
       </c>
       <c r="O494" t="n">
-        <v>809033.4053177113</v>
+        <v>809033.4759871686</v>
       </c>
       <c r="P494" t="n">
         <v>2900</v>
@@ -23204,10 +23204,10 @@
         <v>192</v>
       </c>
       <c r="N506" t="n">
-        <v>1008.8171243043</v>
+        <v>1008.8169793621</v>
       </c>
       <c r="O506" t="n">
-        <v>193692.8878664256</v>
+        <v>193692.8600375232</v>
       </c>
       <c r="P506" t="n">
         <v>1500</v>
@@ -23239,22 +23239,22 @@
         <v>0</v>
       </c>
       <c r="L507" t="n">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="M507" t="n">
-        <v>1083</v>
+        <v>915</v>
       </c>
       <c r="N507" t="n">
         <v>1176.57</v>
       </c>
       <c r="O507" t="n">
-        <v>1274225.31</v>
+        <v>1076561.55</v>
       </c>
       <c r="P507" t="n">
         <v>1900</v>
       </c>
       <c r="Q507" t="n">
-        <v>2057700</v>
+        <v>1738500</v>
       </c>
     </row>
     <row r="508">
@@ -23280,25 +23280,25 @@
         <v>772</v>
       </c>
       <c r="K508" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L508" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M508" t="n">
-        <v>772</v>
+        <v>742</v>
       </c>
       <c r="N508" t="n">
         <v>3181.9</v>
       </c>
       <c r="O508" t="n">
-        <v>2456426.8</v>
+        <v>2360969.8</v>
       </c>
       <c r="P508" t="n">
         <v>5100</v>
       </c>
       <c r="Q508" t="n">
-        <v>3937200</v>
+        <v>3784200</v>
       </c>
     </row>
     <row r="509">
@@ -23507,10 +23507,10 @@
         <v>11</v>
       </c>
       <c r="N513" t="n">
-        <v>22951.7048659</v>
+        <v>22951.704852753</v>
       </c>
       <c r="O513" t="n">
-        <v>252468.7535249</v>
+        <v>252468.753380283</v>
       </c>
       <c r="P513" t="n">
         <v>37900</v>
@@ -24033,22 +24033,22 @@
         <v>0</v>
       </c>
       <c r="L525" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M525" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="N525" t="n">
         <v>6270.21</v>
       </c>
       <c r="O525" t="n">
-        <v>727344.36</v>
+        <v>652101.84</v>
       </c>
       <c r="P525" t="n">
         <v>8900</v>
       </c>
       <c r="Q525" t="n">
-        <v>1032400</v>
+        <v>925600</v>
       </c>
     </row>
     <row r="526">
@@ -24171,22 +24171,22 @@
         <v>0</v>
       </c>
       <c r="L528" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M528" t="n">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="N528" t="n">
         <v>1952.41</v>
       </c>
       <c r="O528" t="n">
-        <v>542769.98</v>
+        <v>503721.78</v>
       </c>
       <c r="P528" t="n">
         <v>2700</v>
       </c>
       <c r="Q528" t="n">
-        <v>750600</v>
+        <v>696600</v>
       </c>
     </row>
     <row r="529">
@@ -24937,22 +24937,22 @@
         <v>0</v>
       </c>
       <c r="L544" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M544" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="N544" t="n">
         <v>3982.6707619048</v>
       </c>
       <c r="O544" t="n">
-        <v>410215.0884761944</v>
+        <v>370388.3808571464</v>
       </c>
       <c r="P544" t="n">
         <v>10900</v>
       </c>
       <c r="Q544" t="n">
-        <v>1122700</v>
+        <v>1013700</v>
       </c>
     </row>
     <row r="545">
@@ -25040,10 +25040,10 @@
         <v>3</v>
       </c>
       <c r="N546" t="n">
-        <v>2432.1346938776</v>
+        <v>2432.1347916667</v>
       </c>
       <c r="O546" t="n">
-        <v>7296.4040816328</v>
+        <v>7296.4043750001</v>
       </c>
       <c r="P546" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q560"/>
+  <dimension ref="A1:Q571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-26</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464728365</v>
+        <v>3376.7464699454</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.179555025</v>
+        <v>1982150.17785795</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8546451613</v>
+        <v>6272.8546905537</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.428516132</v>
+        <v>1794036.441498358</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1193,10 +1193,10 @@
         <v>36</v>
       </c>
       <c r="N20" t="n">
-        <v>11491.096989247</v>
+        <v>11491.097142857</v>
       </c>
       <c r="O20" t="n">
-        <v>413679.491612892</v>
+        <v>413679.497142852</v>
       </c>
       <c r="P20" t="n">
         <v>23000</v>
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.6281632653</v>
+        <v>3910.6281595092</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.2640816319</v>
+        <v>481007.2636196316</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -1708,10 +1708,10 @@
         <v>18</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.965957447</v>
+        <v>15711.965922747</v>
       </c>
       <c r="O33" t="n">
-        <v>282815.387234046</v>
+        <v>282815.386609446</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.874048257</v>
+        <v>61666.874070081</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.339785509</v>
+        <v>2281674.340592997</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -2461,10 +2461,10 @@
         <v>4</v>
       </c>
       <c r="N51" t="n">
-        <v>4878.2859036145</v>
+        <v>4878.2859393939</v>
       </c>
       <c r="O51" t="n">
-        <v>19513.143614458</v>
+        <v>19513.1437575756</v>
       </c>
       <c r="P51" t="n">
         <v>13500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0591631908</v>
+        <v>1098.0593600211</v>
       </c>
       <c r="O73" t="n">
-        <v>131767.099582896</v>
+        <v>131767.123202532</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4826,10 +4826,10 @@
         <v>219</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100075415</v>
+        <v>3795.7100075514</v>
       </c>
       <c r="O105" t="n">
-        <v>831260.4916515885</v>
+        <v>831260.4916537566</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
@@ -5005,10 +5005,10 @@
         <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300485437</v>
+        <v>4890.9300486322</v>
       </c>
       <c r="O109" t="n">
-        <v>2284064.332669908</v>
+        <v>2284064.332711237</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.850031746</v>
+        <v>3240.8500325733</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.00380952</v>
+        <v>388902.003908796</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5721,10 +5721,10 @@
         <v>14</v>
       </c>
       <c r="N125" t="n">
-        <v>12267.648987342</v>
+        <v>12267.648701299</v>
       </c>
       <c r="O125" t="n">
-        <v>171747.085822788</v>
+        <v>171747.081818186</v>
       </c>
       <c r="P125" t="n">
         <v>19900</v>
@@ -5940,10 +5940,10 @@
         <v>501</v>
       </c>
       <c r="N130" t="n">
-        <v>3041.6600130804</v>
+        <v>3041.6600131579</v>
       </c>
       <c r="O130" t="n">
-        <v>1523871.66655328</v>
+        <v>1523871.666592108</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -7479,10 +7479,10 @@
         <v>191</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9235527836</v>
+        <v>1630.9235742505</v>
       </c>
       <c r="O164" t="n">
-        <v>311506.3985816676</v>
+        <v>311506.4026818455</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>36</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1935823921</v>
+        <v>1550.1936350279</v>
       </c>
       <c r="O165" t="n">
-        <v>55806.9689661156</v>
+        <v>55806.9708610044</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -8461,10 +8461,10 @@
         <v>674</v>
       </c>
       <c r="N186" t="n">
-        <v>4196.872528417</v>
+        <v>4196.8725291181</v>
       </c>
       <c r="O186" t="n">
-        <v>2828692.084153058</v>
+        <v>2828692.084625599</v>
       </c>
       <c r="P186" t="n">
         <v>5900</v>
@@ -8912,10 +8912,10 @@
         <v>348</v>
       </c>
       <c r="N197" t="n">
-        <v>2029.8737443834</v>
+        <v>2029.8737669513</v>
       </c>
       <c r="O197" t="n">
-        <v>706396.0630454232</v>
+        <v>706396.0708990524</v>
       </c>
       <c r="P197" t="n">
         <v>3600</v>
@@ -8953,10 +8953,10 @@
         <v>157</v>
       </c>
       <c r="N198" t="n">
-        <v>22485.695577396</v>
+        <v>22485.695571956</v>
       </c>
       <c r="O198" t="n">
-        <v>3530254.205651172</v>
+        <v>3530254.204797092</v>
       </c>
       <c r="P198" t="n">
         <v>36500</v>
@@ -9888,10 +9888,10 @@
         <v>37</v>
       </c>
       <c r="N220" t="n">
-        <v>27123.765232775</v>
+        <v>27123.765223881</v>
       </c>
       <c r="O220" t="n">
-        <v>1003579.313612675</v>
+        <v>1003579.313283597</v>
       </c>
       <c r="P220" t="n">
         <v>44500</v>
@@ -10313,10 +10313,10 @@
         <v>180</v>
       </c>
       <c r="N230" t="n">
-        <v>7969.9501665405</v>
+        <v>7969.9501669196</v>
       </c>
       <c r="O230" t="n">
-        <v>1434591.02997729</v>
+        <v>1434591.030045528</v>
       </c>
       <c r="P230" t="n">
         <v>12900</v>
@@ -11718,10 +11718,10 @@
         <v>1111</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4726172988</v>
+        <v>1778.4726251691</v>
       </c>
       <c r="O261" t="n">
-        <v>1975883.077818967</v>
+        <v>1975883.08656287</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
@@ -14219,10 +14219,10 @@
         <v>504</v>
       </c>
       <c r="N315" t="n">
-        <v>2328.1187184938</v>
+        <v>2328.1187161545</v>
       </c>
       <c r="O315" t="n">
-        <v>1173371.834120875</v>
+        <v>1173371.832941868</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -14633,10 +14633,10 @@
         <v>170</v>
       </c>
       <c r="N324" t="n">
-        <v>4907.8220751634</v>
+        <v>4907.822092257</v>
       </c>
       <c r="O324" t="n">
-        <v>834329.752777778</v>
+        <v>834329.75568369</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
@@ -14863,10 +14863,10 @@
         <v>84</v>
       </c>
       <c r="N329" t="n">
-        <v>3903.7364581763</v>
+        <v>3903.7365705615</v>
       </c>
       <c r="O329" t="n">
-        <v>327913.8624868092</v>
+        <v>327913.871927166</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -16468,10 +16468,10 @@
         <v>839</v>
       </c>
       <c r="N364" t="n">
-        <v>1516.038799961</v>
+        <v>1516.0387986728</v>
       </c>
       <c r="O364" t="n">
-        <v>1271956.553167279</v>
+        <v>1271956.552086479</v>
       </c>
       <c r="P364" t="n">
         <v>2300</v>
@@ -17975,10 +17975,10 @@
         <v>47</v>
       </c>
       <c r="N396" t="n">
-        <v>2270.3211627907</v>
+        <v>2270.3211764706</v>
       </c>
       <c r="O396" t="n">
-        <v>106705.0946511629</v>
+        <v>106705.0952941182</v>
       </c>
       <c r="P396" t="n">
         <v>3900</v>
@@ -18019,10 +18019,10 @@
         <v>1602</v>
       </c>
       <c r="N397" t="n">
-        <v>481.48791460674</v>
+        <v>481.48791273054</v>
       </c>
       <c r="O397" t="n">
-        <v>771343.6391999974</v>
+        <v>771343.6361943251</v>
       </c>
       <c r="P397" t="n">
         <v>650</v>
@@ -18857,10 +18857,10 @@
         <v>2</v>
       </c>
       <c r="N415" t="n">
-        <v>3110.8418772978</v>
+        <v>3110.8416960301</v>
       </c>
       <c r="O415" t="n">
-        <v>6221.6837545956</v>
+        <v>6221.6833920602</v>
       </c>
       <c r="P415" t="n">
         <v>4500</v>
@@ -19791,10 +19791,10 @@
         <v>381</v>
       </c>
       <c r="N435" t="n">
-        <v>1595.5128965225</v>
+        <v>1595.5127943686</v>
       </c>
       <c r="O435" t="n">
-        <v>607890.4135750724</v>
+        <v>607890.3746544366</v>
       </c>
       <c r="P435" t="n">
         <v>2500</v>
@@ -22887,10 +22887,10 @@
         <v>41050</v>
       </c>
       <c r="N499" t="n">
-        <v>2703.2000014447</v>
+        <v>2703.2000014448</v>
       </c>
       <c r="O499" t="n">
-        <v>110966360.0593049</v>
+        <v>110966360.059309</v>
       </c>
       <c r="P499" t="n">
         <v>4500</v>
@@ -23158,10 +23158,10 @@
         <v>192</v>
       </c>
       <c r="N505" t="n">
-        <v>1008.8169793621</v>
+        <v>1008.8168311195</v>
       </c>
       <c r="O505" t="n">
-        <v>193692.8600375232</v>
+        <v>193692.831574944</v>
       </c>
       <c r="P505" t="n">
         <v>1500</v>
@@ -23328,10 +23328,10 @@
         <v>-72</v>
       </c>
       <c r="N509" t="n">
-        <v>1794.2879721384</v>
+        <v>1794.2879692219</v>
       </c>
       <c r="O509" t="n">
-        <v>-129188.7339939648</v>
+        <v>-129188.7337839768</v>
       </c>
       <c r="P509" t="n">
         <v>1600</v>
@@ -23461,10 +23461,10 @@
         <v>11</v>
       </c>
       <c r="N512" t="n">
-        <v>22951.704852753</v>
+        <v>22951.704839538</v>
       </c>
       <c r="O512" t="n">
-        <v>252468.753380283</v>
+        <v>252468.753234918</v>
       </c>
       <c r="P512" t="n">
         <v>37900</v>
@@ -24192,17 +24192,17 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>MG040</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>ABACO ANIMALES PT17058</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -24211,7 +24211,7 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>23</v>
+        <v>360</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -24220,40 +24220,35 @@
         <v>0</v>
       </c>
       <c r="M529" t="n">
-        <v>23</v>
+        <v>360</v>
       </c>
       <c r="N529" t="n">
-        <v>5280</v>
+        <v>7480</v>
       </c>
       <c r="O529" t="n">
-        <v>121440</v>
+        <v>2692800</v>
       </c>
       <c r="P529" t="n">
-        <v>6600</v>
+        <v>9500</v>
       </c>
       <c r="Q529" t="n">
-        <v>151800</v>
+        <v>3420000</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>MG044</t>
-        </is>
-      </c>
-      <c r="B530" t="inlineStr">
-        <is>
-          <t>PT19323</t>
+          <t>J-1314</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>ABACO TREN PT19323</t>
+          <t>PERRO CON GAFAS CAMINA J-1314</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -24262,7 +24257,7 @@
         </is>
       </c>
       <c r="J530" t="n">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="K530" t="n">
         <v>0</v>
@@ -24271,35 +24266,35 @@
         <v>0</v>
       </c>
       <c r="M530" t="n">
-        <v>24</v>
+        <v>144</v>
       </c>
       <c r="N530" t="n">
-        <v>7760</v>
+        <v>6336</v>
       </c>
       <c r="O530" t="n">
-        <v>186240</v>
+        <v>912384</v>
       </c>
       <c r="P530" t="n">
-        <v>9700</v>
+        <v>7500</v>
       </c>
       <c r="Q530" t="n">
-        <v>232800</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>MG051</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>CAJON DIDACTICO RELOJ PT21204</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -24308,7 +24303,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24317,40 +24312,35 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="N531" t="n">
-        <v>22320</v>
+        <v>5280</v>
       </c>
       <c r="O531" t="n">
-        <v>624960</v>
+        <v>232320</v>
       </c>
       <c r="P531" t="n">
-        <v>27900</v>
+        <v>6900</v>
       </c>
       <c r="Q531" t="n">
-        <v>781200</v>
+        <v>303600</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>MG067</t>
-        </is>
-      </c>
-      <c r="B532" t="inlineStr">
-        <is>
-          <t>MG21283</t>
+          <t>J-1317</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>KARAOKE BLUETOOTH MG21283MG</t>
+          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -24359,7 +24349,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24368,40 +24358,35 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="N532" t="n">
-        <v>41161.350714286</v>
+        <v>5280</v>
       </c>
       <c r="O532" t="n">
-        <v>1029033.76785715</v>
+        <v>792000</v>
       </c>
       <c r="P532" t="n">
-        <v>55000</v>
+        <v>6900</v>
       </c>
       <c r="Q532" t="n">
-        <v>1375000</v>
+        <v>1035000</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>MG094</t>
-        </is>
-      </c>
-      <c r="B533" t="inlineStr">
-        <is>
-          <t>mg33153</t>
+          <t>J-1320</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>LANZA DISCOS MED MULTICOLOR MG33153</t>
+          <t>CARRO TODO TERRENO J-1320</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -24410,7 +24395,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>17</v>
+        <v>288</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24419,35 +24404,35 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>17</v>
+        <v>288</v>
       </c>
       <c r="N533" t="n">
-        <v>3840</v>
+        <v>1584</v>
       </c>
       <c r="O533" t="n">
-        <v>65280</v>
+        <v>456192</v>
       </c>
       <c r="P533" t="n">
-        <v>3900</v>
+        <v>2000</v>
       </c>
       <c r="Q533" t="n">
-        <v>66300</v>
+        <v>576000</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>J-1323</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>CARRO FRICCION TODO TERRENO OJITOS J-1323</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -24456,7 +24441,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24465,35 +24450,35 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>9</v>
+        <v>168</v>
       </c>
       <c r="N534" t="n">
-        <v>910.85</v>
+        <v>3872</v>
       </c>
       <c r="O534" t="n">
-        <v>8197.65</v>
+        <v>650496</v>
       </c>
       <c r="P534" t="n">
-        <v>7900</v>
+        <v>4900</v>
       </c>
       <c r="Q534" t="n">
-        <v>71100</v>
+        <v>823200</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>MG16421</t>
+          <t>J-1328</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>CARRO MEZCALDOR BOLSA MDE MG16421</t>
+          <t>CUATRIMOTO LUZ IMPULSO J-1328</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -24502,7 +24487,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24511,40 +24496,35 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="N535" t="n">
-        <v>2775.86</v>
+        <v>6160</v>
       </c>
       <c r="O535" t="n">
-        <v>141568.86</v>
+        <v>517440</v>
       </c>
       <c r="P535" t="n">
-        <v>12500</v>
+        <v>7900</v>
       </c>
       <c r="Q535" t="n">
-        <v>637500</v>
+        <v>663600</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>MG18991</t>
-        </is>
-      </c>
-      <c r="B536" t="inlineStr">
-        <is>
-          <t>MG18991</t>
+          <t>J-1331</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER PILAS MG18991</t>
+          <t>CARRO TODO TERRENO DOBLE IMAGEN J-1331</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24553,7 +24533,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24562,35 +24542,35 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="N536" t="n">
-        <v>8949.32</v>
+        <v>4400</v>
       </c>
       <c r="O536" t="n">
-        <v>125290.48</v>
+        <v>739200</v>
       </c>
       <c r="P536" t="n">
-        <v>28900</v>
+        <v>5900</v>
       </c>
       <c r="Q536" t="n">
-        <v>404600</v>
+        <v>991200</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>J-455</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>TABLETA MAGICA J-455</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -24599,7 +24579,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24608,40 +24588,35 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="N537" t="n">
-        <v>1482.84</v>
+        <v>3520</v>
       </c>
       <c r="O537" t="n">
-        <v>250599.96</v>
+        <v>704000</v>
       </c>
       <c r="P537" t="n">
-        <v>6500</v>
+        <v>4500</v>
       </c>
       <c r="Q537" t="n">
-        <v>1098500</v>
+        <v>900000</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>MG20930</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>MG20930</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>CARRO BUGGY RECARGABLE MG20930</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -24650,7 +24625,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24659,35 +24634,35 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>6</v>
+        <v>192</v>
       </c>
       <c r="N538" t="n">
-        <v>63353.92</v>
+        <v>4576</v>
       </c>
       <c r="O538" t="n">
-        <v>380123.52</v>
+        <v>878592</v>
       </c>
       <c r="P538" t="n">
-        <v>128000</v>
+        <v>5900</v>
       </c>
       <c r="Q538" t="n">
-        <v>768000</v>
+        <v>1132800</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -24696,7 +24671,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -24705,35 +24680,35 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>81</v>
+        <v>300</v>
       </c>
       <c r="N539" t="n">
-        <v>1129.14</v>
+        <v>5280</v>
       </c>
       <c r="O539" t="n">
-        <v>91460.34000000001</v>
+        <v>1584000</v>
       </c>
       <c r="P539" t="n">
         <v>6900</v>
       </c>
       <c r="Q539" t="n">
-        <v>558900</v>
+        <v>2070000</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>MG27668</t>
+          <t>MG040</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
+          <t>ABACO ANIMALES PT17058</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -24742,7 +24717,7 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
@@ -24751,35 +24726,40 @@
         <v>0</v>
       </c>
       <c r="M540" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N540" t="n">
-        <v>15239.8</v>
+        <v>5280</v>
       </c>
       <c r="O540" t="n">
-        <v>320035.8</v>
+        <v>121440</v>
       </c>
       <c r="P540" t="n">
-        <v>15900</v>
+        <v>6600</v>
       </c>
       <c r="Q540" t="n">
-        <v>333900</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>MG28914</t>
+          <t>MG044</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>PT19323</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
+          <t>ABACO TREN PT19323</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24800,32 +24780,32 @@
         <v>24</v>
       </c>
       <c r="N541" t="n">
-        <v>5563</v>
+        <v>7760</v>
       </c>
       <c r="O541" t="n">
-        <v>133512</v>
+        <v>186240</v>
       </c>
       <c r="P541" t="n">
-        <v>11900</v>
+        <v>9700</v>
       </c>
       <c r="Q541" t="n">
-        <v>285600</v>
+        <v>232800</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG051</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>CAJON DIDACTICO RELOJ PT21204</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -24834,7 +24814,7 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
@@ -24843,40 +24823,40 @@
         <v>0</v>
       </c>
       <c r="M542" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N542" t="n">
-        <v>9046.99</v>
+        <v>22320</v>
       </c>
       <c r="O542" t="n">
-        <v>217127.76</v>
+        <v>624960</v>
       </c>
       <c r="P542" t="n">
-        <v>22500</v>
+        <v>27900</v>
       </c>
       <c r="Q542" t="n">
-        <v>540000</v>
+        <v>781200</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>MG30183</t>
+          <t>MG067</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>MG30183</t>
+          <t>MG21283</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
+          <t>KARAOKE BLUETOOTH MG21283MG</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -24885,7 +24865,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -24894,35 +24874,40 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="N543" t="n">
-        <v>3982.6707619048</v>
+        <v>41161.350714286</v>
       </c>
       <c r="O543" t="n">
-        <v>370388.3808571464</v>
+        <v>1029033.76785715</v>
       </c>
       <c r="P543" t="n">
-        <v>10900</v>
+        <v>55000</v>
       </c>
       <c r="Q543" t="n">
-        <v>1013700</v>
+        <v>1375000</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG094</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>mg33153</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>LANZA DISCOS MED MULTICOLOR MG33153</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -24931,7 +24916,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>399</v>
+        <v>17</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -24940,35 +24925,30 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>399</v>
+        <v>17</v>
       </c>
       <c r="N544" t="n">
-        <v>571.87</v>
+        <v>3840</v>
       </c>
       <c r="O544" t="n">
-        <v>228176.13</v>
+        <v>65280</v>
       </c>
       <c r="P544" t="n">
-        <v>2500</v>
+        <v>3900</v>
       </c>
       <c r="Q544" t="n">
-        <v>997500</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B545" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>MG16348</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>SET DE COCINA FOGON GDE MG16348</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -24982,7 +24962,7 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -24991,40 +24971,35 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="N545" t="n">
-        <v>2432.1347916667</v>
+        <v>910.85</v>
       </c>
       <c r="O545" t="n">
-        <v>7296.4043750001</v>
+        <v>8197.65</v>
       </c>
       <c r="P545" t="n">
-        <v>4500</v>
+        <v>7900</v>
       </c>
       <c r="Q545" t="n">
-        <v>13500</v>
+        <v>71100</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>MG40324</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>MG40324</t>
+          <t>MG16421</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>JUEGO DE PESCA MG40324</t>
+          <t>CARRO MEZCALDOR BOLSA MDE MG16421</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -25033,7 +25008,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25042,35 +25017,40 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="N546" t="n">
-        <v>2005.78</v>
+        <v>2775.86</v>
       </c>
       <c r="O546" t="n">
-        <v>2005.78</v>
+        <v>141568.86</v>
       </c>
       <c r="P546" t="n">
-        <v>9500</v>
+        <v>12500</v>
       </c>
       <c r="Q546" t="n">
-        <v>9500</v>
+        <v>637500</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG18991</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>MG18991</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MAQUINA DE COSER PILAS MG18991</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -25079,7 +25059,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>271</v>
+        <v>14</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25088,40 +25068,35 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>271</v>
+        <v>14</v>
       </c>
       <c r="N547" t="n">
-        <v>227.41601620029</v>
+        <v>8949.32</v>
       </c>
       <c r="O547" t="n">
-        <v>61629.74039027859</v>
+        <v>125290.48</v>
       </c>
       <c r="P547" t="n">
-        <v>1200</v>
+        <v>28900</v>
       </c>
       <c r="Q547" t="n">
-        <v>325200</v>
+        <v>404600</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>MG40642</t>
-        </is>
-      </c>
-      <c r="B548" t="inlineStr">
-        <is>
-          <t>MG40642</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>MORRAL TOCADOR PORTABLE MG40642</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -25130,7 +25105,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25139,40 +25114,40 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="N548" t="n">
-        <v>19081.85</v>
+        <v>1482.84</v>
       </c>
       <c r="O548" t="n">
-        <v>286227.75</v>
+        <v>250599.96</v>
       </c>
       <c r="P548" t="n">
-        <v>36900</v>
+        <v>6500</v>
       </c>
       <c r="Q548" t="n">
-        <v>553500</v>
+        <v>1098500</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>MG40888</t>
+          <t>MG20930</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>MG40888</t>
+          <t>MG20930</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>SET DE RESCATE EN BOLSA MG40888</t>
+          <t>CARRO BUGGY RECARGABLE MG20930</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -25181,7 +25156,7 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -25190,35 +25165,35 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N549" t="n">
-        <v>7540.09</v>
+        <v>63353.92</v>
       </c>
       <c r="O549" t="n">
-        <v>82940.99000000001</v>
+        <v>380123.52</v>
       </c>
       <c r="P549" t="n">
-        <v>18500</v>
+        <v>128000</v>
       </c>
       <c r="Q549" t="n">
-        <v>203500</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -25227,7 +25202,7 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25236,34 +25211,44 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
       <c r="N550" t="n">
-        <v>25110.1</v>
+        <v>1129.14</v>
       </c>
       <c r="O550" t="n">
-        <v>778413.1</v>
+        <v>91460.34000000001</v>
       </c>
       <c r="P550" t="n">
-        <v>27900</v>
+        <v>6900</v>
       </c>
       <c r="Q550" t="n">
-        <v>864900</v>
+        <v>558900</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>MR044</t>
+          <t>MG27668</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
+          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>MUÑECA</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J551" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25272,35 +25257,35 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N551" t="n">
-        <v>20720</v>
+        <v>15239.8</v>
       </c>
       <c r="O551" t="n">
-        <v>124320</v>
+        <v>320035.8</v>
       </c>
       <c r="P551" t="n">
-        <v>25900</v>
+        <v>15900</v>
       </c>
       <c r="Q551" t="n">
-        <v>155400</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>MR045</t>
+          <t>MG28914</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>MORRAL ANIMALES STD 0230-02-002</t>
+          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -25309,7 +25294,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25318,34 +25303,44 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="N552" t="n">
-        <v>22080.08</v>
+        <v>5563</v>
       </c>
       <c r="O552" t="n">
-        <v>287041.04</v>
+        <v>133512</v>
       </c>
       <c r="P552" t="n">
-        <v>29900</v>
+        <v>11900</v>
       </c>
       <c r="Q552" t="n">
-        <v>388700</v>
+        <v>285600</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>MR081</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>MORRAL GATICO STD MR081</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>CARROS</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J553" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25354,35 +25349,40 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="N553" t="n">
-        <v>22865</v>
+        <v>9046.99</v>
       </c>
       <c r="O553" t="n">
-        <v>91460</v>
+        <v>217127.76</v>
       </c>
       <c r="P553" t="n">
-        <v>26900</v>
+        <v>22500</v>
       </c>
       <c r="Q553" t="n">
-        <v>107600</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>MG30183</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>MG30183</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -25391,7 +25391,7 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -25400,34 +25400,44 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="N554" t="n">
-        <v>1950.7</v>
+        <v>3982.6707619048</v>
       </c>
       <c r="O554" t="n">
-        <v>64373.1</v>
+        <v>370388.3808571464</v>
       </c>
       <c r="P554" t="n">
-        <v>7500</v>
+        <v>10900</v>
       </c>
       <c r="Q554" t="n">
-        <v>247500</v>
+        <v>1013700</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>SLBT04</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>BOLSA DE REGALO  SLT2023</t>
+          <t>SONAJERO OSO MG40210</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>DIDACTICO</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J555" t="n">
-        <v>146</v>
+        <v>399</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25436,30 +25446,35 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>146</v>
+        <v>399</v>
       </c>
       <c r="N555" t="n">
-        <v>480</v>
+        <v>571.87</v>
       </c>
       <c r="O555" t="n">
-        <v>70080</v>
+        <v>228176.13</v>
       </c>
       <c r="P555" t="n">
-        <v>600</v>
+        <v>2500</v>
       </c>
       <c r="Q555" t="n">
-        <v>87600</v>
+        <v>997500</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>SLT014</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
@@ -25473,7 +25488,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -25482,30 +25497,35 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="N556" t="n">
-        <v>12000</v>
+        <v>2432.1347916667</v>
       </c>
       <c r="O556" t="n">
-        <v>864000</v>
+        <v>7296.4043750001</v>
       </c>
       <c r="P556" t="n">
-        <v>15000</v>
+        <v>4500</v>
       </c>
       <c r="Q556" t="n">
-        <v>1080000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>SLT035</t>
+          <t>MG40324</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>MG40324</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
+          <t>JUEGO DE PESCA MG40324</t>
         </is>
       </c>
       <c r="E557" t="inlineStr">
@@ -25519,7 +25539,7 @@
         </is>
       </c>
       <c r="J557" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -25528,35 +25548,35 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="N557" t="n">
-        <v>6917.54</v>
+        <v>2005.78</v>
       </c>
       <c r="O557" t="n">
-        <v>380464.7</v>
+        <v>2005.78</v>
       </c>
       <c r="P557" t="n">
-        <v>11500</v>
+        <v>9500</v>
       </c>
       <c r="Q557" t="n">
-        <v>632500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>SLT05</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>ESPADA DOBLE SLT2074</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -25565,7 +25585,7 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -25574,35 +25594,40 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>238</v>
+        <v>271</v>
       </c>
       <c r="N558" t="n">
-        <v>4720</v>
+        <v>227.41601620029</v>
       </c>
       <c r="O558" t="n">
-        <v>1123360</v>
+        <v>61629.74039027859</v>
       </c>
       <c r="P558" t="n">
-        <v>5900</v>
+        <v>1200</v>
       </c>
       <c r="Q558" t="n">
-        <v>1404200</v>
+        <v>325200</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>SLT2640</t>
+          <t>MG40642</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>MG40642</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
+          <t>MORRAL TOCADOR PORTABLE MG40642</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -25611,7 +25636,7 @@
         </is>
       </c>
       <c r="J559" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K559" t="n">
         <v>0</v>
@@ -25620,64 +25645,545 @@
         <v>0</v>
       </c>
       <c r="M559" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="N559" t="n">
-        <v>1059.1847727273</v>
+        <v>19081.85</v>
       </c>
       <c r="O559" t="n">
-        <v>22242.8802272733</v>
+        <v>286227.75</v>
       </c>
       <c r="P559" t="n">
-        <v>9500</v>
+        <v>36900</v>
       </c>
       <c r="Q559" t="n">
-        <v>199500</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
+          <t>MG40888</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>MG40888</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>SET DE RESCATE EN BOLSA MG40888</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J560" t="n">
+        <v>11</v>
+      </c>
+      <c r="K560" t="n">
+        <v>0</v>
+      </c>
+      <c r="L560" t="n">
+        <v>0</v>
+      </c>
+      <c r="M560" t="n">
+        <v>11</v>
+      </c>
+      <c r="N560" t="n">
+        <v>7540.09</v>
+      </c>
+      <c r="O560" t="n">
+        <v>82940.99000000001</v>
+      </c>
+      <c r="P560" t="n">
+        <v>18500</v>
+      </c>
+      <c r="Q560" t="n">
+        <v>203500</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>MG41171</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>LANZADORES</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J561" t="n">
+        <v>31</v>
+      </c>
+      <c r="K561" t="n">
+        <v>0</v>
+      </c>
+      <c r="L561" t="n">
+        <v>0</v>
+      </c>
+      <c r="M561" t="n">
+        <v>31</v>
+      </c>
+      <c r="N561" t="n">
+        <v>25110.1</v>
+      </c>
+      <c r="O561" t="n">
+        <v>778413.1</v>
+      </c>
+      <c r="P561" t="n">
+        <v>27900</v>
+      </c>
+      <c r="Q561" t="n">
+        <v>864900</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>MR044</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
+        </is>
+      </c>
+      <c r="J562" t="n">
+        <v>6</v>
+      </c>
+      <c r="K562" t="n">
+        <v>0</v>
+      </c>
+      <c r="L562" t="n">
+        <v>0</v>
+      </c>
+      <c r="M562" t="n">
+        <v>6</v>
+      </c>
+      <c r="N562" t="n">
+        <v>20720</v>
+      </c>
+      <c r="O562" t="n">
+        <v>124320</v>
+      </c>
+      <c r="P562" t="n">
+        <v>25900</v>
+      </c>
+      <c r="Q562" t="n">
+        <v>155400</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>MR045</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>MORRAL ANIMALES STD 0230-02-002</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J563" t="n">
+        <v>13</v>
+      </c>
+      <c r="K563" t="n">
+        <v>0</v>
+      </c>
+      <c r="L563" t="n">
+        <v>0</v>
+      </c>
+      <c r="M563" t="n">
+        <v>13</v>
+      </c>
+      <c r="N563" t="n">
+        <v>22080.08</v>
+      </c>
+      <c r="O563" t="n">
+        <v>287041.04</v>
+      </c>
+      <c r="P563" t="n">
+        <v>29900</v>
+      </c>
+      <c r="Q563" t="n">
+        <v>388700</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>MR081</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>MORRAL GATICO STD MR081</t>
+        </is>
+      </c>
+      <c r="J564" t="n">
+        <v>4</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0</v>
+      </c>
+      <c r="L564" t="n">
+        <v>0</v>
+      </c>
+      <c r="M564" t="n">
+        <v>4</v>
+      </c>
+      <c r="N564" t="n">
+        <v>22865</v>
+      </c>
+      <c r="O564" t="n">
+        <v>91460</v>
+      </c>
+      <c r="P564" t="n">
+        <v>26900</v>
+      </c>
+      <c r="Q564" t="n">
+        <v>107600</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>PT14019</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>DIDACTICOS</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J565" t="n">
+        <v>33</v>
+      </c>
+      <c r="K565" t="n">
+        <v>0</v>
+      </c>
+      <c r="L565" t="n">
+        <v>0</v>
+      </c>
+      <c r="M565" t="n">
+        <v>33</v>
+      </c>
+      <c r="N565" t="n">
+        <v>1950.7</v>
+      </c>
+      <c r="O565" t="n">
+        <v>64373.1</v>
+      </c>
+      <c r="P565" t="n">
+        <v>7500</v>
+      </c>
+      <c r="Q565" t="n">
+        <v>247500</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>SLBT04</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>BOLSA DE REGALO  SLT2023</t>
+        </is>
+      </c>
+      <c r="J566" t="n">
+        <v>146</v>
+      </c>
+      <c r="K566" t="n">
+        <v>0</v>
+      </c>
+      <c r="L566" t="n">
+        <v>0</v>
+      </c>
+      <c r="M566" t="n">
+        <v>146</v>
+      </c>
+      <c r="N566" t="n">
+        <v>480</v>
+      </c>
+      <c r="O566" t="n">
+        <v>70080</v>
+      </c>
+      <c r="P566" t="n">
+        <v>600</v>
+      </c>
+      <c r="Q566" t="n">
+        <v>87600</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>SLT014</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J567" t="n">
+        <v>72</v>
+      </c>
+      <c r="K567" t="n">
+        <v>0</v>
+      </c>
+      <c r="L567" t="n">
+        <v>0</v>
+      </c>
+      <c r="M567" t="n">
+        <v>72</v>
+      </c>
+      <c r="N567" t="n">
+        <v>12000</v>
+      </c>
+      <c r="O567" t="n">
+        <v>864000</v>
+      </c>
+      <c r="P567" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q567" t="n">
+        <v>1080000</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>SLT035</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J568" t="n">
+        <v>55</v>
+      </c>
+      <c r="K568" t="n">
+        <v>0</v>
+      </c>
+      <c r="L568" t="n">
+        <v>0</v>
+      </c>
+      <c r="M568" t="n">
+        <v>55</v>
+      </c>
+      <c r="N568" t="n">
+        <v>6917.54</v>
+      </c>
+      <c r="O568" t="n">
+        <v>380464.7</v>
+      </c>
+      <c r="P568" t="n">
+        <v>11500</v>
+      </c>
+      <c r="Q568" t="n">
+        <v>632500</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>SLT05</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>ESPADA DOBLE SLT2074</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J569" t="n">
+        <v>238</v>
+      </c>
+      <c r="K569" t="n">
+        <v>0</v>
+      </c>
+      <c r="L569" t="n">
+        <v>0</v>
+      </c>
+      <c r="M569" t="n">
+        <v>238</v>
+      </c>
+      <c r="N569" t="n">
+        <v>4720</v>
+      </c>
+      <c r="O569" t="n">
+        <v>1123360</v>
+      </c>
+      <c r="P569" t="n">
+        <v>5900</v>
+      </c>
+      <c r="Q569" t="n">
+        <v>1404200</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>SLT2640</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J570" t="n">
+        <v>21</v>
+      </c>
+      <c r="K570" t="n">
+        <v>0</v>
+      </c>
+      <c r="L570" t="n">
+        <v>0</v>
+      </c>
+      <c r="M570" t="n">
+        <v>21</v>
+      </c>
+      <c r="N570" t="n">
+        <v>1059.1847727273</v>
+      </c>
+      <c r="O570" t="n">
+        <v>22242.8802272733</v>
+      </c>
+      <c r="P570" t="n">
+        <v>9500</v>
+      </c>
+      <c r="Q570" t="n">
+        <v>199500</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
           <t>SLT2642</t>
         </is>
       </c>
-      <c r="C560" t="inlineStr">
+      <c r="C571" t="inlineStr">
         <is>
           <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
-      <c r="E560" t="inlineStr">
+      <c r="E571" t="inlineStr">
         <is>
           <t>JUGUETERIA</t>
         </is>
       </c>
-      <c r="I560" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J560" t="n">
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Und</t>
+        </is>
+      </c>
+      <c r="J571" t="n">
         <v>53</v>
       </c>
-      <c r="K560" t="n">
-        <v>0</v>
-      </c>
-      <c r="L560" t="n">
-        <v>0</v>
-      </c>
-      <c r="M560" t="n">
+      <c r="K571" t="n">
+        <v>0</v>
+      </c>
+      <c r="L571" t="n">
+        <v>0</v>
+      </c>
+      <c r="M571" t="n">
         <v>53</v>
       </c>
-      <c r="N560" t="n">
+      <c r="N571" t="n">
         <v>341.02143442623</v>
       </c>
-      <c r="O560" t="n">
+      <c r="O571" t="n">
         <v>18074.13602459019</v>
       </c>
-      <c r="P560" t="n">
+      <c r="P571" t="n">
         <v>14500</v>
       </c>
-      <c r="Q560" t="n">
+      <c r="Q571" t="n">
         <v>768500</v>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464699454</v>
+        <v>3376.7464660832</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.17785795</v>
+        <v>1982150.175590839</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.6281595092</v>
+        <v>3910.6281481481</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.2636196316</v>
+        <v>481007.2622222163</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.874070081</v>
+        <v>61666.874081081</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.340592997</v>
+        <v>2281674.340999997</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0593600211</v>
+        <v>1098.059452236</v>
       </c>
       <c r="O73" t="n">
-        <v>131767.123202532</v>
+        <v>131767.13426832</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -4826,10 +4826,10 @@
         <v>219</v>
       </c>
       <c r="N105" t="n">
-        <v>3795.7100075514</v>
+        <v>3795.7100075529</v>
       </c>
       <c r="O105" t="n">
-        <v>831260.4916537566</v>
+        <v>831260.4916540851</v>
       </c>
       <c r="P105" t="n">
         <v>6200</v>
@@ -5005,10 +5005,10 @@
         <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300486322</v>
+        <v>4890.9300487805</v>
       </c>
       <c r="O109" t="n">
-        <v>2284064.332711237</v>
+        <v>2284064.332780493</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.8500369004</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003908796</v>
+        <v>388902.004428048</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5885,22 +5885,22 @@
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M129" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
         <v>4193.85</v>
       </c>
       <c r="O129" t="n">
-        <v>71295.45000000001</v>
+        <v>0</v>
       </c>
       <c r="P129" t="n">
         <v>7500</v>
       </c>
       <c r="Q129" t="n">
-        <v>127500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5940,10 +5940,10 @@
         <v>501</v>
       </c>
       <c r="N130" t="n">
-        <v>3041.6600131579</v>
+        <v>3041.660013245</v>
       </c>
       <c r="O130" t="n">
-        <v>1523871.666592108</v>
+        <v>1523871.666635745</v>
       </c>
       <c r="P130" t="n">
         <v>5500</v>
@@ -6027,10 +6027,10 @@
         <v>1116</v>
       </c>
       <c r="N132" t="n">
-        <v>4372.2107896237</v>
+        <v>4372.2107901305</v>
       </c>
       <c r="O132" t="n">
-        <v>4879387.24122005</v>
+        <v>4879387.241785638</v>
       </c>
       <c r="P132" t="n">
         <v>7500</v>
@@ -7479,10 +7479,10 @@
         <v>191</v>
       </c>
       <c r="N164" t="n">
-        <v>1630.9235742505</v>
+        <v>1630.9236077879</v>
       </c>
       <c r="O164" t="n">
-        <v>311506.4026818455</v>
+        <v>311506.4090874889</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7525,10 +7525,10 @@
         <v>36</v>
       </c>
       <c r="N165" t="n">
-        <v>1550.1936350279</v>
+        <v>1550.1936746212</v>
       </c>
       <c r="O165" t="n">
-        <v>55806.9708610044</v>
+        <v>55806.9722863632</v>
       </c>
       <c r="P165" t="n">
         <v>2500</v>
@@ -7571,10 +7571,10 @@
         <v>48</v>
       </c>
       <c r="N166" t="n">
-        <v>1579.3906753247</v>
+        <v>1579.3905526316</v>
       </c>
       <c r="O166" t="n">
-        <v>75810.75241558559</v>
+        <v>75810.7465263168</v>
       </c>
       <c r="P166" t="n">
         <v>2900</v>
@@ -8912,10 +8912,10 @@
         <v>348</v>
       </c>
       <c r="N197" t="n">
-        <v>2029.8737669513</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O197" t="n">
-        <v>706396.0708990524</v>
+        <v>706396.1032835844</v>
       </c>
       <c r="P197" t="n">
         <v>3600</v>
@@ -9117,10 +9117,10 @@
         <v>170</v>
       </c>
       <c r="N202" t="n">
-        <v>2680.7396995708</v>
+        <v>2680.739699202</v>
       </c>
       <c r="O202" t="n">
-        <v>455725.748927036</v>
+        <v>455725.74886434</v>
       </c>
       <c r="P202" t="n">
         <v>4900</v>
@@ -9459,22 +9459,22 @@
         <v>0</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="M210" t="n">
-        <v>364</v>
+        <v>333</v>
       </c>
       <c r="N210" t="n">
         <v>3877.89</v>
       </c>
       <c r="O210" t="n">
-        <v>1411551.96</v>
+        <v>1291337.37</v>
       </c>
       <c r="P210" t="n">
         <v>6500</v>
       </c>
       <c r="Q210" t="n">
-        <v>2366000</v>
+        <v>2164500</v>
       </c>
     </row>
     <row r="211">
@@ -9888,10 +9888,10 @@
         <v>37</v>
       </c>
       <c r="N220" t="n">
-        <v>27123.765223881</v>
+        <v>27123.765205993</v>
       </c>
       <c r="O220" t="n">
-        <v>1003579.313283597</v>
+        <v>1003579.312621741</v>
       </c>
       <c r="P220" t="n">
         <v>44500</v>
@@ -10313,10 +10313,10 @@
         <v>180</v>
       </c>
       <c r="N230" t="n">
-        <v>7969.9501669196</v>
+        <v>7969.9501671733</v>
       </c>
       <c r="O230" t="n">
-        <v>1434591.030045528</v>
+        <v>1434591.030091194</v>
       </c>
       <c r="P230" t="n">
         <v>12900</v>
@@ -11718,10 +11718,10 @@
         <v>1111</v>
       </c>
       <c r="N261" t="n">
-        <v>1778.4726251691</v>
+        <v>1778.4726394558</v>
       </c>
       <c r="O261" t="n">
-        <v>1975883.08656287</v>
+        <v>1975883.102435394</v>
       </c>
       <c r="P261" t="n">
         <v>4900</v>
@@ -14032,10 +14032,10 @@
         <v>263</v>
       </c>
       <c r="N311" t="n">
-        <v>2252.2968774194</v>
+        <v>2252.2969855832</v>
       </c>
       <c r="O311" t="n">
-        <v>592354.0787613022</v>
+        <v>592354.1072083815</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
@@ -14219,10 +14219,10 @@
         <v>504</v>
       </c>
       <c r="N315" t="n">
-        <v>2328.1187161545</v>
+        <v>2328.1187114504</v>
       </c>
       <c r="O315" t="n">
-        <v>1173371.832941868</v>
+        <v>1173371.830571002</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -14443,22 +14443,22 @@
         <v>0</v>
       </c>
       <c r="L320" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M320" t="n">
-        <v>468</v>
+        <v>432</v>
       </c>
       <c r="N320" t="n">
         <v>4544</v>
       </c>
       <c r="O320" t="n">
-        <v>2126592</v>
+        <v>1963008</v>
       </c>
       <c r="P320" t="n">
         <v>7900</v>
       </c>
       <c r="Q320" t="n">
-        <v>3697200</v>
+        <v>3412800</v>
       </c>
     </row>
     <row r="321">
@@ -14627,22 +14627,22 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M324" t="n">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N324" t="n">
         <v>4907.822092257</v>
       </c>
       <c r="O324" t="n">
-        <v>834329.75568369</v>
+        <v>804882.823130148</v>
       </c>
       <c r="P324" t="n">
         <v>8200</v>
       </c>
       <c r="Q324" t="n">
-        <v>1394000</v>
+        <v>1344800</v>
       </c>
     </row>
     <row r="325">
@@ -14863,10 +14863,10 @@
         <v>84</v>
       </c>
       <c r="N329" t="n">
-        <v>3903.7365705615</v>
+        <v>3903.736684492</v>
       </c>
       <c r="O329" t="n">
-        <v>327913.871927166</v>
+        <v>327913.881497328</v>
       </c>
       <c r="P329" t="n">
         <v>7500</v>
@@ -16468,10 +16468,10 @@
         <v>839</v>
       </c>
       <c r="N364" t="n">
-        <v>1516.0387986728</v>
+        <v>1516.0387953812</v>
       </c>
       <c r="O364" t="n">
-        <v>1271956.552086479</v>
+        <v>1271956.549324827</v>
       </c>
       <c r="P364" t="n">
         <v>2300</v>
@@ -16646,22 +16646,22 @@
         <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="M368" t="n">
-        <v>1269</v>
+        <v>1239</v>
       </c>
       <c r="N368" t="n">
         <v>2454</v>
       </c>
       <c r="O368" t="n">
-        <v>3114126</v>
+        <v>3040506</v>
       </c>
       <c r="P368" t="n">
         <v>4200</v>
       </c>
       <c r="Q368" t="n">
-        <v>5329800</v>
+        <v>5203800</v>
       </c>
     </row>
     <row r="369">
@@ -16875,10 +16875,10 @@
         <v>2243</v>
       </c>
       <c r="N373" t="n">
-        <v>692.15222061657</v>
+        <v>692.15222920696</v>
       </c>
       <c r="O373" t="n">
-        <v>1552497.430842967</v>
+        <v>1552497.450111211</v>
       </c>
       <c r="P373" t="n">
         <v>1200</v>
@@ -18857,10 +18857,10 @@
         <v>2</v>
       </c>
       <c r="N415" t="n">
-        <v>3110.8416960301</v>
+        <v>3110.8415531661</v>
       </c>
       <c r="O415" t="n">
-        <v>6221.6833920602</v>
+        <v>6221.6831063322</v>
       </c>
       <c r="P415" t="n">
         <v>4500</v>
@@ -19791,10 +19791,10 @@
         <v>381</v>
       </c>
       <c r="N435" t="n">
-        <v>1595.5127943686</v>
+        <v>1595.5120596085</v>
       </c>
       <c r="O435" t="n">
-        <v>607890.3746544366</v>
+        <v>607890.0947108385</v>
       </c>
       <c r="P435" t="n">
         <v>2500</v>
@@ -19935,10 +19935,10 @@
         <v>54</v>
       </c>
       <c r="N438" t="n">
-        <v>2098.4049712644</v>
+        <v>2098.405</v>
       </c>
       <c r="O438" t="n">
-        <v>113313.8684482776</v>
+        <v>113313.87</v>
       </c>
       <c r="P438" t="n">
         <v>9500</v>
@@ -20226,10 +20226,10 @@
         <v>23</v>
       </c>
       <c r="N444" t="n">
-        <v>2832.1949275362</v>
+        <v>2832.195</v>
       </c>
       <c r="O444" t="n">
-        <v>65140.4833333326</v>
+        <v>65140.485</v>
       </c>
       <c r="P444" t="n">
         <v>12900</v>
@@ -22601,10 +22601,10 @@
         <v>1216</v>
       </c>
       <c r="N493" t="n">
-        <v>665.32358222629</v>
+        <v>665.32359209922</v>
       </c>
       <c r="O493" t="n">
-        <v>809033.4759871686</v>
+        <v>809033.4879926515</v>
       </c>
       <c r="P493" t="n">
         <v>2900</v>
@@ -22843,10 +22843,10 @@
         <v>288</v>
       </c>
       <c r="N498" t="n">
-        <v>430.60997624703</v>
+        <v>430.6099761621</v>
       </c>
       <c r="O498" t="n">
-        <v>124015.6731591446</v>
+        <v>124015.6731346848</v>
       </c>
       <c r="P498" t="n">
         <v>2200</v>
@@ -23284,10 +23284,10 @@
         <v>116</v>
       </c>
       <c r="N508" t="n">
-        <v>1213.6821194605</v>
+        <v>1213.6821359223</v>
       </c>
       <c r="O508" t="n">
-        <v>140787.125857418</v>
+        <v>140787.1277669868</v>
       </c>
       <c r="P508" t="n">
         <v>1500</v>
@@ -23461,10 +23461,10 @@
         <v>11</v>
       </c>
       <c r="N512" t="n">
-        <v>22951.704839538</v>
+        <v>22951.704819588</v>
       </c>
       <c r="O512" t="n">
-        <v>252468.753234918</v>
+        <v>252468.753015468</v>
       </c>
       <c r="P512" t="n">
         <v>37900</v>
@@ -24263,22 +24263,22 @@
         <v>0</v>
       </c>
       <c r="L530" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M530" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="N530" t="n">
         <v>6336</v>
       </c>
       <c r="O530" t="n">
-        <v>912384</v>
+        <v>0</v>
       </c>
       <c r="P530" t="n">
         <v>7500</v>
       </c>
       <c r="Q530" t="n">
-        <v>1080000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
@@ -24309,22 +24309,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M531" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N531" t="n">
         <v>5280</v>
       </c>
       <c r="O531" t="n">
-        <v>232320</v>
+        <v>200640</v>
       </c>
       <c r="P531" t="n">
         <v>6900</v>
       </c>
       <c r="Q531" t="n">
-        <v>303600</v>
+        <v>262200</v>
       </c>
     </row>
     <row r="532">
@@ -24355,22 +24355,22 @@
         <v>0</v>
       </c>
       <c r="L532" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M532" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="N532" t="n">
         <v>5280</v>
       </c>
       <c r="O532" t="n">
-        <v>792000</v>
+        <v>760320</v>
       </c>
       <c r="P532" t="n">
         <v>6900</v>
       </c>
       <c r="Q532" t="n">
-        <v>1035000</v>
+        <v>993600</v>
       </c>
     </row>
     <row r="533">
@@ -24401,22 +24401,22 @@
         <v>0</v>
       </c>
       <c r="L533" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M533" t="n">
-        <v>288</v>
+        <v>144</v>
       </c>
       <c r="N533" t="n">
         <v>1584</v>
       </c>
       <c r="O533" t="n">
-        <v>456192</v>
+        <v>228096</v>
       </c>
       <c r="P533" t="n">
         <v>2000</v>
       </c>
       <c r="Q533" t="n">
-        <v>576000</v>
+        <v>288000</v>
       </c>
     </row>
     <row r="534">
@@ -24447,22 +24447,22 @@
         <v>0</v>
       </c>
       <c r="L534" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M534" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="N534" t="n">
         <v>3872</v>
       </c>
       <c r="O534" t="n">
-        <v>650496</v>
+        <v>371712</v>
       </c>
       <c r="P534" t="n">
         <v>4900</v>
       </c>
       <c r="Q534" t="n">
-        <v>823200</v>
+        <v>470400</v>
       </c>
     </row>
     <row r="535">
@@ -24493,22 +24493,22 @@
         <v>0</v>
       </c>
       <c r="L535" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M535" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="N535" t="n">
         <v>6160</v>
       </c>
       <c r="O535" t="n">
-        <v>517440</v>
+        <v>0</v>
       </c>
       <c r="P535" t="n">
         <v>7900</v>
       </c>
       <c r="Q535" t="n">
-        <v>663600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="536">
@@ -24539,22 +24539,22 @@
         <v>0</v>
       </c>
       <c r="L536" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="M536" t="n">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="N536" t="n">
         <v>4400</v>
       </c>
       <c r="O536" t="n">
-        <v>739200</v>
+        <v>422400</v>
       </c>
       <c r="P536" t="n">
         <v>5900</v>
       </c>
       <c r="Q536" t="n">
-        <v>991200</v>
+        <v>566400</v>
       </c>
     </row>
     <row r="537">
@@ -24585,22 +24585,22 @@
         <v>0</v>
       </c>
       <c r="L537" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M537" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="N537" t="n">
         <v>3520</v>
       </c>
       <c r="O537" t="n">
-        <v>704000</v>
+        <v>422400</v>
       </c>
       <c r="P537" t="n">
         <v>4500</v>
       </c>
       <c r="Q537" t="n">
-        <v>900000</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="538">
@@ -24631,22 +24631,22 @@
         <v>0</v>
       </c>
       <c r="L538" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M538" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="N538" t="n">
         <v>4576</v>
       </c>
       <c r="O538" t="n">
-        <v>878592</v>
+        <v>851136</v>
       </c>
       <c r="P538" t="n">
         <v>5900</v>
       </c>
       <c r="Q538" t="n">
-        <v>1132800</v>
+        <v>1097400</v>
       </c>
     </row>
     <row r="539">
@@ -24677,22 +24677,22 @@
         <v>0</v>
       </c>
       <c r="L539" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M539" t="n">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="N539" t="n">
         <v>5280</v>
       </c>
       <c r="O539" t="n">
-        <v>1584000</v>
+        <v>1552320</v>
       </c>
       <c r="P539" t="n">
         <v>6900</v>
       </c>
       <c r="Q539" t="n">
-        <v>2070000</v>
+        <v>2028600</v>
       </c>
     </row>
     <row r="540">
@@ -25500,10 +25500,10 @@
         <v>3</v>
       </c>
       <c r="N556" t="n">
-        <v>2432.1347916667</v>
+        <v>2432.1351111111</v>
       </c>
       <c r="O556" t="n">
-        <v>7296.4043750001</v>
+        <v>7296.405333333299</v>
       </c>
       <c r="P556" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -673,10 +673,10 @@
         <v>587</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464660832</v>
+        <v>3376.7464651163</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.175590839</v>
+        <v>1982150.175023268</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8547682119</v>
+        <v>6272.8547761194</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.463708603</v>
+        <v>1794036.465970149</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -2194,10 +2194,10 @@
         <v>37</v>
       </c>
       <c r="N45" t="n">
-        <v>61666.874092141</v>
+        <v>61666.874114441</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.341409217</v>
+        <v>2281674.342234317</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
@@ -3047,10 +3047,10 @@
         <v>434</v>
       </c>
       <c r="N65" t="n">
-        <v>4937.3101635688</v>
+        <v>4937.3101636905</v>
       </c>
       <c r="O65" t="n">
-        <v>2142792.610988859</v>
+        <v>2142792.611041677</v>
       </c>
       <c r="P65" t="n">
         <v>7500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0595661432</v>
+        <v>1098.0597873486</v>
       </c>
       <c r="O73" t="n">
-        <v>131767.147937184</v>
+        <v>131767.174481832</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -5005,10 +5005,10 @@
         <v>467</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.9300487805</v>
+        <v>4890.93004884</v>
       </c>
       <c r="O109" t="n">
-        <v>2284064.332780493</v>
+        <v>2284064.33280828</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.8500325733</v>
+        <v>3240.850037037</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.003908796</v>
+        <v>388902.00444444</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5899,10 +5899,10 @@
         <v>501</v>
       </c>
       <c r="N129" t="n">
-        <v>3041.660013245</v>
+        <v>3041.6600132802</v>
       </c>
       <c r="O129" t="n">
-        <v>1523871.666635745</v>
+        <v>1523871.66665338</v>
       </c>
       <c r="P129" t="n">
         <v>5500</v>
@@ -7438,10 +7438,10 @@
         <v>191</v>
       </c>
       <c r="N163" t="n">
-        <v>1630.9235901027</v>
+        <v>1630.9236367936</v>
       </c>
       <c r="O163" t="n">
-        <v>311506.4057096157</v>
+        <v>311506.4146275776</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -7484,10 +7484,10 @@
         <v>36</v>
       </c>
       <c r="N164" t="n">
-        <v>1550.1936753491</v>
+        <v>1550.1936973199</v>
       </c>
       <c r="O164" t="n">
-        <v>55806.9723125676</v>
+        <v>55806.9731035164</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7530,10 +7530,10 @@
         <v>48</v>
       </c>
       <c r="N165" t="n">
-        <v>1579.3905526316</v>
+        <v>1579.3904266667</v>
       </c>
       <c r="O165" t="n">
-        <v>75810.7465263168</v>
+        <v>75810.74048000161</v>
       </c>
       <c r="P165" t="n">
         <v>2900</v>
@@ -8420,10 +8420,10 @@
         <v>674</v>
       </c>
       <c r="N185" t="n">
-        <v>4196.8725291181</v>
+        <v>4196.8725298197</v>
       </c>
       <c r="O185" t="n">
-        <v>2828692.084625599</v>
+        <v>2828692.085098478</v>
       </c>
       <c r="P185" t="n">
         <v>5900</v>
@@ -8543,10 +8543,10 @@
         <v>93</v>
       </c>
       <c r="N188" t="n">
-        <v>7537.4721969697</v>
+        <v>7537.4722307692</v>
       </c>
       <c r="O188" t="n">
-        <v>700984.9143181822</v>
+        <v>700984.9174615355</v>
       </c>
       <c r="P188" t="n">
         <v>8900</v>
@@ -8871,10 +8871,10 @@
         <v>348</v>
       </c>
       <c r="N196" t="n">
-        <v>2029.8738129131</v>
+        <v>2029.8738600103</v>
       </c>
       <c r="O196" t="n">
-        <v>706396.0868937587</v>
+        <v>706396.1032835844</v>
       </c>
       <c r="P196" t="n">
         <v>3600</v>
@@ -10544,10 +10544,10 @@
         <v>154</v>
       </c>
       <c r="N235" t="n">
-        <v>548.14720461095</v>
+        <v>548.1471884058</v>
       </c>
       <c r="O235" t="n">
-        <v>84414.6695100863</v>
+        <v>84414.6670144932</v>
       </c>
       <c r="P235" t="n">
         <v>2000</v>
@@ -11677,10 +11677,10 @@
         <v>1111</v>
       </c>
       <c r="N260" t="n">
-        <v>1778.4726299141</v>
+        <v>1778.4726458554</v>
       </c>
       <c r="O260" t="n">
-        <v>1975883.091834565</v>
+        <v>1975883.109545349</v>
       </c>
       <c r="P260" t="n">
         <v>4900</v>
@@ -14178,10 +14178,10 @@
         <v>504</v>
       </c>
       <c r="N314" t="n">
-        <v>2328.1187114504</v>
+        <v>2328.1187098747</v>
       </c>
       <c r="O314" t="n">
-        <v>1173371.830571002</v>
+        <v>1173371.829776849</v>
       </c>
       <c r="P314" t="n">
         <v>4500</v>
@@ -16427,10 +16427,10 @@
         <v>839</v>
       </c>
       <c r="N363" t="n">
-        <v>1516.0387982037</v>
+        <v>1516.0387951453</v>
       </c>
       <c r="O363" t="n">
-        <v>1271956.551692904</v>
+        <v>1271956.549126907</v>
       </c>
       <c r="P363" t="n">
         <v>2300</v>
@@ -18816,10 +18816,10 @@
         <v>2</v>
       </c>
       <c r="N414" t="n">
-        <v>3110.8415227818</v>
+        <v>3110.8414032101</v>
       </c>
       <c r="O414" t="n">
-        <v>6221.6830455636</v>
+        <v>6221.6828064202</v>
       </c>
       <c r="P414" t="n">
         <v>4500</v>
@@ -19750,10 +19750,10 @@
         <v>381</v>
       </c>
       <c r="N434" t="n">
-        <v>1595.5123423818</v>
+        <v>1595.5119633274</v>
       </c>
       <c r="O434" t="n">
-        <v>607890.2024474657</v>
+        <v>607890.0580277394</v>
       </c>
       <c r="P434" t="n">
         <v>2500</v>
@@ -21834,10 +21834,10 @@
         <v>152</v>
       </c>
       <c r="N477" t="n">
-        <v>7046.9398281418</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O477" t="n">
-        <v>1071134.853877553</v>
+        <v>1071134.85384384</v>
       </c>
       <c r="P477" t="n">
         <v>9900</v>
@@ -22802,10 +22802,10 @@
         <v>288</v>
       </c>
       <c r="N497" t="n">
-        <v>430.6099761621</v>
+        <v>430.60997607656</v>
       </c>
       <c r="O497" t="n">
-        <v>124015.6731346848</v>
+        <v>124015.6731100493</v>
       </c>
       <c r="P497" t="n">
         <v>2200</v>
@@ -23420,10 +23420,10 @@
         <v>11</v>
       </c>
       <c r="N511" t="n">
-        <v>22951.704812903</v>
+        <v>22951.704799483</v>
       </c>
       <c r="O511" t="n">
-        <v>252468.752941933</v>
+        <v>252468.752794313</v>
       </c>
       <c r="P511" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q568"/>
+  <dimension ref="A1:Q566"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-28</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-29</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -670,19 +670,19 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="N7" t="n">
         <v>3376.7464651163</v>
       </c>
       <c r="O7" t="n">
-        <v>1982150.175023268</v>
+        <v>1931498.978046524</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
       </c>
       <c r="Q7" t="n">
-        <v>2641500</v>
+        <v>2574000</v>
       </c>
     </row>
     <row r="8">
@@ -1666,10 +1666,10 @@
         <v>123</v>
       </c>
       <c r="N32" t="n">
-        <v>3910.6281404959</v>
+        <v>3910.628136646</v>
       </c>
       <c r="O32" t="n">
-        <v>481007.2612809957</v>
+        <v>481007.260807458</v>
       </c>
       <c r="P32" t="n">
         <v>9100</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2191,19 +2191,19 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="N45" t="n">
         <v>61666.874114441</v>
       </c>
       <c r="O45" t="n">
-        <v>2281674.342234317</v>
+        <v>2096673.719890994</v>
       </c>
       <c r="P45" t="n">
         <v>98900</v>
       </c>
       <c r="Q45" t="n">
-        <v>3659300</v>
+        <v>3362600</v>
       </c>
     </row>
     <row r="46">
@@ -4640,7 +4640,7 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4649,19 +4649,19 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="N101" t="n">
         <v>5002</v>
       </c>
       <c r="O101" t="n">
-        <v>2706082</v>
+        <v>2646058</v>
       </c>
       <c r="P101" t="n">
         <v>8400</v>
       </c>
       <c r="Q101" t="n">
-        <v>4544400</v>
+        <v>4443600</v>
       </c>
     </row>
     <row r="102">
@@ -4993,7 +4993,7 @@
         </is>
       </c>
       <c r="J109" t="n">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="K109" t="n">
         <v>0</v>
@@ -5002,19 +5002,19 @@
         <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="N109" t="n">
-        <v>4890.93004884</v>
+        <v>4890.9300488998</v>
       </c>
       <c r="O109" t="n">
-        <v>2284064.33280828</v>
+        <v>2244936.892445008</v>
       </c>
       <c r="P109" t="n">
         <v>8200</v>
       </c>
       <c r="Q109" t="n">
-        <v>3829400</v>
+        <v>3763800</v>
       </c>
     </row>
     <row r="110">
@@ -5453,10 +5453,10 @@
         <v>120</v>
       </c>
       <c r="N119" t="n">
-        <v>3240.850037037</v>
+        <v>3240.8500371058</v>
       </c>
       <c r="O119" t="n">
-        <v>388902.00444444</v>
+        <v>388902.004452696</v>
       </c>
       <c r="P119" t="n">
         <v>5200</v>
@@ -5538,10 +5538,10 @@
         <v>135</v>
       </c>
       <c r="N121" t="n">
-        <v>5191.4800278552</v>
+        <v>5191.4800280899</v>
       </c>
       <c r="O121" t="n">
-        <v>700849.8037604521</v>
+        <v>700849.8037921365</v>
       </c>
       <c r="P121" t="n">
         <v>9100</v>
@@ -5986,10 +5986,10 @@
         <v>1116</v>
       </c>
       <c r="N131" t="n">
-        <v>4372.2107902432</v>
+        <v>4372.2107903559</v>
       </c>
       <c r="O131" t="n">
-        <v>4879387.241911411</v>
+        <v>4879387.242037185</v>
       </c>
       <c r="P131" t="n">
         <v>7500</v>
@@ -6148,7 +6148,7 @@
         </is>
       </c>
       <c r="J135" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K135" t="n">
         <v>0</v>
@@ -6157,19 +6157,19 @@
         <v>0</v>
       </c>
       <c r="M135" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="N135" t="n">
         <v>2695.04</v>
       </c>
       <c r="O135" t="n">
-        <v>191347.84</v>
+        <v>175177.6</v>
       </c>
       <c r="P135" t="n">
         <v>7300</v>
       </c>
       <c r="Q135" t="n">
-        <v>518300</v>
+        <v>474500</v>
       </c>
     </row>
     <row r="136">
@@ -7438,10 +7438,10 @@
         <v>191</v>
       </c>
       <c r="N163" t="n">
-        <v>1630.9236367936</v>
+        <v>1630.9236471425</v>
       </c>
       <c r="O163" t="n">
-        <v>311506.4146275776</v>
+        <v>311506.4166042175</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -7484,10 +7484,10 @@
         <v>36</v>
       </c>
       <c r="N164" t="n">
-        <v>1550.1936973199</v>
+        <v>1550.1936995315</v>
       </c>
       <c r="O164" t="n">
-        <v>55806.9731035164</v>
+        <v>55806.973183134</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -8531,7 +8531,7 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K188" t="n">
         <v>0</v>
@@ -8540,19 +8540,19 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N188" t="n">
         <v>7537.4722307692</v>
       </c>
       <c r="O188" t="n">
-        <v>700984.9174615355</v>
+        <v>685909.9729999972</v>
       </c>
       <c r="P188" t="n">
         <v>8900</v>
       </c>
       <c r="Q188" t="n">
-        <v>827700</v>
+        <v>809900</v>
       </c>
     </row>
     <row r="189">
@@ -9076,10 +9076,10 @@
         <v>170</v>
       </c>
       <c r="N201" t="n">
-        <v>2680.7396988322</v>
+        <v>2680.739695084</v>
       </c>
       <c r="O201" t="n">
-        <v>455725.748801474</v>
+        <v>455725.74816428</v>
       </c>
       <c r="P201" t="n">
         <v>4900</v>
@@ -11491,7 +11491,7 @@
         </is>
       </c>
       <c r="J256" t="n">
-        <v>188</v>
+        <v>5</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11500,19 +11500,19 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>188</v>
+        <v>5</v>
       </c>
       <c r="N256" t="n">
         <v>3646</v>
       </c>
       <c r="O256" t="n">
-        <v>685448</v>
+        <v>18230</v>
       </c>
       <c r="P256" t="n">
         <v>6900</v>
       </c>
       <c r="Q256" t="n">
-        <v>1297200</v>
+        <v>34500</v>
       </c>
     </row>
     <row r="257">
@@ -13519,7 +13519,7 @@
         </is>
       </c>
       <c r="J300" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
@@ -13528,19 +13528,19 @@
         <v>0</v>
       </c>
       <c r="M300" t="n">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="N300" t="n">
         <v>4024</v>
       </c>
       <c r="O300" t="n">
-        <v>547264</v>
+        <v>523120</v>
       </c>
       <c r="P300" t="n">
         <v>6900</v>
       </c>
       <c r="Q300" t="n">
-        <v>938400</v>
+        <v>897000</v>
       </c>
     </row>
     <row r="301">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="J358" t="n">
-        <v>1766</v>
+        <v>1758</v>
       </c>
       <c r="K358" t="n">
         <v>0</v>
@@ -16194,19 +16194,19 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>1766</v>
+        <v>1758</v>
       </c>
       <c r="N358" t="n">
         <v>1326</v>
       </c>
       <c r="O358" t="n">
-        <v>2341716</v>
+        <v>2331108</v>
       </c>
       <c r="P358" t="n">
         <v>2500</v>
       </c>
       <c r="Q358" t="n">
-        <v>4415000</v>
+        <v>4395000</v>
       </c>
     </row>
     <row r="359">
@@ -17729,7 +17729,7 @@
         </is>
       </c>
       <c r="J391" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="K391" t="n">
         <v>0</v>
@@ -17738,19 +17738,19 @@
         <v>0</v>
       </c>
       <c r="M391" t="n">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="N391" t="n">
         <v>7559.75</v>
       </c>
       <c r="O391" t="n">
-        <v>703056.75</v>
+        <v>612339.75</v>
       </c>
       <c r="P391" t="n">
         <v>7900</v>
       </c>
       <c r="Q391" t="n">
-        <v>734700</v>
+        <v>639900</v>
       </c>
     </row>
     <row r="392">
@@ -18395,10 +18395,10 @@
         <v>45</v>
       </c>
       <c r="N405" t="n">
-        <v>4032.3968461538</v>
+        <v>4032.3968380463</v>
       </c>
       <c r="O405" t="n">
-        <v>181457.858076921</v>
+        <v>181457.8577120835</v>
       </c>
       <c r="P405" t="n">
         <v>4200</v>
@@ -18619,7 +18619,7 @@
         </is>
       </c>
       <c r="J410" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K410" t="n">
         <v>0</v>
@@ -18628,19 +18628,19 @@
         <v>0</v>
       </c>
       <c r="M410" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N410" t="n">
         <v>10682.62</v>
       </c>
       <c r="O410" t="n">
-        <v>320478.6</v>
+        <v>288430.74</v>
       </c>
       <c r="P410" t="n">
         <v>13500</v>
       </c>
       <c r="Q410" t="n">
-        <v>405000</v>
+        <v>364500</v>
       </c>
     </row>
     <row r="411">
@@ -18714,7 +18714,7 @@
         </is>
       </c>
       <c r="J412" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K412" t="n">
         <v>0</v>
@@ -18723,19 +18723,19 @@
         <v>0</v>
       </c>
       <c r="M412" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N412" t="n">
         <v>9447.25</v>
       </c>
       <c r="O412" t="n">
-        <v>226734</v>
+        <v>188945</v>
       </c>
       <c r="P412" t="n">
         <v>9900</v>
       </c>
       <c r="Q412" t="n">
-        <v>237600</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="413">
@@ -18816,10 +18816,10 @@
         <v>2</v>
       </c>
       <c r="N414" t="n">
-        <v>3110.8414032101</v>
+        <v>3110.8413822526</v>
       </c>
       <c r="O414" t="n">
-        <v>6221.6828064202</v>
+        <v>6221.6827645052</v>
       </c>
       <c r="P414" t="n">
         <v>4500</v>
@@ -20559,7 +20559,7 @@
         </is>
       </c>
       <c r="J451" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K451" t="n">
         <v>0</v>
@@ -20568,19 +20568,19 @@
         <v>0</v>
       </c>
       <c r="M451" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N451" t="n">
         <v>12448.353571429</v>
       </c>
       <c r="O451" t="n">
-        <v>224070.364285722</v>
+        <v>161828.596428577</v>
       </c>
       <c r="P451" t="n">
         <v>22900</v>
       </c>
       <c r="Q451" t="n">
-        <v>412200</v>
+        <v>297700</v>
       </c>
     </row>
     <row r="452">
@@ -21558,20 +21558,17 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>C7457</t>
-        </is>
-      </c>
-      <c r="B472" t="n">
-        <v>6957768811154</v>
+          <t>C7470</t>
+        </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>AVION CON LUZ Y SONIDO C7457</t>
+          <t>CARRO COLECCION METALICO MERCECES GLS C7470</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -21580,7 +21577,7 @@
         </is>
       </c>
       <c r="J472" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K472" t="n">
         <v>0</v>
@@ -21589,30 +21586,33 @@
         <v>0</v>
       </c>
       <c r="M472" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="N472" t="n">
-        <v>11939.92</v>
+        <v>14170.65</v>
       </c>
       <c r="O472" t="n">
-        <v>59699.6</v>
+        <v>425119.5</v>
       </c>
       <c r="P472" t="n">
-        <v>25900</v>
+        <v>49000</v>
       </c>
       <c r="Q472" t="n">
-        <v>129500</v>
+        <v>1470000</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>C7470</t>
-        </is>
+          <t>C7475</t>
+        </is>
+      </c>
+      <c r="B473" t="n">
+        <v>6896988512536</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>CARRO COLECCION METALICO MERCECES GLS C7470</t>
+          <t>CARRO METALICO COLECCION BMW C7475</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
@@ -21626,7 +21626,7 @@
         </is>
       </c>
       <c r="J473" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="K473" t="n">
         <v>0</v>
@@ -21635,38 +21635,38 @@
         <v>0</v>
       </c>
       <c r="M473" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="N473" t="n">
-        <v>14170.65</v>
+        <v>10798.03</v>
       </c>
       <c r="O473" t="n">
-        <v>425119.5</v>
+        <v>280748.78</v>
       </c>
       <c r="P473" t="n">
-        <v>49000</v>
+        <v>45000</v>
       </c>
       <c r="Q473" t="n">
-        <v>1470000</v>
+        <v>1170000</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>C7475</t>
+          <t>C7513</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>6896988512536</v>
+        <v>6905698382824</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>CARRO METALICO COLECCION BMW C7475</t>
+          <t>SONAJERO BOLA LUZ GDE C7513</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="J474" t="n">
-        <v>26</v>
+        <v>306</v>
       </c>
       <c r="K474" t="n">
         <v>0</v>
@@ -21684,33 +21684,33 @@
         <v>0</v>
       </c>
       <c r="M474" t="n">
-        <v>26</v>
+        <v>306</v>
       </c>
       <c r="N474" t="n">
-        <v>10798.03</v>
+        <v>1024.29</v>
       </c>
       <c r="O474" t="n">
-        <v>280748.78</v>
+        <v>313432.74</v>
       </c>
       <c r="P474" t="n">
-        <v>45000</v>
+        <v>2900</v>
       </c>
       <c r="Q474" t="n">
-        <v>1170000</v>
+        <v>887400</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>C7513</t>
+          <t>C7514</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>6905698382824</v>
+        <v>6905698386815</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>SONAJERO BOLA LUZ GDE C7513</t>
+          <t>SONAJERO LUZ BOLSA C7514</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
@@ -21724,7 +21724,7 @@
         </is>
       </c>
       <c r="J475" t="n">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="K475" t="n">
         <v>0</v>
@@ -21733,33 +21733,33 @@
         <v>0</v>
       </c>
       <c r="M475" t="n">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="N475" t="n">
-        <v>1024.29</v>
+        <v>711.48</v>
       </c>
       <c r="O475" t="n">
-        <v>313432.74</v>
+        <v>239057.28</v>
       </c>
       <c r="P475" t="n">
-        <v>2900</v>
+        <v>2500</v>
       </c>
       <c r="Q475" t="n">
-        <v>887400</v>
+        <v>840000</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>C7514</t>
+          <t>C7534</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>6905698386815</v>
+        <v>6951241752002</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>SONAJERO LUZ BOLSA C7514</t>
+          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
@@ -21773,7 +21773,7 @@
         </is>
       </c>
       <c r="J476" t="n">
-        <v>336</v>
+        <v>152</v>
       </c>
       <c r="K476" t="n">
         <v>0</v>
@@ -21782,38 +21782,38 @@
         <v>0</v>
       </c>
       <c r="M476" t="n">
-        <v>336</v>
+        <v>152</v>
       </c>
       <c r="N476" t="n">
-        <v>711.48</v>
+        <v>7046.93982792</v>
       </c>
       <c r="O476" t="n">
-        <v>239057.28</v>
+        <v>1071134.85384384</v>
       </c>
       <c r="P476" t="n">
-        <v>2500</v>
+        <v>9900</v>
       </c>
       <c r="Q476" t="n">
-        <v>840000</v>
+        <v>1504800</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>C7534</t>
+          <t>C7553-A</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>6951241752002</v>
+        <v>6970635795647</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>GORRO PELUCHE LUZ C7534-A-B-C-D-E-F</t>
+          <t>FICHAS DE ARMAR PEERO TERRY SMALL 1350PCS/16064</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>FICHA DE ARMAR</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -21822,7 +21822,7 @@
         </is>
       </c>
       <c r="J477" t="n">
-        <v>152</v>
+        <v>6</v>
       </c>
       <c r="K477" t="n">
         <v>0</v>
@@ -21831,33 +21831,33 @@
         <v>0</v>
       </c>
       <c r="M477" t="n">
-        <v>152</v>
+        <v>6</v>
       </c>
       <c r="N477" t="n">
-        <v>7046.93982792</v>
+        <v>12400.38</v>
       </c>
       <c r="O477" t="n">
-        <v>1071134.85384384</v>
+        <v>74402.28</v>
       </c>
       <c r="P477" t="n">
-        <v>9900</v>
+        <v>26900</v>
       </c>
       <c r="Q477" t="n">
-        <v>1504800</v>
+        <v>161400</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>C7553-A</t>
+          <t>C7554-B</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>6970635795647</v>
+        <v>6970635793926</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR PEERO TERRY SMALL 1350PCS/16064</t>
+          <t>FICHAS 3D MINI PERRITO SIBERIANO HUSKY C7554-B/18392</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
@@ -21871,7 +21871,7 @@
         </is>
       </c>
       <c r="J478" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K478" t="n">
         <v>0</v>
@@ -21880,33 +21880,33 @@
         <v>0</v>
       </c>
       <c r="M478" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N478" t="n">
-        <v>12400.38</v>
+        <v>15577.048235294</v>
       </c>
       <c r="O478" t="n">
-        <v>74402.28</v>
+        <v>140193.434117646</v>
       </c>
       <c r="P478" t="n">
-        <v>26900</v>
+        <v>19900</v>
       </c>
       <c r="Q478" t="n">
-        <v>161400</v>
+        <v>179100</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>C7554-B</t>
+          <t>C7554-C</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>6970635793926</v>
+        <v>6970635793933</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>FICHAS 3D MINI PERRITO SIBERIANO HUSKY C7554-B/18392</t>
+          <t>FICHAS 3D MINI PERRITO LABRADOR CON GAFAS C7554/18393</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
@@ -21932,10 +21932,10 @@
         <v>9</v>
       </c>
       <c r="N479" t="n">
-        <v>15577.048235294</v>
+        <v>15571.056923077</v>
       </c>
       <c r="O479" t="n">
-        <v>140193.434117646</v>
+        <v>140139.512307693</v>
       </c>
       <c r="P479" t="n">
         <v>19900</v>
@@ -21947,15 +21947,15 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>C7554-C</t>
+          <t>C7554-D</t>
         </is>
       </c>
       <c r="B480" t="n">
-        <v>6970635793933</v>
+        <v>6970635793940</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>FICHAS 3D MINI PERRITO LABRADOR CON GAFAS C7554/18393</t>
+          <t>FICHAS 3D PERRITO BULLDOG C7554-D/18394</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
@@ -21969,7 +21969,7 @@
         </is>
       </c>
       <c r="J480" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K480" t="n">
         <v>0</v>
@@ -21978,33 +21978,33 @@
         <v>0</v>
       </c>
       <c r="M480" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N480" t="n">
-        <v>15571.056923077</v>
+        <v>8931.441052631601</v>
       </c>
       <c r="O480" t="n">
-        <v>140139.512307693</v>
+        <v>35725.7642105264</v>
       </c>
       <c r="P480" t="n">
         <v>19900</v>
       </c>
       <c r="Q480" t="n">
-        <v>179100</v>
+        <v>79600</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>C7554-D</t>
+          <t>C7554-E</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>6970635793940</v>
+        <v>6970635793964</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>FICHAS 3D PERRITO BULLDOG C7554-D/18394</t>
+          <t>FICHAS 3D MINI PERRITO WELSH CORGI 997PCS C7554-E/18396</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
@@ -22018,7 +22018,7 @@
         </is>
       </c>
       <c r="J481" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K481" t="n">
         <v>0</v>
@@ -22027,33 +22027,33 @@
         <v>0</v>
       </c>
       <c r="M481" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N481" t="n">
-        <v>8931.441052631601</v>
+        <v>14320.330526316</v>
       </c>
       <c r="O481" t="n">
-        <v>35725.7642105264</v>
+        <v>100242.313684212</v>
       </c>
       <c r="P481" t="n">
         <v>19900</v>
       </c>
       <c r="Q481" t="n">
-        <v>79600</v>
+        <v>139300</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>C7554-E</t>
+          <t>C7555-B</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>6970635793964</v>
+        <v>6970635795388</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>FICHAS 3D MINI PERRITO WELSH CORGI 997PCS C7554-E/18396</t>
+          <t>FICHAS DE ARMAR 3D GATO OREJAS ROSADAS SMALL C7555-B/16038</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -22067,7 +22067,7 @@
         </is>
       </c>
       <c r="J482" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="K482" t="n">
         <v>0</v>
@@ -22076,33 +22076,33 @@
         <v>0</v>
       </c>
       <c r="M482" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N482" t="n">
-        <v>14320.330526316</v>
+        <v>16146.4984</v>
       </c>
       <c r="O482" t="n">
-        <v>100242.313684212</v>
+        <v>242197.476</v>
       </c>
       <c r="P482" t="n">
-        <v>19900</v>
+        <v>26900</v>
       </c>
       <c r="Q482" t="n">
-        <v>139300</v>
+        <v>403500</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>C7555-B</t>
+          <t>C7557-B</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>6970635795388</v>
+        <v>6970635794909</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>FICHAS DE ARMAR 3D GATO OREJAS ROSADAS SMALL C7555-B/16038</t>
+          <t>FICHAS 3D TIENDA DE TE C7557-B/18490</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
@@ -22116,7 +22116,7 @@
         </is>
       </c>
       <c r="J483" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K483" t="n">
         <v>0</v>
@@ -22125,33 +22125,33 @@
         <v>0</v>
       </c>
       <c r="M483" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N483" t="n">
-        <v>16146.4984</v>
+        <v>15419</v>
       </c>
       <c r="O483" t="n">
-        <v>242197.476</v>
+        <v>169609</v>
       </c>
       <c r="P483" t="n">
-        <v>26900</v>
+        <v>19900</v>
       </c>
       <c r="Q483" t="n">
-        <v>403500</v>
+        <v>218900</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>C7557-B</t>
+          <t>C7557-E</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>6970635794909</v>
+        <v>6970635795166</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>FICHAS 3D TIENDA DE TE C7557-B/18490</t>
+          <t>FICHAS 3D TIENDA DE FLORES C7557-E/16354</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -22165,7 +22165,7 @@
         </is>
       </c>
       <c r="J484" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K484" t="n">
         <v>0</v>
@@ -22174,33 +22174,33 @@
         <v>0</v>
       </c>
       <c r="M484" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="N484" t="n">
         <v>15419</v>
       </c>
       <c r="O484" t="n">
-        <v>169609</v>
+        <v>107933</v>
       </c>
       <c r="P484" t="n">
         <v>19900</v>
       </c>
       <c r="Q484" t="n">
-        <v>218900</v>
+        <v>139300</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>C7557-E</t>
+          <t>C7557-F</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>6970635795166</v>
+        <v>6970635795180</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>FICHAS 3D TIENDA DE FLORES C7557-E/16354</t>
+          <t>FICHAS 3D TIENDA HELLO C7557-F/16355</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
@@ -22214,7 +22214,7 @@
         </is>
       </c>
       <c r="J485" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K485" t="n">
         <v>0</v>
@@ -22223,33 +22223,33 @@
         <v>0</v>
       </c>
       <c r="M485" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="N485" t="n">
-        <v>15419</v>
+        <v>10279.67</v>
       </c>
       <c r="O485" t="n">
-        <v>107933</v>
+        <v>92517.03</v>
       </c>
       <c r="P485" t="n">
         <v>19900</v>
       </c>
       <c r="Q485" t="n">
-        <v>139300</v>
+        <v>179100</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>C7557-F</t>
+          <t>C7557-G</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>6970635795180</v>
+        <v>6970635795227</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>FICHAS 3D TIENDA HELLO C7557-F/16355</t>
+          <t>FICHAS 3D TIENDA MOOTY MILK-TEA C7557-G/16356</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
@@ -22263,7 +22263,7 @@
         </is>
       </c>
       <c r="J486" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K486" t="n">
         <v>0</v>
@@ -22272,33 +22272,33 @@
         <v>0</v>
       </c>
       <c r="M486" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N486" t="n">
-        <v>10279.67</v>
+        <v>15307.69</v>
       </c>
       <c r="O486" t="n">
-        <v>92517.03</v>
+        <v>214307.66</v>
       </c>
       <c r="P486" t="n">
         <v>19900</v>
       </c>
       <c r="Q486" t="n">
-        <v>179100</v>
+        <v>278600</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>C7557-G</t>
+          <t>C7557-H</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>6970635795227</v>
+        <v>6970635795234</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>FICHAS 3D TIENDA MOOTY MILK-TEA C7557-G/16356</t>
+          <t>FICHAS 3D TIENDA VIDEO JUEGOS C7557-H/16357</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -22312,7 +22312,7 @@
         </is>
       </c>
       <c r="J487" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K487" t="n">
         <v>0</v>
@@ -22321,38 +22321,35 @@
         <v>0</v>
       </c>
       <c r="M487" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N487" t="n">
         <v>15307.69</v>
       </c>
       <c r="O487" t="n">
-        <v>214307.66</v>
+        <v>91846.14</v>
       </c>
       <c r="P487" t="n">
         <v>19900</v>
       </c>
       <c r="Q487" t="n">
-        <v>278600</v>
+        <v>119400</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>C7557-H</t>
-        </is>
-      </c>
-      <c r="B488" t="n">
-        <v>6970635795234</v>
+          <t>C7560</t>
+        </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>FICHAS 3D TIENDA VIDEO JUEGOS C7557-H/16357</t>
+          <t>BARRA LUMINOSA 48CM C7560/211</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>FICHA DE ARMAR</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -22361,7 +22358,7 @@
         </is>
       </c>
       <c r="J488" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K488" t="n">
         <v>0</v>
@@ -22370,35 +22367,35 @@
         <v>0</v>
       </c>
       <c r="M488" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N488" t="n">
-        <v>15307.69</v>
+        <v>796.3099999999999</v>
       </c>
       <c r="O488" t="n">
-        <v>91846.14</v>
+        <v>3185.24</v>
       </c>
       <c r="P488" t="n">
-        <v>19900</v>
+        <v>2500</v>
       </c>
       <c r="Q488" t="n">
-        <v>119400</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>C7560</t>
+          <t>C7560AC</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>BARRA LUMINOSA 48CM C7560/211</t>
+          <t>TRICICLO INFANTIL OSITO C756AC</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -22407,7 +22404,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="K489" t="n">
         <v>0</v>
@@ -22416,35 +22413,35 @@
         <v>0</v>
       </c>
       <c r="M489" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="N489" t="n">
-        <v>796.3099999999999</v>
+        <v>44113.603841808</v>
       </c>
       <c r="O489" t="n">
-        <v>3185.24</v>
+        <v>2955611.457401136</v>
       </c>
       <c r="P489" t="n">
-        <v>2500</v>
+        <v>71900</v>
       </c>
       <c r="Q489" t="n">
-        <v>10000</v>
+        <v>4817300</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>C7560AC</t>
+          <t>C7561-AB</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>TRICICLO INFANTIL OSITO C756AC</t>
+          <t>PATINES BASE DE ALUMINIO  LUZ EN LAS LLANTAS STD C7561-AB</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -22453,7 +22450,7 @@
         </is>
       </c>
       <c r="J490" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="K490" t="n">
         <v>0</v>
@@ -22462,35 +22459,38 @@
         <v>0</v>
       </c>
       <c r="M490" t="n">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="N490" t="n">
-        <v>44113.603841808</v>
+        <v>38508.28</v>
       </c>
       <c r="O490" t="n">
-        <v>2955611.457401136</v>
+        <v>231049.68</v>
       </c>
       <c r="P490" t="n">
-        <v>71900</v>
+        <v>40000</v>
       </c>
       <c r="Q490" t="n">
-        <v>4817300</v>
+        <v>240000</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>C7561-AB</t>
-        </is>
+          <t>C7586</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>7808880075865</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>PATINES BASE DE ALUMINIO  LUZ EN LAS LLANTAS STD C7561-AB</t>
+          <t>BOLITRON ELMO TORNASOL 60gr C7586</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -22499,7 +22499,7 @@
         </is>
       </c>
       <c r="J491" t="n">
-        <v>6</v>
+        <v>1216</v>
       </c>
       <c r="K491" t="n">
         <v>0</v>
@@ -22508,33 +22508,33 @@
         <v>0</v>
       </c>
       <c r="M491" t="n">
-        <v>6</v>
+        <v>1216</v>
       </c>
       <c r="N491" t="n">
-        <v>38508.28</v>
+        <v>665.32359209922</v>
       </c>
       <c r="O491" t="n">
-        <v>231049.68</v>
+        <v>809033.4879926515</v>
       </c>
       <c r="P491" t="n">
-        <v>40000</v>
+        <v>2900</v>
       </c>
       <c r="Q491" t="n">
-        <v>240000</v>
+        <v>3526400</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>C7586</t>
+          <t>C7587</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>7808880075865</v>
+        <v>7587228020247</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>BOLITRON ELMO TORNASOL 60gr C7586</t>
+          <t>TROMPO LUCES DEPORTES C7587</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
@@ -22548,7 +22548,7 @@
         </is>
       </c>
       <c r="J492" t="n">
-        <v>1216</v>
+        <v>396</v>
       </c>
       <c r="K492" t="n">
         <v>0</v>
@@ -22557,33 +22557,30 @@
         <v>0</v>
       </c>
       <c r="M492" t="n">
-        <v>1216</v>
+        <v>396</v>
       </c>
       <c r="N492" t="n">
-        <v>665.32359209922</v>
+        <v>1080.18</v>
       </c>
       <c r="O492" t="n">
-        <v>809033.4879926515</v>
+        <v>427751.28</v>
       </c>
       <c r="P492" t="n">
-        <v>2900</v>
+        <v>4900</v>
       </c>
       <c r="Q492" t="n">
-        <v>3526400</v>
+        <v>1940400</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>C7587</t>
-        </is>
-      </c>
-      <c r="B493" t="n">
-        <v>7587228020247</v>
+          <t>C7589</t>
+        </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>TROMPO LUCES DEPORTES C7587</t>
+          <t>RELOJ BLISTER C7589</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
@@ -22597,7 +22594,7 @@
         </is>
       </c>
       <c r="J493" t="n">
-        <v>396</v>
+        <v>3</v>
       </c>
       <c r="K493" t="n">
         <v>0</v>
@@ -22606,35 +22603,38 @@
         <v>0</v>
       </c>
       <c r="M493" t="n">
-        <v>396</v>
+        <v>3</v>
       </c>
       <c r="N493" t="n">
-        <v>1080.18</v>
+        <v>1139.206</v>
       </c>
       <c r="O493" t="n">
-        <v>427751.28</v>
+        <v>3417.617999999999</v>
       </c>
       <c r="P493" t="n">
-        <v>4900</v>
+        <v>4500</v>
       </c>
       <c r="Q493" t="n">
-        <v>1940400</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>C7589</t>
-        </is>
+          <t>C7610</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>6999899236093</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>RELOJ BLISTER C7589</t>
+          <t>BOTE TIMON PISCINA 80X60 C7610</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>INFLABLES</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -22643,7 +22643,7 @@
         </is>
       </c>
       <c r="J494" t="n">
-        <v>3</v>
+        <v>434</v>
       </c>
       <c r="K494" t="n">
         <v>0</v>
@@ -22652,33 +22652,33 @@
         <v>0</v>
       </c>
       <c r="M494" t="n">
-        <v>3</v>
+        <v>434</v>
       </c>
       <c r="N494" t="n">
-        <v>1139.206</v>
+        <v>7811.9</v>
       </c>
       <c r="O494" t="n">
-        <v>3417.617999999999</v>
+        <v>3390364.6</v>
       </c>
       <c r="P494" t="n">
-        <v>4500</v>
+        <v>13900</v>
       </c>
       <c r="Q494" t="n">
-        <v>13500</v>
+        <v>6032600</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>C7610</t>
+          <t>C7614</t>
         </is>
       </c>
       <c r="B495" t="n">
-        <v>6999899236093</v>
+        <v>6999899236130</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>BOTE TIMON PISCINA 80X60 C7610</t>
+          <t>FLOTADOR DONA PATO C7614</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
@@ -22692,7 +22692,7 @@
         </is>
       </c>
       <c r="J495" t="n">
-        <v>434</v>
+        <v>42</v>
       </c>
       <c r="K495" t="n">
         <v>0</v>
@@ -22701,33 +22701,33 @@
         <v>0</v>
       </c>
       <c r="M495" t="n">
-        <v>434</v>
+        <v>42</v>
       </c>
       <c r="N495" t="n">
-        <v>7811.9</v>
+        <v>4581.84</v>
       </c>
       <c r="O495" t="n">
-        <v>3390364.6</v>
+        <v>192437.28</v>
       </c>
       <c r="P495" t="n">
-        <v>13900</v>
+        <v>7900</v>
       </c>
       <c r="Q495" t="n">
-        <v>6032600</v>
+        <v>331800</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>C7614</t>
+          <t>C7629</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>6999899236130</v>
+        <v>6999899236338</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>FLOTADOR DONA PATO C7614</t>
+          <t>PELOTA PISCINA KIKO C7629</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -22741,7 +22741,7 @@
         </is>
       </c>
       <c r="J496" t="n">
-        <v>42</v>
+        <v>288</v>
       </c>
       <c r="K496" t="n">
         <v>0</v>
@@ -22750,47 +22750,42 @@
         <v>0</v>
       </c>
       <c r="M496" t="n">
-        <v>42</v>
+        <v>288</v>
       </c>
       <c r="N496" t="n">
-        <v>4581.84</v>
+        <v>430.60997607656</v>
       </c>
       <c r="O496" t="n">
-        <v>192437.28</v>
+        <v>124015.6731100493</v>
       </c>
       <c r="P496" t="n">
-        <v>7900</v>
+        <v>2200</v>
       </c>
       <c r="Q496" t="n">
-        <v>331800</v>
+        <v>633600</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>C7629</t>
+          <t>C773</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>6999899236338</v>
+        <v>2021071411128</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>PELOTA PISCINA KIKO C7629</t>
-        </is>
-      </c>
-      <c r="E497" t="inlineStr">
-        <is>
-          <t>INFLABLES</t>
+          <t>GLOBO HBD 32</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J497" t="n">
-        <v>288</v>
+        <v>41050</v>
       </c>
       <c r="K497" t="n">
         <v>0</v>
@@ -22799,42 +22794,47 @@
         <v>0</v>
       </c>
       <c r="M497" t="n">
-        <v>288</v>
+        <v>41050</v>
       </c>
       <c r="N497" t="n">
-        <v>430.60997607656</v>
+        <v>2703.2000014448</v>
       </c>
       <c r="O497" t="n">
-        <v>124015.6731100493</v>
+        <v>110966360.059309</v>
       </c>
       <c r="P497" t="n">
-        <v>2200</v>
+        <v>4500</v>
       </c>
       <c r="Q497" t="n">
-        <v>633600</v>
+        <v>184725000</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>C773</t>
+          <t>C80-IO</t>
         </is>
       </c>
       <c r="B498" t="n">
-        <v>2021071411128</v>
+        <v>6524521011221</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>GLOBO HBD 32</t>
+          <t>GLOBO BOUQUET VIDEO JUEGOS 2021-25</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J498" t="n">
-        <v>41050</v>
+        <v>350</v>
       </c>
       <c r="K498" t="n">
         <v>0</v>
@@ -22843,47 +22843,42 @@
         <v>0</v>
       </c>
       <c r="M498" t="n">
-        <v>41050</v>
+        <v>350</v>
       </c>
       <c r="N498" t="n">
-        <v>2703.2000014448</v>
+        <v>2235.19</v>
       </c>
       <c r="O498" t="n">
-        <v>110966360.059309</v>
+        <v>782316.5</v>
       </c>
       <c r="P498" t="n">
-        <v>4500</v>
+        <v>3000</v>
       </c>
       <c r="Q498" t="n">
-        <v>184725000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>C80-IO</t>
+          <t>C808</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>6524521011221</v>
+        <v>8989201808061</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET VIDEO JUEGOS 2021-25</t>
-        </is>
-      </c>
-      <c r="E499" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>ESPADA LUZ SENCILLAS</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J499" t="n">
-        <v>350</v>
+        <v>288</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
@@ -22892,33 +22887,33 @@
         <v>0</v>
       </c>
       <c r="M499" t="n">
-        <v>350</v>
+        <v>288</v>
       </c>
       <c r="N499" t="n">
-        <v>2235.19</v>
+        <v>1297.52</v>
       </c>
       <c r="O499" t="n">
-        <v>782316.5</v>
+        <v>373685.76</v>
       </c>
       <c r="P499" t="n">
-        <v>3000</v>
+        <v>1800</v>
       </c>
       <c r="Q499" t="n">
-        <v>1050000</v>
+        <v>518400</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>C808</t>
+          <t>C81</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>8989201808061</v>
+        <v>6903282589802</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>ESPADA LUZ SENCILLAS</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -22927,7 +22922,7 @@
         </is>
       </c>
       <c r="J500" t="n">
-        <v>288</v>
+        <v>51</v>
       </c>
       <c r="K500" t="n">
         <v>0</v>
@@ -22936,33 +22931,33 @@
         <v>0</v>
       </c>
       <c r="M500" t="n">
-        <v>288</v>
+        <v>51</v>
       </c>
       <c r="N500" t="n">
-        <v>1297.52</v>
+        <v>2308.89</v>
       </c>
       <c r="O500" t="n">
-        <v>373685.76</v>
+        <v>117753.39</v>
       </c>
       <c r="P500" t="n">
-        <v>1800</v>
+        <v>5000</v>
       </c>
       <c r="Q500" t="n">
-        <v>518400</v>
+        <v>255000</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>C81</t>
+          <t>C819</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>6903282589802</v>
+        <v>2087202108190</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>TROMPO EMOJI</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -22971,7 +22966,7 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>51</v>
+        <v>288</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -22980,42 +22975,44 @@
         <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>51</v>
+        <v>288</v>
       </c>
       <c r="N501" t="n">
-        <v>2308.89</v>
+        <v>6761.25</v>
       </c>
       <c r="O501" t="n">
-        <v>117753.39</v>
+        <v>1947240</v>
       </c>
       <c r="P501" t="n">
-        <v>5000</v>
+        <v>5200</v>
       </c>
       <c r="Q501" t="n">
-        <v>255000</v>
+        <v>1497600</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>C819</t>
-        </is>
-      </c>
-      <c r="B502" t="n">
-        <v>2087202108190</v>
+          <t>C829</t>
+        </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>TROMPO EMOJI</t>
+          <t>PERRO LOBITO CAMINA SONIDO</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J502" t="n">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="K502" t="n">
         <v>0</v>
@@ -23024,44 +23021,42 @@
         <v>0</v>
       </c>
       <c r="M502" t="n">
-        <v>288</v>
+        <v>34</v>
       </c>
       <c r="N502" t="n">
-        <v>6761.25</v>
+        <v>4703.6208602151</v>
       </c>
       <c r="O502" t="n">
-        <v>1947240</v>
+        <v>159923.1092473134</v>
       </c>
       <c r="P502" t="n">
-        <v>5200</v>
+        <v>5900</v>
       </c>
       <c r="Q502" t="n">
-        <v>1497600</v>
+        <v>200600</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>C829</t>
-        </is>
+          <t>C84</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>2021010563031</v>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>PERRO LOBITO CAMINA SONIDO</t>
-        </is>
-      </c>
-      <c r="E503" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADOR DE AGUA</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J503" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="K503" t="n">
         <v>0</v>
@@ -23070,33 +23065,30 @@
         <v>0</v>
       </c>
       <c r="M503" t="n">
-        <v>34</v>
+        <v>132</v>
       </c>
       <c r="N503" t="n">
-        <v>4703.6208602151</v>
+        <v>1008.8168311195</v>
       </c>
       <c r="O503" t="n">
-        <v>159923.1092473134</v>
+        <v>133163.821707774</v>
       </c>
       <c r="P503" t="n">
-        <v>5900</v>
+        <v>1500</v>
       </c>
       <c r="Q503" t="n">
-        <v>200600</v>
+        <v>198000</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>C84</t>
-        </is>
-      </c>
-      <c r="B504" t="n">
-        <v>2021010563031</v>
+          <t>C866</t>
+        </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>LANZADOR DE AGUA</t>
+          <t>YOYO SURTIDO</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -23105,7 +23097,7 @@
         </is>
       </c>
       <c r="J504" t="n">
-        <v>192</v>
+        <v>915</v>
       </c>
       <c r="K504" t="n">
         <v>0</v>
@@ -23114,30 +23106,33 @@
         <v>0</v>
       </c>
       <c r="M504" t="n">
-        <v>192</v>
+        <v>915</v>
       </c>
       <c r="N504" t="n">
-        <v>1008.8168311195</v>
+        <v>1176.57</v>
       </c>
       <c r="O504" t="n">
-        <v>193692.831574944</v>
+        <v>1076561.55</v>
       </c>
       <c r="P504" t="n">
-        <v>1500</v>
+        <v>1900</v>
       </c>
       <c r="Q504" t="n">
-        <v>288000</v>
+        <v>1738500</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>C866</t>
-        </is>
+          <t>C887</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>6920210213929</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>YOYO SURTIDO</t>
+          <t>BALON FOOTBALL SURTIDO #2</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -23146,7 +23141,7 @@
         </is>
       </c>
       <c r="J505" t="n">
-        <v>915</v>
+        <v>742</v>
       </c>
       <c r="K505" t="n">
         <v>0</v>
@@ -23155,33 +23150,30 @@
         <v>0</v>
       </c>
       <c r="M505" t="n">
-        <v>915</v>
+        <v>742</v>
       </c>
       <c r="N505" t="n">
-        <v>1176.57</v>
+        <v>3181.9</v>
       </c>
       <c r="O505" t="n">
-        <v>1076561.55</v>
+        <v>2360969.8</v>
       </c>
       <c r="P505" t="n">
-        <v>1900</v>
+        <v>5100</v>
       </c>
       <c r="Q505" t="n">
-        <v>1738500</v>
+        <v>3784200</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>C887</t>
-        </is>
-      </c>
-      <c r="B506" t="n">
-        <v>6920210213929</v>
+          <t>C888</t>
+        </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>BALON FOOTBALL SURTIDO #2</t>
+          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -23190,7 +23182,7 @@
         </is>
       </c>
       <c r="J506" t="n">
-        <v>742</v>
+        <v>116</v>
       </c>
       <c r="K506" t="n">
         <v>0</v>
@@ -23199,30 +23191,33 @@
         <v>0</v>
       </c>
       <c r="M506" t="n">
-        <v>742</v>
+        <v>116</v>
       </c>
       <c r="N506" t="n">
-        <v>3181.9</v>
+        <v>1213.6821359223</v>
       </c>
       <c r="O506" t="n">
-        <v>2360969.8</v>
+        <v>140787.1277669868</v>
       </c>
       <c r="P506" t="n">
-        <v>5100</v>
+        <v>1500</v>
       </c>
       <c r="Q506" t="n">
-        <v>3784200</v>
+        <v>174000</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>C888</t>
-        </is>
+          <t>C890</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>6913545113699</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>PELOTA CHILLON PUYAS SIN LUZ</t>
+          <t>CORTINA FEST</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -23231,7 +23226,7 @@
         </is>
       </c>
       <c r="J507" t="n">
-        <v>116</v>
+        <v>-72</v>
       </c>
       <c r="K507" t="n">
         <v>0</v>
@@ -23240,42 +23235,44 @@
         <v>0</v>
       </c>
       <c r="M507" t="n">
-        <v>116</v>
+        <v>-72</v>
       </c>
       <c r="N507" t="n">
-        <v>1213.6821359223</v>
+        <v>1794.2879686376</v>
       </c>
       <c r="O507" t="n">
-        <v>140787.1277669868</v>
+        <v>-129188.7337419072</v>
       </c>
       <c r="P507" t="n">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="Q507" t="n">
-        <v>174000</v>
+        <v>-115200</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>C890</t>
-        </is>
-      </c>
-      <c r="B508" t="n">
-        <v>6913545113699</v>
+          <t>C92-IO</t>
+        </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>CORTINA FEST</t>
+          <t>GLOBO BOUQUET X 8 PCS STD 202-18</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>GLOBOS</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>und</t>
+          <t>Und</t>
         </is>
       </c>
       <c r="J508" t="n">
-        <v>-72</v>
+        <v>158</v>
       </c>
       <c r="K508" t="n">
         <v>0</v>
@@ -23284,44 +23281,39 @@
         <v>0</v>
       </c>
       <c r="M508" t="n">
-        <v>-72</v>
+        <v>158</v>
       </c>
       <c r="N508" t="n">
-        <v>1794.2879692219</v>
+        <v>1520</v>
       </c>
       <c r="O508" t="n">
-        <v>-129188.7337839768</v>
+        <v>240160</v>
       </c>
       <c r="P508" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="Q508" t="n">
-        <v>-115200</v>
+        <v>300200</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>C92-IO</t>
+          <t>C94</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>GLOBO BOUQUET X 8 PCS STD 202-18</t>
-        </is>
-      </c>
-      <c r="E509" t="inlineStr">
-        <is>
-          <t>GLOBOS</t>
+          <t>PITO ESPANTA SUEGRA PUNTOS</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>Und</t>
+          <t>und</t>
         </is>
       </c>
       <c r="J509" t="n">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="K509" t="n">
         <v>0</v>
@@ -23330,30 +23322,35 @@
         <v>0</v>
       </c>
       <c r="M509" t="n">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="N509" t="n">
-        <v>1520</v>
+        <v>7308.87</v>
       </c>
       <c r="O509" t="n">
-        <v>240160</v>
+        <v>518929.77</v>
       </c>
       <c r="P509" t="n">
-        <v>1900</v>
+        <v>6000</v>
       </c>
       <c r="Q509" t="n">
-        <v>300200</v>
+        <v>426000</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>C94</t>
+          <t>C943</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>PITO ESPANTA SUEGRA PUNTOS</t>
+          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -23362,7 +23359,7 @@
         </is>
       </c>
       <c r="J510" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="K510" t="n">
         <v>0</v>
@@ -23371,44 +23368,34 @@
         <v>0</v>
       </c>
       <c r="M510" t="n">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="N510" t="n">
-        <v>7308.87</v>
+        <v>22951.704799483</v>
       </c>
       <c r="O510" t="n">
-        <v>518929.77</v>
+        <v>252468.752794313</v>
       </c>
       <c r="P510" t="n">
-        <v>6000</v>
+        <v>37900</v>
       </c>
       <c r="Q510" t="n">
-        <v>426000</v>
+        <v>416900</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>C943</t>
+          <t>DV003</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>MUÑECA PRINCESA CON ACCESORIOS LUZ Y M</t>
-        </is>
-      </c>
-      <c r="E511" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I511" t="inlineStr">
-        <is>
-          <t>und</t>
+          <t>ALCANCIA PQÑ DV003</t>
         </is>
       </c>
       <c r="J511" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K511" t="n">
         <v>0</v>
@@ -23417,34 +23404,44 @@
         <v>0</v>
       </c>
       <c r="M511" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="N511" t="n">
-        <v>22951.704799483</v>
+        <v>480</v>
       </c>
       <c r="O511" t="n">
-        <v>252468.752794313</v>
+        <v>7680</v>
       </c>
       <c r="P511" t="n">
-        <v>37900</v>
+        <v>600</v>
       </c>
       <c r="Q511" t="n">
-        <v>416900</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>DV003</t>
+          <t>FG011</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>ALCANCIA PQÑ DV003</t>
+          <t>HELICOPTERO LUZ CUERDA 1012A</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J512" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="K512" t="n">
         <v>0</v>
@@ -23453,35 +23450,35 @@
         <v>0</v>
       </c>
       <c r="M512" t="n">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="N512" t="n">
-        <v>480</v>
+        <v>2713.26</v>
       </c>
       <c r="O512" t="n">
-        <v>7680</v>
+        <v>187214.94</v>
       </c>
       <c r="P512" t="n">
-        <v>600</v>
+        <v>2900</v>
       </c>
       <c r="Q512" t="n">
-        <v>9600</v>
+        <v>200100</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>FG011</t>
+          <t>FG026</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>HELICOPTERO LUZ CUERDA 1012A</t>
+          <t>CARRO CONSTRUCCION DIDACTICO X2 YM-622</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -23490,7 +23487,7 @@
         </is>
       </c>
       <c r="J513" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
@@ -23499,35 +23496,35 @@
         <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="N513" t="n">
-        <v>2713.26</v>
+        <v>12000</v>
       </c>
       <c r="O513" t="n">
-        <v>187214.94</v>
+        <v>132000</v>
       </c>
       <c r="P513" t="n">
-        <v>2900</v>
+        <v>15000</v>
       </c>
       <c r="Q513" t="n">
-        <v>200100</v>
+        <v>165000</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>FG026</t>
+          <t>FG032</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>CARRO CONSTRUCCION DIDACTICO X2 YM-622</t>
+          <t>CHILLONES DINOSAURIOS X6 FR8673</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -23536,7 +23533,7 @@
         </is>
       </c>
       <c r="J514" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="K514" t="n">
         <v>0</v>
@@ -23545,35 +23542,35 @@
         <v>0</v>
       </c>
       <c r="M514" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="N514" t="n">
-        <v>12000</v>
+        <v>10376.37097561</v>
       </c>
       <c r="O514" t="n">
-        <v>132000</v>
+        <v>352796.61317074</v>
       </c>
       <c r="P514" t="n">
-        <v>15000</v>
+        <v>13200</v>
       </c>
       <c r="Q514" t="n">
-        <v>165000</v>
+        <v>448800</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>FG032</t>
+          <t>FG037</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>CHILLONES DINOSAURIOS X6 FR8673</t>
+          <t>SNORKEL 66046A</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -23582,7 +23579,7 @@
         </is>
       </c>
       <c r="J515" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="K515" t="n">
         <v>0</v>
@@ -23591,30 +23588,30 @@
         <v>0</v>
       </c>
       <c r="M515" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="N515" t="n">
-        <v>10376.37097561</v>
+        <v>13493.858308157</v>
       </c>
       <c r="O515" t="n">
-        <v>352796.61317074</v>
+        <v>823125.356797577</v>
       </c>
       <c r="P515" t="n">
-        <v>13200</v>
+        <v>16900</v>
       </c>
       <c r="Q515" t="n">
-        <v>448800</v>
+        <v>1030900</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>FG037</t>
+          <t>FG038</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>SNORKEL 66046A</t>
+          <t>GAFA PISCINA GOGGLES 63017</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
@@ -23628,7 +23625,7 @@
         </is>
       </c>
       <c r="J516" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="K516" t="n">
         <v>0</v>
@@ -23637,30 +23634,30 @@
         <v>0</v>
       </c>
       <c r="M516" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="N516" t="n">
-        <v>13493.858308157</v>
+        <v>5107.03</v>
       </c>
       <c r="O516" t="n">
-        <v>823125.356797577</v>
+        <v>229816.35</v>
       </c>
       <c r="P516" t="n">
-        <v>16900</v>
+        <v>9500</v>
       </c>
       <c r="Q516" t="n">
-        <v>1030900</v>
+        <v>427500</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>FG038</t>
+          <t>FG039</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>GAFA PISCINA GOGGLES 63017</t>
+          <t>GAFA DE NATACION BLISTER 2404-2</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
@@ -23674,7 +23671,7 @@
         </is>
       </c>
       <c r="J517" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="K517" t="n">
         <v>0</v>
@@ -23683,35 +23680,35 @@
         <v>0</v>
       </c>
       <c r="M517" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="N517" t="n">
-        <v>5107.03</v>
+        <v>2644.9</v>
       </c>
       <c r="O517" t="n">
-        <v>229816.35</v>
+        <v>185143</v>
       </c>
       <c r="P517" t="n">
-        <v>9500</v>
+        <v>3900</v>
       </c>
       <c r="Q517" t="n">
-        <v>427500</v>
+        <v>273000</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>FG039</t>
+          <t>FG044</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>GAFA DE NATACION BLISTER 2404-2</t>
+          <t>CARRO BOLSA 757-46</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -23720,7 +23717,7 @@
         </is>
       </c>
       <c r="J518" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="K518" t="n">
         <v>0</v>
@@ -23729,44 +23726,34 @@
         <v>0</v>
       </c>
       <c r="M518" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="N518" t="n">
-        <v>2644.9</v>
+        <v>19923.070060241</v>
       </c>
       <c r="O518" t="n">
-        <v>185143</v>
+        <v>6574613.11987953</v>
       </c>
       <c r="P518" t="n">
-        <v>3900</v>
+        <v>25900</v>
       </c>
       <c r="Q518" t="n">
-        <v>273000</v>
+        <v>8547000</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>FG044</t>
+          <t>FG046</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>CARRO BOLSA 757-46</t>
-        </is>
-      </c>
-      <c r="E519" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I519" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>CARRO DINOSAURIO JD1899-108A</t>
         </is>
       </c>
       <c r="J519" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="K519" t="n">
         <v>0</v>
@@ -23775,34 +23762,44 @@
         <v>0</v>
       </c>
       <c r="M519" t="n">
-        <v>330</v>
+        <v>370</v>
       </c>
       <c r="N519" t="n">
-        <v>19923.070060241</v>
+        <v>3885.95</v>
       </c>
       <c r="O519" t="n">
-        <v>6574613.11987953</v>
+        <v>1437801.5</v>
       </c>
       <c r="P519" t="n">
-        <v>25900</v>
+        <v>6700</v>
       </c>
       <c r="Q519" t="n">
-        <v>8547000</v>
+        <v>2479000</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>FG046</t>
+          <t>FG05</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>CARRO DINOSAURIO JD1899-108A</t>
+          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J520" t="n">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="K520" t="n">
         <v>0</v>
@@ -23811,35 +23808,35 @@
         <v>0</v>
       </c>
       <c r="M520" t="n">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="N520" t="n">
-        <v>3885.95</v>
+        <v>1952.66</v>
       </c>
       <c r="O520" t="n">
-        <v>1437801.5</v>
+        <v>72248.42</v>
       </c>
       <c r="P520" t="n">
-        <v>6700</v>
+        <v>3500</v>
       </c>
       <c r="Q520" t="n">
-        <v>2479000</v>
+        <v>129500</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>FG05</t>
+          <t>FG056</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>ANIMALES DINOSAURIO EN TUBO 093-7</t>
+          <t>FICHAS DIDACTICAS TRENCITO 6078-1</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -23848,7 +23845,7 @@
         </is>
       </c>
       <c r="J521" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="K521" t="n">
         <v>0</v>
@@ -23857,35 +23854,35 @@
         <v>0</v>
       </c>
       <c r="M521" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="N521" t="n">
-        <v>1952.66</v>
+        <v>8480.110000000001</v>
       </c>
       <c r="O521" t="n">
-        <v>72248.42</v>
+        <v>746249.6800000001</v>
       </c>
       <c r="P521" t="n">
-        <v>3500</v>
+        <v>11900</v>
       </c>
       <c r="Q521" t="n">
-        <v>129500</v>
+        <v>1047200</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>FG056</t>
+          <t>FG067</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>FICHAS DIDACTICAS TRENCITO 6078-1</t>
+          <t>COCINA BOLSA 7003-1</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -23894,7 +23891,7 @@
         </is>
       </c>
       <c r="J522" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="K522" t="n">
         <v>0</v>
@@ -23903,30 +23900,30 @@
         <v>0</v>
       </c>
       <c r="M522" t="n">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="N522" t="n">
-        <v>8480.110000000001</v>
+        <v>6270.21</v>
       </c>
       <c r="O522" t="n">
-        <v>746249.6800000001</v>
+        <v>652101.84</v>
       </c>
       <c r="P522" t="n">
-        <v>11900</v>
+        <v>8900</v>
       </c>
       <c r="Q522" t="n">
-        <v>1047200</v>
+        <v>925600</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>FG067</t>
+          <t>FG080</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>COCINA BOLSA 7003-1</t>
+          <t>DINOSAURIO X2 DIDACTICO 706-2-4</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -23940,7 +23937,7 @@
         </is>
       </c>
       <c r="J523" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="K523" t="n">
         <v>0</v>
@@ -23949,35 +23946,35 @@
         <v>0</v>
       </c>
       <c r="M523" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="N523" t="n">
-        <v>6270.21</v>
+        <v>15920</v>
       </c>
       <c r="O523" t="n">
-        <v>652101.84</v>
+        <v>525360</v>
       </c>
       <c r="P523" t="n">
-        <v>8900</v>
+        <v>19900</v>
       </c>
       <c r="Q523" t="n">
-        <v>925600</v>
+        <v>656700</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>FG080</t>
+          <t>FG081</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>DINOSAURIO X2 DIDACTICO 706-2-4</t>
+          <t>CARRO LLANTON BOLSA THUNDER 6969-44</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -23986,7 +23983,7 @@
         </is>
       </c>
       <c r="J524" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="K524" t="n">
         <v>0</v>
@@ -23995,35 +23992,35 @@
         <v>0</v>
       </c>
       <c r="M524" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="N524" t="n">
-        <v>15920</v>
+        <v>9726.98</v>
       </c>
       <c r="O524" t="n">
-        <v>525360</v>
+        <v>943517.0599999999</v>
       </c>
       <c r="P524" t="n">
-        <v>19900</v>
+        <v>12900</v>
       </c>
       <c r="Q524" t="n">
-        <v>656700</v>
+        <v>1251300</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>FG081</t>
+          <t>FG083</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>CARRO LLANTON BOLSA THUNDER 6969-44</t>
+          <t>SONAJERO BOLSA RANA XZM5XS</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -24032,7 +24029,7 @@
         </is>
       </c>
       <c r="J525" t="n">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="K525" t="n">
         <v>0</v>
@@ -24041,35 +24038,35 @@
         <v>0</v>
       </c>
       <c r="M525" t="n">
-        <v>97</v>
+        <v>258</v>
       </c>
       <c r="N525" t="n">
-        <v>9726.98</v>
+        <v>1952.41</v>
       </c>
       <c r="O525" t="n">
-        <v>943517.0599999999</v>
+        <v>503721.78</v>
       </c>
       <c r="P525" t="n">
-        <v>12900</v>
+        <v>2700</v>
       </c>
       <c r="Q525" t="n">
-        <v>1251300</v>
+        <v>696600</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>FG083</t>
+          <t>FG086</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA RANA XZM5XS</t>
+          <t>BLISTER SALA COMEDOR NIÑA 1107C</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -24078,7 +24075,7 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>258</v>
+        <v>34</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -24087,35 +24084,35 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>258</v>
+        <v>34</v>
       </c>
       <c r="N526" t="n">
-        <v>1952.41</v>
+        <v>2828.99</v>
       </c>
       <c r="O526" t="n">
-        <v>503721.78</v>
+        <v>96185.65999999999</v>
       </c>
       <c r="P526" t="n">
-        <v>2700</v>
+        <v>8200</v>
       </c>
       <c r="Q526" t="n">
-        <v>696600</v>
+        <v>278800</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>FG086</t>
+          <t>J-1313</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>BLISTER SALA COMEDOR NIÑA 1107C</t>
+          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -24124,7 +24121,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>34</v>
+        <v>360</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24133,30 +24130,30 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>34</v>
+        <v>360</v>
       </c>
       <c r="N527" t="n">
-        <v>2828.99</v>
+        <v>7480</v>
       </c>
       <c r="O527" t="n">
-        <v>96185.65999999999</v>
+        <v>2692800</v>
       </c>
       <c r="P527" t="n">
-        <v>8200</v>
+        <v>9500</v>
       </c>
       <c r="Q527" t="n">
-        <v>278800</v>
+        <v>3420000</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>J-1313</t>
+          <t>J-1316</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>CONEJO CAMINA ZANAHORIA LUZ J-1313</t>
+          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
@@ -24170,7 +24167,7 @@
         </is>
       </c>
       <c r="J528" t="n">
-        <v>360</v>
+        <v>38</v>
       </c>
       <c r="K528" t="n">
         <v>0</v>
@@ -24179,30 +24176,30 @@
         <v>0</v>
       </c>
       <c r="M528" t="n">
-        <v>360</v>
+        <v>38</v>
       </c>
       <c r="N528" t="n">
-        <v>7480</v>
+        <v>5280</v>
       </c>
       <c r="O528" t="n">
-        <v>2692800</v>
+        <v>200640</v>
       </c>
       <c r="P528" t="n">
-        <v>9500</v>
+        <v>6900</v>
       </c>
       <c r="Q528" t="n">
-        <v>3420000</v>
+        <v>262200</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>J-1316</t>
+          <t>J-1317</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CELULAR Y BILLETERA J-1316</t>
+          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -24216,7 +24213,7 @@
         </is>
       </c>
       <c r="J529" t="n">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="K529" t="n">
         <v>0</v>
@@ -24225,30 +24222,30 @@
         <v>0</v>
       </c>
       <c r="M529" t="n">
-        <v>38</v>
+        <v>144</v>
       </c>
       <c r="N529" t="n">
         <v>5280</v>
       </c>
       <c r="O529" t="n">
-        <v>200640</v>
+        <v>760320</v>
       </c>
       <c r="P529" t="n">
         <v>6900</v>
       </c>
       <c r="Q529" t="n">
-        <v>262200</v>
+        <v>993600</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>J-1317</t>
+          <t>J-1320</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>SET DE GAFAS CON CELULAR Y BILLETERA J-1317</t>
+          <t>CARRO TODO TERRENO J-1320</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -24274,27 +24271,27 @@
         <v>144</v>
       </c>
       <c r="N530" t="n">
-        <v>5280</v>
+        <v>1584</v>
       </c>
       <c r="O530" t="n">
-        <v>760320</v>
+        <v>228096</v>
       </c>
       <c r="P530" t="n">
-        <v>6900</v>
+        <v>2000</v>
       </c>
       <c r="Q530" t="n">
-        <v>993600</v>
+        <v>288000</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>J-1320</t>
+          <t>J-1323</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>CARRO TODO TERRENO J-1320</t>
+          <t>CARRO FRICCION TODO TERRENO OJITOS J-1323</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -24308,7 +24305,7 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
@@ -24317,30 +24314,30 @@
         <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>144</v>
+        <v>96</v>
       </c>
       <c r="N531" t="n">
-        <v>1584</v>
+        <v>3872</v>
       </c>
       <c r="O531" t="n">
-        <v>228096</v>
+        <v>371712</v>
       </c>
       <c r="P531" t="n">
-        <v>2000</v>
+        <v>4900</v>
       </c>
       <c r="Q531" t="n">
-        <v>288000</v>
+        <v>470400</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>J-1323</t>
+          <t>J-1331</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>CARRO FRICCION TODO TERRENO OJITOS J-1323</t>
+          <t>CARRO TODO TERRENO DOBLE IMAGEN J-1331</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -24366,27 +24363,27 @@
         <v>96</v>
       </c>
       <c r="N532" t="n">
-        <v>3872</v>
+        <v>4400</v>
       </c>
       <c r="O532" t="n">
-        <v>371712</v>
+        <v>422400</v>
       </c>
       <c r="P532" t="n">
-        <v>4900</v>
+        <v>5900</v>
       </c>
       <c r="Q532" t="n">
-        <v>470400</v>
+        <v>566400</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>J-1331</t>
+          <t>J-455</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>CARRO TODO TERRENO DOBLE IMAGEN J-1331</t>
+          <t>TABLETA MAGICA J-455</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
@@ -24400,7 +24397,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24409,30 +24406,30 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="N533" t="n">
-        <v>4400</v>
+        <v>3520</v>
       </c>
       <c r="O533" t="n">
         <v>422400</v>
       </c>
       <c r="P533" t="n">
-        <v>5900</v>
+        <v>4500</v>
       </c>
       <c r="Q533" t="n">
-        <v>566400</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>J-455</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>TABLETA MAGICA J-455</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -24446,7 +24443,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24455,30 +24452,30 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="N534" t="n">
-        <v>3520</v>
+        <v>4576</v>
       </c>
       <c r="O534" t="n">
-        <v>422400</v>
+        <v>851136</v>
       </c>
       <c r="P534" t="n">
-        <v>4500</v>
+        <v>5900</v>
       </c>
       <c r="Q534" t="n">
-        <v>540000</v>
+        <v>1097400</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>J-718</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -24492,7 +24489,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>186</v>
+        <v>294</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24501,35 +24498,35 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>186</v>
+        <v>294</v>
       </c>
       <c r="N535" t="n">
-        <v>4576</v>
+        <v>5280</v>
       </c>
       <c r="O535" t="n">
-        <v>851136</v>
+        <v>1552320</v>
       </c>
       <c r="P535" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q535" t="n">
-        <v>1097400</v>
+        <v>2028600</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>MG040</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>ABACO ANIMALES PT17058</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24538,7 +24535,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>294</v>
+        <v>23</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24547,30 +24544,35 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>294</v>
+        <v>23</v>
       </c>
       <c r="N536" t="n">
         <v>5280</v>
       </c>
       <c r="O536" t="n">
-        <v>1552320</v>
+        <v>121440</v>
       </c>
       <c r="P536" t="n">
-        <v>6900</v>
+        <v>6600</v>
       </c>
       <c r="Q536" t="n">
-        <v>2028600</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>MG040</t>
+          <t>MG044</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>PT19323</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>ABACO ANIMALES PT17058</t>
+          <t>ABACO TREN PT19323</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
@@ -24584,7 +24586,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24593,35 +24595,30 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N537" t="n">
-        <v>5280</v>
+        <v>7760</v>
       </c>
       <c r="O537" t="n">
-        <v>121440</v>
+        <v>186240</v>
       </c>
       <c r="P537" t="n">
-        <v>6600</v>
+        <v>9700</v>
       </c>
       <c r="Q537" t="n">
-        <v>151800</v>
+        <v>232800</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>MG044</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>PT19323</t>
+          <t>MG051</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>ABACO TREN PT19323</t>
+          <t>CAJON DIDACTICO RELOJ PT21204</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
@@ -24635,7 +24632,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24644,35 +24641,40 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N538" t="n">
-        <v>7760</v>
+        <v>22320</v>
       </c>
       <c r="O538" t="n">
-        <v>186240</v>
+        <v>624960</v>
       </c>
       <c r="P538" t="n">
-        <v>9700</v>
+        <v>27900</v>
       </c>
       <c r="Q538" t="n">
-        <v>232800</v>
+        <v>781200</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>MG051</t>
+          <t>MG067</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>MG21283</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>CAJON DIDACTICO RELOJ PT21204</t>
+          <t>KARAOKE BLUETOOTH MG21283MG</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -24681,7 +24683,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -24690,40 +24692,40 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N539" t="n">
-        <v>22320</v>
+        <v>41161.350714286</v>
       </c>
       <c r="O539" t="n">
-        <v>624960</v>
+        <v>1029033.76785715</v>
       </c>
       <c r="P539" t="n">
-        <v>27900</v>
+        <v>55000</v>
       </c>
       <c r="Q539" t="n">
-        <v>781200</v>
+        <v>1375000</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>MG067</t>
+          <t>MG094</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MG21283</t>
+          <t>mg33153</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>KARAOKE BLUETOOTH MG21283MG</t>
+          <t>LANZA DISCOS MED MULTICOLOR MG33153</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -24732,7 +24734,7 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
@@ -24741,40 +24743,35 @@
         <v>0</v>
       </c>
       <c r="M540" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N540" t="n">
-        <v>41161.350714286</v>
+        <v>3840</v>
       </c>
       <c r="O540" t="n">
-        <v>1029033.76785715</v>
+        <v>65280</v>
       </c>
       <c r="P540" t="n">
-        <v>55000</v>
+        <v>3900</v>
       </c>
       <c r="Q540" t="n">
-        <v>1375000</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>MG094</t>
-        </is>
-      </c>
-      <c r="B541" t="inlineStr">
-        <is>
-          <t>mg33153</t>
+          <t>MG16421</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>LANZA DISCOS MED MULTICOLOR MG33153</t>
+          <t>CARRO MEZCALDOR BOLSA MDE MG16421</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24783,7 +24780,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24792,30 +24789,35 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="N541" t="n">
-        <v>3840</v>
+        <v>2775.86</v>
       </c>
       <c r="O541" t="n">
-        <v>65280</v>
+        <v>141568.86</v>
       </c>
       <c r="P541" t="n">
-        <v>3900</v>
+        <v>12500</v>
       </c>
       <c r="Q541" t="n">
-        <v>66300</v>
+        <v>637500</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MG16348</t>
+          <t>MG18991</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>MG18991</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>SET DE COCINA FOGON GDE MG16348</t>
+          <t>MAQUINA DE COSER PILAS MG18991</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -24829,7 +24831,7 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
@@ -24838,35 +24840,35 @@
         <v>0</v>
       </c>
       <c r="M542" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N542" t="n">
-        <v>910.85</v>
+        <v>8949.32</v>
       </c>
       <c r="O542" t="n">
-        <v>8197.65</v>
+        <v>125290.48</v>
       </c>
       <c r="P542" t="n">
-        <v>7900</v>
+        <v>28900</v>
       </c>
       <c r="Q542" t="n">
-        <v>71100</v>
+        <v>404600</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>MG16421</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>CARRO MEZCALDOR BOLSA MDE MG16421</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -24875,7 +24877,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -24884,40 +24886,40 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="N543" t="n">
-        <v>2775.86</v>
+        <v>1482.84</v>
       </c>
       <c r="O543" t="n">
-        <v>141568.86</v>
+        <v>250599.96</v>
       </c>
       <c r="P543" t="n">
-        <v>12500</v>
+        <v>6500</v>
       </c>
       <c r="Q543" t="n">
-        <v>637500</v>
+        <v>1098500</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>MG18991</t>
+          <t>MG20930</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>MG18991</t>
+          <t>MG20930</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER PILAS MG18991</t>
+          <t>CARRO BUGGY RECARGABLE MG20930</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -24926,7 +24928,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -24935,35 +24937,35 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="N544" t="n">
-        <v>8949.32</v>
+        <v>63353.92</v>
       </c>
       <c r="O544" t="n">
-        <v>125290.48</v>
+        <v>380123.52</v>
       </c>
       <c r="P544" t="n">
-        <v>28900</v>
+        <v>128000</v>
       </c>
       <c r="Q544" t="n">
-        <v>404600</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -24972,7 +24974,7 @@
         </is>
       </c>
       <c r="J545" t="n">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="K545" t="n">
         <v>0</v>
@@ -24981,40 +24983,35 @@
         <v>0</v>
       </c>
       <c r="M545" t="n">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="N545" t="n">
-        <v>1482.84</v>
+        <v>1129.14</v>
       </c>
       <c r="O545" t="n">
-        <v>250599.96</v>
+        <v>91460.34000000001</v>
       </c>
       <c r="P545" t="n">
-        <v>6500</v>
+        <v>6900</v>
       </c>
       <c r="Q545" t="n">
-        <v>1098500</v>
+        <v>558900</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>MG20930</t>
-        </is>
-      </c>
-      <c r="B546" t="inlineStr">
-        <is>
-          <t>MG20930</t>
+          <t>MG27668</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>CARRO BUGGY RECARGABLE MG20930</t>
+          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -25023,7 +25020,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25032,35 +25029,35 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="N546" t="n">
-        <v>63353.92</v>
+        <v>15239.8</v>
       </c>
       <c r="O546" t="n">
-        <v>380123.52</v>
+        <v>320035.8</v>
       </c>
       <c r="P546" t="n">
-        <v>128000</v>
+        <v>15900</v>
       </c>
       <c r="Q546" t="n">
-        <v>768000</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG28914</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -25069,7 +25066,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25078,35 +25075,35 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="N547" t="n">
-        <v>1129.14</v>
+        <v>5563</v>
       </c>
       <c r="O547" t="n">
-        <v>91460.34000000001</v>
+        <v>133512</v>
       </c>
       <c r="P547" t="n">
-        <v>6900</v>
+        <v>11900</v>
       </c>
       <c r="Q547" t="n">
-        <v>558900</v>
+        <v>285600</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>MG27668</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -25115,7 +25112,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25124,35 +25121,40 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N548" t="n">
-        <v>15239.8</v>
+        <v>9046.99</v>
       </c>
       <c r="O548" t="n">
-        <v>320035.8</v>
+        <v>217127.76</v>
       </c>
       <c r="P548" t="n">
-        <v>15900</v>
+        <v>22500</v>
       </c>
       <c r="Q548" t="n">
-        <v>333900</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>MG28914</t>
+          <t>MG30183</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>MG30183</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
+          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -25161,7 +25163,7 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -25170,35 +25172,35 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="N549" t="n">
-        <v>5563</v>
+        <v>3982.6707619048</v>
       </c>
       <c r="O549" t="n">
-        <v>133512</v>
+        <v>370388.3808571464</v>
       </c>
       <c r="P549" t="n">
-        <v>11900</v>
+        <v>10900</v>
       </c>
       <c r="Q549" t="n">
-        <v>285600</v>
+        <v>1013700</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -25207,7 +25209,7 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>24</v>
+        <v>399</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25216,40 +25218,40 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>24</v>
+        <v>399</v>
       </c>
       <c r="N550" t="n">
-        <v>9046.99</v>
+        <v>571.87</v>
       </c>
       <c r="O550" t="n">
-        <v>217127.76</v>
+        <v>228176.13</v>
       </c>
       <c r="P550" t="n">
-        <v>22500</v>
+        <v>2500</v>
       </c>
       <c r="Q550" t="n">
-        <v>540000</v>
+        <v>997500</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>MG30183</t>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>MG30183</t>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -25258,7 +25260,7 @@
         </is>
       </c>
       <c r="J551" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25267,35 +25269,40 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>93</v>
+        <v>3</v>
       </c>
       <c r="N551" t="n">
-        <v>3982.6707619048</v>
+        <v>2432.1351111111</v>
       </c>
       <c r="O551" t="n">
-        <v>370388.3808571464</v>
+        <v>7296.405333333299</v>
       </c>
       <c r="P551" t="n">
-        <v>10900</v>
+        <v>4500</v>
       </c>
       <c r="Q551" t="n">
-        <v>1013700</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40324</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>MG40324</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>JUEGO DE PESCA MG40324</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I552" t="inlineStr">
@@ -25304,7 +25311,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>399</v>
+        <v>1</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25313,40 +25320,35 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>399</v>
+        <v>1</v>
       </c>
       <c r="N552" t="n">
-        <v>571.87</v>
+        <v>2005.78</v>
       </c>
       <c r="O552" t="n">
-        <v>228176.13</v>
+        <v>2005.78</v>
       </c>
       <c r="P552" t="n">
-        <v>2500</v>
+        <v>9500</v>
       </c>
       <c r="Q552" t="n">
-        <v>997500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>MG40269</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>MG40269</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -25355,7 +25357,7 @@
         </is>
       </c>
       <c r="J553" t="n">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25364,35 +25366,35 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>3</v>
+        <v>271</v>
       </c>
       <c r="N553" t="n">
-        <v>2432.1351111111</v>
+        <v>227.41601620029</v>
       </c>
       <c r="O553" t="n">
-        <v>7296.405333333299</v>
+        <v>61629.74039027859</v>
       </c>
       <c r="P553" t="n">
-        <v>4500</v>
+        <v>1200</v>
       </c>
       <c r="Q553" t="n">
-        <v>13500</v>
+        <v>325200</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>MG40324</t>
+          <t>MG40642</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>MG40324</t>
+          <t>MG40642</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>JUEGO DE PESCA MG40324</t>
+          <t>MORRAL TOCADOR PORTABLE MG40642</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -25406,7 +25408,7 @@
         </is>
       </c>
       <c r="J554" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -25415,35 +25417,40 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="N554" t="n">
-        <v>2005.78</v>
+        <v>19081.85</v>
       </c>
       <c r="O554" t="n">
-        <v>2005.78</v>
+        <v>286227.75</v>
       </c>
       <c r="P554" t="n">
-        <v>9500</v>
+        <v>36900</v>
       </c>
       <c r="Q554" t="n">
-        <v>9500</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40888</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>MG40888</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>SET DE RESCATE EN BOLSA MG40888</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -25452,7 +25459,7 @@
         </is>
       </c>
       <c r="J555" t="n">
-        <v>271</v>
+        <v>11</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25461,40 +25468,35 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>271</v>
+        <v>11</v>
       </c>
       <c r="N555" t="n">
-        <v>227.41601620029</v>
+        <v>7540.09</v>
       </c>
       <c r="O555" t="n">
-        <v>61629.74039027859</v>
+        <v>82940.99000000001</v>
       </c>
       <c r="P555" t="n">
-        <v>1200</v>
+        <v>18500</v>
       </c>
       <c r="Q555" t="n">
-        <v>325200</v>
+        <v>203500</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>MG40642</t>
-        </is>
-      </c>
-      <c r="B556" t="inlineStr">
-        <is>
-          <t>MG40642</t>
+          <t>MG41171</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>MORRAL TOCADOR PORTABLE MG40642</t>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -25503,7 +25505,7 @@
         </is>
       </c>
       <c r="J556" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -25512,49 +25514,34 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="N556" t="n">
-        <v>19081.85</v>
+        <v>25110.1</v>
       </c>
       <c r="O556" t="n">
-        <v>286227.75</v>
+        <v>778413.1</v>
       </c>
       <c r="P556" t="n">
-        <v>36900</v>
+        <v>27900</v>
       </c>
       <c r="Q556" t="n">
-        <v>553500</v>
+        <v>864900</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>MG40888</t>
-        </is>
-      </c>
-      <c r="B557" t="inlineStr">
-        <is>
-          <t>MG40888</t>
+          <t>MR044</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>SET DE RESCATE EN BOLSA MG40888</t>
-        </is>
-      </c>
-      <c r="E557" t="inlineStr">
-        <is>
-          <t>PIÑATERIA</t>
-        </is>
-      </c>
-      <c r="I557" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
         </is>
       </c>
       <c r="J557" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -25563,35 +25550,35 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="N557" t="n">
-        <v>7540.09</v>
+        <v>20720</v>
       </c>
       <c r="O557" t="n">
-        <v>82940.99000000001</v>
+        <v>124320</v>
       </c>
       <c r="P557" t="n">
-        <v>18500</v>
+        <v>25900</v>
       </c>
       <c r="Q557" t="n">
-        <v>203500</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MR045</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
+          <t>MORRAL ANIMALES STD 0230-02-002</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -25600,7 +25587,7 @@
         </is>
       </c>
       <c r="J558" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -25609,34 +25596,34 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="N558" t="n">
-        <v>25110.1</v>
+        <v>22080.08</v>
       </c>
       <c r="O558" t="n">
-        <v>778413.1</v>
+        <v>287041.04</v>
       </c>
       <c r="P558" t="n">
-        <v>27900</v>
+        <v>29900</v>
       </c>
       <c r="Q558" t="n">
-        <v>864900</v>
+        <v>388700</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>MR044</t>
+          <t>MR081</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
+          <t>MORRAL GATICO STD MR081</t>
         </is>
       </c>
       <c r="J559" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K559" t="n">
         <v>0</v>
@@ -25645,35 +25632,35 @@
         <v>0</v>
       </c>
       <c r="M559" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N559" t="n">
-        <v>20720</v>
+        <v>22865</v>
       </c>
       <c r="O559" t="n">
-        <v>124320</v>
+        <v>91460</v>
       </c>
       <c r="P559" t="n">
-        <v>25900</v>
+        <v>26900</v>
       </c>
       <c r="Q559" t="n">
-        <v>155400</v>
+        <v>107600</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>MR045</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>MORRAL ANIMALES STD 0230-02-002</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -25682,7 +25669,7 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="K560" t="n">
         <v>0</v>
@@ -25691,34 +25678,34 @@
         <v>0</v>
       </c>
       <c r="M560" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="N560" t="n">
-        <v>22080.08</v>
+        <v>1950.7</v>
       </c>
       <c r="O560" t="n">
-        <v>287041.04</v>
+        <v>64373.1</v>
       </c>
       <c r="P560" t="n">
-        <v>29900</v>
+        <v>7500</v>
       </c>
       <c r="Q560" t="n">
-        <v>388700</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>MR081</t>
+          <t>SLBT04</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>MORRAL GATICO STD MR081</t>
+          <t>BOLSA DE REGALO  SLT2023</t>
         </is>
       </c>
       <c r="J561" t="n">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25727,35 +25714,35 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="N561" t="n">
-        <v>22865</v>
+        <v>480</v>
       </c>
       <c r="O561" t="n">
-        <v>91460</v>
+        <v>70080</v>
       </c>
       <c r="P561" t="n">
-        <v>26900</v>
+        <v>600</v>
       </c>
       <c r="Q561" t="n">
-        <v>107600</v>
+        <v>87600</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>SLT014</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -25764,7 +25751,7 @@
         </is>
       </c>
       <c r="J562" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
@@ -25773,34 +25760,44 @@
         <v>0</v>
       </c>
       <c r="M562" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="N562" t="n">
-        <v>1950.7</v>
+        <v>12000</v>
       </c>
       <c r="O562" t="n">
-        <v>64373.1</v>
+        <v>864000</v>
       </c>
       <c r="P562" t="n">
-        <v>7500</v>
+        <v>15000</v>
       </c>
       <c r="Q562" t="n">
-        <v>247500</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>SLBT04</t>
+          <t>SLT035</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>BOLSA DE REGALO  SLT2023</t>
+          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J563" t="n">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
@@ -25809,30 +25806,30 @@
         <v>0</v>
       </c>
       <c r="M563" t="n">
-        <v>146</v>
+        <v>55</v>
       </c>
       <c r="N563" t="n">
-        <v>480</v>
+        <v>6917.54</v>
       </c>
       <c r="O563" t="n">
-        <v>70080</v>
+        <v>380464.7</v>
       </c>
       <c r="P563" t="n">
-        <v>600</v>
+        <v>11500</v>
       </c>
       <c r="Q563" t="n">
-        <v>87600</v>
+        <v>632500</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>SLT014</t>
+          <t>SLT05</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
+          <t>ESPADA DOBLE SLT2074</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
@@ -25846,7 +25843,7 @@
         </is>
       </c>
       <c r="J564" t="n">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="K564" t="n">
         <v>0</v>
@@ -25855,35 +25852,35 @@
         <v>0</v>
       </c>
       <c r="M564" t="n">
-        <v>72</v>
+        <v>238</v>
       </c>
       <c r="N564" t="n">
-        <v>12000</v>
+        <v>4720</v>
       </c>
       <c r="O564" t="n">
-        <v>864000</v>
+        <v>1123360</v>
       </c>
       <c r="P564" t="n">
-        <v>15000</v>
+        <v>5900</v>
       </c>
       <c r="Q564" t="n">
-        <v>1080000</v>
+        <v>1404200</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>SLT035</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -25892,7 +25889,7 @@
         </is>
       </c>
       <c r="J565" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="K565" t="n">
         <v>0</v>
@@ -25901,35 +25898,35 @@
         <v>0</v>
       </c>
       <c r="M565" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="N565" t="n">
-        <v>6917.54</v>
+        <v>1059.1847727273</v>
       </c>
       <c r="O565" t="n">
-        <v>380464.7</v>
+        <v>22242.8802272733</v>
       </c>
       <c r="P565" t="n">
-        <v>11500</v>
+        <v>9500</v>
       </c>
       <c r="Q565" t="n">
-        <v>632500</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>SLT05</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>ESPADA DOBLE SLT2074</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -25938,7 +25935,7 @@
         </is>
       </c>
       <c r="J566" t="n">
-        <v>238</v>
+        <v>53</v>
       </c>
       <c r="K566" t="n">
         <v>0</v>
@@ -25947,110 +25944,18 @@
         <v>0</v>
       </c>
       <c r="M566" t="n">
-        <v>238</v>
+        <v>53</v>
       </c>
       <c r="N566" t="n">
-        <v>4720</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O566" t="n">
-        <v>1123360</v>
+        <v>18074.13602459019</v>
       </c>
       <c r="P566" t="n">
-        <v>5900</v>
+        <v>14500</v>
       </c>
       <c r="Q566" t="n">
-        <v>1404200</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>SLT2640</t>
-        </is>
-      </c>
-      <c r="C567" t="inlineStr">
-        <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
-        </is>
-      </c>
-      <c r="E567" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J567" t="n">
-        <v>21</v>
-      </c>
-      <c r="K567" t="n">
-        <v>0</v>
-      </c>
-      <c r="L567" t="n">
-        <v>0</v>
-      </c>
-      <c r="M567" t="n">
-        <v>21</v>
-      </c>
-      <c r="N567" t="n">
-        <v>1059.1847727273</v>
-      </c>
-      <c r="O567" t="n">
-        <v>22242.8802272733</v>
-      </c>
-      <c r="P567" t="n">
-        <v>9500</v>
-      </c>
-      <c r="Q567" t="n">
-        <v>199500</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>SLT2642</t>
-        </is>
-      </c>
-      <c r="C568" t="inlineStr">
-        <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
-        </is>
-      </c>
-      <c r="E568" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I568" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J568" t="n">
-        <v>53</v>
-      </c>
-      <c r="K568" t="n">
-        <v>0</v>
-      </c>
-      <c r="L568" t="n">
-        <v>0</v>
-      </c>
-      <c r="M568" t="n">
-        <v>53</v>
-      </c>
-      <c r="N568" t="n">
-        <v>341.02143442623</v>
-      </c>
-      <c r="O568" t="n">
-        <v>18074.13602459019</v>
-      </c>
-      <c r="P568" t="n">
-        <v>14500</v>
-      </c>
-      <c r="Q568" t="n">
         <v>768500</v>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1151,10 +1151,10 @@
         <v>440</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8370969414</v>
+        <v>3926.8370954357</v>
       </c>
       <c r="O19" t="n">
-        <v>1727808.322654216</v>
+        <v>1727808.321991708</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1708,10 +1708,10 @@
         <v>18</v>
       </c>
       <c r="N33" t="n">
-        <v>15711.965922747</v>
+        <v>15711.965905172</v>
       </c>
       <c r="O33" t="n">
-        <v>282815.386609446</v>
+        <v>282815.386293096</v>
       </c>
       <c r="P33" t="n">
         <v>28500</v>
@@ -3401,10 +3401,10 @@
         <v>120</v>
       </c>
       <c r="N73" t="n">
-        <v>1098.0597873486</v>
+        <v>1098.0598890693</v>
       </c>
       <c r="O73" t="n">
-        <v>131767.174481832</v>
+        <v>131767.186688316</v>
       </c>
       <c r="P73" t="n">
         <v>1500</v>
@@ -5497,10 +5497,10 @@
         <v>2706</v>
       </c>
       <c r="N120" t="n">
-        <v>2090.85</v>
+        <v>2091.1308394896</v>
       </c>
       <c r="O120" t="n">
-        <v>5657840.1</v>
+        <v>5658600.051658858</v>
       </c>
       <c r="P120" t="n">
         <v>2900</v>
@@ -5986,10 +5986,10 @@
         <v>1116</v>
       </c>
       <c r="N131" t="n">
-        <v>4372.2107903559</v>
+        <v>4372.2107904123</v>
       </c>
       <c r="O131" t="n">
-        <v>4879387.242037185</v>
+        <v>4879387.242100127</v>
       </c>
       <c r="P131" t="n">
         <v>7500</v>
@@ -7266,10 +7266,10 @@
         <v>279</v>
       </c>
       <c r="N159" t="n">
-        <v>3761.6</v>
+        <v>3775.3787545788</v>
       </c>
       <c r="O159" t="n">
-        <v>1049486.4</v>
+        <v>1053330.672527485</v>
       </c>
       <c r="P159" t="n">
         <v>6900</v>
@@ -7438,10 +7438,10 @@
         <v>191</v>
       </c>
       <c r="N163" t="n">
-        <v>1630.9236471425</v>
+        <v>1630.9236566809</v>
       </c>
       <c r="O163" t="n">
-        <v>311506.4166042175</v>
+        <v>311506.4184260519</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -7484,10 +7484,10 @@
         <v>36</v>
       </c>
       <c r="N164" t="n">
-        <v>1550.1936995315</v>
+        <v>1550.1937050719</v>
       </c>
       <c r="O164" t="n">
-        <v>55806.973183134</v>
+        <v>55806.9733825884</v>
       </c>
       <c r="P164" t="n">
         <v>2500</v>
@@ -7530,10 +7530,10 @@
         <v>48</v>
       </c>
       <c r="N165" t="n">
-        <v>1579.3904266667</v>
+        <v>1579.3903753351</v>
       </c>
       <c r="O165" t="n">
-        <v>75810.74048000161</v>
+        <v>75810.7380160848</v>
       </c>
       <c r="P165" t="n">
         <v>2900</v>
@@ -9076,10 +9076,10 @@
         <v>170</v>
       </c>
       <c r="N201" t="n">
-        <v>2680.739695084</v>
+        <v>2680.7396948941</v>
       </c>
       <c r="O201" t="n">
-        <v>455725.74816428</v>
+        <v>455725.748131997</v>
       </c>
       <c r="P201" t="n">
         <v>4900</v>
@@ -14592,10 +14592,10 @@
         <v>164</v>
       </c>
       <c r="N323" t="n">
-        <v>4907.822092257</v>
+        <v>4956.8186522463</v>
       </c>
       <c r="O323" t="n">
-        <v>804882.823130148</v>
+        <v>812918.2589683932</v>
       </c>
       <c r="P323" t="n">
         <v>8200</v>
@@ -17459,10 +17459,10 @@
         <v>190</v>
       </c>
       <c r="N385" t="n">
-        <v>3629.36</v>
+        <v>3642.7032352941</v>
       </c>
       <c r="O385" t="n">
-        <v>689578.4</v>
+        <v>692113.614705879</v>
       </c>
       <c r="P385" t="n">
         <v>3900</v>
@@ -17885,10 +17885,10 @@
         <v>94</v>
       </c>
       <c r="N394" t="n">
-        <v>6090.22</v>
+        <v>6160.2225287356</v>
       </c>
       <c r="O394" t="n">
-        <v>572480.6800000001</v>
+        <v>579060.9177011463</v>
       </c>
       <c r="P394" t="n">
         <v>8500</v>
@@ -18816,10 +18816,10 @@
         <v>2</v>
       </c>
       <c r="N414" t="n">
-        <v>3110.8413822526</v>
+        <v>3110.8413717354</v>
       </c>
       <c r="O414" t="n">
-        <v>6221.6827645052</v>
+        <v>6221.6827434708</v>
       </c>
       <c r="P414" t="n">
         <v>4500</v>
@@ -19190,10 +19190,10 @@
         <v>4</v>
       </c>
       <c r="N422" t="n">
-        <v>2501.3849767442</v>
+        <v>2501.384953271</v>
       </c>
       <c r="O422" t="n">
-        <v>10005.5399069768</v>
+        <v>10005.539813084</v>
       </c>
       <c r="P422" t="n">
         <v>4100</v>
@@ -19894,10 +19894,10 @@
         <v>54</v>
       </c>
       <c r="N437" t="n">
-        <v>2098.4050144928</v>
+        <v>2110.6406122449</v>
       </c>
       <c r="O437" t="n">
-        <v>113313.8707826112</v>
+        <v>113974.5930612246</v>
       </c>
       <c r="P437" t="n">
         <v>9500</v>
@@ -22511,10 +22511,10 @@
         <v>1216</v>
       </c>
       <c r="N491" t="n">
-        <v>665.32359209922</v>
+        <v>665.32360534809</v>
       </c>
       <c r="O491" t="n">
-        <v>809033.4879926515</v>
+        <v>809033.5041032775</v>
       </c>
       <c r="P491" t="n">
         <v>2900</v>
@@ -23068,10 +23068,10 @@
         <v>132</v>
       </c>
       <c r="N503" t="n">
-        <v>1008.8168311195</v>
+        <v>1008.8166794626</v>
       </c>
       <c r="O503" t="n">
-        <v>133163.821707774</v>
+        <v>133163.8016890632</v>
       </c>
       <c r="P503" t="n">
         <v>1500</v>
@@ -24179,10 +24179,10 @@
         <v>38</v>
       </c>
       <c r="N528" t="n">
-        <v>5280</v>
+        <v>5305.2631578947</v>
       </c>
       <c r="O528" t="n">
-        <v>200640</v>
+        <v>201599.9999999986</v>
       </c>
       <c r="P528" t="n">
         <v>6900</v>
@@ -24225,10 +24225,10 @@
         <v>144</v>
       </c>
       <c r="N529" t="n">
-        <v>5280</v>
+        <v>5301.8181818182</v>
       </c>
       <c r="O529" t="n">
-        <v>760320</v>
+        <v>763461.8181818208</v>
       </c>
       <c r="P529" t="n">
         <v>6900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -14553,10 +14553,10 @@
         <v>164</v>
       </c>
       <c r="N322" t="n">
-        <v>4956.8186522463</v>
+        <v>4907.8221131448</v>
       </c>
       <c r="O322" t="n">
-        <v>812918.2589683932</v>
+        <v>804882.8265557472</v>
       </c>
       <c r="P322" t="n">
         <v>8200</v>
@@ -17420,10 +17420,10 @@
         <v>190</v>
       </c>
       <c r="N384" t="n">
-        <v>3642.7032352941</v>
+        <v>3629.36</v>
       </c>
       <c r="O384" t="n">
-        <v>692113.614705879</v>
+        <v>689578.4</v>
       </c>
       <c r="P384" t="n">
         <v>3900</v>
@@ -17846,10 +17846,10 @@
         <v>94</v>
       </c>
       <c r="N393" t="n">
-        <v>6160.2225287356</v>
+        <v>6090.22</v>
       </c>
       <c r="O393" t="n">
-        <v>579060.9177011463</v>
+        <v>572480.6800000001</v>
       </c>
       <c r="P393" t="n">
         <v>8500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-30</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1271,10 +1271,10 @@
         <v>103</v>
       </c>
       <c r="N22" t="n">
-        <v>2474.7041355932</v>
+        <v>2474.7040753425</v>
       </c>
       <c r="O22" t="n">
-        <v>254894.5259660996</v>
+        <v>254894.5197602775</v>
       </c>
       <c r="P22" t="n">
         <v>4500</v>
@@ -3362,10 +3362,10 @@
         <v>120</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0599864057</v>
+        <v>1098.0603685231</v>
       </c>
       <c r="O72" t="n">
-        <v>131767.198368684</v>
+        <v>131767.244222772</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -4966,10 +4966,10 @@
         <v>459</v>
       </c>
       <c r="N108" t="n">
-        <v>4890.9300489297</v>
+        <v>4890.9300489596</v>
       </c>
       <c r="O108" t="n">
-        <v>2244936.892458732</v>
+        <v>2244936.892472456</v>
       </c>
       <c r="P108" t="n">
         <v>8200</v>
@@ -5414,10 +5414,10 @@
         <v>120</v>
       </c>
       <c r="N118" t="n">
-        <v>3240.8500374532</v>
+        <v>3240.850037594</v>
       </c>
       <c r="O118" t="n">
-        <v>388902.004494384</v>
+        <v>388902.00451128</v>
       </c>
       <c r="P118" t="n">
         <v>5200</v>
@@ -5860,10 +5860,10 @@
         <v>501</v>
       </c>
       <c r="N128" t="n">
-        <v>3041.6600134228</v>
+        <v>3041.660013459</v>
       </c>
       <c r="O128" t="n">
-        <v>1523871.666724823</v>
+        <v>1523871.666742959</v>
       </c>
       <c r="P128" t="n">
         <v>5500</v>
@@ -5947,10 +5947,10 @@
         <v>1116</v>
       </c>
       <c r="N130" t="n">
-        <v>4372.2107907508</v>
+        <v>4372.2107910895</v>
       </c>
       <c r="O130" t="n">
-        <v>4879387.242477893</v>
+        <v>4879387.242855882</v>
       </c>
       <c r="P130" t="n">
         <v>7500</v>
@@ -7399,10 +7399,10 @@
         <v>191</v>
       </c>
       <c r="N162" t="n">
-        <v>1630.923733916</v>
+        <v>1630.9237493905</v>
       </c>
       <c r="O162" t="n">
-        <v>311506.433177956</v>
+        <v>311506.4361335855</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1937906027</v>
+        <v>1550.1937917646</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9764616972</v>
+        <v>55806.9765035256</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -8832,10 +8832,10 @@
         <v>348</v>
       </c>
       <c r="N195" t="n">
-        <v>2029.8738739669</v>
+        <v>2029.8739473684</v>
       </c>
       <c r="O195" t="n">
-        <v>706396.1081404812</v>
+        <v>706396.1336842031</v>
       </c>
       <c r="P195" t="n">
         <v>3600</v>
@@ -13952,10 +13952,10 @@
         <v>263</v>
       </c>
       <c r="N309" t="n">
-        <v>2252.2972418478</v>
+        <v>2252.2973618785</v>
       </c>
       <c r="O309" t="n">
-        <v>592354.1746059713</v>
+        <v>592354.2061740455</v>
       </c>
       <c r="P309" t="n">
         <v>3900</v>
@@ -14139,10 +14139,10 @@
         <v>504</v>
       </c>
       <c r="N313" t="n">
-        <v>2328.1187082951</v>
+        <v>2328.1186987357</v>
       </c>
       <c r="O313" t="n">
-        <v>1173371.82898073</v>
+        <v>1173371.824162793</v>
       </c>
       <c r="P313" t="n">
         <v>4500</v>
@@ -14553,10 +14553,10 @@
         <v>164</v>
       </c>
       <c r="N322" t="n">
-        <v>4907.8221131448</v>
+        <v>4907.8221561969</v>
       </c>
       <c r="O322" t="n">
-        <v>804882.8265557472</v>
+        <v>804882.8336162916</v>
       </c>
       <c r="P322" t="n">
         <v>8200</v>
@@ -15928,10 +15928,10 @@
         <v>60</v>
       </c>
       <c r="N352" t="n">
-        <v>4268.7071078431</v>
+        <v>4268.70745</v>
       </c>
       <c r="O352" t="n">
-        <v>256122.426470586</v>
+        <v>256122.447</v>
       </c>
       <c r="P352" t="n">
         <v>6900</v>
@@ -16566,22 +16566,22 @@
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M366" t="n">
-        <v>1239</v>
+        <v>1179</v>
       </c>
       <c r="N366" t="n">
         <v>2454</v>
       </c>
       <c r="O366" t="n">
-        <v>3040506</v>
+        <v>2893266</v>
       </c>
       <c r="P366" t="n">
         <v>4200</v>
       </c>
       <c r="Q366" t="n">
-        <v>5203800</v>
+        <v>4951800</v>
       </c>
     </row>
     <row r="367">
@@ -17080,22 +17080,22 @@
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M377" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N377" t="n">
         <v>2438.7</v>
       </c>
       <c r="O377" t="n">
-        <v>26825.7</v>
+        <v>19509.6</v>
       </c>
       <c r="P377" t="n">
         <v>11500</v>
       </c>
       <c r="Q377" t="n">
-        <v>126500</v>
+        <v>92000</v>
       </c>
     </row>
     <row r="378">
@@ -17748,10 +17748,10 @@
         <v>178</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700091449</v>
+        <v>1690.8700091701</v>
       </c>
       <c r="O391" t="n">
-        <v>300974.8616277922</v>
+        <v>300974.8616322778</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -18641,10 +18641,10 @@
         <v>132</v>
       </c>
       <c r="N410" t="n">
-        <v>3259.1342692308</v>
+        <v>3259.1343023256</v>
       </c>
       <c r="O410" t="n">
-        <v>430205.7235384656</v>
+        <v>430205.7279069792</v>
       </c>
       <c r="P410" t="n">
         <v>3600</v>
@@ -18777,10 +18777,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8411757364</v>
+        <v>3110.8406506215</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6823514728</v>
+        <v>6221.681301243</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -23106,10 +23106,10 @@
         <v>116</v>
       </c>
       <c r="N504" t="n">
-        <v>1213.6821359223</v>
+        <v>1213.6821400778</v>
       </c>
       <c r="O504" t="n">
-        <v>140787.1277669868</v>
+        <v>140787.1282490248</v>
       </c>
       <c r="P504" t="n">
         <v>1500</v>
@@ -24315,22 +24315,22 @@
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="M531" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="N531" t="n">
         <v>3520</v>
       </c>
       <c r="O531" t="n">
-        <v>422400</v>
+        <v>0</v>
       </c>
       <c r="P531" t="n">
         <v>4500</v>
       </c>
       <c r="Q531" t="n">
-        <v>540000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="532">

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q564"/>
+  <dimension ref="A1:Q563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-08-31</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-01</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464631809</v>
+        <v>3376.746460274</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.976939475</v>
+        <v>1931498.975276728</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8548484848</v>
+        <v>6272.8549315068</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.486666653</v>
+        <v>1794036.510410945</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1349,10 +1349,10 @@
         <v>48</v>
       </c>
       <c r="N24" t="n">
-        <v>3716.3301954397</v>
+        <v>3716.3301957586</v>
       </c>
       <c r="O24" t="n">
-        <v>178383.8493811056</v>
+        <v>178383.8493964128</v>
       </c>
       <c r="P24" t="n">
         <v>9500</v>
@@ -3362,10 +3362,10 @@
         <v>120</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0603685231</v>
+        <v>1098.0605968058</v>
       </c>
       <c r="O72" t="n">
-        <v>131767.244222772</v>
+        <v>131767.271616696</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -5860,10 +5860,10 @@
         <v>501</v>
       </c>
       <c r="N128" t="n">
-        <v>3041.660013459</v>
+        <v>3041.6600135135</v>
       </c>
       <c r="O128" t="n">
-        <v>1523871.666742959</v>
+        <v>1523871.666770264</v>
       </c>
       <c r="P128" t="n">
         <v>5500</v>
@@ -7399,10 +7399,10 @@
         <v>191</v>
       </c>
       <c r="N162" t="n">
-        <v>1630.9237493905</v>
+        <v>1630.9237512195</v>
       </c>
       <c r="O162" t="n">
-        <v>311506.4361335855</v>
+        <v>311506.4364829245</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1937917646</v>
+        <v>1550.193804203</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9765035256</v>
+        <v>55806.976951308</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -7491,10 +7491,10 @@
         <v>48</v>
       </c>
       <c r="N164" t="n">
-        <v>1579.3897428571</v>
+        <v>1579.3895639535</v>
       </c>
       <c r="O164" t="n">
-        <v>75810.7076571408</v>
+        <v>75810.699069768</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -10105,10 +10105,10 @@
         <v>97</v>
       </c>
       <c r="N225" t="n">
-        <v>2568.8354697987</v>
+        <v>2568.8354237288</v>
       </c>
       <c r="O225" t="n">
-        <v>249177.0405704739</v>
+        <v>249177.0361016936</v>
       </c>
       <c r="P225" t="n">
         <v>4500</v>
@@ -10505,10 +10505,10 @@
         <v>154</v>
       </c>
       <c r="N234" t="n">
-        <v>548.1471884058</v>
+        <v>548.14718568665</v>
       </c>
       <c r="O234" t="n">
-        <v>84414.6670144932</v>
+        <v>84414.6665957441</v>
       </c>
       <c r="P234" t="n">
         <v>2000</v>
@@ -14139,10 +14139,10 @@
         <v>504</v>
       </c>
       <c r="N313" t="n">
-        <v>2328.1186987357</v>
+        <v>2328.1186979327</v>
       </c>
       <c r="O313" t="n">
-        <v>1173371.824162793</v>
+        <v>1173371.823758081</v>
       </c>
       <c r="P313" t="n">
         <v>4500</v>
@@ -14783,10 +14783,10 @@
         <v>84</v>
       </c>
       <c r="N327" t="n">
-        <v>3903.736710023</v>
+        <v>3903.7367356322</v>
       </c>
       <c r="O327" t="n">
-        <v>327913.883641932</v>
+        <v>327913.8857931048</v>
       </c>
       <c r="P327" t="n">
         <v>7500</v>
@@ -16388,10 +16388,10 @@
         <v>839</v>
       </c>
       <c r="N362" t="n">
-        <v>1516.0387934921</v>
+        <v>1516.0387920714</v>
       </c>
       <c r="O362" t="n">
-        <v>1271956.547739872</v>
+        <v>1271956.546547905</v>
       </c>
       <c r="P362" t="n">
         <v>2300</v>
@@ -16560,13 +16560,13 @@
         </is>
       </c>
       <c r="J366" t="n">
-        <v>1239</v>
+        <v>1179</v>
       </c>
       <c r="K366" t="n">
         <v>0</v>
       </c>
       <c r="L366" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M366" t="n">
         <v>1179</v>
@@ -16751,10 +16751,10 @@
         <v>145</v>
       </c>
       <c r="N370" t="n">
-        <v>2842.2737341772</v>
+        <v>2842.2744460028</v>
       </c>
       <c r="O370" t="n">
-        <v>412129.691455694</v>
+        <v>412129.794670406</v>
       </c>
       <c r="P370" t="n">
         <v>4900</v>
@@ -16795,10 +16795,10 @@
         <v>2243</v>
       </c>
       <c r="N371" t="n">
-        <v>692.1522422179</v>
+        <v>692.15225097656</v>
       </c>
       <c r="O371" t="n">
-        <v>1552497.47929475</v>
+        <v>1552497.498940424</v>
       </c>
       <c r="P371" t="n">
         <v>1200</v>
@@ -17074,13 +17074,13 @@
         </is>
       </c>
       <c r="J377" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K377" t="n">
         <v>0</v>
       </c>
       <c r="L377" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M377" t="n">
         <v>8</v>
@@ -18125,10 +18125,10 @@
         <v>7734</v>
       </c>
       <c r="N399" t="n">
-        <v>711.3366494881</v>
+        <v>711.33664937221</v>
       </c>
       <c r="O399" t="n">
-        <v>5501477.647140965</v>
+        <v>5501477.646244672</v>
       </c>
       <c r="P399" t="n">
         <v>900</v>
@@ -18356,10 +18356,10 @@
         <v>45</v>
       </c>
       <c r="N404" t="n">
-        <v>4032.3968134715</v>
+        <v>4032.3968051948</v>
       </c>
       <c r="O404" t="n">
-        <v>181457.8566062175</v>
+        <v>181457.856233766</v>
       </c>
       <c r="P404" t="n">
         <v>4200</v>
@@ -18641,10 +18641,10 @@
         <v>132</v>
       </c>
       <c r="N410" t="n">
-        <v>3259.1343023256</v>
+        <v>3259.1343529412</v>
       </c>
       <c r="O410" t="n">
-        <v>430205.7279069792</v>
+        <v>430205.7345882384</v>
       </c>
       <c r="P410" t="n">
         <v>3600</v>
@@ -18777,10 +18777,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8406506215</v>
+        <v>3110.8406407201</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.681301243</v>
+        <v>6221.6812814402</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -19151,10 +19151,10 @@
         <v>4</v>
       </c>
       <c r="N421" t="n">
-        <v>2501.3849295775</v>
+        <v>2501.3848325359</v>
       </c>
       <c r="O421" t="n">
-        <v>10005.53971831</v>
+        <v>10005.5393301436</v>
       </c>
       <c r="P421" t="n">
         <v>4100</v>
@@ -19855,10 +19855,10 @@
         <v>54</v>
       </c>
       <c r="N436" t="n">
-        <v>2098.4050733138</v>
+        <v>2098.4050882353</v>
       </c>
       <c r="O436" t="n">
-        <v>113313.8739589452</v>
+        <v>113313.8747647062</v>
       </c>
       <c r="P436" t="n">
         <v>9500</v>
@@ -20146,10 +20146,10 @@
         <v>23</v>
       </c>
       <c r="N442" t="n">
-        <v>2832.195</v>
+        <v>2832.1951515152</v>
       </c>
       <c r="O442" t="n">
-        <v>65140.485</v>
+        <v>65140.4884848496</v>
       </c>
       <c r="P442" t="n">
         <v>12900</v>
@@ -23283,10 +23283,10 @@
         <v>11</v>
       </c>
       <c r="N508" t="n">
-        <v>22951.704799483</v>
+        <v>22951.704792746</v>
       </c>
       <c r="O508" t="n">
-        <v>252468.752794313</v>
+        <v>252468.752720206</v>
       </c>
       <c r="P508" t="n">
         <v>37900</v>
@@ -24290,12 +24290,12 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>J-455</t>
+          <t>J-718</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>TABLETA MAGICA J-455</t>
+          <t>MOTO DE IMPULSO BLISTER J-718</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
@@ -24309,39 +24309,39 @@
         </is>
       </c>
       <c r="J531" t="n">
-        <v>120</v>
+        <v>166</v>
       </c>
       <c r="K531" t="n">
         <v>0</v>
       </c>
       <c r="L531" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="M531" t="n">
-        <v>0</v>
+        <v>166</v>
       </c>
       <c r="N531" t="n">
-        <v>3520</v>
+        <v>4576</v>
       </c>
       <c r="O531" t="n">
-        <v>0</v>
+        <v>759616</v>
       </c>
       <c r="P531" t="n">
-        <v>4500</v>
+        <v>5900</v>
       </c>
       <c r="Q531" t="n">
-        <v>0</v>
+        <v>979400</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>J-718</t>
+          <t>J-719</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>MOTO DE IMPULSO BLISTER J-718</t>
+          <t>MOTO ENCARTONADA J-719</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
@@ -24355,7 +24355,7 @@
         </is>
       </c>
       <c r="J532" t="n">
-        <v>166</v>
+        <v>274</v>
       </c>
       <c r="K532" t="n">
         <v>0</v>
@@ -24364,35 +24364,35 @@
         <v>0</v>
       </c>
       <c r="M532" t="n">
-        <v>166</v>
+        <v>274</v>
       </c>
       <c r="N532" t="n">
-        <v>4576</v>
+        <v>5280</v>
       </c>
       <c r="O532" t="n">
-        <v>759616</v>
+        <v>1446720</v>
       </c>
       <c r="P532" t="n">
-        <v>5900</v>
+        <v>6900</v>
       </c>
       <c r="Q532" t="n">
-        <v>979400</v>
+        <v>1890600</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>J-719</t>
+          <t>MG040</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>MOTO ENCARTONADA J-719</t>
+          <t>ABACO ANIMALES PT17058</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>JUGUETERIA</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -24401,7 +24401,7 @@
         </is>
       </c>
       <c r="J533" t="n">
-        <v>274</v>
+        <v>23</v>
       </c>
       <c r="K533" t="n">
         <v>0</v>
@@ -24410,30 +24410,35 @@
         <v>0</v>
       </c>
       <c r="M533" t="n">
-        <v>274</v>
+        <v>23</v>
       </c>
       <c r="N533" t="n">
         <v>5280</v>
       </c>
       <c r="O533" t="n">
-        <v>1446720</v>
+        <v>121440</v>
       </c>
       <c r="P533" t="n">
-        <v>6900</v>
+        <v>6600</v>
       </c>
       <c r="Q533" t="n">
-        <v>1890600</v>
+        <v>151800</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>MG040</t>
+          <t>MG044</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>PT19323</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>ABACO ANIMALES PT17058</t>
+          <t>ABACO TREN PT19323</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -24447,7 +24452,7 @@
         </is>
       </c>
       <c r="J534" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K534" t="n">
         <v>0</v>
@@ -24456,35 +24461,30 @@
         <v>0</v>
       </c>
       <c r="M534" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N534" t="n">
-        <v>5280</v>
+        <v>7760</v>
       </c>
       <c r="O534" t="n">
-        <v>121440</v>
+        <v>186240</v>
       </c>
       <c r="P534" t="n">
-        <v>6600</v>
+        <v>9700</v>
       </c>
       <c r="Q534" t="n">
-        <v>151800</v>
+        <v>232800</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>MG044</t>
-        </is>
-      </c>
-      <c r="B535" t="inlineStr">
-        <is>
-          <t>PT19323</t>
+          <t>MG051</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>ABACO TREN PT19323</t>
+          <t>CAJON DIDACTICO RELOJ PT21204</t>
         </is>
       </c>
       <c r="E535" t="inlineStr">
@@ -24498,7 +24498,7 @@
         </is>
       </c>
       <c r="J535" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K535" t="n">
         <v>0</v>
@@ -24507,35 +24507,40 @@
         <v>0</v>
       </c>
       <c r="M535" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N535" t="n">
-        <v>7760</v>
+        <v>22320</v>
       </c>
       <c r="O535" t="n">
-        <v>186240</v>
+        <v>624960</v>
       </c>
       <c r="P535" t="n">
-        <v>9700</v>
+        <v>27900</v>
       </c>
       <c r="Q535" t="n">
-        <v>232800</v>
+        <v>781200</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>MG051</t>
+          <t>MG067</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>MG21283</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>CAJON DIDACTICO RELOJ PT21204</t>
+          <t>KARAOKE BLUETOOTH MG21283MG</t>
         </is>
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MICELANEOS</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -24544,7 +24549,7 @@
         </is>
       </c>
       <c r="J536" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="K536" t="n">
         <v>0</v>
@@ -24553,40 +24558,40 @@
         <v>0</v>
       </c>
       <c r="M536" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="N536" t="n">
-        <v>22320</v>
+        <v>41161.350714286</v>
       </c>
       <c r="O536" t="n">
-        <v>624960</v>
+        <v>1029033.76785715</v>
       </c>
       <c r="P536" t="n">
-        <v>27900</v>
+        <v>55000</v>
       </c>
       <c r="Q536" t="n">
-        <v>781200</v>
+        <v>1375000</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>MG067</t>
+          <t>MG094</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MG21283</t>
+          <t>mg33153</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>KARAOKE BLUETOOTH MG21283MG</t>
+          <t>LANZA DISCOS MED MULTICOLOR MG33153</t>
         </is>
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>MICELANEOS</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -24595,7 +24600,7 @@
         </is>
       </c>
       <c r="J537" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="K537" t="n">
         <v>0</v>
@@ -24604,40 +24609,35 @@
         <v>0</v>
       </c>
       <c r="M537" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="N537" t="n">
-        <v>41161.350714286</v>
+        <v>3840</v>
       </c>
       <c r="O537" t="n">
-        <v>1029033.76785715</v>
+        <v>65280</v>
       </c>
       <c r="P537" t="n">
-        <v>55000</v>
+        <v>3900</v>
       </c>
       <c r="Q537" t="n">
-        <v>1375000</v>
+        <v>66300</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>MG094</t>
-        </is>
-      </c>
-      <c r="B538" t="inlineStr">
-        <is>
-          <t>mg33153</t>
+          <t>MG16421</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>LANZA DISCOS MED MULTICOLOR MG33153</t>
+          <t>CARRO MEZCALDOR BOLSA MDE MG16421</t>
         </is>
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>LANZADORES</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -24646,7 +24646,7 @@
         </is>
       </c>
       <c r="J538" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="K538" t="n">
         <v>0</v>
@@ -24655,35 +24655,40 @@
         <v>0</v>
       </c>
       <c r="M538" t="n">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="N538" t="n">
-        <v>3840</v>
+        <v>2775.86</v>
       </c>
       <c r="O538" t="n">
-        <v>65280</v>
+        <v>141568.86</v>
       </c>
       <c r="P538" t="n">
-        <v>3900</v>
+        <v>12500</v>
       </c>
       <c r="Q538" t="n">
-        <v>66300</v>
+        <v>637500</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>MG16421</t>
+          <t>MG18991</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>MG18991</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>CARRO MEZCALDOR BOLSA MDE MG16421</t>
+          <t>MAQUINA DE COSER PILAS MG18991</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -24692,7 +24697,7 @@
         </is>
       </c>
       <c r="J539" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="K539" t="n">
         <v>0</v>
@@ -24701,40 +24706,35 @@
         <v>0</v>
       </c>
       <c r="M539" t="n">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="N539" t="n">
-        <v>2775.86</v>
+        <v>8949.32</v>
       </c>
       <c r="O539" t="n">
-        <v>141568.86</v>
+        <v>125290.48</v>
       </c>
       <c r="P539" t="n">
-        <v>12500</v>
+        <v>28900</v>
       </c>
       <c r="Q539" t="n">
-        <v>637500</v>
+        <v>404600</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>MG18991</t>
-        </is>
-      </c>
-      <c r="B540" t="inlineStr">
-        <is>
-          <t>MG18991</t>
+          <t>MG20906</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>MAQUINA DE COSER PILAS MG18991</t>
+          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -24743,7 +24743,7 @@
         </is>
       </c>
       <c r="J540" t="n">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="K540" t="n">
         <v>0</v>
@@ -24752,35 +24752,40 @@
         <v>0</v>
       </c>
       <c r="M540" t="n">
-        <v>14</v>
+        <v>169</v>
       </c>
       <c r="N540" t="n">
-        <v>8949.32</v>
+        <v>1482.84</v>
       </c>
       <c r="O540" t="n">
-        <v>125290.48</v>
+        <v>250599.96</v>
       </c>
       <c r="P540" t="n">
-        <v>28900</v>
+        <v>6500</v>
       </c>
       <c r="Q540" t="n">
-        <v>404600</v>
+        <v>1098500</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>MG20906</t>
+          <t>MG20930</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>MG20930</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>DINOSAURIO DIDACTICO EN BOLSA MG20906</t>
+          <t>CARRO BUGGY RECARGABLE MG20930</t>
         </is>
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -24789,7 +24794,7 @@
         </is>
       </c>
       <c r="J541" t="n">
-        <v>169</v>
+        <v>6</v>
       </c>
       <c r="K541" t="n">
         <v>0</v>
@@ -24798,40 +24803,35 @@
         <v>0</v>
       </c>
       <c r="M541" t="n">
-        <v>169</v>
+        <v>6</v>
       </c>
       <c r="N541" t="n">
-        <v>1482.84</v>
+        <v>63353.92</v>
       </c>
       <c r="O541" t="n">
-        <v>250599.96</v>
+        <v>380123.52</v>
       </c>
       <c r="P541" t="n">
-        <v>6500</v>
+        <v>128000</v>
       </c>
       <c r="Q541" t="n">
-        <v>1098500</v>
+        <v>768000</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MG20930</t>
-        </is>
-      </c>
-      <c r="B542" t="inlineStr">
-        <is>
-          <t>MG20930</t>
+          <t>MG22320</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>CARRO BUGGY RECARGABLE MG20930</t>
+          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>DIDACTICOS</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -24840,7 +24840,7 @@
         </is>
       </c>
       <c r="J542" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="K542" t="n">
         <v>0</v>
@@ -24849,35 +24849,35 @@
         <v>0</v>
       </c>
       <c r="M542" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="N542" t="n">
-        <v>63353.92</v>
+        <v>1129.14</v>
       </c>
       <c r="O542" t="n">
-        <v>380123.52</v>
+        <v>91460.34000000001</v>
       </c>
       <c r="P542" t="n">
-        <v>128000</v>
+        <v>6900</v>
       </c>
       <c r="Q542" t="n">
-        <v>768000</v>
+        <v>558900</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>MG22320</t>
+          <t>MG27668</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>CABALLO DIDACTICO DESARMABLE PQÑ MG22320</t>
+          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>DIDACTICOS</t>
+          <t>MUÑECA</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="J543" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="K543" t="n">
         <v>0</v>
@@ -24895,30 +24895,30 @@
         <v>0</v>
       </c>
       <c r="M543" t="n">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="N543" t="n">
-        <v>1129.14</v>
+        <v>15239.8</v>
       </c>
       <c r="O543" t="n">
-        <v>91460.34000000001</v>
+        <v>320035.8</v>
       </c>
       <c r="P543" t="n">
-        <v>6900</v>
+        <v>15900</v>
       </c>
       <c r="Q543" t="n">
-        <v>558900</v>
+        <v>333900</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>MG27668</t>
+          <t>MG28914</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>MUÑECA ARTICULADA EJECUTIVA CON BOLSO MG27668</t>
+          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
         </is>
       </c>
       <c r="E544" t="inlineStr">
@@ -24932,7 +24932,7 @@
         </is>
       </c>
       <c r="J544" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K544" t="n">
         <v>0</v>
@@ -24941,35 +24941,35 @@
         <v>0</v>
       </c>
       <c r="M544" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N544" t="n">
-        <v>15239.8</v>
+        <v>5563</v>
       </c>
       <c r="O544" t="n">
-        <v>320035.8</v>
+        <v>133512</v>
       </c>
       <c r="P544" t="n">
-        <v>15900</v>
+        <v>11900</v>
       </c>
       <c r="Q544" t="n">
-        <v>333900</v>
+        <v>285600</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>MG28914</t>
+          <t>MG30041</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>MUÑECA CON MASCOTA ACCESORIOS MG28914</t>
+          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>MUÑECA</t>
+          <t>CARROS</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -24990,32 +24990,37 @@
         <v>24</v>
       </c>
       <c r="N545" t="n">
-        <v>5563</v>
+        <v>9046.99</v>
       </c>
       <c r="O545" t="n">
-        <v>133512</v>
+        <v>217127.76</v>
       </c>
       <c r="P545" t="n">
-        <v>11900</v>
+        <v>22500</v>
       </c>
       <c r="Q545" t="n">
-        <v>285600</v>
+        <v>540000</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>MG30041</t>
+          <t>MG30183</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>MG30183</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>SET CARROS DIDACTICOS VEGETALES X4 PCS MG30041</t>
+          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
         </is>
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>CARROS</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -25024,7 +25029,7 @@
         </is>
       </c>
       <c r="J546" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="K546" t="n">
         <v>0</v>
@@ -25033,40 +25038,35 @@
         <v>0</v>
       </c>
       <c r="M546" t="n">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="N546" t="n">
-        <v>9046.99</v>
+        <v>3982.6707619048</v>
       </c>
       <c r="O546" t="n">
-        <v>217127.76</v>
+        <v>370388.3808571464</v>
       </c>
       <c r="P546" t="n">
-        <v>22500</v>
+        <v>10900</v>
       </c>
       <c r="Q546" t="n">
-        <v>540000</v>
+        <v>1013700</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>MG30183</t>
-        </is>
-      </c>
-      <c r="B547" t="inlineStr">
-        <is>
-          <t>MG30183</t>
+          <t>MG40210</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>SET SONAJERO BOLSA X6 PCS  MG30183</t>
+          <t>SONAJERO OSO MG40210</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>DIDACTICO</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -25075,7 +25075,7 @@
         </is>
       </c>
       <c r="J547" t="n">
-        <v>93</v>
+        <v>399</v>
       </c>
       <c r="K547" t="n">
         <v>0</v>
@@ -25084,35 +25084,40 @@
         <v>0</v>
       </c>
       <c r="M547" t="n">
-        <v>93</v>
+        <v>399</v>
       </c>
       <c r="N547" t="n">
-        <v>3982.6707619048</v>
+        <v>571.87</v>
       </c>
       <c r="O547" t="n">
-        <v>370388.3808571464</v>
+        <v>228176.13</v>
       </c>
       <c r="P547" t="n">
-        <v>10900</v>
+        <v>2500</v>
       </c>
       <c r="Q547" t="n">
-        <v>1013700</v>
+        <v>997500</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>MG40210</t>
+          <t>MG40269</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>MG40269</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>SONAJERO OSO MG40210</t>
+          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>DIDACTICO</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -25121,7 +25126,7 @@
         </is>
       </c>
       <c r="J548" t="n">
-        <v>399</v>
+        <v>3</v>
       </c>
       <c r="K548" t="n">
         <v>0</v>
@@ -25130,35 +25135,35 @@
         <v>0</v>
       </c>
       <c r="M548" t="n">
-        <v>399</v>
+        <v>3</v>
       </c>
       <c r="N548" t="n">
-        <v>571.87</v>
+        <v>2432.1352873563</v>
       </c>
       <c r="O548" t="n">
-        <v>228176.13</v>
+        <v>7296.4058620689</v>
       </c>
       <c r="P548" t="n">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="Q548" t="n">
-        <v>997500</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>MG40269</t>
+          <t>MG40324</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>MG40269</t>
+          <t>MG40324</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>SONAJERO BOLSA ELEFANTE MG40269</t>
+          <t>JUEGO DE PESCA MG40324</t>
         </is>
       </c>
       <c r="E549" t="inlineStr">
@@ -25172,7 +25177,7 @@
         </is>
       </c>
       <c r="J549" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K549" t="n">
         <v>0</v>
@@ -25181,40 +25186,35 @@
         <v>0</v>
       </c>
       <c r="M549" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N549" t="n">
-        <v>2432.1351111111</v>
+        <v>2005.78</v>
       </c>
       <c r="O549" t="n">
-        <v>7296.405333333299</v>
+        <v>2005.78</v>
       </c>
       <c r="P549" t="n">
-        <v>4500</v>
+        <v>9500</v>
       </c>
       <c r="Q549" t="n">
-        <v>13500</v>
+        <v>9500</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>MG40324</t>
-        </is>
-      </c>
-      <c r="B550" t="inlineStr">
-        <is>
-          <t>MG40324</t>
+          <t>MG40334</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>JUEGO DE PESCA MG40324</t>
+          <t>MARIMBA 4 NOTAS MG40334</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>MUSICALES</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -25223,7 +25223,7 @@
         </is>
       </c>
       <c r="J550" t="n">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="K550" t="n">
         <v>0</v>
@@ -25232,35 +25232,40 @@
         <v>0</v>
       </c>
       <c r="M550" t="n">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="N550" t="n">
-        <v>2005.78</v>
+        <v>227.41613363363</v>
       </c>
       <c r="O550" t="n">
-        <v>2005.78</v>
+        <v>61629.77221471373</v>
       </c>
       <c r="P550" t="n">
-        <v>9500</v>
+        <v>1200</v>
       </c>
       <c r="Q550" t="n">
-        <v>9500</v>
+        <v>325200</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>MG40334</t>
+          <t>MG40642</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>MG40642</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>MARIMBA 4 NOTAS MG40334</t>
+          <t>MORRAL TOCADOR PORTABLE MG40642</t>
         </is>
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>MUSICALES</t>
+          <t>PIÑATERIA</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -25269,7 +25274,7 @@
         </is>
       </c>
       <c r="J551" t="n">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="K551" t="n">
         <v>0</v>
@@ -25278,35 +25283,35 @@
         <v>0</v>
       </c>
       <c r="M551" t="n">
-        <v>271</v>
+        <v>15</v>
       </c>
       <c r="N551" t="n">
-        <v>227.41613363363</v>
+        <v>19081.85</v>
       </c>
       <c r="O551" t="n">
-        <v>61629.77221471373</v>
+        <v>286227.75</v>
       </c>
       <c r="P551" t="n">
-        <v>1200</v>
+        <v>36900</v>
       </c>
       <c r="Q551" t="n">
-        <v>325200</v>
+        <v>553500</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>MG40642</t>
+          <t>MG40888</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>MG40642</t>
+          <t>MG40888</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>MORRAL TOCADOR PORTABLE MG40642</t>
+          <t>SET DE RESCATE EN BOLSA MG40888</t>
         </is>
       </c>
       <c r="E552" t="inlineStr">
@@ -25320,7 +25325,7 @@
         </is>
       </c>
       <c r="J552" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K552" t="n">
         <v>0</v>
@@ -25329,40 +25334,35 @@
         <v>0</v>
       </c>
       <c r="M552" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N552" t="n">
-        <v>19081.85</v>
+        <v>7540.09</v>
       </c>
       <c r="O552" t="n">
-        <v>286227.75</v>
+        <v>82940.99000000001</v>
       </c>
       <c r="P552" t="n">
-        <v>36900</v>
+        <v>18500</v>
       </c>
       <c r="Q552" t="n">
-        <v>553500</v>
+        <v>203500</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>MG40888</t>
-        </is>
-      </c>
-      <c r="B553" t="inlineStr">
-        <is>
-          <t>MG40888</t>
+          <t>MG41171</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>SET DE RESCATE EN BOLSA MG40888</t>
+          <t>LANZA AGUA COLORES GDE MG41171</t>
         </is>
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>LANZADORES</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -25371,7 +25371,7 @@
         </is>
       </c>
       <c r="J553" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="K553" t="n">
         <v>0</v>
@@ -25380,44 +25380,34 @@
         <v>0</v>
       </c>
       <c r="M553" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="N553" t="n">
-        <v>7540.09</v>
+        <v>25110.1</v>
       </c>
       <c r="O553" t="n">
-        <v>82940.99000000001</v>
+        <v>778413.1</v>
       </c>
       <c r="P553" t="n">
-        <v>18500</v>
+        <v>27900</v>
       </c>
       <c r="Q553" t="n">
-        <v>203500</v>
+        <v>864900</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>MG41171</t>
+          <t>MR044</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>LANZA AGUA COLORES GDE MG41171</t>
-        </is>
-      </c>
-      <c r="E554" t="inlineStr">
-        <is>
-          <t>LANZADORES</t>
-        </is>
-      </c>
-      <c r="I554" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
         </is>
       </c>
       <c r="J554" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K554" t="n">
         <v>0</v>
@@ -25426,34 +25416,44 @@
         <v>0</v>
       </c>
       <c r="M554" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="N554" t="n">
-        <v>25110.1</v>
+        <v>20720</v>
       </c>
       <c r="O554" t="n">
-        <v>778413.1</v>
+        <v>124320</v>
       </c>
       <c r="P554" t="n">
-        <v>27900</v>
+        <v>25900</v>
       </c>
       <c r="Q554" t="n">
-        <v>864900</v>
+        <v>155400</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>MR044</t>
+          <t>MR045</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>MORRAL STD PELUCHE 0227-0231-0121-001</t>
+          <t>MORRAL ANIMALES STD 0230-02-002</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>JUGUETERIA</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J555" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K555" t="n">
         <v>0</v>
@@ -25462,44 +25462,34 @@
         <v>0</v>
       </c>
       <c r="M555" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="N555" t="n">
-        <v>20720</v>
+        <v>22080.08</v>
       </c>
       <c r="O555" t="n">
-        <v>124320</v>
+        <v>287041.04</v>
       </c>
       <c r="P555" t="n">
-        <v>25900</v>
+        <v>29900</v>
       </c>
       <c r="Q555" t="n">
-        <v>155400</v>
+        <v>388700</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>MR045</t>
+          <t>MR081</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>MORRAL ANIMALES STD 0230-02-002</t>
-        </is>
-      </c>
-      <c r="E556" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I556" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>MORRAL GATICO STD MR081</t>
         </is>
       </c>
       <c r="J556" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="K556" t="n">
         <v>0</v>
@@ -25508,34 +25498,44 @@
         <v>0</v>
       </c>
       <c r="M556" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N556" t="n">
-        <v>22080.08</v>
+        <v>22865</v>
       </c>
       <c r="O556" t="n">
-        <v>287041.04</v>
+        <v>91460</v>
       </c>
       <c r="P556" t="n">
-        <v>29900</v>
+        <v>26900</v>
       </c>
       <c r="Q556" t="n">
-        <v>388700</v>
+        <v>107600</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>MR081</t>
+          <t>PT14019</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>MORRAL GATICO STD MR081</t>
+          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>DIDACTICOS</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J557" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="K557" t="n">
         <v>0</v>
@@ -25544,44 +25544,34 @@
         <v>0</v>
       </c>
       <c r="M557" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="N557" t="n">
-        <v>22865</v>
+        <v>1950.7</v>
       </c>
       <c r="O557" t="n">
-        <v>91460</v>
+        <v>64373.1</v>
       </c>
       <c r="P557" t="n">
-        <v>26900</v>
+        <v>7500</v>
       </c>
       <c r="Q557" t="n">
-        <v>107600</v>
+        <v>247500</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>PT14019</t>
+          <t>SLBT04</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>CUATRIMOTO CON DESTORNILLADOR DIDACTICA PT14019</t>
-        </is>
-      </c>
-      <c r="E558" t="inlineStr">
-        <is>
-          <t>DIDACTICOS</t>
-        </is>
-      </c>
-      <c r="I558" t="inlineStr">
-        <is>
-          <t>Und</t>
+          <t>BOLSA DE REGALO  SLT2023</t>
         </is>
       </c>
       <c r="J558" t="n">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="K558" t="n">
         <v>0</v>
@@ -25590,34 +25580,44 @@
         <v>0</v>
       </c>
       <c r="M558" t="n">
-        <v>33</v>
+        <v>146</v>
       </c>
       <c r="N558" t="n">
-        <v>1950.7</v>
+        <v>480</v>
       </c>
       <c r="O558" t="n">
-        <v>64373.1</v>
+        <v>70080</v>
       </c>
       <c r="P558" t="n">
-        <v>7500</v>
+        <v>600</v>
       </c>
       <c r="Q558" t="n">
-        <v>247500</v>
+        <v>87600</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>SLBT04</t>
+          <t>SLT014</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>BOLSA DE REGALO  SLT2023</t>
+          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>PIÑATERIA</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Und</t>
         </is>
       </c>
       <c r="J559" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="K559" t="n">
         <v>0</v>
@@ -25626,30 +25626,30 @@
         <v>0</v>
       </c>
       <c r="M559" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="N559" t="n">
-        <v>480</v>
+        <v>12000</v>
       </c>
       <c r="O559" t="n">
-        <v>70080</v>
+        <v>864000</v>
       </c>
       <c r="P559" t="n">
-        <v>600</v>
+        <v>15000</v>
       </c>
       <c r="Q559" t="n">
-        <v>87600</v>
+        <v>1080000</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>SLT014</t>
+          <t>SLT035</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>BALON FUTBOL #5 SLT2061/2062/2063</t>
+          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -25663,7 +25663,7 @@
         </is>
       </c>
       <c r="J560" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="K560" t="n">
         <v>0</v>
@@ -25672,30 +25672,30 @@
         <v>0</v>
       </c>
       <c r="M560" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="N560" t="n">
-        <v>12000</v>
+        <v>6917.54</v>
       </c>
       <c r="O560" t="n">
-        <v>864000</v>
+        <v>380464.7</v>
       </c>
       <c r="P560" t="n">
-        <v>15000</v>
+        <v>11500</v>
       </c>
       <c r="Q560" t="n">
-        <v>1080000</v>
+        <v>632500</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>SLT035</t>
+          <t>SLT05</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>JUGUETE SET ANIMALES DE GRANJA X 6  BOLSA  NC716-4</t>
+          <t>ESPADA DOBLE SLT2074</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
@@ -25709,7 +25709,7 @@
         </is>
       </c>
       <c r="J561" t="n">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="K561" t="n">
         <v>0</v>
@@ -25718,35 +25718,35 @@
         <v>0</v>
       </c>
       <c r="M561" t="n">
-        <v>55</v>
+        <v>238</v>
       </c>
       <c r="N561" t="n">
-        <v>6917.54</v>
+        <v>4720</v>
       </c>
       <c r="O561" t="n">
-        <v>380464.7</v>
+        <v>1123360</v>
       </c>
       <c r="P561" t="n">
-        <v>11500</v>
+        <v>5900</v>
       </c>
       <c r="Q561" t="n">
-        <v>632500</v>
+        <v>1404200</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>SLT05</t>
+          <t>SLT2640</t>
         </is>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>ESPADA DOBLE SLT2074</t>
+          <t>BALON BASQUEBOL # 3 SLT2640</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>PIÑATERIA</t>
+          <t>JUGUETERIA</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -25755,7 +25755,7 @@
         </is>
       </c>
       <c r="J562" t="n">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="K562" t="n">
         <v>0</v>
@@ -25764,30 +25764,30 @@
         <v>0</v>
       </c>
       <c r="M562" t="n">
-        <v>238</v>
+        <v>21</v>
       </c>
       <c r="N562" t="n">
-        <v>4720</v>
+        <v>1059.1847727273</v>
       </c>
       <c r="O562" t="n">
-        <v>1123360</v>
+        <v>22242.8802272733</v>
       </c>
       <c r="P562" t="n">
-        <v>5900</v>
+        <v>9500</v>
       </c>
       <c r="Q562" t="n">
-        <v>1404200</v>
+        <v>199500</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>SLT2640</t>
+          <t>SLT2642</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>BALON BASQUEBOL # 3 SLT2640</t>
+          <t>BALON BASQUEBOL # 7 ST2642</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -25801,7 +25801,7 @@
         </is>
       </c>
       <c r="J563" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="K563" t="n">
         <v>0</v>
@@ -25810,64 +25810,18 @@
         <v>0</v>
       </c>
       <c r="M563" t="n">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="N563" t="n">
-        <v>1059.1847727273</v>
+        <v>341.02143442623</v>
       </c>
       <c r="O563" t="n">
-        <v>22242.8802272733</v>
+        <v>18074.13602459019</v>
       </c>
       <c r="P563" t="n">
-        <v>9500</v>
+        <v>14500</v>
       </c>
       <c r="Q563" t="n">
-        <v>199500</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>SLT2642</t>
-        </is>
-      </c>
-      <c r="C564" t="inlineStr">
-        <is>
-          <t>BALON BASQUEBOL # 7 ST2642</t>
-        </is>
-      </c>
-      <c r="E564" t="inlineStr">
-        <is>
-          <t>JUGUETERIA</t>
-        </is>
-      </c>
-      <c r="I564" t="inlineStr">
-        <is>
-          <t>Und</t>
-        </is>
-      </c>
-      <c r="J564" t="n">
-        <v>53</v>
-      </c>
-      <c r="K564" t="n">
-        <v>0</v>
-      </c>
-      <c r="L564" t="n">
-        <v>0</v>
-      </c>
-      <c r="M564" t="n">
-        <v>53</v>
-      </c>
-      <c r="N564" t="n">
-        <v>341.02143442623</v>
-      </c>
-      <c r="O564" t="n">
-        <v>18074.13602459019</v>
-      </c>
-      <c r="P564" t="n">
-        <v>14500</v>
-      </c>
-      <c r="Q564" t="n">
         <v>768500</v>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1669,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>15711.965869565</v>
+        <v>15711.965851528</v>
       </c>
       <c r="O32" t="n">
-        <v>282815.38565217</v>
+        <v>282815.385327504</v>
       </c>
       <c r="P32" t="n">
         <v>28500</v>
@@ -5414,10 +5414,10 @@
         <v>120</v>
       </c>
       <c r="N118" t="n">
-        <v>3240.850037594</v>
+        <v>3240.8500375235</v>
       </c>
       <c r="O118" t="n">
-        <v>388902.00451128</v>
+        <v>388902.00450282</v>
       </c>
       <c r="P118" t="n">
         <v>5200</v>
@@ -23283,10 +23283,10 @@
         <v>11</v>
       </c>
       <c r="N508" t="n">
-        <v>22951.704792746</v>
+        <v>22951.704785992</v>
       </c>
       <c r="O508" t="n">
-        <v>252468.752720206</v>
+        <v>252468.752645912</v>
       </c>
       <c r="P508" t="n">
         <v>37900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-01</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.746460274</v>
+        <v>3376.7464583333</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.975276728</v>
+        <v>1931498.974166648</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1112,10 +1112,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.96041958</v>
+        <v>12357.960422535</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.57510488</v>
+        <v>444886.57521126</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -1193,10 +1193,10 @@
         <v>36</v>
       </c>
       <c r="N20" t="n">
-        <v>11491.097142857</v>
+        <v>11491.097222222</v>
       </c>
       <c r="O20" t="n">
-        <v>413679.497142852</v>
+        <v>413679.499999992</v>
       </c>
       <c r="P20" t="n">
         <v>23000</v>
@@ -1271,10 +1271,10 @@
         <v>103</v>
       </c>
       <c r="N22" t="n">
-        <v>2474.7040753425</v>
+        <v>2474.7040344828</v>
       </c>
       <c r="O22" t="n">
-        <v>254894.5197602775</v>
+        <v>254894.5155517284</v>
       </c>
       <c r="P22" t="n">
         <v>4500</v>
@@ -1310,10 +1310,10 @@
         <v>55</v>
       </c>
       <c r="N23" t="n">
-        <v>12793.68008658</v>
+        <v>12793.680086957</v>
       </c>
       <c r="O23" t="n">
-        <v>703652.4047619</v>
+        <v>703652.4047826349</v>
       </c>
       <c r="P23" t="n">
         <v>24000</v>
@@ -1349,10 +1349,10 @@
         <v>48</v>
       </c>
       <c r="N24" t="n">
-        <v>3716.3301957586</v>
+        <v>3716.3301963993</v>
       </c>
       <c r="O24" t="n">
-        <v>178383.8493964128</v>
+        <v>178383.8494271664</v>
       </c>
       <c r="P24" t="n">
         <v>9500</v>
@@ -1627,10 +1627,10 @@
         <v>99</v>
       </c>
       <c r="N31" t="n">
-        <v>3910.628089172</v>
+        <v>3910.6280686695</v>
       </c>
       <c r="O31" t="n">
-        <v>387152.180828028</v>
+        <v>387152.1787982805</v>
       </c>
       <c r="P31" t="n">
         <v>9100</v>
@@ -1669,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>15711.965851528</v>
+        <v>15711.965814978</v>
       </c>
       <c r="O32" t="n">
-        <v>282815.385327504</v>
+        <v>282815.384669604</v>
       </c>
       <c r="P32" t="n">
         <v>28500</v>
@@ -2617,10 +2617,10 @@
         <v>178</v>
       </c>
       <c r="N55" t="n">
-        <v>3340.6800824742</v>
+        <v>3340.6800833333</v>
       </c>
       <c r="O55" t="n">
-        <v>594641.0546804076</v>
+        <v>594641.0548333274</v>
       </c>
       <c r="P55" t="n">
         <v>7100</v>
@@ -3008,10 +3008,10 @@
         <v>434</v>
       </c>
       <c r="N64" t="n">
-        <v>4937.3101636905</v>
+        <v>4937.3101649175</v>
       </c>
       <c r="O64" t="n">
-        <v>2142792.611041677</v>
+        <v>2142792.611574195</v>
       </c>
       <c r="P64" t="n">
         <v>7500</v>
@@ -3362,10 +3362,10 @@
         <v>120</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0605968058</v>
+        <v>1098.0608598184</v>
       </c>
       <c r="O72" t="n">
-        <v>131767.271616696</v>
+        <v>131767.303178208</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -4787,10 +4787,10 @@
         <v>219</v>
       </c>
       <c r="N104" t="n">
-        <v>3795.7100075657</v>
+        <v>3795.7100075672</v>
       </c>
       <c r="O104" t="n">
-        <v>831260.4916568883</v>
+        <v>831260.4916572168</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -5947,10 +5947,10 @@
         <v>1116</v>
       </c>
       <c r="N130" t="n">
-        <v>4372.2107910895</v>
+        <v>4372.2107914851</v>
       </c>
       <c r="O130" t="n">
-        <v>4879387.242855882</v>
+        <v>4879387.243297372</v>
       </c>
       <c r="P130" t="n">
         <v>7500</v>
@@ -7399,10 +7399,10 @@
         <v>191</v>
       </c>
       <c r="N162" t="n">
-        <v>1630.9237512195</v>
+        <v>1630.9238354115</v>
       </c>
       <c r="O162" t="n">
-        <v>311506.4364829245</v>
+        <v>311506.4525635965</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.193804203</v>
+        <v>1550.1938475894</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.976951308</v>
+        <v>55806.9785132184</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -7491,10 +7491,10 @@
         <v>48</v>
       </c>
       <c r="N164" t="n">
-        <v>1579.3895639535</v>
+        <v>1579.3893154762</v>
       </c>
       <c r="O164" t="n">
-        <v>75810.699069768</v>
+        <v>75810.6871428576</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -8381,10 +8381,10 @@
         <v>674</v>
       </c>
       <c r="N184" t="n">
-        <v>4196.8725298197</v>
+        <v>4196.8725305216</v>
       </c>
       <c r="O184" t="n">
-        <v>2828692.085098478</v>
+        <v>2828692.085571559</v>
       </c>
       <c r="P184" t="n">
         <v>5900</v>
@@ -8832,10 +8832,10 @@
         <v>348</v>
       </c>
       <c r="N195" t="n">
-        <v>2029.8739473684</v>
+        <v>2029.8739515279</v>
       </c>
       <c r="O195" t="n">
-        <v>706396.1336842031</v>
+        <v>706396.1351317093</v>
       </c>
       <c r="P195" t="n">
         <v>3600</v>
@@ -8873,10 +8873,10 @@
         <v>157</v>
       </c>
       <c r="N196" t="n">
-        <v>22485.695571956</v>
+        <v>22485.695561036</v>
       </c>
       <c r="O196" t="n">
-        <v>3530254.204797092</v>
+        <v>3530254.203082652</v>
       </c>
       <c r="P196" t="n">
         <v>36500</v>
@@ -10233,10 +10233,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7969.9501671733</v>
+        <v>7969.9501675552</v>
       </c>
       <c r="O228" t="n">
-        <v>1434591.030091194</v>
+        <v>1434591.030159936</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -10505,10 +10505,10 @@
         <v>154</v>
       </c>
       <c r="N234" t="n">
-        <v>548.14718568665</v>
+        <v>548.1471609756099</v>
       </c>
       <c r="O234" t="n">
-        <v>84414.6665957441</v>
+        <v>84414.66279024394</v>
       </c>
       <c r="P234" t="n">
         <v>2000</v>
@@ -14783,10 +14783,10 @@
         <v>84</v>
       </c>
       <c r="N327" t="n">
-        <v>3903.7367356322</v>
+        <v>3903.736877898</v>
       </c>
       <c r="O327" t="n">
-        <v>327913.8857931048</v>
+        <v>327913.897743432</v>
       </c>
       <c r="P327" t="n">
         <v>7500</v>
@@ -15928,10 +15928,10 @@
         <v>60</v>
       </c>
       <c r="N352" t="n">
-        <v>4268.70745</v>
+        <v>4268.7078061224</v>
       </c>
       <c r="O352" t="n">
-        <v>256122.447</v>
+        <v>256122.468367344</v>
       </c>
       <c r="P352" t="n">
         <v>6900</v>
@@ -16388,10 +16388,10 @@
         <v>839</v>
       </c>
       <c r="N362" t="n">
-        <v>1516.0387920714</v>
+        <v>1516.0387919529</v>
       </c>
       <c r="O362" t="n">
-        <v>1271956.546547905</v>
+        <v>1271956.546448483</v>
       </c>
       <c r="P362" t="n">
         <v>2300</v>
@@ -17328,10 +17328,10 @@
         <v>780</v>
       </c>
       <c r="N382" t="n">
-        <v>1530.4499195171</v>
+        <v>1530.4499191266</v>
       </c>
       <c r="O382" t="n">
-        <v>1193750.937223338</v>
+        <v>1193750.936918748</v>
       </c>
       <c r="P382" t="n">
         <v>2600</v>
@@ -17748,10 +17748,10 @@
         <v>178</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700091701</v>
+        <v>1690.8700091743</v>
       </c>
       <c r="O391" t="n">
-        <v>300974.8616322778</v>
+        <v>300974.8616330254</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -18777,10 +18777,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8406407201</v>
+        <v>3110.8404252438</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6812814402</v>
+        <v>6221.6808504876</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18811,7 +18811,7 @@
         </is>
       </c>
       <c r="J414" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="K414" t="n">
         <v>0</v>
@@ -18820,19 +18820,19 @@
         <v>0</v>
       </c>
       <c r="M414" t="n">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="N414" t="n">
         <v>6300.61</v>
       </c>
       <c r="O414" t="n">
-        <v>554453.6799999999</v>
+        <v>428441.48</v>
       </c>
       <c r="P414" t="n">
         <v>8900</v>
       </c>
       <c r="Q414" t="n">
-        <v>783200</v>
+        <v>605200</v>
       </c>
     </row>
     <row r="415">
@@ -19577,10 +19577,10 @@
         <v>21</v>
       </c>
       <c r="N430" t="n">
-        <v>712.62853403141</v>
+        <v>712.62845303867</v>
       </c>
       <c r="O430" t="n">
-        <v>14965.19921465961</v>
+        <v>14965.19751381207</v>
       </c>
       <c r="P430" t="n">
         <v>700</v>
@@ -19711,10 +19711,10 @@
         <v>381</v>
       </c>
       <c r="N433" t="n">
-        <v>1595.5118087506</v>
+        <v>1595.5116515014</v>
       </c>
       <c r="O433" t="n">
-        <v>607889.9991339786</v>
+        <v>607889.9392220334</v>
       </c>
       <c r="P433" t="n">
         <v>2500</v>
@@ -21697,10 +21697,10 @@
         <v>152</v>
       </c>
       <c r="N474" t="n">
-        <v>7046.939827883</v>
+        <v>7046.9398275862</v>
       </c>
       <c r="O474" t="n">
-        <v>1071134.853838216</v>
+        <v>1071134.853793103</v>
       </c>
       <c r="P474" t="n">
         <v>9900</v>
@@ -22423,10 +22423,10 @@
         <v>1216</v>
       </c>
       <c r="N489" t="n">
-        <v>665.32360867559</v>
+        <v>665.32361367837</v>
       </c>
       <c r="O489" t="n">
-        <v>809033.5081495175</v>
+        <v>809033.5142328979</v>
       </c>
       <c r="P489" t="n">
         <v>2900</v>
@@ -22980,10 +22980,10 @@
         <v>132</v>
       </c>
       <c r="N501" t="n">
-        <v>1008.8166794626</v>
+        <v>1008.8165242718</v>
       </c>
       <c r="O501" t="n">
-        <v>133163.8016890632</v>
+        <v>133163.7812038776</v>
       </c>
       <c r="P501" t="n">
         <v>1500</v>
@@ -25138,10 +25138,10 @@
         <v>3</v>
       </c>
       <c r="N548" t="n">
-        <v>2432.1352873563</v>
+        <v>2432.1354117647</v>
       </c>
       <c r="O548" t="n">
-        <v>7296.4058620689</v>
+        <v>7296.4062352941</v>
       </c>
       <c r="P548" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1669,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>15711.965814978</v>
+        <v>15711.96579646</v>
       </c>
       <c r="O32" t="n">
-        <v>282815.384669604</v>
+        <v>282815.38433628</v>
       </c>
       <c r="P32" t="n">
         <v>28500</v>
@@ -18777,10 +18777,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8404252438</v>
+        <v>3110.840414859</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6808504876</v>
+        <v>6221.680829718</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -19711,10 +19711,10 @@
         <v>381</v>
       </c>
       <c r="N433" t="n">
-        <v>1595.5116515014</v>
+        <v>1595.5116012774</v>
       </c>
       <c r="O433" t="n">
-        <v>607889.9392220334</v>
+        <v>607889.9200866894</v>
       </c>
       <c r="P433" t="n">
         <v>2500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-02</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464583333</v>
+        <v>3376.7464524986</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.974166648</v>
+        <v>1931498.970829199</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1268,19 +1268,19 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>103</v>
+        <v>67</v>
       </c>
       <c r="N22" t="n">
-        <v>2474.7040344828</v>
+        <v>2474.7040138408</v>
       </c>
       <c r="O22" t="n">
-        <v>254894.5155517284</v>
+        <v>165805.1689273336</v>
       </c>
       <c r="P22" t="n">
         <v>4500</v>
       </c>
       <c r="Q22" t="n">
-        <v>463500</v>
+        <v>301500</v>
       </c>
     </row>
     <row r="23">
@@ -1627,10 +1627,10 @@
         <v>99</v>
       </c>
       <c r="N31" t="n">
-        <v>3910.6280686695</v>
+        <v>3910.6280519481</v>
       </c>
       <c r="O31" t="n">
-        <v>387152.1787982805</v>
+        <v>387152.1771428619</v>
       </c>
       <c r="P31" t="n">
         <v>9100</v>
@@ -1669,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>15711.96579646</v>
+        <v>15711.965777778</v>
       </c>
       <c r="O32" t="n">
-        <v>282815.38433628</v>
+        <v>282815.384000004</v>
       </c>
       <c r="P32" t="n">
         <v>28500</v>
@@ -2617,10 +2617,10 @@
         <v>178</v>
       </c>
       <c r="N55" t="n">
-        <v>3340.6800833333</v>
+        <v>3340.6800835073</v>
       </c>
       <c r="O55" t="n">
-        <v>594641.0548333274</v>
+        <v>594641.0548642994</v>
       </c>
       <c r="P55" t="n">
         <v>7100</v>
@@ -2921,10 +2921,10 @@
         <v>148</v>
       </c>
       <c r="N62" t="n">
-        <v>1950.2145987654</v>
+        <v>1950.214568029</v>
       </c>
       <c r="O62" t="n">
-        <v>288631.7606172792</v>
+        <v>288631.756068292</v>
       </c>
       <c r="P62" t="n">
         <v>2900</v>
@@ -3350,7 +3350,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3359,19 +3359,19 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0608598184</v>
+        <v>1098.0616971665</v>
       </c>
       <c r="O72" t="n">
-        <v>131767.303178208</v>
+        <v>129571.280265647</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
       </c>
       <c r="Q72" t="n">
-        <v>180000</v>
+        <v>177000</v>
       </c>
     </row>
     <row r="73">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4610,19 +4610,19 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>529</v>
+        <v>499</v>
       </c>
       <c r="N100" t="n">
         <v>5002</v>
       </c>
       <c r="O100" t="n">
-        <v>2646058</v>
+        <v>2495998</v>
       </c>
       <c r="P100" t="n">
         <v>8400</v>
       </c>
       <c r="Q100" t="n">
-        <v>4443600</v>
+        <v>4191600</v>
       </c>
     </row>
     <row r="101">
@@ -4787,10 +4787,10 @@
         <v>219</v>
       </c>
       <c r="N104" t="n">
-        <v>3795.7100075672</v>
+        <v>3795.7100075815</v>
       </c>
       <c r="O104" t="n">
-        <v>831260.4916572168</v>
+        <v>831260.4916603485</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -5499,10 +5499,10 @@
         <v>135</v>
       </c>
       <c r="N120" t="n">
-        <v>5191.4800280899</v>
+        <v>5191.4800283688</v>
       </c>
       <c r="O120" t="n">
-        <v>700849.8037921365</v>
+        <v>700849.803829788</v>
       </c>
       <c r="P120" t="n">
         <v>9100</v>
@@ -5682,10 +5682,10 @@
         <v>14</v>
       </c>
       <c r="N124" t="n">
-        <v>12267.648552632</v>
+        <v>12267.6484</v>
       </c>
       <c r="O124" t="n">
-        <v>171747.079736848</v>
+        <v>171747.0776</v>
       </c>
       <c r="P124" t="n">
         <v>19900</v>
@@ -5860,10 +5860,10 @@
         <v>501</v>
       </c>
       <c r="N128" t="n">
-        <v>3041.6600135135</v>
+        <v>3041.660013541</v>
       </c>
       <c r="O128" t="n">
-        <v>1523871.666770264</v>
+        <v>1523871.666784041</v>
       </c>
       <c r="P128" t="n">
         <v>5500</v>
@@ -5947,10 +5947,10 @@
         <v>1116</v>
       </c>
       <c r="N130" t="n">
-        <v>4372.2107914851</v>
+        <v>4372.2107916548</v>
       </c>
       <c r="O130" t="n">
-        <v>4879387.243297372</v>
+        <v>4879387.243486757</v>
       </c>
       <c r="P130" t="n">
         <v>7500</v>
@@ -7399,10 +7399,10 @@
         <v>191</v>
       </c>
       <c r="N162" t="n">
-        <v>1630.9238354115</v>
+        <v>1630.9238750315</v>
       </c>
       <c r="O162" t="n">
-        <v>311506.4525635965</v>
+        <v>311506.4601310165</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1938475894</v>
+        <v>1550.1938919769</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9785132184</v>
+        <v>55806.9801111684</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -7491,10 +7491,10 @@
         <v>48</v>
       </c>
       <c r="N164" t="n">
-        <v>1579.3893154762</v>
+        <v>1579.3891212121</v>
       </c>
       <c r="O164" t="n">
-        <v>75810.6871428576</v>
+        <v>75810.6778181808</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -8381,10 +8381,10 @@
         <v>674</v>
       </c>
       <c r="N184" t="n">
-        <v>4196.8725305216</v>
+        <v>4196.872531224</v>
       </c>
       <c r="O184" t="n">
-        <v>2828692.085571559</v>
+        <v>2828692.086044976</v>
       </c>
       <c r="P184" t="n">
         <v>5900</v>
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="J210" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9472,19 +9472,19 @@
         <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="N210" t="n">
         <v>2178.64</v>
       </c>
       <c r="O210" t="n">
-        <v>357296.96</v>
+        <v>305009.6</v>
       </c>
       <c r="P210" t="n">
         <v>3600</v>
       </c>
       <c r="Q210" t="n">
-        <v>590400</v>
+        <v>504000</v>
       </c>
     </row>
     <row r="211">
@@ -9808,10 +9808,10 @@
         <v>37</v>
       </c>
       <c r="N218" t="n">
-        <v>27123.765196998</v>
+        <v>27123.76518797</v>
       </c>
       <c r="O218" t="n">
-        <v>1003579.312288926</v>
+        <v>1003579.31195489</v>
       </c>
       <c r="P218" t="n">
         <v>44500</v>
@@ -11510,10 +11510,10 @@
         <v>3</v>
       </c>
       <c r="N256" t="n">
-        <v>23521.624067797</v>
+        <v>23521.623965517</v>
       </c>
       <c r="O256" t="n">
-        <v>70564.872203391</v>
+        <v>70564.87189655099</v>
       </c>
       <c r="P256" t="n">
         <v>39000</v>
@@ -11638,10 +11638,10 @@
         <v>1111</v>
       </c>
       <c r="N259" t="n">
-        <v>1778.4726494689</v>
+        <v>1778.4726526892</v>
       </c>
       <c r="O259" t="n">
-        <v>1975883.113559948</v>
+        <v>1975883.117137701</v>
       </c>
       <c r="P259" t="n">
         <v>4900</v>
@@ -13952,10 +13952,10 @@
         <v>263</v>
       </c>
       <c r="N309" t="n">
-        <v>2252.2973618785</v>
+        <v>2252.2974859551</v>
       </c>
       <c r="O309" t="n">
-        <v>592354.2061740455</v>
+        <v>592354.2388061912</v>
       </c>
       <c r="P309" t="n">
         <v>3900</v>
@@ -14139,10 +14139,10 @@
         <v>504</v>
       </c>
       <c r="N313" t="n">
-        <v>2328.1186979327</v>
+        <v>2328.1186975309</v>
       </c>
       <c r="O313" t="n">
-        <v>1173371.823758081</v>
+        <v>1173371.823555574</v>
       </c>
       <c r="P313" t="n">
         <v>4500</v>
@@ -14553,10 +14553,10 @@
         <v>164</v>
       </c>
       <c r="N322" t="n">
-        <v>4907.8221561969</v>
+        <v>4907.8221972318</v>
       </c>
       <c r="O322" t="n">
-        <v>804882.8336162916</v>
+        <v>804882.8403460152</v>
       </c>
       <c r="P322" t="n">
         <v>8200</v>
@@ -14783,10 +14783,10 @@
         <v>84</v>
       </c>
       <c r="N327" t="n">
-        <v>3903.736877898</v>
+        <v>3903.7369302326</v>
       </c>
       <c r="O327" t="n">
-        <v>327913.897743432</v>
+        <v>327913.9021395384</v>
       </c>
       <c r="P327" t="n">
         <v>7500</v>
@@ -16388,10 +16388,10 @@
         <v>839</v>
       </c>
       <c r="N362" t="n">
-        <v>1516.0387919529</v>
+        <v>1516.0387905286</v>
       </c>
       <c r="O362" t="n">
-        <v>1271956.546448483</v>
+        <v>1271956.545253495</v>
       </c>
       <c r="P362" t="n">
         <v>2300</v>
@@ -16795,10 +16795,10 @@
         <v>2243</v>
       </c>
       <c r="N371" t="n">
-        <v>692.15225097656</v>
+        <v>692.1522598039199</v>
       </c>
       <c r="O371" t="n">
-        <v>1552497.498940424</v>
+        <v>1552497.518740193</v>
       </c>
       <c r="P371" t="n">
         <v>1200</v>
@@ -17748,10 +17748,10 @@
         <v>178</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700091743</v>
+        <v>1690.8700092251</v>
       </c>
       <c r="O391" t="n">
-        <v>300974.8616330254</v>
+        <v>300974.8616420678</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -17895,10 +17895,10 @@
         <v>47</v>
       </c>
       <c r="N394" t="n">
-        <v>2270.3212345679</v>
+        <v>2270.3212658228</v>
       </c>
       <c r="O394" t="n">
-        <v>106705.0980246913</v>
+        <v>106705.0994936716</v>
       </c>
       <c r="P394" t="n">
         <v>3900</v>
@@ -18641,10 +18641,10 @@
         <v>132</v>
       </c>
       <c r="N410" t="n">
-        <v>3259.1343529412</v>
+        <v>3259.1343700787</v>
       </c>
       <c r="O410" t="n">
-        <v>430205.7345882384</v>
+        <v>430205.7368503884</v>
       </c>
       <c r="P410" t="n">
         <v>3600</v>
@@ -18777,10 +18777,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.840414859</v>
+        <v>3110.8403177212</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.680829718</v>
+        <v>6221.6806354424</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -19650,7 +19650,7 @@
         </is>
       </c>
       <c r="J432" t="n">
-        <v>875</v>
+        <v>823</v>
       </c>
       <c r="K432" t="n">
         <v>0</v>
@@ -19659,19 +19659,19 @@
         <v>0</v>
       </c>
       <c r="M432" t="n">
-        <v>875</v>
+        <v>823</v>
       </c>
       <c r="N432" t="n">
         <v>1755.74</v>
       </c>
       <c r="O432" t="n">
-        <v>1536272.5</v>
+        <v>1444974.02</v>
       </c>
       <c r="P432" t="n">
         <v>1500</v>
       </c>
       <c r="Q432" t="n">
-        <v>1312500</v>
+        <v>1234500</v>
       </c>
     </row>
     <row r="433">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="J489" t="n">
-        <v>1216</v>
+        <v>1061</v>
       </c>
       <c r="K489" t="n">
         <v>0</v>
@@ -22420,19 +22420,19 @@
         <v>0</v>
       </c>
       <c r="M489" t="n">
-        <v>1216</v>
+        <v>1061</v>
       </c>
       <c r="N489" t="n">
-        <v>665.32361367837</v>
+        <v>665.32370265152</v>
       </c>
       <c r="O489" t="n">
-        <v>809033.5142328979</v>
+        <v>705908.4485132627</v>
       </c>
       <c r="P489" t="n">
         <v>2900</v>
       </c>
       <c r="Q489" t="n">
-        <v>3526400</v>
+        <v>3076900</v>
       </c>
     </row>
     <row r="490">
@@ -22980,10 +22980,10 @@
         <v>132</v>
       </c>
       <c r="N501" t="n">
-        <v>1008.8165242718</v>
+        <v>1008.8156907216</v>
       </c>
       <c r="O501" t="n">
-        <v>133163.7812038776</v>
+        <v>133163.6711752512</v>
       </c>
       <c r="P501" t="n">
         <v>1500</v>
@@ -25138,10 +25138,10 @@
         <v>3</v>
       </c>
       <c r="N548" t="n">
-        <v>2432.1354117647</v>
+        <v>2432.1354761905</v>
       </c>
       <c r="O548" t="n">
-        <v>7296.4062352941</v>
+        <v>7296.406428571499</v>
       </c>
       <c r="P548" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1938919769</v>
+        <v>1550.1938936103</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9801111684</v>
+        <v>55806.9801699708</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-03</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464524986</v>
+        <v>3376.7464515243</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.970829199</v>
+        <v>1931498.9702719</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -953,10 +953,10 @@
         <v>58</v>
       </c>
       <c r="N14" t="n">
-        <v>1854.2405454545</v>
+        <v>1854.2405936073</v>
       </c>
       <c r="O14" t="n">
-        <v>107545.951636361</v>
+        <v>107545.9544292234</v>
       </c>
       <c r="P14" t="n">
         <v>3200</v>
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8549315068</v>
+        <v>6272.8549740933</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.510410945</v>
+        <v>1794036.522590684</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -1151,10 +1151,10 @@
         <v>440</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8370954357</v>
+        <v>3926.8370909091</v>
       </c>
       <c r="O19" t="n">
-        <v>1727808.321991708</v>
+        <v>1727808.320000004</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1505,10 +1505,10 @@
         <v>62</v>
       </c>
       <c r="N28" t="n">
-        <v>14857.623257919</v>
+        <v>14857.623272727</v>
       </c>
       <c r="O28" t="n">
-        <v>921172.641990978</v>
+        <v>921172.642909074</v>
       </c>
       <c r="P28" t="n">
         <v>34900</v>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1624,19 +1624,19 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="N31" t="n">
-        <v>3910.6280519481</v>
+        <v>3910.6280349345</v>
       </c>
       <c r="O31" t="n">
-        <v>387152.1771428619</v>
+        <v>348045.8951091705</v>
       </c>
       <c r="P31" t="n">
         <v>9100</v>
       </c>
       <c r="Q31" t="n">
-        <v>900900</v>
+        <v>809900</v>
       </c>
     </row>
     <row r="32">
@@ -1669,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>15711.965777778</v>
+        <v>15711.96573991</v>
       </c>
       <c r="O32" t="n">
-        <v>282815.384000004</v>
+        <v>282815.38331838</v>
       </c>
       <c r="P32" t="n">
         <v>28500</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
@@ -2327,19 +2327,19 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="N48" t="n">
         <v>5686.27</v>
       </c>
       <c r="O48" t="n">
-        <v>170588.1</v>
+        <v>102352.86</v>
       </c>
       <c r="P48" t="n">
         <v>11500</v>
       </c>
       <c r="Q48" t="n">
-        <v>345000</v>
+        <v>207000</v>
       </c>
     </row>
     <row r="49">
@@ -2488,7 +2488,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -2497,19 +2497,19 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="N52" t="n">
         <v>2791.02</v>
       </c>
       <c r="O52" t="n">
-        <v>329340.36</v>
+        <v>295848.12</v>
       </c>
       <c r="P52" t="n">
         <v>3900</v>
       </c>
       <c r="Q52" t="n">
-        <v>460200</v>
+        <v>413400</v>
       </c>
     </row>
     <row r="53">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2536,19 +2536,19 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="N53" t="n">
         <v>3564.14</v>
       </c>
       <c r="O53" t="n">
-        <v>716392.14</v>
+        <v>645109.34</v>
       </c>
       <c r="P53" t="n">
         <v>5500</v>
       </c>
       <c r="Q53" t="n">
-        <v>1105500</v>
+        <v>995500</v>
       </c>
     </row>
     <row r="54">
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -2575,19 +2575,19 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="N54" t="n">
         <v>4378</v>
       </c>
       <c r="O54" t="n">
-        <v>551628</v>
+        <v>516604</v>
       </c>
       <c r="P54" t="n">
         <v>3900</v>
       </c>
       <c r="Q54" t="n">
-        <v>491400</v>
+        <v>460200</v>
       </c>
     </row>
     <row r="55">
@@ -2617,10 +2617,10 @@
         <v>178</v>
       </c>
       <c r="N55" t="n">
-        <v>3340.6800835073</v>
+        <v>3340.680083682</v>
       </c>
       <c r="O55" t="n">
-        <v>594641.0548642994</v>
+        <v>594641.054895396</v>
       </c>
       <c r="P55" t="n">
         <v>7100</v>
@@ -2921,10 +2921,10 @@
         <v>148</v>
       </c>
       <c r="N62" t="n">
-        <v>1950.214568029</v>
+        <v>1950.2145482866</v>
       </c>
       <c r="O62" t="n">
-        <v>288631.756068292</v>
+        <v>288631.7531464168</v>
       </c>
       <c r="P62" t="n">
         <v>2900</v>
@@ -3362,10 +3362,10 @@
         <v>118</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0616971665</v>
+        <v>1098.0617613973</v>
       </c>
       <c r="O72" t="n">
-        <v>129571.280265647</v>
+        <v>129571.2878448814</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="K100" t="n">
         <v>0</v>
@@ -4610,19 +4610,19 @@
         <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="N100" t="n">
         <v>5002</v>
       </c>
       <c r="O100" t="n">
-        <v>2495998</v>
+        <v>2435974</v>
       </c>
       <c r="P100" t="n">
         <v>8400</v>
       </c>
       <c r="Q100" t="n">
-        <v>4191600</v>
+        <v>4090800</v>
       </c>
     </row>
     <row r="101">
@@ -4787,10 +4787,10 @@
         <v>219</v>
       </c>
       <c r="N104" t="n">
-        <v>3795.7100075815</v>
+        <v>3795.7100075887</v>
       </c>
       <c r="O104" t="n">
-        <v>831260.4916603485</v>
+        <v>831260.4916619253</v>
       </c>
       <c r="P104" t="n">
         <v>6200</v>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="J106" t="n">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4871,19 +4871,19 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>221</v>
+        <v>173</v>
       </c>
       <c r="N106" t="n">
         <v>2612.77</v>
       </c>
       <c r="O106" t="n">
-        <v>577422.17</v>
+        <v>452009.21</v>
       </c>
       <c r="P106" t="n">
         <v>4900</v>
       </c>
       <c r="Q106" t="n">
-        <v>1082900</v>
+        <v>847700</v>
       </c>
     </row>
     <row r="107">
@@ -4966,10 +4966,10 @@
         <v>459</v>
       </c>
       <c r="N108" t="n">
-        <v>4890.9300489596</v>
+        <v>4890.9300493218</v>
       </c>
       <c r="O108" t="n">
-        <v>2244936.892472456</v>
+        <v>2244936.892638706</v>
       </c>
       <c r="P108" t="n">
         <v>8200</v>
@@ -5947,10 +5947,10 @@
         <v>1116</v>
       </c>
       <c r="N130" t="n">
-        <v>4372.2107916548</v>
+        <v>4372.2107917679</v>
       </c>
       <c r="O130" t="n">
-        <v>4879387.243486757</v>
+        <v>4879387.243612977</v>
       </c>
       <c r="P130" t="n">
         <v>7500</v>
@@ -7399,10 +7399,10 @@
         <v>191</v>
       </c>
       <c r="N162" t="n">
-        <v>1630.9238750315</v>
+        <v>1630.9238760081</v>
       </c>
       <c r="O162" t="n">
-        <v>311506.4601310165</v>
+        <v>311506.4603175471</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1938936103</v>
+        <v>1550.1939063158</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9801699708</v>
+        <v>55806.9806273688</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -7491,10 +7491,10 @@
         <v>48</v>
       </c>
       <c r="N164" t="n">
-        <v>1579.3891212121</v>
+        <v>1579.3888161994</v>
       </c>
       <c r="O164" t="n">
-        <v>75810.6778181808</v>
+        <v>75810.6631775712</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -7787,7 +7787,7 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="K171" t="n">
         <v>0</v>
@@ -7796,19 +7796,19 @@
         <v>0</v>
       </c>
       <c r="M171" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="N171" t="n">
         <v>2973.29</v>
       </c>
       <c r="O171" t="n">
-        <v>214076.88</v>
+        <v>142717.92</v>
       </c>
       <c r="P171" t="n">
         <v>4900</v>
       </c>
       <c r="Q171" t="n">
-        <v>352800</v>
+        <v>235200</v>
       </c>
     </row>
     <row r="172">
@@ -8381,10 +8381,10 @@
         <v>674</v>
       </c>
       <c r="N184" t="n">
-        <v>4196.872531224</v>
+        <v>4196.8725319267</v>
       </c>
       <c r="O184" t="n">
-        <v>2828692.086044976</v>
+        <v>2828692.086518595</v>
       </c>
       <c r="P184" t="n">
         <v>5900</v>
@@ -8873,10 +8873,10 @@
         <v>157</v>
       </c>
       <c r="N196" t="n">
-        <v>22485.695561036</v>
+        <v>22485.695555556</v>
       </c>
       <c r="O196" t="n">
-        <v>3530254.203082652</v>
+        <v>3530254.202222292</v>
       </c>
       <c r="P196" t="n">
         <v>36500</v>
@@ -9037,10 +9037,10 @@
         <v>170</v>
       </c>
       <c r="N200" t="n">
-        <v>2680.7396948941</v>
+        <v>2680.739694704</v>
       </c>
       <c r="O200" t="n">
-        <v>455725.748131997</v>
+        <v>455725.74809968</v>
       </c>
       <c r="P200" t="n">
         <v>4900</v>
@@ -9668,7 +9668,7 @@
         </is>
       </c>
       <c r="J215" t="n">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="K215" t="n">
         <v>0</v>
@@ -9677,19 +9677,19 @@
         <v>0</v>
       </c>
       <c r="M215" t="n">
-        <v>993</v>
+        <v>973</v>
       </c>
       <c r="N215" t="n">
         <v>3591.13</v>
       </c>
       <c r="O215" t="n">
-        <v>3565992.09</v>
+        <v>3494169.49</v>
       </c>
       <c r="P215" t="n">
         <v>6300</v>
       </c>
       <c r="Q215" t="n">
-        <v>6255900</v>
+        <v>6129900</v>
       </c>
     </row>
     <row r="216">
@@ -9808,10 +9808,10 @@
         <v>37</v>
       </c>
       <c r="N218" t="n">
-        <v>27123.76518797</v>
+        <v>27123.765160681</v>
       </c>
       <c r="O218" t="n">
-        <v>1003579.31195489</v>
+        <v>1003579.310945197</v>
       </c>
       <c r="P218" t="n">
         <v>44500</v>
@@ -10505,10 +10505,10 @@
         <v>154</v>
       </c>
       <c r="N234" t="n">
-        <v>548.1471609756099</v>
+        <v>548.14714985309</v>
       </c>
       <c r="O234" t="n">
-        <v>84414.66279024394</v>
+        <v>84414.66107737586</v>
       </c>
       <c r="P234" t="n">
         <v>2000</v>
@@ -11638,10 +11638,10 @@
         <v>1111</v>
       </c>
       <c r="N259" t="n">
-        <v>1778.4726526892</v>
+        <v>1778.4726559172</v>
       </c>
       <c r="O259" t="n">
-        <v>1975883.117137701</v>
+        <v>1975883.120724009</v>
       </c>
       <c r="P259" t="n">
         <v>4900</v>
@@ -13664,7 +13664,7 @@
         </is>
       </c>
       <c r="J303" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -13673,19 +13673,19 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="N303" t="n">
         <v>8858.16</v>
       </c>
       <c r="O303" t="n">
-        <v>3188937.6</v>
+        <v>3082639.68</v>
       </c>
       <c r="P303" t="n">
         <v>15500</v>
       </c>
       <c r="Q303" t="n">
-        <v>5580000</v>
+        <v>5394000</v>
       </c>
     </row>
     <row r="304">
@@ -14553,10 +14553,10 @@
         <v>164</v>
       </c>
       <c r="N322" t="n">
-        <v>4907.8221972318</v>
+        <v>4907.8222048611</v>
       </c>
       <c r="O322" t="n">
-        <v>804882.8403460152</v>
+        <v>804882.8415972204</v>
       </c>
       <c r="P322" t="n">
         <v>8200</v>
@@ -14783,10 +14783,10 @@
         <v>84</v>
       </c>
       <c r="N327" t="n">
-        <v>3903.7369302326</v>
+        <v>3903.736969697</v>
       </c>
       <c r="O327" t="n">
-        <v>327913.9021395384</v>
+        <v>327913.905454548</v>
       </c>
       <c r="P327" t="n">
         <v>7500</v>
@@ -15686,7 +15686,7 @@
         </is>
       </c>
       <c r="J347" t="n">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="K347" t="n">
         <v>0</v>
@@ -15695,19 +15695,19 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="N347" t="n">
         <v>59834</v>
       </c>
       <c r="O347" t="n">
-        <v>12445472</v>
+        <v>10530784</v>
       </c>
       <c r="P347" t="n">
         <v>7900</v>
       </c>
       <c r="Q347" t="n">
-        <v>1643200</v>
+        <v>1390400</v>
       </c>
     </row>
     <row r="348">
@@ -15916,7 +15916,7 @@
         </is>
       </c>
       <c r="J352" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -15925,19 +15925,19 @@
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N352" t="n">
         <v>4268.7078061224</v>
       </c>
       <c r="O352" t="n">
-        <v>256122.468367344</v>
+        <v>204897.9746938752</v>
       </c>
       <c r="P352" t="n">
         <v>6900</v>
       </c>
       <c r="Q352" t="n">
-        <v>414000</v>
+        <v>331200</v>
       </c>
     </row>
     <row r="353">
@@ -16330,7 +16330,7 @@
         </is>
       </c>
       <c r="J361" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -16339,19 +16339,19 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="N361" t="n">
         <v>5476</v>
       </c>
       <c r="O361" t="n">
-        <v>306656</v>
+        <v>262848</v>
       </c>
       <c r="P361" t="n">
         <v>8900</v>
       </c>
       <c r="Q361" t="n">
-        <v>498400</v>
+        <v>427200</v>
       </c>
     </row>
     <row r="362">
@@ -16388,10 +16388,10 @@
         <v>839</v>
       </c>
       <c r="N362" t="n">
-        <v>1516.0387905286</v>
+        <v>1516.0387891009</v>
       </c>
       <c r="O362" t="n">
-        <v>1271956.545253495</v>
+        <v>1271956.544055655</v>
       </c>
       <c r="P362" t="n">
         <v>2300</v>
@@ -17748,10 +17748,10 @@
         <v>178</v>
       </c>
       <c r="N391" t="n">
-        <v>1690.8700092251</v>
+        <v>1690.8700092336</v>
       </c>
       <c r="O391" t="n">
-        <v>300974.8616420678</v>
+        <v>300974.8616435808</v>
       </c>
       <c r="P391" t="n">
         <v>3000</v>
@@ -17895,10 +17895,10 @@
         <v>47</v>
       </c>
       <c r="N394" t="n">
-        <v>2270.3212658228</v>
+        <v>2270.3212987013</v>
       </c>
       <c r="O394" t="n">
-        <v>106705.0994936716</v>
+        <v>106705.1010389611</v>
       </c>
       <c r="P394" t="n">
         <v>3900</v>
@@ -18300,7 +18300,7 @@
         </is>
       </c>
       <c r="J403" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="K403" t="n">
         <v>0</v>
@@ -18309,19 +18309,19 @@
         <v>0</v>
       </c>
       <c r="M403" t="n">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="N403" t="n">
         <v>1326</v>
       </c>
       <c r="O403" t="n">
-        <v>71604</v>
+        <v>45084</v>
       </c>
       <c r="P403" t="n">
         <v>2900</v>
       </c>
       <c r="Q403" t="n">
-        <v>156600</v>
+        <v>98600</v>
       </c>
     </row>
     <row r="404">
@@ -18777,10 +18777,10 @@
         <v>2</v>
       </c>
       <c r="N413" t="n">
-        <v>3110.8403177212</v>
+        <v>3110.8402590245</v>
       </c>
       <c r="O413" t="n">
-        <v>6221.6806354424</v>
+        <v>6221.680518049</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18967,10 +18967,10 @@
         <v>127</v>
       </c>
       <c r="N417" t="n">
-        <v>3182.2511173184</v>
+        <v>3182.251119403</v>
       </c>
       <c r="O417" t="n">
-        <v>404145.8918994368</v>
+        <v>404145.892164181</v>
       </c>
       <c r="P417" t="n">
         <v>6900</v>
@@ -19711,10 +19711,10 @@
         <v>381</v>
       </c>
       <c r="N433" t="n">
-        <v>1595.5116012774</v>
+        <v>1595.5115507777</v>
       </c>
       <c r="O433" t="n">
-        <v>607889.9200866894</v>
+        <v>607889.9008463037</v>
       </c>
       <c r="P433" t="n">
         <v>2500</v>
@@ -22328,10 +22328,10 @@
         <v>67</v>
       </c>
       <c r="N487" t="n">
-        <v>44113.603841808</v>
+        <v>44113.603953488</v>
       </c>
       <c r="O487" t="n">
-        <v>2955611.457401136</v>
+        <v>2955611.464883696</v>
       </c>
       <c r="P487" t="n">
         <v>71900</v>
@@ -22709,10 +22709,10 @@
         <v>41050</v>
       </c>
       <c r="N495" t="n">
-        <v>2703.2000014448</v>
+        <v>2703.2000014449</v>
       </c>
       <c r="O495" t="n">
-        <v>110966360.059309</v>
+        <v>110966360.0593131</v>
       </c>
       <c r="P495" t="n">
         <v>4500</v>
@@ -22878,7 +22878,7 @@
         </is>
       </c>
       <c r="J499" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="K499" t="n">
         <v>0</v>
@@ -22887,19 +22887,19 @@
         <v>0</v>
       </c>
       <c r="M499" t="n">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="N499" t="n">
         <v>6761.25</v>
       </c>
       <c r="O499" t="n">
-        <v>1947240</v>
+        <v>1866105</v>
       </c>
       <c r="P499" t="n">
         <v>5200</v>
       </c>
       <c r="Q499" t="n">
-        <v>1497600</v>
+        <v>1435200</v>
       </c>
     </row>
     <row r="500">
@@ -22968,7 +22968,7 @@
         </is>
       </c>
       <c r="J501" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="K501" t="n">
         <v>0</v>
@@ -22977,19 +22977,19 @@
         <v>0</v>
       </c>
       <c r="M501" t="n">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="N501" t="n">
-        <v>1008.8156907216</v>
+        <v>1008.8155114823</v>
       </c>
       <c r="O501" t="n">
-        <v>133163.6711752512</v>
+        <v>60528.930688938</v>
       </c>
       <c r="P501" t="n">
         <v>1500</v>
       </c>
       <c r="Q501" t="n">
-        <v>198000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="502">
@@ -23150,10 +23150,10 @@
         <v>-72</v>
       </c>
       <c r="N505" t="n">
-        <v>1794.287968053</v>
+        <v>1794.287966297</v>
       </c>
       <c r="O505" t="n">
-        <v>-129188.733699816</v>
+        <v>-129188.733573384</v>
       </c>
       <c r="P505" t="n">
         <v>1600</v>
@@ -25235,10 +25235,10 @@
         <v>271</v>
       </c>
       <c r="N550" t="n">
-        <v>227.41613363363</v>
+        <v>227.41613824192</v>
       </c>
       <c r="O550" t="n">
-        <v>61629.77221471373</v>
+        <v>61629.77346356032</v>
       </c>
       <c r="P550" t="n">
         <v>1200</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -4613,10 +4613,10 @@
         <v>487</v>
       </c>
       <c r="N100" t="n">
-        <v>5002</v>
+        <v>5013.3940774487</v>
       </c>
       <c r="O100" t="n">
-        <v>2435974</v>
+        <v>2441522.915717517</v>
       </c>
       <c r="P100" t="n">
         <v>8400</v>
@@ -4966,10 +4966,10 @@
         <v>459</v>
       </c>
       <c r="N108" t="n">
-        <v>4890.9300493218</v>
+        <v>4890.9300493827</v>
       </c>
       <c r="O108" t="n">
-        <v>2244936.892638706</v>
+        <v>2244936.892666659</v>
       </c>
       <c r="P108" t="n">
         <v>8200</v>
@@ -5458,10 +5458,10 @@
         <v>2706</v>
       </c>
       <c r="N119" t="n">
-        <v>2090.85</v>
+        <v>2092.643951094</v>
       </c>
       <c r="O119" t="n">
-        <v>5657840.1</v>
+        <v>5662694.531660364</v>
       </c>
       <c r="P119" t="n">
         <v>2900</v>
@@ -5947,10 +5947,10 @@
         <v>1116</v>
       </c>
       <c r="N130" t="n">
-        <v>4372.2107917679</v>
+        <v>4372.2107918811</v>
       </c>
       <c r="O130" t="n">
-        <v>4879387.243612977</v>
+        <v>4879387.243739307</v>
       </c>
       <c r="P130" t="n">
         <v>7500</v>
@@ -7399,10 +7399,10 @@
         <v>191</v>
       </c>
       <c r="N162" t="n">
-        <v>1630.9238760081</v>
+        <v>1630.9238867829</v>
       </c>
       <c r="O162" t="n">
-        <v>311506.4603175471</v>
+        <v>311506.4623755339</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1939063158</v>
+        <v>1550.1939133186</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9806273688</v>
+        <v>55806.9808794696</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -8791,10 +8791,10 @@
         <v>551</v>
       </c>
       <c r="N194" t="n">
-        <v>2517.22</v>
+        <v>2541.6788178138</v>
       </c>
       <c r="O194" t="n">
-        <v>1386988.22</v>
+        <v>1400465.028615404</v>
       </c>
       <c r="P194" t="n">
         <v>4200</v>
@@ -16388,10 +16388,10 @@
         <v>839</v>
       </c>
       <c r="N362" t="n">
-        <v>1516.0387891009</v>
+        <v>1517.8304441599</v>
       </c>
       <c r="O362" t="n">
-        <v>1271956.544055655</v>
+        <v>1273459.742650156</v>
       </c>
       <c r="P362" t="n">
         <v>2300</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -7399,10 +7399,10 @@
         <v>191</v>
       </c>
       <c r="N162" t="n">
-        <v>1630.9239095069</v>
+        <v>1630.9239154786</v>
       </c>
       <c r="O162" t="n">
-        <v>311506.4667158179</v>
+        <v>311506.4678564126</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -595,10 +595,10 @@
         <v>245</v>
       </c>
       <c r="N5" t="n">
-        <v>27035.809018568</v>
+        <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>6623773.209549161</v>
+        <v>6615000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -3629,10 +3629,10 @@
         <v>98</v>
       </c>
       <c r="N78" t="n">
-        <v>17234.854035088</v>
+        <v>17207.41</v>
       </c>
       <c r="O78" t="n">
-        <v>1689015.695438624</v>
+        <v>1686326.18</v>
       </c>
       <c r="P78" t="n">
         <v>20000</v>
@@ -5587,10 +5587,10 @@
         <v>650</v>
       </c>
       <c r="N122" t="n">
-        <v>2667.0463248919</v>
+        <v>2665.4</v>
       </c>
       <c r="O122" t="n">
-        <v>1733580.111179735</v>
+        <v>1732510</v>
       </c>
       <c r="P122" t="n">
         <v>20900</v>
@@ -5947,10 +5947,10 @@
         <v>1110</v>
       </c>
       <c r="N130" t="n">
-        <v>4372.5234503719</v>
+        <v>4372.2107923341</v>
       </c>
       <c r="O130" t="n">
-        <v>4853501.029912809</v>
+        <v>4853153.979490851</v>
       </c>
       <c r="P130" t="n">
         <v>7500</v>
@@ -6532,10 +6532,10 @@
         <v>2575</v>
       </c>
       <c r="N143" t="n">
-        <v>17473.953844316</v>
+        <v>17472.91</v>
       </c>
       <c r="O143" t="n">
-        <v>44995431.14911371</v>
+        <v>44992743.25</v>
       </c>
       <c r="P143" t="n">
         <v>2900</v>
@@ -6620,10 +6620,10 @@
         <v>2660</v>
       </c>
       <c r="N145" t="n">
-        <v>1530.7162764218</v>
+        <v>1530.63</v>
       </c>
       <c r="O145" t="n">
-        <v>4071705.295281988</v>
+        <v>4071475.8</v>
       </c>
       <c r="P145" t="n">
         <v>2900</v>
@@ -10233,10 +10233,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7982.1180305344</v>
+        <v>7969.9501679389</v>
       </c>
       <c r="O228" t="n">
-        <v>1436781.245496192</v>
+        <v>1434591.030229002</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -10992,10 +10992,10 @@
         <v>80</v>
       </c>
       <c r="N245" t="n">
-        <v>14447.670588235</v>
+        <v>14380</v>
       </c>
       <c r="O245" t="n">
-        <v>1155813.6470588</v>
+        <v>1150400</v>
       </c>
       <c r="P245" t="n">
         <v>23000</v>
@@ -15652,10 +15652,10 @@
         <v>176</v>
       </c>
       <c r="N346" t="n">
-        <v>59958.524453694</v>
+        <v>59834</v>
       </c>
       <c r="O346" t="n">
-        <v>10552700.30385014</v>
+        <v>10530784</v>
       </c>
       <c r="P346" t="n">
         <v>7900</v>
@@ -15744,10 +15744,10 @@
         <v>84</v>
       </c>
       <c r="N348" t="n">
-        <v>10270.481108312</v>
+        <v>10219</v>
       </c>
       <c r="O348" t="n">
-        <v>862720.413098208</v>
+        <v>858396</v>
       </c>
       <c r="P348" t="n">
         <v>16900</v>
@@ -16158,10 +16158,10 @@
         <v>1189</v>
       </c>
       <c r="N357" t="n">
-        <v>3821.6520477816</v>
+        <v>3821</v>
       </c>
       <c r="O357" t="n">
-        <v>4543944.284812322</v>
+        <v>4543169</v>
       </c>
       <c r="P357" t="n">
         <v>5900</v>
@@ -16250,10 +16250,10 @@
         <v>48</v>
       </c>
       <c r="N359" t="n">
-        <v>5486.9301397206</v>
+        <v>5476</v>
       </c>
       <c r="O359" t="n">
-        <v>263372.6467065888</v>
+        <v>262848</v>
       </c>
       <c r="P359" t="n">
         <v>8900</v>
@@ -16752,10 +16752,10 @@
         <v>1</v>
       </c>
       <c r="N370" t="n">
-        <v>18654.637168142</v>
+        <v>18491</v>
       </c>
       <c r="O370" t="n">
-        <v>18654.637168142</v>
+        <v>18491</v>
       </c>
       <c r="P370" t="n">
         <v>13500</v>
@@ -21605,10 +21605,10 @@
         <v>152</v>
       </c>
       <c r="N472" t="n">
-        <v>7049.9805782093</v>
+        <v>7046.9398274002</v>
       </c>
       <c r="O472" t="n">
-        <v>1071597.047887814</v>
+        <v>1071134.85376483</v>
       </c>
       <c r="P472" t="n">
         <v>9900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-06</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
         </is>
       </c>
     </row>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1112,10 +1112,10 @@
         <v>36</v>
       </c>
       <c r="N18" t="n">
-        <v>12357.960422535</v>
+        <v>12357.960425532</v>
       </c>
       <c r="O18" t="n">
-        <v>444886.57521126</v>
+        <v>444886.575319152</v>
       </c>
       <c r="P18" t="n">
         <v>15900</v>
@@ -1193,10 +1193,10 @@
         <v>36</v>
       </c>
       <c r="N20" t="n">
-        <v>11491.097222222</v>
+        <v>11491.09755814</v>
       </c>
       <c r="O20" t="n">
-        <v>413679.499999992</v>
+        <v>413679.51209304</v>
       </c>
       <c r="P20" t="n">
         <v>23000</v>
@@ -1669,10 +1669,10 @@
         <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>15711.96562212</v>
+        <v>15711.965560748</v>
       </c>
       <c r="O32" t="n">
-        <v>282815.38119816</v>
+        <v>282815.380093464</v>
       </c>
       <c r="P32" t="n">
         <v>28500</v>
@@ -2155,10 +2155,10 @@
         <v>34</v>
       </c>
       <c r="N44" t="n">
-        <v>61666.874148352</v>
+        <v>61666.87415978</v>
       </c>
       <c r="O44" t="n">
-        <v>2096673.721043968</v>
+        <v>2096673.72143252</v>
       </c>
       <c r="P44" t="n">
         <v>98900</v>
@@ -3362,10 +3362,10 @@
         <v>118</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0624184202</v>
+        <v>1098.0625007652</v>
       </c>
       <c r="O72" t="n">
-        <v>129571.3653735836</v>
+        <v>129571.3750902936</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1940319426</v>
+        <v>1550.1940372063</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9851499336</v>
+        <v>55806.9853394268</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -8832,10 +8832,10 @@
         <v>348</v>
       </c>
       <c r="N195" t="n">
-        <v>2029.8739872408</v>
+        <v>2029.8739957379</v>
       </c>
       <c r="O195" t="n">
-        <v>706396.1475597984</v>
+        <v>706396.1505167892</v>
       </c>
       <c r="P195" t="n">
         <v>3600</v>
@@ -11638,10 +11638,10 @@
         <v>1111</v>
       </c>
       <c r="N259" t="n">
-        <v>1778.4726973583</v>
+        <v>1778.472697775</v>
       </c>
       <c r="O259" t="n">
-        <v>1975883.166765071</v>
+        <v>1975883.167228025</v>
       </c>
       <c r="P259" t="n">
         <v>4900</v>
@@ -14507,10 +14507,10 @@
         <v>100</v>
       </c>
       <c r="N321" t="n">
-        <v>4907.8223782772</v>
+        <v>4907.8223917137</v>
       </c>
       <c r="O321" t="n">
-        <v>490782.23782772</v>
+        <v>490782.23917137</v>
       </c>
       <c r="P321" t="n">
         <v>8200</v>
@@ -18685,10 +18685,10 @@
         <v>2</v>
       </c>
       <c r="N411" t="n">
-        <v>3110.8400113026</v>
+        <v>3110.8399744753</v>
       </c>
       <c r="O411" t="n">
-        <v>6221.6800226052</v>
+        <v>6221.6799489506</v>
       </c>
       <c r="P411" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-07</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-08</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.746444689</v>
+        <v>3376.7464407714</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.966362108</v>
+        <v>1931498.964121241</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -3362,10 +3362,10 @@
         <v>118</v>
       </c>
       <c r="N72" t="n">
-        <v>1098.0625007652</v>
+        <v>1098.0625698496</v>
       </c>
       <c r="O72" t="n">
-        <v>129571.3750902936</v>
+        <v>129571.3832422528</v>
       </c>
       <c r="P72" t="n">
         <v>1500</v>
@@ -4966,10 +4966,10 @@
         <v>459</v>
       </c>
       <c r="N108" t="n">
-        <v>4890.930049597</v>
+        <v>4890.9300496586</v>
       </c>
       <c r="O108" t="n">
-        <v>2244936.892765023</v>
+        <v>2244936.892793297</v>
       </c>
       <c r="P108" t="n">
         <v>8200</v>
@@ -5414,10 +5414,10 @@
         <v>120</v>
       </c>
       <c r="N118" t="n">
-        <v>3240.8500395257</v>
+        <v>3240.8500399202</v>
       </c>
       <c r="O118" t="n">
-        <v>388902.004743084</v>
+        <v>388902.004790424</v>
       </c>
       <c r="P118" t="n">
         <v>5200</v>
@@ -5860,10 +5860,10 @@
         <v>501</v>
       </c>
       <c r="N128" t="n">
-        <v>3041.6600136893</v>
+        <v>3041.660013708</v>
       </c>
       <c r="O128" t="n">
-        <v>1523871.666858339</v>
+        <v>1523871.666867708</v>
       </c>
       <c r="P128" t="n">
         <v>5500</v>
@@ -5947,10 +5947,10 @@
         <v>1110</v>
       </c>
       <c r="N130" t="n">
-        <v>4372.2107923341</v>
+        <v>4372.2107923908</v>
       </c>
       <c r="O130" t="n">
-        <v>4853153.979490851</v>
+        <v>4853153.979553788</v>
       </c>
       <c r="P130" t="n">
         <v>7500</v>
@@ -7399,10 +7399,10 @@
         <v>191</v>
       </c>
       <c r="N162" t="n">
-        <v>1630.9239476386</v>
+        <v>1630.9239618753</v>
       </c>
       <c r="O162" t="n">
-        <v>311506.4739989726</v>
+        <v>311506.4767181823</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1940372063</v>
+        <v>1550.1940686328</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9853394268</v>
+        <v>55806.9864707808</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -7491,10 +7491,10 @@
         <v>48</v>
       </c>
       <c r="N164" t="n">
-        <v>1579.3884193548</v>
+        <v>1579.388381877</v>
       </c>
       <c r="O164" t="n">
-        <v>75810.64412903039</v>
+        <v>75810.642330096</v>
       </c>
       <c r="P164" t="n">
         <v>2900</v>
@@ -7658,10 +7658,10 @@
         <v>420</v>
       </c>
       <c r="N168" t="n">
-        <v>2069.4655762082</v>
+        <v>2069.4655430712</v>
       </c>
       <c r="O168" t="n">
-        <v>869175.5420074441</v>
+        <v>869175.528089904</v>
       </c>
       <c r="P168" t="n">
         <v>6500</v>
@@ -8504,10 +8504,10 @@
         <v>91</v>
       </c>
       <c r="N187" t="n">
-        <v>7537.4722307692</v>
+        <v>7537.472248062</v>
       </c>
       <c r="O187" t="n">
-        <v>685909.9729999972</v>
+        <v>685909.974573642</v>
       </c>
       <c r="P187" t="n">
         <v>8900</v>
@@ -8832,10 +8832,10 @@
         <v>348</v>
       </c>
       <c r="N195" t="n">
-        <v>2029.8739957379</v>
+        <v>2029.8740214477</v>
       </c>
       <c r="O195" t="n">
-        <v>706396.1505167892</v>
+        <v>706396.1594637996</v>
       </c>
       <c r="P195" t="n">
         <v>3600</v>
@@ -10233,10 +10233,10 @@
         <v>180</v>
       </c>
       <c r="N228" t="n">
-        <v>7969.9501679389</v>
+        <v>7969.9501684533</v>
       </c>
       <c r="O228" t="n">
-        <v>1434591.030229002</v>
+        <v>1434591.030321594</v>
       </c>
       <c r="P228" t="n">
         <v>12900</v>
@@ -10888,7 +10888,7 @@
         </is>
       </c>
       <c r="J243" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -10897,19 +10897,19 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="N243" t="n">
         <v>3590.77</v>
       </c>
       <c r="O243" t="n">
-        <v>427301.63</v>
+        <v>351895.46</v>
       </c>
       <c r="P243" t="n">
         <v>3900</v>
       </c>
       <c r="Q243" t="n">
-        <v>464100</v>
+        <v>382200</v>
       </c>
     </row>
     <row r="244">
@@ -11510,10 +11510,10 @@
         <v>3</v>
       </c>
       <c r="N256" t="n">
-        <v>23521.623269231</v>
+        <v>23521.623137255</v>
       </c>
       <c r="O256" t="n">
-        <v>70564.869807693</v>
+        <v>70564.869411765</v>
       </c>
       <c r="P256" t="n">
         <v>39000</v>
@@ -11638,10 +11638,10 @@
         <v>1111</v>
       </c>
       <c r="N259" t="n">
-        <v>1778.472697775</v>
+        <v>1778.4727006961</v>
       </c>
       <c r="O259" t="n">
-        <v>1975883.167228025</v>
+        <v>1975883.170473367</v>
       </c>
       <c r="P259" t="n">
         <v>4900</v>
@@ -14093,10 +14093,10 @@
         <v>504</v>
       </c>
       <c r="N312" t="n">
-        <v>2328.1186869944</v>
+        <v>2328.1186861768</v>
       </c>
       <c r="O312" t="n">
-        <v>1173371.818245178</v>
+        <v>1173371.817833107</v>
       </c>
       <c r="P312" t="n">
         <v>4500</v>
@@ -14507,10 +14507,10 @@
         <v>100</v>
       </c>
       <c r="N321" t="n">
-        <v>4907.8223917137</v>
+        <v>4907.822405303</v>
       </c>
       <c r="O321" t="n">
-        <v>490782.23917137</v>
+        <v>490782.2405303</v>
       </c>
       <c r="P321" t="n">
         <v>8200</v>
@@ -16296,10 +16296,10 @@
         <v>839</v>
       </c>
       <c r="N360" t="n">
-        <v>1516.0387762203</v>
+        <v>1516.0387732935</v>
       </c>
       <c r="O360" t="n">
-        <v>1271956.533248832</v>
+        <v>1271956.530793247</v>
       </c>
       <c r="P360" t="n">
         <v>2300</v>
@@ -16659,10 +16659,10 @@
         <v>145</v>
       </c>
       <c r="N368" t="n">
-        <v>2842.2744382022</v>
+        <v>2842.2744146685</v>
       </c>
       <c r="O368" t="n">
-        <v>412129.793539319</v>
+        <v>412129.7901269325</v>
       </c>
       <c r="P368" t="n">
         <v>4900</v>
@@ -16703,10 +16703,10 @@
         <v>2243</v>
       </c>
       <c r="N369" t="n">
-        <v>692.15226870079</v>
+        <v>692.15227579398</v>
       </c>
       <c r="O369" t="n">
-        <v>1552497.538695872</v>
+        <v>1552497.554605897</v>
       </c>
       <c r="P369" t="n">
         <v>1200</v>
@@ -17656,10 +17656,10 @@
         <v>178</v>
       </c>
       <c r="N389" t="n">
-        <v>1690.8700092421</v>
+        <v>1690.8700092764</v>
       </c>
       <c r="O389" t="n">
-        <v>300974.8616450938</v>
+        <v>300974.8616511992</v>
       </c>
       <c r="P389" t="n">
         <v>3000</v>
@@ -17940,10 +17940,10 @@
         <v>68</v>
       </c>
       <c r="N395" t="n">
-        <v>3907.5003319502</v>
+        <v>3907.5003333333</v>
       </c>
       <c r="O395" t="n">
-        <v>265710.0225726136</v>
+        <v>265710.0226666644</v>
       </c>
       <c r="P395" t="n">
         <v>3900</v>
@@ -18685,10 +18685,10 @@
         <v>2</v>
       </c>
       <c r="N411" t="n">
-        <v>3110.8399744753</v>
+        <v>3110.8399287749</v>
       </c>
       <c r="O411" t="n">
-        <v>6221.6799489506</v>
+        <v>6221.6798575498</v>
       </c>
       <c r="P411" t="n">
         <v>4500</v>
@@ -19059,10 +19059,10 @@
         <v>4</v>
       </c>
       <c r="N419" t="n">
-        <v>2501.3847317073</v>
+        <v>2501.3847058824</v>
       </c>
       <c r="O419" t="n">
-        <v>10005.5389268292</v>
+        <v>10005.5388235296</v>
       </c>
       <c r="P419" t="n">
         <v>4100</v>
@@ -19619,10 +19619,10 @@
         <v>381</v>
       </c>
       <c r="N431" t="n">
-        <v>1595.4999702159</v>
+        <v>1595.499947839</v>
       </c>
       <c r="O431" t="n">
-        <v>607885.4886522579</v>
+        <v>607885.480126659</v>
       </c>
       <c r="P431" t="n">
         <v>2500</v>
@@ -19763,10 +19763,10 @@
         <v>54</v>
       </c>
       <c r="N434" t="n">
-        <v>2098.4050882353</v>
+        <v>2098.4051032448</v>
       </c>
       <c r="O434" t="n">
-        <v>113313.8747647062</v>
+        <v>113313.8755752192</v>
       </c>
       <c r="P434" t="n">
         <v>9500</v>
@@ -22331,10 +22331,10 @@
         <v>1061</v>
       </c>
       <c r="N487" t="n">
-        <v>665.32374700527</v>
+        <v>665.3237759536501</v>
       </c>
       <c r="O487" t="n">
-        <v>705908.4955725914</v>
+        <v>705908.5262868227</v>
       </c>
       <c r="P487" t="n">
         <v>2900</v>
@@ -22844,10 +22844,10 @@
         <v>34</v>
       </c>
       <c r="N498" t="n">
-        <v>4703.6208602151</v>
+        <v>4703.6208791209</v>
       </c>
       <c r="O498" t="n">
-        <v>159923.1092473134</v>
+        <v>159923.1098901106</v>
       </c>
       <c r="P498" t="n">
         <v>5900</v>
@@ -22888,10 +22888,10 @@
         <v>60</v>
       </c>
       <c r="N499" t="n">
-        <v>1008.8141189931</v>
+        <v>1008.8134367542</v>
       </c>
       <c r="O499" t="n">
-        <v>60528.847139586</v>
+        <v>60528.806205252</v>
       </c>
       <c r="P499" t="n">
         <v>1500</v>
@@ -23191,10 +23191,10 @@
         <v>11</v>
       </c>
       <c r="N506" t="n">
-        <v>22951.704751958</v>
+        <v>22951.704745098</v>
       </c>
       <c r="O506" t="n">
-        <v>252468.752271538</v>
+        <v>252468.752196078</v>
       </c>
       <c r="P506" t="n">
         <v>37900</v>
@@ -23491,7 +23491,7 @@
         </is>
       </c>
       <c r="J513" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K513" t="n">
         <v>0</v>
@@ -23500,19 +23500,19 @@
         <v>0</v>
       </c>
       <c r="M513" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="N513" t="n">
         <v>2644.9</v>
       </c>
       <c r="O513" t="n">
-        <v>105796</v>
+        <v>79347</v>
       </c>
       <c r="P513" t="n">
         <v>3900</v>
       </c>
       <c r="Q513" t="n">
-        <v>156000</v>
+        <v>117000</v>
       </c>
     </row>
     <row r="514">

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -5767,10 +5767,10 @@
         <v>85</v>
       </c>
       <c r="N126" t="n">
-        <v>15851.61</v>
+        <v>15976.425826772</v>
       </c>
       <c r="O126" t="n">
-        <v>1347386.85</v>
+        <v>1357996.19527562</v>
       </c>
       <c r="P126" t="n">
         <v>23900</v>
@@ -7445,10 +7445,10 @@
         <v>36</v>
       </c>
       <c r="N163" t="n">
-        <v>1550.1940686328</v>
+        <v>1550.1940704179</v>
       </c>
       <c r="O163" t="n">
-        <v>55806.9864707808</v>
+        <v>55806.9865350444</v>
       </c>
       <c r="P163" t="n">
         <v>2500</v>
@@ -11638,10 +11638,10 @@
         <v>1111</v>
       </c>
       <c r="N259" t="n">
-        <v>1778.4727006961</v>
+        <v>1778.4727011139</v>
       </c>
       <c r="O259" t="n">
-        <v>1975883.170473367</v>
+        <v>1975883.170937543</v>
       </c>
       <c r="P259" t="n">
         <v>4900</v>
@@ -15243,10 +15243,10 @@
         <v>12</v>
       </c>
       <c r="N337" t="n">
-        <v>27186</v>
+        <v>27309.572727273</v>
       </c>
       <c r="O337" t="n">
-        <v>326232</v>
+        <v>327714.872727276</v>
       </c>
       <c r="P337" t="n">
         <v>43900</v>
@@ -23953,10 +23953,10 @@
         <v>360</v>
       </c>
       <c r="N523" t="n">
-        <v>7480</v>
+        <v>7524.8351648352</v>
       </c>
       <c r="O523" t="n">
-        <v>2692800</v>
+        <v>2708940.659340672</v>
       </c>
       <c r="P523" t="n">
         <v>9500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -1073,10 +1073,10 @@
         <v>286</v>
       </c>
       <c r="N17" t="n">
-        <v>6272.8550526316</v>
+        <v>6272.8550704225</v>
       </c>
       <c r="O17" t="n">
-        <v>1794036.545052638</v>
+        <v>1794036.550140835</v>
       </c>
       <c r="P17" t="n">
         <v>7900</v>
@@ -3320,10 +3320,10 @@
         <v>118</v>
       </c>
       <c r="N71" t="n">
-        <v>1098.0627514701</v>
+        <v>1098.0628221049</v>
       </c>
       <c r="O71" t="n">
-        <v>129571.4046734718</v>
+        <v>129571.4130083782</v>
       </c>
       <c r="P71" t="n">
         <v>1500</v>
@@ -3546,10 +3546,10 @@
         <v>218</v>
       </c>
       <c r="N76" t="n">
-        <v>13642.54185766</v>
+        <v>13593.35</v>
       </c>
       <c r="O76" t="n">
-        <v>2974074.12496988</v>
+        <v>2963350.3</v>
       </c>
       <c r="P76" t="n">
         <v>25500</v>
@@ -3843,10 +3843,10 @@
         <v>300</v>
       </c>
       <c r="N83" t="n">
-        <v>2808.3040151157</v>
+        <v>2804.33</v>
       </c>
       <c r="O83" t="n">
-        <v>842491.20453471</v>
+        <v>841299</v>
       </c>
       <c r="P83" t="n">
         <v>4900</v>
@@ -4433,10 +4433,10 @@
         <v>484</v>
       </c>
       <c r="N96" t="n">
-        <v>1482.16796875</v>
+        <v>1480</v>
       </c>
       <c r="O96" t="n">
-        <v>717369.296875</v>
+        <v>716320</v>
       </c>
       <c r="P96" t="n">
         <v>2600</v>
@@ -4832,10 +4832,10 @@
         <v>173</v>
       </c>
       <c r="N105" t="n">
-        <v>2619.5155335628</v>
+        <v>2612.77</v>
       </c>
       <c r="O105" t="n">
-        <v>453176.1873063644</v>
+        <v>452009.21</v>
       </c>
       <c r="P105" t="n">
         <v>4900</v>
@@ -4878,10 +4878,10 @@
         <v>540</v>
       </c>
       <c r="N106" t="n">
-        <v>4362.7231895528</v>
+        <v>4357.55</v>
       </c>
       <c r="O106" t="n">
-        <v>2355870.522358512</v>
+        <v>2353077</v>
       </c>
       <c r="P106" t="n">
         <v>7500</v>
@@ -4924,10 +4924,10 @@
         <v>459</v>
       </c>
       <c r="N107" t="n">
-        <v>4890.9300496586</v>
+        <v>4890.9300497203</v>
       </c>
       <c r="O107" t="n">
-        <v>2244936.892793297</v>
+        <v>2244936.892821618</v>
       </c>
       <c r="P107" t="n">
         <v>8200</v>
@@ -5154,10 +5154,10 @@
         <v>2</v>
       </c>
       <c r="N112" t="n">
-        <v>8670.9576008273</v>
+        <v>8662</v>
       </c>
       <c r="O112" t="n">
-        <v>17341.9152016546</v>
+        <v>17324</v>
       </c>
       <c r="P112" t="n">
         <v>14200</v>
@@ -5244,10 +5244,10 @@
         <v>23</v>
       </c>
       <c r="N114" t="n">
-        <v>500.91436884092</v>
+        <v>489.88</v>
       </c>
       <c r="O114" t="n">
-        <v>11521.03048334116</v>
+        <v>11267.24</v>
       </c>
       <c r="P114" t="n">
         <v>700</v>
@@ -5545,10 +5545,10 @@
         <v>650</v>
       </c>
       <c r="N121" t="n">
-        <v>2672.0057001239</v>
+        <v>2665.4</v>
       </c>
       <c r="O121" t="n">
-        <v>1736803.705080535</v>
+        <v>1732510</v>
       </c>
       <c r="P121" t="n">
         <v>20900</v>
@@ -5640,10 +5640,10 @@
         <v>12</v>
       </c>
       <c r="N123" t="n">
-        <v>12618.152142857</v>
+        <v>12267.647571429</v>
       </c>
       <c r="O123" t="n">
-        <v>151417.825714284</v>
+        <v>147211.770857148</v>
       </c>
       <c r="P123" t="n">
         <v>19900</v>
@@ -5818,10 +5818,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600137268</v>
+        <v>3041.6600137646</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.666877127</v>
+        <v>1523871.666896065</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5905,10 +5905,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4372.2107926742</v>
+        <v>4374.7145640659</v>
       </c>
       <c r="O129" t="n">
-        <v>4853153.979868362</v>
+        <v>4855933.166113149</v>
       </c>
       <c r="P129" t="n">
         <v>7500</v>
@@ -6622,10 +6622,10 @@
         <v>55</v>
       </c>
       <c r="N145" t="n">
-        <v>9422.619187996501</v>
+        <v>9414.309999999999</v>
       </c>
       <c r="O145" t="n">
-        <v>518244.0553398075</v>
+        <v>517787.05</v>
       </c>
       <c r="P145" t="n">
         <v>16900</v>
@@ -6950,10 +6950,10 @@
         <v>116</v>
       </c>
       <c r="N152" t="n">
-        <v>16960.16635514</v>
+        <v>16897</v>
       </c>
       <c r="O152" t="n">
-        <v>1967379.29719624</v>
+        <v>1960052</v>
       </c>
       <c r="P152" t="n">
         <v>27900</v>
@@ -7403,10 +7403,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.194110545</v>
+        <v>1550.1942738685</v>
       </c>
       <c r="O162" t="n">
-        <v>55806.98797962</v>
+        <v>55806.993859266</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -8295,10 +8295,10 @@
         <v>169</v>
       </c>
       <c r="N182" t="n">
-        <v>9396.9148264984</v>
+        <v>9338</v>
       </c>
       <c r="O182" t="n">
-        <v>1588078.60567823</v>
+        <v>1578122</v>
       </c>
       <c r="P182" t="n">
         <v>15500</v>
@@ -8626,10 +8626,10 @@
         <v>195</v>
       </c>
       <c r="N190" t="n">
-        <v>8799.4430248307</v>
+        <v>8794.48</v>
       </c>
       <c r="O190" t="n">
-        <v>1715891.389841987</v>
+        <v>1714923.6</v>
       </c>
       <c r="P190" t="n">
         <v>14500</v>
@@ -8749,10 +8749,10 @@
         <v>527</v>
       </c>
       <c r="N193" t="n">
-        <v>2523.5712699748</v>
+        <v>2517.22</v>
       </c>
       <c r="O193" t="n">
-        <v>1329922.05927672</v>
+        <v>1326574.94</v>
       </c>
       <c r="P193" t="n">
         <v>4200</v>
@@ -9082,10 +9082,10 @@
         <v>32</v>
       </c>
       <c r="N201" t="n">
-        <v>14161.073142857</v>
+        <v>14060.64</v>
       </c>
       <c r="O201" t="n">
-        <v>453154.340571424</v>
+        <v>449940.48</v>
       </c>
       <c r="P201" t="n">
         <v>22900</v>
@@ -9766,10 +9766,10 @@
         <v>37</v>
       </c>
       <c r="N217" t="n">
-        <v>27871.270433071</v>
+        <v>27123.76496063</v>
       </c>
       <c r="O217" t="n">
-        <v>1031237.006023627</v>
+        <v>1003579.30354331</v>
       </c>
       <c r="P217" t="n">
         <v>44500</v>
@@ -9807,10 +9807,10 @@
         <v>233</v>
       </c>
       <c r="N218" t="n">
-        <v>4110.4025485437</v>
+        <v>4100.45</v>
       </c>
       <c r="O218" t="n">
-        <v>957723.793810682</v>
+        <v>955404.85</v>
       </c>
       <c r="P218" t="n">
         <v>26900</v>
@@ -11192,10 +11192,10 @@
         <v>3</v>
       </c>
       <c r="N249" t="n">
-        <v>11048.707428571</v>
+        <v>10451.48</v>
       </c>
       <c r="O249" t="n">
-        <v>33146.12228571301</v>
+        <v>31354.44</v>
       </c>
       <c r="P249" t="n">
         <v>16900</v>
@@ -11330,10 +11330,10 @@
         <v>18</v>
       </c>
       <c r="N252" t="n">
-        <v>15867.472527473</v>
+        <v>15824</v>
       </c>
       <c r="O252" t="n">
-        <v>285614.505494514</v>
+        <v>284832</v>
       </c>
       <c r="P252" t="n">
         <v>26900</v>
@@ -11550,10 +11550,10 @@
         <v>620</v>
       </c>
       <c r="N257" t="n">
-        <v>3494.4765957447</v>
+        <v>3486</v>
       </c>
       <c r="O257" t="n">
-        <v>2166575.489361714</v>
+        <v>2161320</v>
       </c>
       <c r="P257" t="n">
         <v>6900</v>
@@ -11596,10 +11596,10 @@
         <v>1111</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4727221703</v>
+        <v>1778.4727234441</v>
       </c>
       <c r="O258" t="n">
-        <v>1975883.194331203</v>
+        <v>1975883.195746395</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -13588,10 +13588,10 @@
         <v>348</v>
       </c>
       <c r="N301" t="n">
-        <v>8872.340618996799</v>
+        <v>8858.16</v>
       </c>
       <c r="O301" t="n">
-        <v>3087574.535410886</v>
+        <v>3082639.68</v>
       </c>
       <c r="P301" t="n">
         <v>15500</v>
@@ -13772,10 +13772,10 @@
         <v>279</v>
       </c>
       <c r="N305" t="n">
-        <v>5040.7413333333</v>
+        <v>5014</v>
       </c>
       <c r="O305" t="n">
-        <v>1406366.831999991</v>
+        <v>1398906</v>
       </c>
       <c r="P305" t="n">
         <v>8200</v>
@@ -14051,10 +14051,10 @@
         <v>504</v>
       </c>
       <c r="N311" t="n">
-        <v>2336.84913125</v>
+        <v>2328.11868125</v>
       </c>
       <c r="O311" t="n">
-        <v>1177771.96215</v>
+        <v>1173371.81535</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14695,10 +14695,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3922.9680788177</v>
+        <v>3903.7379310345</v>
       </c>
       <c r="O325" t="n">
-        <v>329529.3186206868</v>
+        <v>327913.986206898</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -14741,10 +14741,10 @@
         <v>13</v>
       </c>
       <c r="N326" t="n">
-        <v>33317.307692308</v>
+        <v>33000</v>
       </c>
       <c r="O326" t="n">
-        <v>433125.000000004</v>
+        <v>429000</v>
       </c>
       <c r="P326" t="n">
         <v>52900</v>
@@ -15017,10 +15017,10 @@
         <v>8</v>
       </c>
       <c r="N332" t="n">
-        <v>9751.4516129032</v>
+        <v>8637</v>
       </c>
       <c r="O332" t="n">
-        <v>78011.6129032256</v>
+        <v>69096</v>
       </c>
       <c r="P332" t="n">
         <v>14500</v>
@@ -15247,10 +15247,10 @@
         <v>159</v>
       </c>
       <c r="N337" t="n">
-        <v>3901.1562753036</v>
+        <v>3898</v>
       </c>
       <c r="O337" t="n">
-        <v>620283.8477732724</v>
+        <v>619782</v>
       </c>
       <c r="P337" t="n">
         <v>6900</v>
@@ -16208,10 +16208,10 @@
         <v>48</v>
       </c>
       <c r="N358" t="n">
-        <v>5483.2964690207</v>
+        <v>5476</v>
       </c>
       <c r="O358" t="n">
-        <v>263198.2305129936</v>
+        <v>262848</v>
       </c>
       <c r="P358" t="n">
         <v>8900</v>
@@ -18643,10 +18643,10 @@
         <v>2</v>
       </c>
       <c r="N410" t="n">
-        <v>3110.839841954</v>
+        <v>3110.8397979798</v>
       </c>
       <c r="O410" t="n">
-        <v>6221.679683908</v>
+        <v>6221.6795959596</v>
       </c>
       <c r="P410" t="n">
         <v>4500</v>
@@ -24095,10 +24095,10 @@
         <v>166</v>
       </c>
       <c r="N526" t="n">
-        <v>4598.7284768212</v>
+        <v>4576</v>
       </c>
       <c r="O526" t="n">
-        <v>763388.9271523192</v>
+        <v>759616</v>
       </c>
       <c r="P526" t="n">
         <v>5900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-09</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
         </is>
       </c>
     </row>
@@ -1271,10 +1271,10 @@
         <v>67</v>
       </c>
       <c r="N22" t="n">
-        <v>2474.7040138408</v>
+        <v>2474.7039930556</v>
       </c>
       <c r="O22" t="n">
-        <v>165805.1689273336</v>
+        <v>165805.1675347252</v>
       </c>
       <c r="P22" t="n">
         <v>4500</v>
@@ -2879,10 +2879,10 @@
         <v>148</v>
       </c>
       <c r="N61" t="n">
-        <v>1950.2145369407</v>
+        <v>1950.214488189</v>
       </c>
       <c r="O61" t="n">
-        <v>288631.7514672236</v>
+        <v>288631.744251972</v>
       </c>
       <c r="P61" t="n">
         <v>2900</v>
@@ -3320,10 +3320,10 @@
         <v>118</v>
       </c>
       <c r="N71" t="n">
-        <v>1098.0628221049</v>
+        <v>1098.062979056</v>
       </c>
       <c r="O71" t="n">
-        <v>129571.4130083782</v>
+        <v>129571.431528608</v>
       </c>
       <c r="P71" t="n">
         <v>1500</v>
@@ -4236,7 +4236,7 @@
         </is>
       </c>
       <c r="J92" t="n">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4245,19 +4245,19 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="N92" t="n">
         <v>3154</v>
       </c>
       <c r="O92" t="n">
-        <v>782192</v>
+        <v>719112</v>
       </c>
       <c r="P92" t="n">
         <v>5500</v>
       </c>
       <c r="Q92" t="n">
-        <v>1364000</v>
+        <v>1254000</v>
       </c>
     </row>
     <row r="93">
@@ -4924,10 +4924,10 @@
         <v>459</v>
       </c>
       <c r="N107" t="n">
-        <v>4890.9300497203</v>
+        <v>4890.9300498132</v>
       </c>
       <c r="O107" t="n">
-        <v>2244936.892821618</v>
+        <v>2244936.892864258</v>
       </c>
       <c r="P107" t="n">
         <v>8200</v>
@@ -5372,10 +5372,10 @@
         <v>120</v>
       </c>
       <c r="N117" t="n">
-        <v>3240.8500422833</v>
+        <v>3240.8500449438</v>
       </c>
       <c r="O117" t="n">
-        <v>388902.005073996</v>
+        <v>388902.005393256</v>
       </c>
       <c r="P117" t="n">
         <v>5200</v>
@@ -5640,10 +5640,10 @@
         <v>12</v>
       </c>
       <c r="N123" t="n">
-        <v>12267.647571429</v>
+        <v>12267.647205882</v>
       </c>
       <c r="O123" t="n">
-        <v>147211.770857148</v>
+        <v>147211.766470584</v>
       </c>
       <c r="P123" t="n">
         <v>19900</v>
@@ -5818,10 +5818,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600137646</v>
+        <v>3041.6600137931</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.666896065</v>
+        <v>1523871.666910343</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5905,10 +5905,10 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4374.7145640659</v>
+        <v>4372.2107930714</v>
       </c>
       <c r="O129" t="n">
-        <v>4855933.166113149</v>
+        <v>4853153.980309254</v>
       </c>
       <c r="P129" t="n">
         <v>7500</v>
@@ -7357,10 +7357,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9239968815</v>
+        <v>1630.9240698598</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.4834043665</v>
+        <v>311506.4973432218</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7403,10 +7403,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1942738685</v>
+        <v>1550.1941645158</v>
       </c>
       <c r="O162" t="n">
-        <v>55806.993859266</v>
+        <v>55806.9899225688</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7449,10 +7449,10 @@
         <v>48</v>
       </c>
       <c r="N163" t="n">
-        <v>1579.3881518152</v>
+        <v>1579.3874912892</v>
       </c>
       <c r="O163" t="n">
-        <v>75810.6312871296</v>
+        <v>75810.5995818816</v>
       </c>
       <c r="P163" t="n">
         <v>2900</v>
@@ -8339,10 +8339,10 @@
         <v>674</v>
       </c>
       <c r="N183" t="n">
-        <v>4196.8725389755</v>
+        <v>4196.8725410978</v>
       </c>
       <c r="O183" t="n">
-        <v>2828692.091269487</v>
+        <v>2828692.092699917</v>
       </c>
       <c r="P183" t="n">
         <v>5900</v>
@@ -10463,10 +10463,10 @@
         <v>154</v>
       </c>
       <c r="N233" t="n">
-        <v>548.1471442590801</v>
+        <v>548.14712450593</v>
       </c>
       <c r="O233" t="n">
-        <v>84414.66021589833</v>
+        <v>84414.65717391322</v>
       </c>
       <c r="P233" t="n">
         <v>2000</v>
@@ -11596,10 +11596,10 @@
         <v>1111</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4727234441</v>
+        <v>1778.4727448514</v>
       </c>
       <c r="O258" t="n">
-        <v>1975883.195746395</v>
+        <v>1975883.219529905</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -14465,10 +14465,10 @@
         <v>100</v>
       </c>
       <c r="N320" t="n">
-        <v>4907.8224423077</v>
+        <v>4907.822504931</v>
       </c>
       <c r="O320" t="n">
-        <v>490782.24423077</v>
+        <v>490782.2504931</v>
       </c>
       <c r="P320" t="n">
         <v>8200</v>
@@ -14545,7 +14545,7 @@
         </is>
       </c>
       <c r="J322" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="K322" t="n">
         <v>0</v>
@@ -14554,19 +14554,19 @@
         <v>0</v>
       </c>
       <c r="M322" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="N322" t="n">
         <v>4240</v>
       </c>
       <c r="O322" t="n">
-        <v>568160</v>
+        <v>517280</v>
       </c>
       <c r="P322" t="n">
         <v>7300</v>
       </c>
       <c r="Q322" t="n">
-        <v>978200</v>
+        <v>890600</v>
       </c>
     </row>
     <row r="323">
@@ -14695,10 +14695,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3903.7379310345</v>
+        <v>3903.7383067896</v>
       </c>
       <c r="O325" t="n">
-        <v>327913.986206898</v>
+        <v>327914.0177703264</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -16254,10 +16254,10 @@
         <v>839</v>
       </c>
       <c r="N359" t="n">
-        <v>1516.0387724372</v>
+        <v>1516.0387635597</v>
       </c>
       <c r="O359" t="n">
-        <v>1271956.530074811</v>
+        <v>1271956.522626588</v>
       </c>
       <c r="P359" t="n">
         <v>2300</v>
@@ -16661,10 +16661,10 @@
         <v>2243</v>
       </c>
       <c r="N368" t="n">
-        <v>692.15228029678</v>
+        <v>692.15231697102</v>
       </c>
       <c r="O368" t="n">
-        <v>1552497.564705678</v>
+        <v>1552497.646965998</v>
       </c>
       <c r="P368" t="n">
         <v>1200</v>
@@ -18643,10 +18643,10 @@
         <v>2</v>
       </c>
       <c r="N410" t="n">
-        <v>3110.8397979798</v>
+        <v>3110.8397028838</v>
       </c>
       <c r="O410" t="n">
-        <v>6221.6795959596</v>
+        <v>6221.6794057676</v>
       </c>
       <c r="P410" t="n">
         <v>4500</v>
@@ -19017,10 +19017,10 @@
         <v>4</v>
       </c>
       <c r="N418" t="n">
-        <v>2501.3847058824</v>
+        <v>2501.3846268657</v>
       </c>
       <c r="O418" t="n">
-        <v>10005.5388235296</v>
+        <v>10005.5385074628</v>
       </c>
       <c r="P418" t="n">
         <v>4100</v>
@@ -19103,7 +19103,7 @@
         </is>
       </c>
       <c r="J420" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="K420" t="n">
         <v>0</v>
@@ -19112,19 +19112,19 @@
         <v>0</v>
       </c>
       <c r="M420" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="N420" t="n">
         <v>14260.14</v>
       </c>
       <c r="O420" t="n">
-        <v>1311932.88</v>
+        <v>1098030.78</v>
       </c>
       <c r="P420" t="n">
         <v>15900</v>
       </c>
       <c r="Q420" t="n">
-        <v>1462800</v>
+        <v>1224300</v>
       </c>
     </row>
     <row r="421">
@@ -19721,10 +19721,10 @@
         <v>54</v>
       </c>
       <c r="N433" t="n">
-        <v>2098.4051032448</v>
+        <v>2098.4051183432</v>
       </c>
       <c r="O433" t="n">
-        <v>113313.8755752192</v>
+        <v>113313.8763905328</v>
       </c>
       <c r="P433" t="n">
         <v>9500</v>
@@ -22194,10 +22194,10 @@
         <v>67</v>
       </c>
       <c r="N484" t="n">
-        <v>44113.603953488</v>
+        <v>44113.604096386</v>
       </c>
       <c r="O484" t="n">
-        <v>2955611.464883696</v>
+        <v>2955611.474457862</v>
       </c>
       <c r="P484" t="n">
         <v>71900</v>
@@ -22289,10 +22289,10 @@
         <v>1061</v>
       </c>
       <c r="N486" t="n">
-        <v>665.3237759536501</v>
+        <v>665.3237979601701</v>
       </c>
       <c r="O486" t="n">
-        <v>705908.5262868227</v>
+        <v>705908.5496357405</v>
       </c>
       <c r="P486" t="n">
         <v>2900</v>
@@ -24083,7 +24083,7 @@
         </is>
       </c>
       <c r="J526" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="K526" t="n">
         <v>0</v>
@@ -24092,19 +24092,19 @@
         <v>0</v>
       </c>
       <c r="M526" t="n">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="N526" t="n">
         <v>4576</v>
       </c>
       <c r="O526" t="n">
-        <v>759616</v>
+        <v>668096</v>
       </c>
       <c r="P526" t="n">
         <v>5900</v>
       </c>
       <c r="Q526" t="n">
-        <v>979400</v>
+        <v>861400</v>
       </c>
     </row>
     <row r="527">
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="J527" t="n">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="K527" t="n">
         <v>0</v>
@@ -24138,19 +24138,19 @@
         <v>0</v>
       </c>
       <c r="M527" t="n">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="N527" t="n">
         <v>5280</v>
       </c>
       <c r="O527" t="n">
-        <v>1446720</v>
+        <v>1341120</v>
       </c>
       <c r="P527" t="n">
         <v>6900</v>
       </c>
       <c r="Q527" t="n">
-        <v>1890600</v>
+        <v>1752600</v>
       </c>
     </row>
     <row r="528">

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -7357,10 +7357,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9240698598</v>
+        <v>1630.9240720148</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.4973432218</v>
+        <v>311506.4977548268</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7403,10 +7403,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1941645158</v>
+        <v>1550.1941668538</v>
       </c>
       <c r="O162" t="n">
-        <v>55806.9899225688</v>
+        <v>55806.9900067368</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -14695,10 +14695,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3903.7383067896</v>
+        <v>3903.7383529412</v>
       </c>
       <c r="O325" t="n">
-        <v>327914.0177703264</v>
+        <v>327914.0216470608</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -18643,10 +18643,10 @@
         <v>2</v>
       </c>
       <c r="N410" t="n">
-        <v>3110.8397028838</v>
+        <v>3110.8396848556</v>
       </c>
       <c r="O410" t="n">
-        <v>6221.6794057676</v>
+        <v>6221.6793697112</v>
       </c>
       <c r="P410" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-10</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-11</t>
         </is>
       </c>
     </row>
@@ -673,10 +673,10 @@
         <v>572</v>
       </c>
       <c r="N7" t="n">
-        <v>3376.7464407714</v>
+        <v>3376.7464397906</v>
       </c>
       <c r="O7" t="n">
-        <v>1931498.964121241</v>
+        <v>1931498.963560223</v>
       </c>
       <c r="P7" t="n">
         <v>4500</v>
@@ -953,10 +953,10 @@
         <v>58</v>
       </c>
       <c r="N14" t="n">
-        <v>1854.2409952607</v>
+        <v>1854.241047619</v>
       </c>
       <c r="O14" t="n">
-        <v>107545.9777251206</v>
+        <v>107545.980761902</v>
       </c>
       <c r="P14" t="n">
         <v>3200</v>
@@ -1151,10 +1151,10 @@
         <v>440</v>
       </c>
       <c r="N19" t="n">
-        <v>3926.8370909091</v>
+        <v>3926.8370787689</v>
       </c>
       <c r="O19" t="n">
-        <v>1727808.320000004</v>
+        <v>1727808.314658316</v>
       </c>
       <c r="P19" t="n">
         <v>4800</v>
@@ -1271,10 +1271,10 @@
         <v>67</v>
       </c>
       <c r="N22" t="n">
-        <v>2474.7039930556</v>
+        <v>2474.7039826087</v>
       </c>
       <c r="O22" t="n">
-        <v>165805.1675347252</v>
+        <v>165805.1668347829</v>
       </c>
       <c r="P22" t="n">
         <v>4500</v>
@@ -1627,10 +1627,10 @@
         <v>89</v>
       </c>
       <c r="N31" t="n">
-        <v>3910.6280263158</v>
+        <v>3910.6279405034</v>
       </c>
       <c r="O31" t="n">
-        <v>348045.8943421062</v>
+        <v>348045.8867048026</v>
       </c>
       <c r="P31" t="n">
         <v>9100</v>
@@ -2113,10 +2113,10 @@
         <v>34</v>
       </c>
       <c r="N43" t="n">
-        <v>61666.87415978</v>
+        <v>61666.874171271</v>
       </c>
       <c r="O43" t="n">
-        <v>2096673.72143252</v>
+        <v>2096673.721823214</v>
       </c>
       <c r="P43" t="n">
         <v>98900</v>
@@ -2879,10 +2879,10 @@
         <v>148</v>
       </c>
       <c r="N61" t="n">
-        <v>1950.214488189</v>
+        <v>1950.2144852941</v>
       </c>
       <c r="O61" t="n">
-        <v>288631.744251972</v>
+        <v>288631.7438235268</v>
       </c>
       <c r="P61" t="n">
         <v>2900</v>
@@ -3320,10 +3320,10 @@
         <v>118</v>
       </c>
       <c r="N71" t="n">
-        <v>1098.062979056</v>
+        <v>1098.0630078247</v>
       </c>
       <c r="O71" t="n">
-        <v>129571.431528608</v>
+        <v>129571.4349233146</v>
       </c>
       <c r="P71" t="n">
         <v>1500</v>
@@ -4745,10 +4745,10 @@
         <v>179</v>
       </c>
       <c r="N103" t="n">
-        <v>3795.7100075916</v>
+        <v>3795.7100076089</v>
       </c>
       <c r="O103" t="n">
-        <v>679432.0913588965</v>
+        <v>679432.0913619931</v>
       </c>
       <c r="P103" t="n">
         <v>6200</v>
@@ -5372,10 +5372,10 @@
         <v>120</v>
       </c>
       <c r="N117" t="n">
-        <v>3240.8500449438</v>
+        <v>3240.8500464037</v>
       </c>
       <c r="O117" t="n">
-        <v>388902.005393256</v>
+        <v>388902.005568444</v>
       </c>
       <c r="P117" t="n">
         <v>5200</v>
@@ -5640,10 +5640,10 @@
         <v>12</v>
       </c>
       <c r="N123" t="n">
-        <v>12267.647205882</v>
+        <v>12422.024238382</v>
       </c>
       <c r="O123" t="n">
-        <v>147211.766470584</v>
+        <v>149064.290860584</v>
       </c>
       <c r="P123" t="n">
         <v>19900</v>
@@ -5818,10 +5818,10 @@
         <v>501</v>
       </c>
       <c r="N127" t="n">
-        <v>3041.6600137931</v>
+        <v>3041.66001386</v>
       </c>
       <c r="O127" t="n">
-        <v>1523871.666910343</v>
+        <v>1523871.66694386</v>
       </c>
       <c r="P127" t="n">
         <v>5500</v>
@@ -5905,16 +5905,16 @@
         <v>1110</v>
       </c>
       <c r="N129" t="n">
-        <v>4372.2107930714</v>
+        <v>4371.1712607216</v>
       </c>
       <c r="O129" t="n">
-        <v>4853153.980309254</v>
+        <v>4852000.099400977</v>
       </c>
       <c r="P129" t="n">
-        <v>7500</v>
+        <v>8900</v>
       </c>
       <c r="Q129" t="n">
-        <v>8325000</v>
+        <v>9879000</v>
       </c>
     </row>
     <row r="130">
@@ -7357,10 +7357,10 @@
         <v>191</v>
       </c>
       <c r="N161" t="n">
-        <v>1630.9240720148</v>
+        <v>1630.924143319</v>
       </c>
       <c r="O161" t="n">
-        <v>311506.4977548268</v>
+        <v>311506.511373929</v>
       </c>
       <c r="P161" t="n">
         <v>2500</v>
@@ -7403,10 +7403,10 @@
         <v>36</v>
       </c>
       <c r="N162" t="n">
-        <v>1550.1941668538</v>
+        <v>1550.1943181289</v>
       </c>
       <c r="O162" t="n">
-        <v>55806.9900067368</v>
+        <v>55806.9954526404</v>
       </c>
       <c r="P162" t="n">
         <v>2500</v>
@@ -7936,10 +7936,10 @@
         <v>24</v>
       </c>
       <c r="N174" t="n">
-        <v>10836.973589744</v>
+        <v>10836.973612903</v>
       </c>
       <c r="O174" t="n">
-        <v>260087.366153856</v>
+        <v>260087.366709672</v>
       </c>
       <c r="P174" t="n">
         <v>19900</v>
@@ -8831,10 +8831,10 @@
         <v>157</v>
       </c>
       <c r="N195" t="n">
-        <v>22485.695555556</v>
+        <v>22485.69552795</v>
       </c>
       <c r="O195" t="n">
-        <v>3530254.202222292</v>
+        <v>3530254.19788815</v>
       </c>
       <c r="P195" t="n">
         <v>36500</v>
@@ -8995,10 +8995,10 @@
         <v>170</v>
       </c>
       <c r="N199" t="n">
-        <v>2680.739694704</v>
+        <v>2680.7396945137</v>
       </c>
       <c r="O199" t="n">
-        <v>455725.74809968</v>
+        <v>455725.7480673291</v>
       </c>
       <c r="P199" t="n">
         <v>4900</v>
@@ -9766,10 +9766,10 @@
         <v>37</v>
       </c>
       <c r="N217" t="n">
-        <v>27123.76496063</v>
+        <v>27123.764900398</v>
       </c>
       <c r="O217" t="n">
-        <v>1003579.30354331</v>
+        <v>1003579.301314726</v>
       </c>
       <c r="P217" t="n">
         <v>44500</v>
@@ -11596,10 +11596,10 @@
         <v>1111</v>
       </c>
       <c r="N258" t="n">
-        <v>1778.4727448514</v>
+        <v>1778.4727414037</v>
       </c>
       <c r="O258" t="n">
-        <v>1975883.219529905</v>
+        <v>1975883.215699511</v>
       </c>
       <c r="P258" t="n">
         <v>4900</v>
@@ -13864,10 +13864,10 @@
         <v>263</v>
       </c>
       <c r="N307" t="n">
-        <v>2252.2976470588</v>
+        <v>2252.297658046</v>
       </c>
       <c r="O307" t="n">
-        <v>592354.2811764644</v>
+        <v>592354.2840660979</v>
       </c>
       <c r="P307" t="n">
         <v>3900</v>
@@ -14051,10 +14051,10 @@
         <v>504</v>
       </c>
       <c r="N311" t="n">
-        <v>2328.11868125</v>
+        <v>2328.1186779449</v>
       </c>
       <c r="O311" t="n">
-        <v>1173371.81535</v>
+        <v>1173371.81368423</v>
       </c>
       <c r="P311" t="n">
         <v>4500</v>
@@ -14695,10 +14695,10 @@
         <v>84</v>
       </c>
       <c r="N325" t="n">
-        <v>3903.7383529412</v>
+        <v>3903.7383683768</v>
       </c>
       <c r="O325" t="n">
-        <v>327914.0216470608</v>
+        <v>327914.0229436512</v>
       </c>
       <c r="P325" t="n">
         <v>7500</v>
@@ -15840,10 +15840,10 @@
         <v>48</v>
       </c>
       <c r="N350" t="n">
-        <v>4268.7084656085</v>
+        <v>4268.7085638298</v>
       </c>
       <c r="O350" t="n">
-        <v>204898.006349208</v>
+        <v>204898.0110638304</v>
       </c>
       <c r="P350" t="n">
         <v>6900</v>
@@ -16254,10 +16254,10 @@
         <v>839</v>
       </c>
       <c r="N359" t="n">
-        <v>1516.0387635597</v>
+        <v>1516.0387603223</v>
       </c>
       <c r="O359" t="n">
-        <v>1271956.522626588</v>
+        <v>1271956.51991041</v>
       </c>
       <c r="P359" t="n">
         <v>2300</v>
@@ -16661,10 +16661,10 @@
         <v>2243</v>
       </c>
       <c r="N368" t="n">
-        <v>692.15231697102</v>
+        <v>692.1523548442</v>
       </c>
       <c r="O368" t="n">
-        <v>1552497.646965998</v>
+        <v>1552497.731915541</v>
       </c>
       <c r="P368" t="n">
         <v>1200</v>
@@ -17761,10 +17761,10 @@
         <v>47</v>
       </c>
       <c r="N391" t="n">
-        <v>2270.3212987013</v>
+        <v>2270.3213157895</v>
       </c>
       <c r="O391" t="n">
-        <v>106705.1010389611</v>
+        <v>106705.1018421065</v>
       </c>
       <c r="P391" t="n">
         <v>3900</v>
@@ -18643,10 +18643,10 @@
         <v>2</v>
       </c>
       <c r="N410" t="n">
-        <v>3110.8396848556</v>
+        <v>3110.8396334311</v>
       </c>
       <c r="O410" t="n">
-        <v>6221.6793697112</v>
+        <v>6221.6792668622</v>
       </c>
       <c r="P410" t="n">
         <v>4500</v>
@@ -19577,10 +19577,10 @@
         <v>381</v>
       </c>
       <c r="N430" t="n">
-        <v>1595.4998805078</v>
+        <v>1595.4997449362</v>
       </c>
       <c r="O430" t="n">
-        <v>607885.4544734719</v>
+        <v>607885.4028206922</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -22289,10 +22289,10 @@
         <v>1061</v>
       </c>
       <c r="N486" t="n">
-        <v>665.3237979601701</v>
+        <v>665.32380350195</v>
       </c>
       <c r="O486" t="n">
-        <v>705908.5496357405</v>
+        <v>705908.5555155689</v>
       </c>
       <c r="P486" t="n">
         <v>2900</v>
@@ -23369,10 +23369,10 @@
         <v>61</v>
       </c>
       <c r="N510" t="n">
-        <v>13493.858297872</v>
+        <v>13493.858292683</v>
       </c>
       <c r="O510" t="n">
-        <v>823125.356170192</v>
+        <v>823125.3558536631</v>
       </c>
       <c r="P510" t="n">
         <v>16900</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -4559,7 +4559,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4568,19 +4568,19 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="N99" t="n">
         <v>5002</v>
       </c>
       <c r="O99" t="n">
-        <v>2435974</v>
+        <v>2335934</v>
       </c>
       <c r="P99" t="n">
         <v>8400</v>
       </c>
       <c r="Q99" t="n">
-        <v>4090800</v>
+        <v>3922800</v>
       </c>
     </row>
     <row r="100">
@@ -18643,10 +18643,10 @@
         <v>2</v>
       </c>
       <c r="N410" t="n">
-        <v>3110.8396334311</v>
+        <v>3110.8396273474</v>
       </c>
       <c r="O410" t="n">
-        <v>6221.6792668622</v>
+        <v>6221.6792546948</v>
       </c>
       <c r="P410" t="n">
         <v>4500</v>

--- a/bodegas/001.xlsx
+++ b/bodegas/001.xlsx
@@ -595,10 +595,10 @@
         <v>245</v>
       </c>
       <c r="N5" t="n">
-        <v>27108.144192256</v>
+        <v>27000</v>
       </c>
       <c r="O5" t="n">
-        <v>6641495.32710272</v>
+        <v>6615000</v>
       </c>
       <c r="P5" t="n">
         <v>20000</v>
@@ -634,10 +634,10 @@
         <v>27</v>
       </c>
       <c r="N6" t="n">
-        <v>27117.391304348</v>
+        <v>27000</v>
       </c>
       <c r="O6" t="n">
-        <v>732169.565217396</v>
+        <v>729000</v>
       </c>
       <c r="P6" t="n">
         <v>30000</v>
@@ -4924,10 +4924,10 @@
         <v>459</v>
       </c>
       <c r="N107" t="n">
-        <v>4903.3514603175</v>
+        <v>4890.9300507937</v>
       </c>
       <c r="O107" t="n">
-        <v>2250638.320285732</v>
+        <v>2244936.893314308</v>
       </c>
       <c r="P107" t="n">
         <v>8200</v>
@@ -5815,10 +5815,10 @@
         <v>4</v>
       </c>
       <c r="N127" t="n">
-        <v>15071.76</v>
+        <v>14386.68</v>
       </c>
       <c r="O127" t="n">
-        <v>60287.04</v>
+        <v>57546.72</v>
       </c>
       <c r="P127" t="n">
         <v>21900</v>
@@ -7982,10 +7982,10 @@
         <v>24</v>
       </c>
       <c r="N175" t="n">
-        <v>10907.343571429</v>
+        <v>10836.973636364</v>
       </c>
       <c r="O175" t="n">
-        <v>261776.245714296</v>
+        <v>260087.367272736</v>
       </c>
       <c r="P175" t="n">
         <v>19900</v>
@@ -8341,10 +8341,10 @@
         <v>169</v>
       </c>
       <c r="N183" t="n">
-        <v>9460.065359477099</v>
+        <v>9338</v>
       </c>
       <c r="O183" t="n">
-        <v>1598751.04575163</v>
+        <v>1578122</v>
       </c>
       <c r="P183" t="n">
         <v>15500</v>
@@ -8877,10 +8877,10 @@
         <v>157</v>
       </c>
       <c r="N196" t="n">
-        <v>22541.90975</v>
+        <v>22485.6955</v>
       </c>
       <c r="O196" t="n">
-        <v>3539079.83075</v>
+        <v>3530254.1935</v>
       </c>
       <c r="P196" t="n">
         <v>36500</v>
@@ -9904,10 +9904,10 @@
         <v>37</v>
       </c>
       <c r="N220" t="n">
-        <v>27232.25996</v>
+        <v>27123.76488</v>
       </c>
       <c r="O220" t="n">
-        <v>1007593.61852</v>
+        <v>1003579.30056</v>
       </c>
       <c r="P220" t="n">
         <v>44500</v>
@@ -14048,10 +14048,10 @@
         <v>48</v>
       </c>
       <c r="N311" t="n">
-        <v>21456.861702128</v>
+        <v>21231</v>
       </c>
       <c r="O311" t="n">
-        <v>1029929.361702144</v>
+        <v>1019088</v>
       </c>
       <c r="P311" t="n">
         <v>34500</v>
@@ -14373,10 +14373,10 @@
         <v>77</v>
       </c>
       <c r="N318" t="n">
-        <v>9198.3277962348</v>
+        <v>9178</v>
       </c>
       <c r="O318" t="n">
-        <v>708271.2403100797</v>
+        <v>706706</v>
       </c>
       <c r="P318" t="n">
         <v>14900</v>
@@ -14419,10 +14419,10 @@
         <v>432</v>
       </c>
       <c r="N319" t="n">
-        <v>4567.8948290973</v>
+        <v>4544</v>
       </c>
       <c r="O319" t="n">
-        <v>1973330.566170034</v>
+        <v>1963008</v>
       </c>
       <c r="P319" t="n">
         <v>7900</v>
@@ -14465,10 +14465,10 @@
         <v>103</v>
       </c>
       <c r="N320" t="n">
-        <v>13948.467680608</v>
+        <v>13922</v>
       </c>
       <c r="O320" t="n">
-        <v>1436692.171102624</v>
+        <v>1433966</v>
       </c>
       <c r="P320" t="n">
         <v>22900</v>
@@ -14557,10 +14557,10 @@
         <v>12</v>
       </c>
       <c r="N322" t="n">
-        <v>25260.382352941</v>
+        <v>25076</v>
       </c>
       <c r="O322" t="n">
-        <v>303124.588235292</v>
+        <v>300912</v>
       </c>
       <c r="P322" t="n">
         <v>40900</v>
@@ -15201,10 +15201,10 @@
         <v>12</v>
       </c>
       <c r="N336" t="n">
-        <v>14306.769230769</v>
+        <v>14090</v>
       </c>
       <c r="O336" t="n">
-        <v>171681.230769228</v>
+        <v>169080</v>
       </c>
       <c r="P336" t="n">
         <v>22900</v>
@@ -15293,10 +15293,10 @@
         <v>109</v>
       </c>
       <c r="N338" t="n">
-        <v>13121.945155393</v>
+        <v>13098</v>
       </c>
       <c r="O338" t="n">
-        <v>1430292.021937837</v>
+        <v>1427682</v>
       </c>
       <c r="P338" t="n">
         <v>21200</v>
@@ -15886,10 +15886,10 @@
         <v>41</v>
       </c>
       <c r="N351" t="n">
-        <v>17325.987730061</v>
+        <v>17168</v>
       </c>
       <c r="O351" t="n">
-        <v>710365.496932501</v>
+        <v>703888</v>
       </c>
       <c r="P351" t="n">
         <v>27900</v>
@@ -15932,10 +15932,10 @@
         <v>81</v>
       </c>
       <c r="N352" t="n">
-        <v>27289.075933076</v>
+        <v>27254</v>
       </c>
       <c r="O352" t="n">
-        <v>2210415.150579156</v>
+        <v>2207574</v>
       </c>
       <c r="P352" t="n">
         <v>43900</v>
